--- a/Luban/Config/Datas/Levels/L13/EnemyData.xlsx
+++ b/Luban/Config/Datas/Levels/L13/EnemyData.xlsx
@@ -1391,7 +1391,7 @@
         <v>1.1198</v>
       </c>
       <c r="D4" s="0" t="n">
-        <v>6.028</v>
+        <v>13.94571</v>
       </c>
       <c r="E4" s="0" t="inlineStr">
         <is>
@@ -1413,7 +1413,7 @@
         <v>0</v>
       </c>
       <c r="J4" s="0" t="n">
-        <v>2</v>
+        <v>4</v>
       </c>
       <c r="K4" s="0" t="n">
         <v>1</v>
@@ -1442,7 +1442,7 @@
         <v>1.1198</v>
       </c>
       <c r="D5" s="0" t="n">
-        <v>6.028</v>
+        <v>13.94571</v>
       </c>
       <c r="E5" s="0" t="inlineStr">
         <is>
@@ -1464,7 +1464,7 @@
         <v>0</v>
       </c>
       <c r="J5" s="0" t="n">
-        <v>2</v>
+        <v>4</v>
       </c>
       <c r="K5" s="0" t="n">
         <v>1</v>
@@ -1493,7 +1493,7 @@
         <v>1.12145</v>
       </c>
       <c r="D6" s="0" t="n">
-        <v>6.3119188</v>
+        <v>14.602553</v>
       </c>
       <c r="E6" s="0" t="inlineStr">
         <is>
@@ -1515,7 +1515,7 @@
         <v>0</v>
       </c>
       <c r="J6" s="0" t="n">
-        <v>2</v>
+        <v>4</v>
       </c>
       <c r="K6" s="0" t="n">
         <v>1</v>
@@ -1544,7 +1544,7 @@
         <v>1.12145</v>
       </c>
       <c r="D7" s="0" t="n">
-        <v>6.3119188</v>
+        <v>14.602553</v>
       </c>
       <c r="E7" s="0" t="inlineStr">
         <is>
@@ -1566,7 +1566,7 @@
         <v>0</v>
       </c>
       <c r="J7" s="0" t="n">
-        <v>2</v>
+        <v>4</v>
       </c>
       <c r="K7" s="0" t="n">
         <v>1</v>
@@ -1595,7 +1595,7 @@
         <v>1.1231</v>
       </c>
       <c r="D8" s="0" t="n">
-        <v>8.367231721132896</v>
+        <v>19.357497</v>
       </c>
       <c r="E8" s="0" t="inlineStr">
         <is>
@@ -1617,7 +1617,7 @@
         <v>0</v>
       </c>
       <c r="J8" s="0" t="n">
-        <v>2</v>
+        <v>4</v>
       </c>
       <c r="K8" s="0" t="n">
         <v>1</v>
@@ -1646,7 +1646,7 @@
         <v>1.1231</v>
       </c>
       <c r="D9" s="0" t="n">
-        <v>8.367231721132896</v>
+        <v>19.357497</v>
       </c>
       <c r="E9" s="0" t="inlineStr">
         <is>
@@ -1668,7 +1668,7 @@
         <v>0</v>
       </c>
       <c r="J9" s="0" t="n">
-        <v>2</v>
+        <v>4</v>
       </c>
       <c r="K9" s="0" t="n">
         <v>1</v>
@@ -1697,7 +1697,7 @@
         <v>1.07205</v>
       </c>
       <c r="D10" s="0" t="n">
-        <v>5.438700618736383</v>
+        <v>12.582373</v>
       </c>
       <c r="E10" s="0" t="inlineStr">
         <is>
@@ -1719,7 +1719,7 @@
         <v>0</v>
       </c>
       <c r="J10" s="0" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="K10" s="0" t="n">
         <v>1</v>
@@ -1748,7 +1748,7 @@
         <v>1.12475</v>
       </c>
       <c r="D11" s="0" t="n">
-        <v>9.579798851562499</v>
+        <v>22.162757</v>
       </c>
       <c r="E11" s="0" t="inlineStr">
         <is>
@@ -1770,7 +1770,7 @@
         <v>0</v>
       </c>
       <c r="J11" s="0" t="n">
-        <v>2</v>
+        <v>4</v>
       </c>
       <c r="K11" s="0" t="n">
         <v>1</v>
@@ -1799,7 +1799,7 @@
         <v>1.12475</v>
       </c>
       <c r="D12" s="0" t="n">
-        <v>9.579798851562499</v>
+        <v>22.162757</v>
       </c>
       <c r="E12" s="0" t="inlineStr">
         <is>
@@ -1821,7 +1821,7 @@
         <v>0</v>
       </c>
       <c r="J12" s="0" t="n">
-        <v>2</v>
+        <v>4</v>
       </c>
       <c r="K12" s="0" t="n">
         <v>1</v>
@@ -1850,7 +1850,7 @@
         <v>1.073625</v>
       </c>
       <c r="D13" s="0" t="n">
-        <v>6.226869253515625</v>
+        <v>14.405792</v>
       </c>
       <c r="E13" s="0" t="inlineStr">
         <is>
@@ -1872,7 +1872,7 @@
         <v>0</v>
       </c>
       <c r="J13" s="0" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="K13" s="0" t="n">
         <v>1</v>
@@ -1901,7 +1901,7 @@
         <v>1.1264</v>
       </c>
       <c r="D14" s="0" t="n">
-        <v>14.65856776391785</v>
+        <v>33.912432</v>
       </c>
       <c r="E14" s="0" t="inlineStr">
         <is>
@@ -1923,7 +1923,7 @@
         <v>0</v>
       </c>
       <c r="J14" s="0" t="n">
-        <v>2</v>
+        <v>4</v>
       </c>
       <c r="K14" s="0" t="n">
         <v>1</v>
@@ -1952,7 +1952,7 @@
         <v>1.1264</v>
       </c>
       <c r="D15" s="0" t="n">
-        <v>14.65856776391785</v>
+        <v>33.912432</v>
       </c>
       <c r="E15" s="0" t="inlineStr">
         <is>
@@ -1974,7 +1974,7 @@
         <v>0</v>
       </c>
       <c r="J15" s="0" t="n">
-        <v>2</v>
+        <v>4</v>
       </c>
       <c r="K15" s="0" t="n">
         <v>1</v>
@@ -2003,7 +2003,7 @@
         <v>1.024</v>
       </c>
       <c r="D16" s="0" t="n">
-        <v>22.92599998276752</v>
+        <v>53.039043</v>
       </c>
       <c r="E16" s="0" t="inlineStr">
         <is>
@@ -2025,7 +2025,7 @@
         <v>0.08</v>
       </c>
       <c r="J16" s="0" t="n">
-        <v>2</v>
+        <v>4</v>
       </c>
       <c r="K16" s="0" t="n">
         <v>1</v>
@@ -2054,7 +2054,7 @@
         <v>1.0752</v>
       </c>
       <c r="D17" s="0" t="n">
-        <v>9.528069046546603</v>
+        <v>22.043081</v>
       </c>
       <c r="E17" s="0" t="inlineStr">
         <is>
@@ -2076,7 +2076,7 @@
         <v>0</v>
       </c>
       <c r="J17" s="0" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="K17" s="0" t="n">
         <v>1</v>
@@ -2105,7 +2105,7 @@
         <v>1.024</v>
       </c>
       <c r="D18" s="0" t="n">
-        <v>22.92599998276752</v>
+        <v>53.039043</v>
       </c>
       <c r="E18" s="0" t="inlineStr">
         <is>
@@ -2127,7 +2127,7 @@
         <v>0.08</v>
       </c>
       <c r="J18" s="0" t="n">
-        <v>2</v>
+        <v>4</v>
       </c>
       <c r="K18" s="0" t="n">
         <v>1</v>
@@ -2156,7 +2156,7 @@
         <v>1.024</v>
       </c>
       <c r="D19" s="0" t="n">
-        <v>22.92599998276752</v>
+        <v>53.039043</v>
       </c>
       <c r="E19" s="0" t="inlineStr">
         <is>
@@ -2178,7 +2178,7 @@
         <v>0.08</v>
       </c>
       <c r="J19" s="0" t="n">
-        <v>2</v>
+        <v>4</v>
       </c>
       <c r="K19" s="0" t="n">
         <v>1</v>
@@ -2207,7 +2207,7 @@
         <v>1.0255</v>
       </c>
       <c r="D20" s="0" t="n">
-        <v>6.374719521316381</v>
+        <v>19.663789</v>
       </c>
       <c r="E20" s="0" t="inlineStr">
         <is>
@@ -2229,7 +2229,7 @@
         <v>0</v>
       </c>
       <c r="J20" s="0" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="K20" s="0" t="n">
         <v>1</v>
@@ -2258,7 +2258,7 @@
         <v>1.0255</v>
       </c>
       <c r="D21" s="0" t="n">
-        <v>6.374719521316381</v>
+        <v>19.663789</v>
       </c>
       <c r="E21" s="0" t="inlineStr">
         <is>
@@ -2280,7 +2280,7 @@
         <v>0</v>
       </c>
       <c r="J21" s="0" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="K21" s="0" t="n">
         <v>1</v>
@@ -2309,7 +2309,7 @@
         <v>1.12805</v>
       </c>
       <c r="D22" s="0" t="n">
-        <v>14.16604338070307</v>
+        <v>32.772982</v>
       </c>
       <c r="E22" s="0" t="inlineStr">
         <is>
@@ -2331,7 +2331,7 @@
         <v>0</v>
       </c>
       <c r="J22" s="0" t="n">
-        <v>2</v>
+        <v>4</v>
       </c>
       <c r="K22" s="0" t="n">
         <v>1</v>
@@ -2360,7 +2360,7 @@
         <v>1.12805</v>
       </c>
       <c r="D23" s="0" t="n">
-        <v>14.16604338070307</v>
+        <v>32.772982</v>
       </c>
       <c r="E23" s="0" t="inlineStr">
         <is>
@@ -2382,7 +2382,7 @@
         <v>0</v>
       </c>
       <c r="J23" s="0" t="n">
-        <v>2</v>
+        <v>4</v>
       </c>
       <c r="K23" s="0" t="n">
         <v>1</v>
@@ -2411,7 +2411,7 @@
         <v>1.6408</v>
       </c>
       <c r="D24" s="0" t="n">
-        <v>12.04113687359761</v>
+        <v>27.857035</v>
       </c>
       <c r="E24" s="0" t="inlineStr">
         <is>
@@ -2433,7 +2433,7 @@
         <v>0</v>
       </c>
       <c r="J24" s="0" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="K24" s="0" t="n">
         <v>1</v>
@@ -2462,7 +2462,7 @@
         <v>1.6408</v>
       </c>
       <c r="D25" s="0" t="n">
-        <v>12.04113687359761</v>
+        <v>27.857035</v>
       </c>
       <c r="E25" s="0" t="inlineStr">
         <is>
@@ -2484,7 +2484,7 @@
         <v>0</v>
       </c>
       <c r="J25" s="0" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="K25" s="0" t="n">
         <v>1</v>
@@ -2513,7 +2513,7 @@
         <v>1.0255</v>
       </c>
       <c r="D26" s="0" t="n">
-        <v>22.1556918474196</v>
+        <v>51.256944</v>
       </c>
       <c r="E26" s="0" t="inlineStr">
         <is>
@@ -2535,7 +2535,7 @@
         <v>0.08</v>
       </c>
       <c r="J26" s="0" t="n">
-        <v>2</v>
+        <v>4</v>
       </c>
       <c r="K26" s="0" t="n">
         <v>1</v>
@@ -2564,7 +2564,7 @@
         <v>1.076775</v>
       </c>
       <c r="D27" s="0" t="n">
-        <v>9.207928197456996</v>
+        <v>21.302438</v>
       </c>
       <c r="E27" s="0" t="inlineStr">
         <is>
@@ -2586,7 +2586,7 @@
         <v>0</v>
       </c>
       <c r="J27" s="0" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="K27" s="0" t="n">
         <v>1</v>
@@ -2615,7 +2615,7 @@
         <v>1.6408</v>
       </c>
       <c r="D28" s="0" t="n">
-        <v>12.04113687359761</v>
+        <v>27.857035</v>
       </c>
       <c r="E28" s="0" t="inlineStr">
         <is>
@@ -2637,7 +2637,7 @@
         <v>0</v>
       </c>
       <c r="J28" s="0" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="K28" s="0" t="n">
         <v>1</v>
@@ -2666,7 +2666,7 @@
         <v>1.0255</v>
       </c>
       <c r="D29" s="0" t="n">
-        <v>22.1556918474196</v>
+        <v>51.256944</v>
       </c>
       <c r="E29" s="0" t="inlineStr">
         <is>
@@ -2688,7 +2688,7 @@
         <v>0.08</v>
       </c>
       <c r="J29" s="0" t="n">
-        <v>2</v>
+        <v>4</v>
       </c>
       <c r="K29" s="0" t="n">
         <v>1</v>
@@ -2717,7 +2717,7 @@
         <v>1.0255</v>
       </c>
       <c r="D30" s="0" t="n">
-        <v>22.1556918474196</v>
+        <v>51.256944</v>
       </c>
       <c r="E30" s="0" t="inlineStr">
         <is>
@@ -2739,7 +2739,7 @@
         <v>0.08</v>
       </c>
       <c r="J30" s="0" t="n">
-        <v>2</v>
+        <v>4</v>
       </c>
       <c r="K30" s="0" t="n">
         <v>1</v>
@@ -2768,7 +2768,7 @@
         <v>1.027</v>
       </c>
       <c r="D31" s="0" t="n">
-        <v>6.623108665749656</v>
+        <v>20.429983</v>
       </c>
       <c r="E31" s="0" t="inlineStr">
         <is>
@@ -2790,7 +2790,7 @@
         <v>0</v>
       </c>
       <c r="J31" s="0" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="K31" s="0" t="n">
         <v>1</v>
@@ -2819,7 +2819,7 @@
         <v>1.027</v>
       </c>
       <c r="D32" s="0" t="n">
-        <v>6.623108665749656</v>
+        <v>20.429983</v>
       </c>
       <c r="E32" s="0" t="inlineStr">
         <is>
@@ -2841,7 +2841,7 @@
         <v>0</v>
       </c>
       <c r="J32" s="0" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="K32" s="0" t="n">
         <v>1</v>
@@ -2870,7 +2870,7 @@
         <v>1.1297</v>
       </c>
       <c r="D33" s="0" t="n">
-        <v>14.71801925722146</v>
+        <v>34.049972</v>
       </c>
       <c r="E33" s="0" t="inlineStr">
         <is>
@@ -2892,7 +2892,7 @@
         <v>0</v>
       </c>
       <c r="J33" s="0" t="n">
-        <v>2</v>
+        <v>4</v>
       </c>
       <c r="K33" s="0" t="n">
         <v>1</v>
@@ -2921,7 +2921,7 @@
         <v>1.1297</v>
       </c>
       <c r="D34" s="0" t="n">
-        <v>14.71801925722146</v>
+        <v>34.049972</v>
       </c>
       <c r="E34" s="0" t="inlineStr">
         <is>
@@ -2943,7 +2943,7 @@
         <v>0</v>
       </c>
       <c r="J34" s="0" t="n">
-        <v>2</v>
+        <v>4</v>
       </c>
       <c r="K34" s="0" t="n">
         <v>1</v>
@@ -2972,7 +2972,7 @@
         <v>1.6432</v>
       </c>
       <c r="D35" s="0" t="n">
-        <v>12.51031636863824</v>
+        <v>28.942476</v>
       </c>
       <c r="E35" s="0" t="inlineStr">
         <is>
@@ -2994,7 +2994,7 @@
         <v>0</v>
       </c>
       <c r="J35" s="0" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="K35" s="0" t="n">
         <v>1</v>
@@ -3023,7 +3023,7 @@
         <v>1.6432</v>
       </c>
       <c r="D36" s="0" t="n">
-        <v>12.51031636863824</v>
+        <v>28.942476</v>
       </c>
       <c r="E36" s="0" t="inlineStr">
         <is>
@@ -3045,7 +3045,7 @@
         <v>0</v>
       </c>
       <c r="J36" s="0" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="K36" s="0" t="n">
         <v>1</v>
@@ -3074,7 +3074,7 @@
         <v>1.027</v>
       </c>
       <c r="D37" s="0" t="n">
-        <v>23.01898211829436</v>
+        <v>53.254156</v>
       </c>
       <c r="E37" s="0" t="inlineStr">
         <is>
@@ -3096,7 +3096,7 @@
         <v>0.08</v>
       </c>
       <c r="J37" s="0" t="n">
-        <v>2</v>
+        <v>4</v>
       </c>
       <c r="K37" s="0" t="n">
         <v>1</v>
@@ -3125,7 +3125,7 @@
         <v>1.07835</v>
       </c>
       <c r="D38" s="0" t="n">
-        <v>9.566712517193947</v>
+        <v>22.132482</v>
       </c>
       <c r="E38" s="0" t="inlineStr">
         <is>
@@ -3147,7 +3147,7 @@
         <v>0</v>
       </c>
       <c r="J38" s="0" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="K38" s="0" t="n">
         <v>1</v>
@@ -3176,7 +3176,7 @@
         <v>1.6432</v>
       </c>
       <c r="D39" s="0" t="n">
-        <v>12.51031636863824</v>
+        <v>28.942476</v>
       </c>
       <c r="E39" s="0" t="inlineStr">
         <is>
@@ -3198,7 +3198,7 @@
         <v>0</v>
       </c>
       <c r="J39" s="0" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="K39" s="0" t="n">
         <v>1</v>
@@ -3227,7 +3227,7 @@
         <v>1.027</v>
       </c>
       <c r="D40" s="0" t="n">
-        <v>23.01898211829436</v>
+        <v>53.254156</v>
       </c>
       <c r="E40" s="0" t="inlineStr">
         <is>
@@ -3249,7 +3249,7 @@
         <v>0.08</v>
       </c>
       <c r="J40" s="0" t="n">
-        <v>2</v>
+        <v>4</v>
       </c>
       <c r="K40" s="0" t="n">
         <v>1</v>
@@ -3278,7 +3278,7 @@
         <v>1.027</v>
       </c>
       <c r="D41" s="0" t="n">
-        <v>23.01898211829436</v>
+        <v>53.254156</v>
       </c>
       <c r="E41" s="0" t="inlineStr">
         <is>
@@ -3300,7 +3300,7 @@
         <v>0.08</v>
       </c>
       <c r="J41" s="0" t="n">
-        <v>2</v>
+        <v>4</v>
       </c>
       <c r="K41" s="0" t="n">
         <v>1</v>
@@ -3329,7 +3329,7 @@
         <v>1.0285</v>
       </c>
       <c r="D42" s="0" t="n">
-        <v>7.902999361837908</v>
+        <v>24.378</v>
       </c>
       <c r="E42" s="0" t="inlineStr">
         <is>
@@ -3351,7 +3351,7 @@
         <v>0</v>
       </c>
       <c r="J42" s="0" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="K42" s="0" t="n">
         <v>1</v>
@@ -3380,7 +3380,7 @@
         <v>1.0285</v>
       </c>
       <c r="D43" s="0" t="n">
-        <v>7.902999361837908</v>
+        <v>24.378</v>
       </c>
       <c r="E43" s="0" t="inlineStr">
         <is>
@@ -3402,7 +3402,7 @@
         <v>0</v>
       </c>
       <c r="J43" s="0" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="K43" s="0" t="n">
         <v>1</v>
@@ -3431,7 +3431,7 @@
         <v>1.13135</v>
       </c>
       <c r="D44" s="0" t="n">
-        <v>17.56222080408424</v>
+        <v>40.63</v>
       </c>
       <c r="E44" s="0" t="inlineStr">
         <is>
@@ -3453,7 +3453,7 @@
         <v>0</v>
       </c>
       <c r="J44" s="0" t="n">
-        <v>2</v>
+        <v>4</v>
       </c>
       <c r="K44" s="0" t="n">
         <v>1</v>
@@ -3482,7 +3482,7 @@
         <v>1.13135</v>
       </c>
       <c r="D45" s="0" t="n">
-        <v>17.56222080408424</v>
+        <v>40.63</v>
       </c>
       <c r="E45" s="0" t="inlineStr">
         <is>
@@ -3504,7 +3504,7 @@
         <v>0</v>
       </c>
       <c r="J45" s="0" t="n">
-        <v>2</v>
+        <v>4</v>
       </c>
       <c r="K45" s="0" t="n">
         <v>1</v>
@@ -3533,7 +3533,7 @@
         <v>1.6456</v>
       </c>
       <c r="D46" s="0" t="n">
-        <v>14.9278876834716</v>
+        <v>34.5355</v>
       </c>
       <c r="E46" s="0" t="inlineStr">
         <is>
@@ -3555,7 +3555,7 @@
         <v>0</v>
       </c>
       <c r="J46" s="0" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="K46" s="0" t="n">
         <v>1</v>
@@ -3584,7 +3584,7 @@
         <v>1.6456</v>
       </c>
       <c r="D47" s="0" t="n">
-        <v>14.9278876834716</v>
+        <v>34.5355</v>
       </c>
       <c r="E47" s="0" t="inlineStr">
         <is>
@@ -3606,7 +3606,7 @@
         <v>0</v>
       </c>
       <c r="J47" s="0" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="K47" s="0" t="n">
         <v>1</v>
@@ -3635,7 +3635,7 @@
         <v>1.0285</v>
       </c>
       <c r="D48" s="0" t="n">
-        <v>27.46731333758775</v>
+        <v>63.545321</v>
       </c>
       <c r="E48" s="0" t="inlineStr">
         <is>
@@ -3657,7 +3657,7 @@
         <v>0.08</v>
       </c>
       <c r="J48" s="0" t="n">
-        <v>2</v>
+        <v>4</v>
       </c>
       <c r="K48" s="0" t="n">
         <v>1</v>
@@ -3686,7 +3686,7 @@
         <v>1.079925</v>
       </c>
       <c r="D49" s="0" t="n">
-        <v>11.41544352265475</v>
+        <v>26.4095</v>
       </c>
       <c r="E49" s="0" t="inlineStr">
         <is>
@@ -3708,7 +3708,7 @@
         <v>0</v>
       </c>
       <c r="J49" s="0" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="K49" s="0" t="n">
         <v>1</v>
@@ -3737,7 +3737,7 @@
         <v>1.6456</v>
       </c>
       <c r="D50" s="0" t="n">
-        <v>14.9278876834716</v>
+        <v>34.5355</v>
       </c>
       <c r="E50" s="0" t="inlineStr">
         <is>
@@ -3759,7 +3759,7 @@
         <v>0</v>
       </c>
       <c r="J50" s="0" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="K50" s="0" t="n">
         <v>1</v>
@@ -3788,7 +3788,7 @@
         <v>1.0285</v>
       </c>
       <c r="D51" s="0" t="n">
-        <v>27.46731333758775</v>
+        <v>63.545321</v>
       </c>
       <c r="E51" s="0" t="inlineStr">
         <is>
@@ -3810,7 +3810,7 @@
         <v>0.08</v>
       </c>
       <c r="J51" s="0" t="n">
-        <v>2</v>
+        <v>4</v>
       </c>
       <c r="K51" s="0" t="n">
         <v>1</v>
@@ -3839,7 +3839,7 @@
         <v>1.0285</v>
       </c>
       <c r="D52" s="0" t="n">
-        <v>27.46731333758775</v>
+        <v>63.545321</v>
       </c>
       <c r="E52" s="0" t="inlineStr">
         <is>
@@ -3861,7 +3861,7 @@
         <v>0.08</v>
       </c>
       <c r="J52" s="0" t="n">
-        <v>2</v>
+        <v>4</v>
       </c>
       <c r="K52" s="0" t="n">
         <v>1</v>
@@ -3890,7 +3890,7 @@
         <v>1.03</v>
       </c>
       <c r="D53" s="0" t="n">
-        <v>9.434964200477326</v>
+        <v>29.103578</v>
       </c>
       <c r="E53" s="0" t="inlineStr">
         <is>
@@ -3912,7 +3912,7 @@
         <v>0</v>
       </c>
       <c r="J53" s="0" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="K53" s="0" t="n">
         <v>1</v>
@@ -3941,7 +3941,7 @@
         <v>1.03</v>
       </c>
       <c r="D54" s="0" t="n">
-        <v>9.434964200477326</v>
+        <v>29.103578</v>
       </c>
       <c r="E54" s="0" t="inlineStr">
         <is>
@@ -3963,7 +3963,7 @@
         <v>0</v>
       </c>
       <c r="J54" s="0" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="K54" s="0" t="n">
         <v>1</v>
@@ -3992,7 +3992,7 @@
         <v>1.133</v>
       </c>
       <c r="D55" s="0" t="n">
-        <v>20.96658711217183</v>
+        <v>48.505964</v>
       </c>
       <c r="E55" s="0" t="inlineStr">
         <is>
@@ -4014,7 +4014,7 @@
         <v>0</v>
       </c>
       <c r="J55" s="0" t="n">
-        <v>2</v>
+        <v>4</v>
       </c>
       <c r="K55" s="0" t="n">
         <v>1</v>
@@ -4043,7 +4043,7 @@
         <v>1.133</v>
       </c>
       <c r="D56" s="0" t="n">
-        <v>20.96658711217183</v>
+        <v>48.505964</v>
       </c>
       <c r="E56" s="0" t="inlineStr">
         <is>
@@ -4065,7 +4065,7 @@
         <v>0</v>
       </c>
       <c r="J56" s="0" t="n">
-        <v>2</v>
+        <v>4</v>
       </c>
       <c r="K56" s="0" t="n">
         <v>1</v>
@@ -4094,7 +4094,7 @@
         <v>1.648</v>
       </c>
       <c r="D57" s="0" t="n">
-        <v>17.82159904534606</v>
+        <v>41.230069</v>
       </c>
       <c r="E57" s="0" t="inlineStr">
         <is>
@@ -4116,7 +4116,7 @@
         <v>0</v>
       </c>
       <c r="J57" s="0" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="K57" s="0" t="n">
         <v>1</v>
@@ -4145,7 +4145,7 @@
         <v>1.648</v>
       </c>
       <c r="D58" s="0" t="n">
-        <v>17.82159904534606</v>
+        <v>41.230069</v>
       </c>
       <c r="E58" s="0" t="inlineStr">
         <is>
@@ -4167,7 +4167,7 @@
         <v>0</v>
       </c>
       <c r="J58" s="0" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="K58" s="0" t="n">
         <v>1</v>
@@ -4196,7 +4196,7 @@
         <v>1.648</v>
       </c>
       <c r="D59" s="0" t="n">
-        <v>17.82159904534606</v>
+        <v>41.230069</v>
       </c>
       <c r="E59" s="0" t="inlineStr">
         <is>
@@ -4218,7 +4218,7 @@
         <v>0</v>
       </c>
       <c r="J59" s="0" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="K59" s="0" t="n">
         <v>1</v>
@@ -4247,7 +4247,7 @@
         <v>1.03</v>
       </c>
       <c r="D60" s="0" t="n">
-        <v>32.79174224343675</v>
+        <v>75.863327</v>
       </c>
       <c r="E60" s="0" t="inlineStr">
         <is>
@@ -4269,7 +4269,7 @@
         <v>0.08</v>
       </c>
       <c r="J60" s="0" t="n">
-        <v>2</v>
+        <v>4</v>
       </c>
       <c r="K60" s="0" t="n">
         <v>1</v>
@@ -4298,7 +4298,7 @@
         <v>1.0815</v>
       </c>
       <c r="D61" s="0" t="n">
-        <v>13.62828162291169</v>
+        <v>31.528876</v>
       </c>
       <c r="E61" s="0" t="inlineStr">
         <is>
@@ -4320,7 +4320,7 @@
         <v>0</v>
       </c>
       <c r="J61" s="0" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="K61" s="0" t="n">
         <v>1</v>
@@ -4349,7 +4349,7 @@
         <v>1.03</v>
       </c>
       <c r="D62" s="0" t="n">
-        <v>32.79174224343675</v>
+        <v>75.863327</v>
       </c>
       <c r="E62" s="0" t="inlineStr">
         <is>
@@ -4371,7 +4371,7 @@
         <v>0.08</v>
       </c>
       <c r="J62" s="0" t="n">
-        <v>2</v>
+        <v>4</v>
       </c>
       <c r="K62" s="0" t="n">
         <v>1</v>
@@ -4400,7 +4400,7 @@
         <v>1.03</v>
       </c>
       <c r="D63" s="0" t="n">
-        <v>32.79174224343675</v>
+        <v>75.863327</v>
       </c>
       <c r="E63" s="0" t="inlineStr">
         <is>
@@ -4422,7 +4422,7 @@
         <v>0.08</v>
       </c>
       <c r="J63" s="0" t="n">
-        <v>2</v>
+        <v>4</v>
       </c>
       <c r="K63" s="0" t="n">
         <v>1</v>
@@ -4451,7 +4451,7 @@
         <v>1.0315</v>
       </c>
       <c r="D64" s="0" t="n">
-        <v>16.37373737373738</v>
+        <v>50.507277</v>
       </c>
       <c r="E64" s="0" t="inlineStr">
         <is>
@@ -4473,7 +4473,7 @@
         <v>0</v>
       </c>
       <c r="J64" s="0" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="K64" s="0" t="n">
         <v>1</v>
@@ -4502,7 +4502,7 @@
         <v>1.0315</v>
       </c>
       <c r="D65" s="0" t="n">
-        <v>16.37373737373738</v>
+        <v>50.507277</v>
       </c>
       <c r="E65" s="0" t="inlineStr">
         <is>
@@ -4524,7 +4524,7 @@
         <v>0</v>
       </c>
       <c r="J65" s="0" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="K65" s="0" t="n">
         <v>1</v>
@@ -4553,7 +4553,7 @@
         <v>1.13465</v>
       </c>
       <c r="D66" s="0" t="n">
-        <v>36.38608305274972</v>
+        <v>84.178794</v>
       </c>
       <c r="E66" s="0" t="inlineStr">
         <is>
@@ -4575,7 +4575,7 @@
         <v>0</v>
       </c>
       <c r="J66" s="0" t="n">
-        <v>2</v>
+        <v>4</v>
       </c>
       <c r="K66" s="0" t="n">
         <v>1</v>
@@ -4604,7 +4604,7 @@
         <v>1.13465</v>
       </c>
       <c r="D67" s="0" t="n">
-        <v>36.38608305274972</v>
+        <v>84.178794</v>
       </c>
       <c r="E67" s="0" t="inlineStr">
         <is>
@@ -4626,7 +4626,7 @@
         <v>0</v>
       </c>
       <c r="J67" s="0" t="n">
-        <v>2</v>
+        <v>4</v>
       </c>
       <c r="K67" s="0" t="n">
         <v>1</v>
@@ -4655,7 +4655,7 @@
         <v>1.6504</v>
       </c>
       <c r="D68" s="0" t="n">
-        <v>30.92817059483726</v>
+        <v>71.551975</v>
       </c>
       <c r="E68" s="0" t="inlineStr">
         <is>
@@ -4677,7 +4677,7 @@
         <v>0</v>
       </c>
       <c r="J68" s="0" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="K68" s="0" t="n">
         <v>1</v>
@@ -4706,7 +4706,7 @@
         <v>1.6504</v>
       </c>
       <c r="D69" s="0" t="n">
-        <v>30.92817059483726</v>
+        <v>71.551975</v>
       </c>
       <c r="E69" s="0" t="inlineStr">
         <is>
@@ -4728,7 +4728,7 @@
         <v>0</v>
       </c>
       <c r="J69" s="0" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="K69" s="0" t="n">
         <v>1</v>
@@ -4757,7 +4757,7 @@
         <v>1.0315</v>
       </c>
       <c r="D70" s="0" t="n">
-        <v>56.90783389450056</v>
+        <v>131.655634</v>
       </c>
       <c r="E70" s="0" t="inlineStr">
         <is>
@@ -4779,7 +4779,7 @@
         <v>0.08</v>
       </c>
       <c r="J70" s="0" t="n">
-        <v>2</v>
+        <v>4</v>
       </c>
       <c r="K70" s="0" t="n">
         <v>1</v>
@@ -4808,7 +4808,7 @@
         <v>1.083075</v>
       </c>
       <c r="D71" s="0" t="n">
-        <v>23.65095398428732</v>
+        <v>54.716216</v>
       </c>
       <c r="E71" s="0" t="inlineStr">
         <is>
@@ -4830,7 +4830,7 @@
         <v>0</v>
       </c>
       <c r="J71" s="0" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="K71" s="0" t="n">
         <v>1</v>
@@ -4859,7 +4859,7 @@
         <v>1.6504</v>
       </c>
       <c r="D72" s="0" t="n">
-        <v>30.92817059483726</v>
+        <v>71.551975</v>
       </c>
       <c r="E72" s="0" t="inlineStr">
         <is>
@@ -4881,7 +4881,7 @@
         <v>0</v>
       </c>
       <c r="J72" s="0" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="K72" s="0" t="n">
         <v>1</v>
@@ -4910,7 +4910,7 @@
         <v>1.0315</v>
       </c>
       <c r="D73" s="0" t="n">
-        <v>56.90783389450056</v>
+        <v>131.655634</v>
       </c>
       <c r="E73" s="0" t="inlineStr">
         <is>
@@ -4932,7 +4932,7 @@
         <v>0.08</v>
       </c>
       <c r="J73" s="0" t="n">
-        <v>2</v>
+        <v>4</v>
       </c>
       <c r="K73" s="0" t="n">
         <v>1</v>
@@ -4961,7 +4961,7 @@
         <v>1.0315</v>
       </c>
       <c r="D74" s="0" t="n">
-        <v>56.90783389450056</v>
+        <v>131.655634</v>
       </c>
       <c r="E74" s="0" t="inlineStr">
         <is>
@@ -4983,7 +4983,7 @@
         <v>0.08</v>
       </c>
       <c r="J74" s="0" t="n">
-        <v>2</v>
+        <v>4</v>
       </c>
       <c r="K74" s="0" t="n">
         <v>1</v>
@@ -5012,7 +5012,7 @@
         <v>1.1363</v>
       </c>
       <c r="D75" s="0" t="n">
-        <v>30.82013047530289</v>
+        <v>71.302026</v>
       </c>
       <c r="E75" s="0" t="inlineStr">
         <is>
@@ -5034,7 +5034,7 @@
         <v>0</v>
       </c>
       <c r="J75" s="0" t="n">
-        <v>2</v>
+        <v>4</v>
       </c>
       <c r="K75" s="0" t="n">
         <v>1</v>
@@ -5063,7 +5063,7 @@
         <v>1.1363</v>
       </c>
       <c r="D76" s="0" t="n">
-        <v>30.82013047530289</v>
+        <v>71.302026</v>
       </c>
       <c r="E76" s="0" t="inlineStr">
         <is>
@@ -5085,7 +5085,7 @@
         <v>0</v>
       </c>
       <c r="J76" s="0" t="n">
-        <v>2</v>
+        <v>4</v>
       </c>
       <c r="K76" s="0" t="n">
         <v>1</v>
@@ -5114,7 +5114,7 @@
         <v>1.6528</v>
       </c>
       <c r="D77" s="0" t="n">
-        <v>26.19711090400746</v>
+        <v>60.606722</v>
       </c>
       <c r="E77" s="0" t="inlineStr">
         <is>
@@ -5136,7 +5136,7 @@
         <v>0</v>
       </c>
       <c r="J77" s="0" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="K77" s="0" t="n">
         <v>1</v>
@@ -5165,7 +5165,7 @@
         <v>1.6528</v>
       </c>
       <c r="D78" s="0" t="n">
-        <v>26.19711090400746</v>
+        <v>60.606722</v>
       </c>
       <c r="E78" s="0" t="inlineStr">
         <is>
@@ -5187,7 +5187,7 @@
         <v>0</v>
       </c>
       <c r="J78" s="0" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="K78" s="0" t="n">
         <v>1</v>
@@ -5216,7 +5216,7 @@
         <v>0.8264</v>
       </c>
       <c r="D79" s="0" t="n">
-        <v>57.6336439888164</v>
+        <v>133.334788</v>
       </c>
       <c r="E79" s="0" t="inlineStr">
         <is>
@@ -5238,7 +5238,7 @@
         <v>0.15</v>
       </c>
       <c r="J79" s="0" t="n">
-        <v>3</v>
+        <v>6</v>
       </c>
       <c r="K79" s="0" t="n">
         <v>2</v>
@@ -5267,7 +5267,7 @@
         <v>1.033</v>
       </c>
       <c r="D80" s="0" t="n">
-        <v>48.20268406337372</v>
+        <v>111.516368</v>
       </c>
       <c r="E80" s="0" t="inlineStr">
         <is>
@@ -5289,7 +5289,7 @@
         <v>0.08</v>
       </c>
       <c r="J80" s="0" t="n">
-        <v>2</v>
+        <v>4</v>
       </c>
       <c r="K80" s="0" t="n">
         <v>1</v>
@@ -5318,7 +5318,7 @@
         <v>1.08465</v>
       </c>
       <c r="D81" s="0" t="n">
-        <v>20.03308480894688</v>
+        <v>46.346317</v>
       </c>
       <c r="E81" s="0" t="inlineStr">
         <is>
@@ -5340,7 +5340,7 @@
         <v>0</v>
       </c>
       <c r="J81" s="0" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="K81" s="0" t="n">
         <v>1</v>
@@ -5369,7 +5369,7 @@
         <v>0.8264</v>
       </c>
       <c r="D82" s="0" t="n">
-        <v>57.6336439888164</v>
+        <v>133.334788</v>
       </c>
       <c r="E82" s="0" t="inlineStr">
         <is>
@@ -5391,7 +5391,7 @@
         <v>0.15</v>
       </c>
       <c r="J82" s="0" t="n">
-        <v>3</v>
+        <v>6</v>
       </c>
       <c r="K82" s="0" t="n">
         <v>2</v>
@@ -5420,7 +5420,7 @@
         <v>0.8264</v>
       </c>
       <c r="D83" s="0" t="n">
-        <v>57.6336439888164</v>
+        <v>133.334788</v>
       </c>
       <c r="E83" s="0" t="inlineStr">
         <is>
@@ -5442,7 +5442,7 @@
         <v>0.15</v>
       </c>
       <c r="J83" s="0" t="n">
-        <v>3</v>
+        <v>6</v>
       </c>
       <c r="K83" s="0" t="n">
         <v>2</v>
@@ -5471,7 +5471,7 @@
         <v>1.6528</v>
       </c>
       <c r="D84" s="0" t="n">
-        <v>26.19711090400746</v>
+        <v>60.606722</v>
       </c>
       <c r="E84" s="0" t="inlineStr">
         <is>
@@ -5493,7 +5493,7 @@
         <v>0</v>
       </c>
       <c r="J84" s="0" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="K84" s="0" t="n">
         <v>1</v>
@@ -5522,7 +5522,7 @@
         <v>1.033</v>
       </c>
       <c r="D85" s="0" t="n">
-        <v>48.20268406337372</v>
+        <v>111.516368</v>
       </c>
       <c r="E85" s="0" t="inlineStr">
         <is>
@@ -5544,7 +5544,7 @@
         <v>0.08</v>
       </c>
       <c r="J85" s="0" t="n">
-        <v>2</v>
+        <v>4</v>
       </c>
       <c r="K85" s="0" t="n">
         <v>1</v>
@@ -5573,7 +5573,7 @@
         <v>1.033</v>
       </c>
       <c r="D86" s="0" t="n">
-        <v>48.20268406337372</v>
+        <v>111.516368</v>
       </c>
       <c r="E86" s="0" t="inlineStr">
         <is>
@@ -5595,7 +5595,7 @@
         <v>0.08</v>
       </c>
       <c r="J86" s="0" t="n">
-        <v>2</v>
+        <v>4</v>
       </c>
       <c r="K86" s="0" t="n">
         <v>1</v>
@@ -5624,7 +5624,7 @@
         <v>1.0345</v>
       </c>
       <c r="D87" s="0" t="n">
-        <v>13.67984014209591</v>
+        <v>42.197542</v>
       </c>
       <c r="E87" s="0" t="inlineStr">
         <is>
@@ -5646,7 +5646,7 @@
         <v>0</v>
       </c>
       <c r="J87" s="0" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="K87" s="0" t="n">
         <v>1</v>
@@ -5675,7 +5675,7 @@
         <v>1.0345</v>
       </c>
       <c r="D88" s="0" t="n">
-        <v>13.67984014209591</v>
+        <v>42.197542</v>
       </c>
       <c r="E88" s="0" t="inlineStr">
         <is>
@@ -5697,7 +5697,7 @@
         <v>0</v>
       </c>
       <c r="J88" s="0" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="K88" s="0" t="n">
         <v>1</v>
@@ -5726,7 +5726,7 @@
         <v>1.0345</v>
       </c>
       <c r="D89" s="0" t="n">
-        <v>13.67984014209591</v>
+        <v>42.197542</v>
       </c>
       <c r="E89" s="0" t="inlineStr">
         <is>
@@ -5748,7 +5748,7 @@
         <v>0</v>
       </c>
       <c r="J89" s="0" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="K89" s="0" t="n">
         <v>1</v>
@@ -5777,7 +5777,7 @@
         <v>1.13795</v>
       </c>
       <c r="D90" s="0" t="n">
-        <v>30.39964476021314</v>
+        <v>70.32923700000001</v>
       </c>
       <c r="E90" s="0" t="inlineStr">
         <is>
@@ -5799,7 +5799,7 @@
         <v>0</v>
       </c>
       <c r="J90" s="0" t="n">
-        <v>2</v>
+        <v>4</v>
       </c>
       <c r="K90" s="0" t="n">
         <v>1</v>
@@ -5828,7 +5828,7 @@
         <v>1.13795</v>
       </c>
       <c r="D91" s="0" t="n">
-        <v>30.39964476021314</v>
+        <v>70.32923700000001</v>
       </c>
       <c r="E91" s="0" t="inlineStr">
         <is>
@@ -5850,7 +5850,7 @@
         <v>0</v>
       </c>
       <c r="J91" s="0" t="n">
-        <v>2</v>
+        <v>4</v>
       </c>
       <c r="K91" s="0" t="n">
         <v>1</v>
@@ -5879,7 +5879,7 @@
         <v>0.8276</v>
       </c>
       <c r="D92" s="0" t="n">
-        <v>56.84733570159858</v>
+        <v>131.515672</v>
       </c>
       <c r="E92" s="0" t="inlineStr">
         <is>
@@ -5901,7 +5901,7 @@
         <v>0.15</v>
       </c>
       <c r="J92" s="0" t="n">
-        <v>3</v>
+        <v>6</v>
       </c>
       <c r="K92" s="0" t="n">
         <v>2</v>
@@ -5930,7 +5930,7 @@
         <v>1.6552</v>
       </c>
       <c r="D93" s="0" t="n">
-        <v>25.83969804618117</v>
+        <v>59.779851</v>
       </c>
       <c r="E93" s="0" t="inlineStr">
         <is>
@@ -5952,7 +5952,7 @@
         <v>0</v>
       </c>
       <c r="J93" s="0" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="K93" s="0" t="n">
         <v>1</v>
@@ -5981,7 +5981,7 @@
         <v>1.6552</v>
       </c>
       <c r="D94" s="0" t="n">
-        <v>25.83969804618117</v>
+        <v>59.779851</v>
       </c>
       <c r="E94" s="0" t="inlineStr">
         <is>
@@ -6003,7 +6003,7 @@
         <v>0</v>
       </c>
       <c r="J94" s="0" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="K94" s="0" t="n">
         <v>1</v>
@@ -6032,7 +6032,7 @@
         <v>0.8276</v>
       </c>
       <c r="D95" s="0" t="n">
-        <v>56.84733570159858</v>
+        <v>131.515672</v>
       </c>
       <c r="E95" s="0" t="inlineStr">
         <is>
@@ -6054,7 +6054,7 @@
         <v>0.15</v>
       </c>
       <c r="J95" s="0" t="n">
-        <v>3</v>
+        <v>6</v>
       </c>
       <c r="K95" s="0" t="n">
         <v>2</v>
@@ -6083,7 +6083,7 @@
         <v>1.0345</v>
       </c>
       <c r="D96" s="0" t="n">
-        <v>47.54504440497335</v>
+        <v>109.994926</v>
       </c>
       <c r="E96" s="0" t="inlineStr">
         <is>
@@ -6105,7 +6105,7 @@
         <v>0.08</v>
       </c>
       <c r="J96" s="0" t="n">
-        <v>2</v>
+        <v>4</v>
       </c>
       <c r="K96" s="0" t="n">
         <v>1</v>
@@ -6134,7 +6134,7 @@
         <v>1.086225</v>
       </c>
       <c r="D97" s="0" t="n">
-        <v>19.75976909413854</v>
+        <v>45.714004</v>
       </c>
       <c r="E97" s="0" t="inlineStr">
         <is>
@@ -6156,7 +6156,7 @@
         <v>0</v>
       </c>
       <c r="J97" s="0" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="K97" s="0" t="n">
         <v>1</v>
@@ -6185,7 +6185,7 @@
         <v>0.8276</v>
       </c>
       <c r="D98" s="0" t="n">
-        <v>56.84733570159858</v>
+        <v>131.515672</v>
       </c>
       <c r="E98" s="0" t="inlineStr">
         <is>
@@ -6207,7 +6207,7 @@
         <v>0.15</v>
       </c>
       <c r="J98" s="0" t="n">
-        <v>3</v>
+        <v>6</v>
       </c>
       <c r="K98" s="0" t="n">
         <v>2</v>
@@ -6236,7 +6236,7 @@
         <v>1.6552</v>
       </c>
       <c r="D99" s="0" t="n">
-        <v>25.83969804618117</v>
+        <v>59.779851</v>
       </c>
       <c r="E99" s="0" t="inlineStr">
         <is>
@@ -6258,7 +6258,7 @@
         <v>0</v>
       </c>
       <c r="J99" s="0" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="K99" s="0" t="n">
         <v>1</v>
@@ -6287,7 +6287,7 @@
         <v>1.0345</v>
       </c>
       <c r="D100" s="0" t="n">
-        <v>47.54504440497335</v>
+        <v>109.994926</v>
       </c>
       <c r="E100" s="0" t="inlineStr">
         <is>
@@ -6309,7 +6309,7 @@
         <v>0.08</v>
       </c>
       <c r="J100" s="0" t="n">
-        <v>2</v>
+        <v>4</v>
       </c>
       <c r="K100" s="0" t="n">
         <v>1</v>
@@ -6338,7 +6338,7 @@
         <v>1.0345</v>
       </c>
       <c r="D101" s="0" t="n">
-        <v>47.54504440497335</v>
+        <v>109.994926</v>
       </c>
       <c r="E101" s="0" t="inlineStr">
         <is>
@@ -6360,7 +6360,7 @@
         <v>0.08</v>
       </c>
       <c r="J101" s="0" t="n">
-        <v>2</v>
+        <v>4</v>
       </c>
       <c r="K101" s="0" t="n">
         <v>1</v>
@@ -6389,7 +6389,7 @@
         <v>1.036</v>
       </c>
       <c r="D102" s="0" t="n">
-        <v>15.75849056603774</v>
+        <v>48.609454</v>
       </c>
       <c r="E102" s="0" t="inlineStr">
         <is>
@@ -6411,7 +6411,7 @@
         <v>0</v>
       </c>
       <c r="J102" s="0" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="K102" s="0" t="n">
         <v>1</v>
@@ -6440,7 +6440,7 @@
         <v>1.036</v>
       </c>
       <c r="D103" s="0" t="n">
-        <v>15.75849056603774</v>
+        <v>48.609454</v>
       </c>
       <c r="E103" s="0" t="inlineStr">
         <is>
@@ -6462,7 +6462,7 @@
         <v>0</v>
       </c>
       <c r="J103" s="0" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="K103" s="0" t="n">
         <v>1</v>
@@ -6491,7 +6491,7 @@
         <v>1.036</v>
       </c>
       <c r="D104" s="0" t="n">
-        <v>15.75849056603774</v>
+        <v>48.609454</v>
       </c>
       <c r="E104" s="0" t="inlineStr">
         <is>
@@ -6513,7 +6513,7 @@
         <v>0</v>
       </c>
       <c r="J104" s="0" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="K104" s="0" t="n">
         <v>1</v>
@@ -6542,7 +6542,7 @@
         <v>1.1396</v>
       </c>
       <c r="D105" s="0" t="n">
-        <v>35.0188679245283</v>
+        <v>81.01575699999999</v>
       </c>
       <c r="E105" s="0" t="inlineStr">
         <is>
@@ -6564,7 +6564,7 @@
         <v>0</v>
       </c>
       <c r="J105" s="0" t="n">
-        <v>2</v>
+        <v>4</v>
       </c>
       <c r="K105" s="0" t="n">
         <v>1</v>
@@ -6593,7 +6593,7 @@
         <v>1.1396</v>
       </c>
       <c r="D106" s="0" t="n">
-        <v>35.0188679245283</v>
+        <v>81.01575699999999</v>
       </c>
       <c r="E106" s="0" t="inlineStr">
         <is>
@@ -6615,7 +6615,7 @@
         <v>0</v>
       </c>
       <c r="J106" s="0" t="n">
-        <v>2</v>
+        <v>4</v>
       </c>
       <c r="K106" s="0" t="n">
         <v>1</v>
@@ -6644,7 +6644,7 @@
         <v>1.6576</v>
       </c>
       <c r="D107" s="0" t="n">
-        <v>29.76603773584906</v>
+        <v>68.863394</v>
       </c>
       <c r="E107" s="0" t="inlineStr">
         <is>
@@ -6666,7 +6666,7 @@
         <v>0</v>
       </c>
       <c r="J107" s="0" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="K107" s="0" t="n">
         <v>1</v>
@@ -6695,7 +6695,7 @@
         <v>0.8288000000000001</v>
       </c>
       <c r="D108" s="0" t="n">
-        <v>65.48528301886793</v>
+        <v>151.499466</v>
       </c>
       <c r="E108" s="0" t="inlineStr">
         <is>
@@ -6717,7 +6717,7 @@
         <v>0.15</v>
       </c>
       <c r="J108" s="0" t="n">
-        <v>3</v>
+        <v>6</v>
       </c>
       <c r="K108" s="0" t="n">
         <v>2</v>
@@ -6746,7 +6746,7 @@
         <v>0.8288000000000001</v>
       </c>
       <c r="D109" s="0" t="n">
-        <v>65.48528301886793</v>
+        <v>151.499466</v>
       </c>
       <c r="E109" s="0" t="inlineStr">
         <is>
@@ -6768,7 +6768,7 @@
         <v>0.15</v>
       </c>
       <c r="J109" s="0" t="n">
-        <v>3</v>
+        <v>6</v>
       </c>
       <c r="K109" s="0" t="n">
         <v>2</v>
@@ -6797,7 +6797,7 @@
         <v>1.6576</v>
       </c>
       <c r="D110" s="0" t="n">
-        <v>29.76603773584906</v>
+        <v>68.863394</v>
       </c>
       <c r="E110" s="0" t="inlineStr">
         <is>
@@ -6819,7 +6819,7 @@
         <v>0</v>
       </c>
       <c r="J110" s="0" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="K110" s="0" t="n">
         <v>1</v>
@@ -6848,7 +6848,7 @@
         <v>1.6576</v>
       </c>
       <c r="D111" s="0" t="n">
-        <v>29.76603773584906</v>
+        <v>68.863394</v>
       </c>
       <c r="E111" s="0" t="inlineStr">
         <is>
@@ -6870,7 +6870,7 @@
         <v>0</v>
       </c>
       <c r="J111" s="0" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="K111" s="0" t="n">
         <v>1</v>
@@ -6899,7 +6899,7 @@
         <v>1.036</v>
       </c>
       <c r="D112" s="0" t="n">
-        <v>54.76950943396227</v>
+        <v>126.708645</v>
       </c>
       <c r="E112" s="0" t="inlineStr">
         <is>
@@ -6921,7 +6921,7 @@
         <v>0.08</v>
       </c>
       <c r="J112" s="0" t="n">
-        <v>2</v>
+        <v>4</v>
       </c>
       <c r="K112" s="0" t="n">
         <v>1</v>
@@ -6950,7 +6950,7 @@
         <v>1.0878</v>
       </c>
       <c r="D113" s="0" t="n">
-        <v>22.7622641509434</v>
+        <v>52.660242</v>
       </c>
       <c r="E113" s="0" t="inlineStr">
         <is>
@@ -6972,7 +6972,7 @@
         <v>0</v>
       </c>
       <c r="J113" s="0" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="K113" s="0" t="n">
         <v>1</v>
@@ -7001,7 +7001,7 @@
         <v>0.8288000000000001</v>
       </c>
       <c r="D114" s="0" t="n">
-        <v>65.48528301886793</v>
+        <v>151.499466</v>
       </c>
       <c r="E114" s="0" t="inlineStr">
         <is>
@@ -7023,7 +7023,7 @@
         <v>0.15</v>
       </c>
       <c r="J114" s="0" t="n">
-        <v>3</v>
+        <v>6</v>
       </c>
       <c r="K114" s="0" t="n">
         <v>2</v>
@@ -7052,7 +7052,7 @@
         <v>1.036</v>
       </c>
       <c r="D115" s="0" t="n">
-        <v>54.76950943396227</v>
+        <v>126.708645</v>
       </c>
       <c r="E115" s="0" t="inlineStr">
         <is>
@@ -7074,7 +7074,7 @@
         <v>0.08</v>
       </c>
       <c r="J115" s="0" t="n">
-        <v>2</v>
+        <v>4</v>
       </c>
       <c r="K115" s="0" t="n">
         <v>1</v>
@@ -7103,7 +7103,7 @@
         <v>1.036</v>
       </c>
       <c r="D116" s="0" t="n">
-        <v>54.76950943396227</v>
+        <v>126.708645</v>
       </c>
       <c r="E116" s="0" t="inlineStr">
         <is>
@@ -7125,7 +7125,7 @@
         <v>0.08</v>
       </c>
       <c r="J116" s="0" t="n">
-        <v>2</v>
+        <v>4</v>
       </c>
       <c r="K116" s="0" t="n">
         <v>1</v>
@@ -7154,7 +7154,7 @@
         <v>1.0375</v>
       </c>
       <c r="D117" s="0" t="n">
-        <v>17.98215701823949</v>
+        <v>55.468691</v>
       </c>
       <c r="E117" s="0" t="inlineStr">
         <is>
@@ -7176,7 +7176,7 @@
         <v>0</v>
       </c>
       <c r="J117" s="0" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="K117" s="0" t="n">
         <v>1</v>
@@ -7205,7 +7205,7 @@
         <v>1.0375</v>
       </c>
       <c r="D118" s="0" t="n">
-        <v>17.98215701823949</v>
+        <v>55.468691</v>
       </c>
       <c r="E118" s="0" t="inlineStr">
         <is>
@@ -7227,7 +7227,7 @@
         <v>0</v>
       </c>
       <c r="J118" s="0" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="K118" s="0" t="n">
         <v>1</v>
@@ -7256,7 +7256,7 @@
         <v>1.0375</v>
       </c>
       <c r="D119" s="0" t="n">
-        <v>17.98215701823949</v>
+        <v>55.468691</v>
       </c>
       <c r="E119" s="0" t="inlineStr">
         <is>
@@ -7278,7 +7278,7 @@
         <v>0</v>
       </c>
       <c r="J119" s="0" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="K119" s="0" t="n">
         <v>1</v>
@@ -7307,7 +7307,7 @@
         <v>1.14125</v>
       </c>
       <c r="D120" s="0" t="n">
-        <v>39.96034892942109</v>
+        <v>92.447818</v>
       </c>
       <c r="E120" s="0" t="inlineStr">
         <is>
@@ -7329,7 +7329,7 @@
         <v>0</v>
       </c>
       <c r="J120" s="0" t="n">
-        <v>2</v>
+        <v>4</v>
       </c>
       <c r="K120" s="0" t="n">
         <v>1</v>
@@ -7358,7 +7358,7 @@
         <v>1.14125</v>
       </c>
       <c r="D121" s="0" t="n">
-        <v>39.96034892942109</v>
+        <v>92.447818</v>
       </c>
       <c r="E121" s="0" t="inlineStr">
         <is>
@@ -7380,7 +7380,7 @@
         <v>0</v>
       </c>
       <c r="J121" s="0" t="n">
-        <v>2</v>
+        <v>4</v>
       </c>
       <c r="K121" s="0" t="n">
         <v>1</v>
@@ -7409,7 +7409,7 @@
         <v>1.66</v>
       </c>
       <c r="D122" s="0" t="n">
-        <v>33.96629659000793</v>
+        <v>78.580645</v>
       </c>
       <c r="E122" s="0" t="inlineStr">
         <is>
@@ -7431,7 +7431,7 @@
         <v>0</v>
       </c>
       <c r="J122" s="0" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="K122" s="0" t="n">
         <v>1</v>
@@ -7460,7 +7460,7 @@
         <v>0.8300000000000001</v>
       </c>
       <c r="D123" s="0" t="n">
-        <v>74.72585249801745</v>
+        <v>172.87742</v>
       </c>
       <c r="E123" s="0" t="inlineStr">
         <is>
@@ -7482,7 +7482,7 @@
         <v>0.15</v>
       </c>
       <c r="J123" s="0" t="n">
-        <v>3</v>
+        <v>6</v>
       </c>
       <c r="K123" s="0" t="n">
         <v>2</v>
@@ -7511,7 +7511,7 @@
         <v>0.8300000000000001</v>
       </c>
       <c r="D124" s="0" t="n">
-        <v>74.72585249801745</v>
+        <v>172.87742</v>
       </c>
       <c r="E124" s="0" t="inlineStr">
         <is>
@@ -7533,7 +7533,7 @@
         <v>0.15</v>
       </c>
       <c r="J124" s="0" t="n">
-        <v>3</v>
+        <v>6</v>
       </c>
       <c r="K124" s="0" t="n">
         <v>2</v>
@@ -7562,7 +7562,7 @@
         <v>1.66</v>
       </c>
       <c r="D125" s="0" t="n">
-        <v>33.96629659000793</v>
+        <v>78.580645</v>
       </c>
       <c r="E125" s="0" t="inlineStr">
         <is>
@@ -7584,7 +7584,7 @@
         <v>0</v>
       </c>
       <c r="J125" s="0" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="K125" s="0" t="n">
         <v>1</v>
@@ -7613,7 +7613,7 @@
         <v>1.0375</v>
       </c>
       <c r="D126" s="0" t="n">
-        <v>62.49798572561459</v>
+        <v>144.588388</v>
       </c>
       <c r="E126" s="0" t="inlineStr">
         <is>
@@ -7635,7 +7635,7 @@
         <v>0.08</v>
       </c>
       <c r="J126" s="0" t="n">
-        <v>2</v>
+        <v>4</v>
       </c>
       <c r="K126" s="0" t="n">
         <v>1</v>
@@ -7664,7 +7664,7 @@
         <v>1.089375</v>
       </c>
       <c r="D127" s="0" t="n">
-        <v>25.97422680412371</v>
+        <v>60.091082</v>
       </c>
       <c r="E127" s="0" t="inlineStr">
         <is>
@@ -7686,7 +7686,7 @@
         <v>0</v>
       </c>
       <c r="J127" s="0" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="K127" s="0" t="n">
         <v>1</v>
@@ -7715,7 +7715,7 @@
         <v>1.66</v>
       </c>
       <c r="D128" s="0" t="n">
-        <v>33.96629659000793</v>
+        <v>78.580645</v>
       </c>
       <c r="E128" s="0" t="inlineStr">
         <is>
@@ -7737,7 +7737,7 @@
         <v>0</v>
       </c>
       <c r="J128" s="0" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="K128" s="0" t="n">
         <v>1</v>
@@ -7766,7 +7766,7 @@
         <v>1.0375</v>
       </c>
       <c r="D129" s="0" t="n">
-        <v>62.49798572561459</v>
+        <v>144.588388</v>
       </c>
       <c r="E129" s="0" t="inlineStr">
         <is>
@@ -7788,7 +7788,7 @@
         <v>0.08</v>
       </c>
       <c r="J129" s="0" t="n">
-        <v>2</v>
+        <v>4</v>
       </c>
       <c r="K129" s="0" t="n">
         <v>1</v>
@@ -7817,7 +7817,7 @@
         <v>1.0375</v>
       </c>
       <c r="D130" s="0" t="n">
-        <v>62.49798572561459</v>
+        <v>144.588388</v>
       </c>
       <c r="E130" s="0" t="inlineStr">
         <is>
@@ -7839,7 +7839,7 @@
         <v>0.08</v>
       </c>
       <c r="J130" s="0" t="n">
-        <v>2</v>
+        <v>4</v>
       </c>
       <c r="K130" s="0" t="n">
         <v>1</v>
@@ -7868,7 +7868,7 @@
         <v>0.8300000000000001</v>
       </c>
       <c r="D131" s="0" t="n">
-        <v>74.72585249801745</v>
+        <v>172.87742</v>
       </c>
       <c r="E131" s="0" t="inlineStr">
         <is>
@@ -7890,7 +7890,7 @@
         <v>0.15</v>
       </c>
       <c r="J131" s="0" t="n">
-        <v>3</v>
+        <v>6</v>
       </c>
       <c r="K131" s="0" t="n">
         <v>2</v>
@@ -7919,7 +7919,7 @@
         <v>1.039</v>
       </c>
       <c r="D132" s="0" t="n">
-        <v>29.15469613259668</v>
+        <v>89.93208300000001</v>
       </c>
       <c r="E132" s="0" t="inlineStr">
         <is>
@@ -7941,7 +7941,7 @@
         <v>0</v>
       </c>
       <c r="J132" s="0" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="K132" s="0" t="n">
         <v>1</v>
@@ -7970,7 +7970,7 @@
         <v>1.039</v>
       </c>
       <c r="D133" s="0" t="n">
-        <v>29.15469613259668</v>
+        <v>89.93208300000001</v>
       </c>
       <c r="E133" s="0" t="inlineStr">
         <is>
@@ -7992,7 +7992,7 @@
         <v>0</v>
       </c>
       <c r="J133" s="0" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="K133" s="0" t="n">
         <v>1</v>
@@ -8021,7 +8021,7 @@
         <v>1.039</v>
       </c>
       <c r="D134" s="0" t="n">
-        <v>29.15469613259668</v>
+        <v>89.93208300000001</v>
       </c>
       <c r="E134" s="0" t="inlineStr">
         <is>
@@ -8043,7 +8043,7 @@
         <v>0</v>
       </c>
       <c r="J134" s="0" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="K134" s="0" t="n">
         <v>1</v>
@@ -8072,7 +8072,7 @@
         <v>1.1429</v>
       </c>
       <c r="D135" s="0" t="n">
-        <v>64.78821362799263</v>
+        <v>149.886804</v>
       </c>
       <c r="E135" s="0" t="inlineStr">
         <is>
@@ -8094,7 +8094,7 @@
         <v>0</v>
       </c>
       <c r="J135" s="0" t="n">
-        <v>2</v>
+        <v>4</v>
       </c>
       <c r="K135" s="0" t="n">
         <v>1</v>
@@ -8123,7 +8123,7 @@
         <v>1.1429</v>
       </c>
       <c r="D136" s="0" t="n">
-        <v>64.78821362799263</v>
+        <v>149.886804</v>
       </c>
       <c r="E136" s="0" t="inlineStr">
         <is>
@@ -8145,7 +8145,7 @@
         <v>0</v>
       </c>
       <c r="J136" s="0" t="n">
-        <v>2</v>
+        <v>4</v>
       </c>
       <c r="K136" s="0" t="n">
         <v>1</v>
@@ -8174,7 +8174,7 @@
         <v>1.6624</v>
       </c>
       <c r="D137" s="0" t="n">
-        <v>55.06998158379374</v>
+        <v>127.403784</v>
       </c>
       <c r="E137" s="0" t="inlineStr">
         <is>
@@ -8196,7 +8196,7 @@
         <v>0</v>
       </c>
       <c r="J137" s="0" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="K137" s="0" t="n">
         <v>1</v>
@@ -8225,7 +8225,7 @@
         <v>0.8311999999999999</v>
       </c>
       <c r="D138" s="0" t="n">
-        <v>121.1539594843462</v>
+        <v>280.288324</v>
       </c>
       <c r="E138" s="0" t="inlineStr">
         <is>
@@ -8247,7 +8247,7 @@
         <v>0.15</v>
       </c>
       <c r="J138" s="0" t="n">
-        <v>3</v>
+        <v>6</v>
       </c>
       <c r="K138" s="0" t="n">
         <v>2</v>
@@ -8276,7 +8276,7 @@
         <v>1.6624</v>
       </c>
       <c r="D139" s="0" t="n">
-        <v>55.06998158379374</v>
+        <v>127.403784</v>
       </c>
       <c r="E139" s="0" t="inlineStr">
         <is>
@@ -8298,7 +8298,7 @@
         <v>0</v>
       </c>
       <c r="J139" s="0" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="K139" s="0" t="n">
         <v>1</v>
@@ -8327,7 +8327,7 @@
         <v>1.6624</v>
       </c>
       <c r="D140" s="0" t="n">
-        <v>55.06998158379374</v>
+        <v>127.403784</v>
       </c>
       <c r="E140" s="0" t="inlineStr">
         <is>
@@ -8349,7 +8349,7 @@
         <v>0</v>
       </c>
       <c r="J140" s="0" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="K140" s="0" t="n">
         <v>1</v>
@@ -8378,7 +8378,7 @@
         <v>0.77925</v>
       </c>
       <c r="D141" s="0" t="n">
-        <v>242.5670718232044</v>
+        <v>561.176195</v>
       </c>
       <c r="E141" s="0" t="inlineStr">
         <is>
@@ -8400,7 +8400,7 @@
         <v>0.22</v>
       </c>
       <c r="J141" s="0" t="n">
-        <v>5</v>
+        <v>9</v>
       </c>
       <c r="K141" s="0" t="n">
         <v>2</v>
@@ -8429,7 +8429,7 @@
         <v>0.8311999999999999</v>
       </c>
       <c r="D142" s="0" t="n">
-        <v>121.1539594843462</v>
+        <v>280.288324</v>
       </c>
       <c r="E142" s="0" t="inlineStr">
         <is>
@@ -8451,7 +8451,7 @@
         <v>0.15</v>
       </c>
       <c r="J142" s="0" t="n">
-        <v>3</v>
+        <v>6</v>
       </c>
       <c r="K142" s="0" t="n">
         <v>2</v>
@@ -8480,7 +8480,7 @@
         <v>1.039</v>
       </c>
       <c r="D143" s="0" t="n">
-        <v>101.3287661141805</v>
+        <v>234.422962</v>
       </c>
       <c r="E143" s="0" t="inlineStr">
         <is>
@@ -8502,7 +8502,7 @@
         <v>0.08</v>
       </c>
       <c r="J143" s="0" t="n">
-        <v>2</v>
+        <v>4</v>
       </c>
       <c r="K143" s="0" t="n">
         <v>1</v>
@@ -8531,7 +8531,7 @@
         <v>1.09095</v>
       </c>
       <c r="D144" s="0" t="n">
-        <v>42.11233885819521</v>
+        <v>97.426423</v>
       </c>
       <c r="E144" s="0" t="inlineStr">
         <is>
@@ -8553,7 +8553,7 @@
         <v>0</v>
       </c>
       <c r="J144" s="0" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="K144" s="0" t="n">
         <v>1</v>
@@ -8582,7 +8582,7 @@
         <v>1.6624</v>
       </c>
       <c r="D145" s="0" t="n">
-        <v>55.06998158379374</v>
+        <v>127.403784</v>
       </c>
       <c r="E145" s="0" t="inlineStr">
         <is>
@@ -8604,7 +8604,7 @@
         <v>0</v>
       </c>
       <c r="J145" s="0" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="K145" s="0" t="n">
         <v>1</v>
@@ -8633,7 +8633,7 @@
         <v>1.039</v>
       </c>
       <c r="D146" s="0" t="n">
-        <v>101.3287661141805</v>
+        <v>234.422962</v>
       </c>
       <c r="E146" s="0" t="inlineStr">
         <is>
@@ -8655,7 +8655,7 @@
         <v>0.08</v>
       </c>
       <c r="J146" s="0" t="n">
-        <v>2</v>
+        <v>4</v>
       </c>
       <c r="K146" s="0" t="n">
         <v>1</v>
@@ -8684,7 +8684,7 @@
         <v>1.039</v>
       </c>
       <c r="D147" s="0" t="n">
-        <v>101.3287661141805</v>
+        <v>234.422962</v>
       </c>
       <c r="E147" s="0" t="inlineStr">
         <is>
@@ -8706,7 +8706,7 @@
         <v>0.08</v>
       </c>
       <c r="J147" s="0" t="n">
-        <v>2</v>
+        <v>4</v>
       </c>
       <c r="K147" s="0" t="n">
         <v>1</v>
@@ -8735,7 +8735,7 @@
         <v>0.8311999999999999</v>
       </c>
       <c r="D148" s="0" t="n">
-        <v>121.1539594843462</v>
+        <v>280.288324</v>
       </c>
       <c r="E148" s="0" t="inlineStr">
         <is>
@@ -8757,7 +8757,7 @@
         <v>0.15</v>
       </c>
       <c r="J148" s="0" t="n">
-        <v>3</v>
+        <v>6</v>
       </c>
       <c r="K148" s="0" t="n">
         <v>2</v>
@@ -8786,7 +8786,7 @@
         <v>1.14455</v>
       </c>
       <c r="D149" s="0" t="n">
-        <v>65.05438723712835</v>
+        <v>150.502594</v>
       </c>
       <c r="E149" s="0" t="inlineStr">
         <is>
@@ -8808,7 +8808,7 @@
         <v>0</v>
       </c>
       <c r="J149" s="0" t="n">
-        <v>2</v>
+        <v>4</v>
       </c>
       <c r="K149" s="0" t="n">
         <v>1</v>
@@ -8837,7 +8837,7 @@
         <v>1.14455</v>
       </c>
       <c r="D150" s="0" t="n">
-        <v>65.05438723712835</v>
+        <v>150.502594</v>
       </c>
       <c r="E150" s="0" t="inlineStr">
         <is>
@@ -8859,7 +8859,7 @@
         <v>0</v>
       </c>
       <c r="J150" s="0" t="n">
-        <v>2</v>
+        <v>4</v>
       </c>
       <c r="K150" s="0" t="n">
         <v>1</v>
@@ -8888,7 +8888,7 @@
         <v>1.6648</v>
       </c>
       <c r="D151" s="0" t="n">
-        <v>55.2962291515591</v>
+        <v>127.927205</v>
       </c>
       <c r="E151" s="0" t="inlineStr">
         <is>
@@ -8910,7 +8910,7 @@
         <v>0</v>
       </c>
       <c r="J151" s="0" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="K151" s="0" t="n">
         <v>1</v>
@@ -8939,7 +8939,7 @@
         <v>1.6648</v>
       </c>
       <c r="D152" s="0" t="n">
-        <v>55.2962291515591</v>
+        <v>127.927205</v>
       </c>
       <c r="E152" s="0" t="inlineStr">
         <is>
@@ -8961,7 +8961,7 @@
         <v>0</v>
       </c>
       <c r="J152" s="0" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="K152" s="0" t="n">
         <v>1</v>
@@ -8990,7 +8990,7 @@
         <v>1.6648</v>
       </c>
       <c r="D153" s="0" t="n">
-        <v>55.2962291515591</v>
+        <v>127.927205</v>
       </c>
       <c r="E153" s="0" t="inlineStr">
         <is>
@@ -9012,7 +9012,7 @@
         <v>0</v>
       </c>
       <c r="J153" s="0" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="K153" s="0" t="n">
         <v>1</v>
@@ -9041,7 +9041,7 @@
         <v>0.8324</v>
       </c>
       <c r="D154" s="0" t="n">
-        <v>121.65170413343</v>
+        <v>281.43985</v>
       </c>
       <c r="E154" s="0" t="inlineStr">
         <is>
@@ -9063,7 +9063,7 @@
         <v>0.15</v>
       </c>
       <c r="J154" s="0" t="n">
-        <v>3</v>
+        <v>6</v>
       </c>
       <c r="K154" s="0" t="n">
         <v>2</v>
@@ -9092,7 +9092,7 @@
         <v>0.8324</v>
       </c>
       <c r="D155" s="0" t="n">
-        <v>121.65170413343</v>
+        <v>281.43985</v>
       </c>
       <c r="E155" s="0" t="inlineStr">
         <is>
@@ -9114,7 +9114,7 @@
         <v>0.15</v>
       </c>
       <c r="J155" s="0" t="n">
-        <v>3</v>
+        <v>6</v>
       </c>
       <c r="K155" s="0" t="n">
         <v>2</v>
@@ -9143,7 +9143,7 @@
         <v>1.0405</v>
       </c>
       <c r="D156" s="0" t="n">
-        <v>101.7450616388687</v>
+        <v>235.386057</v>
       </c>
       <c r="E156" s="0" t="inlineStr">
         <is>
@@ -9165,7 +9165,7 @@
         <v>0.08</v>
       </c>
       <c r="J156" s="0" t="n">
-        <v>2</v>
+        <v>4</v>
       </c>
       <c r="K156" s="0" t="n">
         <v>1</v>
@@ -9194,7 +9194,7 @@
         <v>1.092525</v>
       </c>
       <c r="D157" s="0" t="n">
-        <v>42.28535170413343</v>
+        <v>97.826686</v>
       </c>
       <c r="E157" s="0" t="inlineStr">
         <is>
@@ -9216,7 +9216,7 @@
         <v>0</v>
       </c>
       <c r="J157" s="0" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="K157" s="0" t="n">
         <v>1</v>
@@ -9245,7 +9245,7 @@
         <v>1.6648</v>
       </c>
       <c r="D158" s="0" t="n">
-        <v>55.2962291515591</v>
+        <v>127.927205</v>
       </c>
       <c r="E158" s="0" t="inlineStr">
         <is>
@@ -9267,7 +9267,7 @@
         <v>0</v>
       </c>
       <c r="J158" s="0" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="K158" s="0" t="n">
         <v>1</v>
@@ -9296,7 +9296,7 @@
         <v>1.0405</v>
       </c>
       <c r="D159" s="0" t="n">
-        <v>101.7450616388687</v>
+        <v>235.386057</v>
       </c>
       <c r="E159" s="0" t="inlineStr">
         <is>
@@ -9318,7 +9318,7 @@
         <v>0.08</v>
       </c>
       <c r="J159" s="0" t="n">
-        <v>2</v>
+        <v>4</v>
       </c>
       <c r="K159" s="0" t="n">
         <v>1</v>
@@ -9347,7 +9347,7 @@
         <v>1.0405</v>
       </c>
       <c r="D160" s="0" t="n">
-        <v>101.7450616388687</v>
+        <v>235.386057</v>
       </c>
       <c r="E160" s="0" t="inlineStr">
         <is>
@@ -9369,7 +9369,7 @@
         <v>0.08</v>
       </c>
       <c r="J160" s="0" t="n">
-        <v>2</v>
+        <v>4</v>
       </c>
       <c r="K160" s="0" t="n">
         <v>1</v>
@@ -9398,7 +9398,7 @@
         <v>0.8324</v>
       </c>
       <c r="D161" s="0" t="n">
-        <v>121.65170413343</v>
+        <v>281.43985</v>
       </c>
       <c r="E161" s="0" t="inlineStr">
         <is>
@@ -9420,7 +9420,7 @@
         <v>0.15</v>
       </c>
       <c r="J161" s="0" t="n">
-        <v>3</v>
+        <v>6</v>
       </c>
       <c r="K161" s="0" t="n">
         <v>2</v>
@@ -9449,7 +9449,7 @@
         <v>1.042</v>
       </c>
       <c r="D162" s="0" t="n">
-        <v>28.68652037617554</v>
+        <v>88.48792299999999</v>
       </c>
       <c r="E162" s="0" t="inlineStr">
         <is>
@@ -9471,7 +9471,7 @@
         <v>0</v>
       </c>
       <c r="J162" s="0" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="K162" s="0" t="n">
         <v>1</v>
@@ -9500,7 +9500,7 @@
         <v>1.042</v>
       </c>
       <c r="D163" s="0" t="n">
-        <v>28.68652037617554</v>
+        <v>88.48792299999999</v>
       </c>
       <c r="E163" s="0" t="inlineStr">
         <is>
@@ -9522,7 +9522,7 @@
         <v>0</v>
       </c>
       <c r="J163" s="0" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="K163" s="0" t="n">
         <v>1</v>
@@ -9551,7 +9551,7 @@
         <v>1.042</v>
       </c>
       <c r="D164" s="0" t="n">
-        <v>28.68652037617554</v>
+        <v>88.48792299999999</v>
       </c>
       <c r="E164" s="0" t="inlineStr">
         <is>
@@ -9573,7 +9573,7 @@
         <v>0</v>
       </c>
       <c r="J164" s="0" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="K164" s="0" t="n">
         <v>1</v>
@@ -9602,7 +9602,7 @@
         <v>1.1462</v>
       </c>
       <c r="D165" s="0" t="n">
-        <v>63.74782305816788</v>
+        <v>147.479872</v>
       </c>
       <c r="E165" s="0" t="inlineStr">
         <is>
@@ -9624,7 +9624,7 @@
         <v>0</v>
       </c>
       <c r="J165" s="0" t="n">
-        <v>2</v>
+        <v>4</v>
       </c>
       <c r="K165" s="0" t="n">
         <v>1</v>
@@ -9653,7 +9653,7 @@
         <v>1.1462</v>
       </c>
       <c r="D166" s="0" t="n">
-        <v>63.74782305816788</v>
+        <v>147.479872</v>
       </c>
       <c r="E166" s="0" t="inlineStr">
         <is>
@@ -9675,7 +9675,7 @@
         <v>0</v>
       </c>
       <c r="J166" s="0" t="n">
-        <v>2</v>
+        <v>4</v>
       </c>
       <c r="K166" s="0" t="n">
         <v>1</v>
@@ -9704,7 +9704,7 @@
         <v>1.6672</v>
       </c>
       <c r="D167" s="0" t="n">
-        <v>54.1856495994427</v>
+        <v>125.357891</v>
       </c>
       <c r="E167" s="0" t="inlineStr">
         <is>
@@ -9726,7 +9726,7 @@
         <v>0</v>
       </c>
       <c r="J167" s="0" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="K167" s="0" t="n">
         <v>1</v>
@@ -9755,7 +9755,7 @@
         <v>1.6672</v>
       </c>
       <c r="D168" s="0" t="n">
-        <v>54.1856495994427</v>
+        <v>125.357891</v>
       </c>
       <c r="E168" s="0" t="inlineStr">
         <is>
@@ -9777,7 +9777,7 @@
         <v>0</v>
       </c>
       <c r="J168" s="0" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="K168" s="0" t="n">
         <v>1</v>
@@ -9806,7 +9806,7 @@
         <v>1.6672</v>
       </c>
       <c r="D169" s="0" t="n">
-        <v>54.1856495994427</v>
+        <v>125.357891</v>
       </c>
       <c r="E169" s="0" t="inlineStr">
         <is>
@@ -9828,7 +9828,7 @@
         <v>0</v>
       </c>
       <c r="J169" s="0" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="K169" s="0" t="n">
         <v>1</v>
@@ -9857,7 +9857,7 @@
         <v>0.8336000000000001</v>
       </c>
       <c r="D170" s="0" t="n">
-        <v>119.2084291187739</v>
+        <v>275.787361</v>
       </c>
       <c r="E170" s="0" t="inlineStr">
         <is>
@@ -9879,7 +9879,7 @@
         <v>0.15</v>
       </c>
       <c r="J170" s="0" t="n">
-        <v>3</v>
+        <v>6</v>
       </c>
       <c r="K170" s="0" t="n">
         <v>2</v>
@@ -9908,7 +9908,7 @@
         <v>0.8336000000000001</v>
       </c>
       <c r="D171" s="0" t="n">
-        <v>119.2084291187739</v>
+        <v>275.787361</v>
       </c>
       <c r="E171" s="0" t="inlineStr">
         <is>
@@ -9930,7 +9930,7 @@
         <v>0.15</v>
       </c>
       <c r="J171" s="0" t="n">
-        <v>3</v>
+        <v>6</v>
       </c>
       <c r="K171" s="0" t="n">
         <v>2</v>
@@ -9959,7 +9959,7 @@
         <v>1.042</v>
       </c>
       <c r="D172" s="0" t="n">
-        <v>99.70159526297456</v>
+        <v>230.65852</v>
       </c>
       <c r="E172" s="0" t="inlineStr">
         <is>
@@ -9981,7 +9981,7 @@
         <v>0.08</v>
       </c>
       <c r="J172" s="0" t="n">
-        <v>2</v>
+        <v>4</v>
       </c>
       <c r="K172" s="0" t="n">
         <v>1</v>
@@ -10010,7 +10010,7 @@
         <v>1.0941</v>
       </c>
       <c r="D173" s="0" t="n">
-        <v>41.43608498780912</v>
+        <v>95.86191700000001</v>
       </c>
       <c r="E173" s="0" t="inlineStr">
         <is>
@@ -10032,7 +10032,7 @@
         <v>0</v>
       </c>
       <c r="J173" s="0" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="K173" s="0" t="n">
         <v>1</v>
@@ -10061,7 +10061,7 @@
         <v>0.8336000000000001</v>
       </c>
       <c r="D174" s="0" t="n">
-        <v>119.2084291187739</v>
+        <v>275.787361</v>
       </c>
       <c r="E174" s="0" t="inlineStr">
         <is>
@@ -10083,7 +10083,7 @@
         <v>0.15</v>
       </c>
       <c r="J174" s="0" t="n">
-        <v>3</v>
+        <v>6</v>
       </c>
       <c r="K174" s="0" t="n">
         <v>2</v>
@@ -10112,7 +10112,7 @@
         <v>1.6672</v>
       </c>
       <c r="D175" s="0" t="n">
-        <v>54.1856495994427</v>
+        <v>125.357891</v>
       </c>
       <c r="E175" s="0" t="inlineStr">
         <is>
@@ -10134,7 +10134,7 @@
         <v>0</v>
       </c>
       <c r="J175" s="0" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="K175" s="0" t="n">
         <v>1</v>
@@ -10163,7 +10163,7 @@
         <v>1.042</v>
       </c>
       <c r="D176" s="0" t="n">
-        <v>99.70159526297456</v>
+        <v>230.65852</v>
       </c>
       <c r="E176" s="0" t="inlineStr">
         <is>
@@ -10185,7 +10185,7 @@
         <v>0.08</v>
       </c>
       <c r="J176" s="0" t="n">
-        <v>2</v>
+        <v>4</v>
       </c>
       <c r="K176" s="0" t="n">
         <v>1</v>
@@ -10214,7 +10214,7 @@
         <v>1.042</v>
       </c>
       <c r="D177" s="0" t="n">
-        <v>99.70159526297456</v>
+        <v>230.65852</v>
       </c>
       <c r="E177" s="0" t="inlineStr">
         <is>
@@ -10236,7 +10236,7 @@
         <v>0.08</v>
       </c>
       <c r="J177" s="0" t="n">
-        <v>2</v>
+        <v>4</v>
       </c>
       <c r="K177" s="0" t="n">
         <v>1</v>
@@ -10265,7 +10265,7 @@
         <v>1.0435</v>
       </c>
       <c r="D178" s="0" t="n">
-        <v>29.21713147410359</v>
+        <v>90.124674</v>
       </c>
       <c r="E178" s="0" t="inlineStr">
         <is>
@@ -10287,7 +10287,7 @@
         <v>0</v>
       </c>
       <c r="J178" s="0" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="K178" s="0" t="n">
         <v>1</v>
@@ -10316,7 +10316,7 @@
         <v>1.0435</v>
       </c>
       <c r="D179" s="0" t="n">
-        <v>29.21713147410359</v>
+        <v>90.124674</v>
       </c>
       <c r="E179" s="0" t="inlineStr">
         <is>
@@ -10338,7 +10338,7 @@
         <v>0</v>
       </c>
       <c r="J179" s="0" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="K179" s="0" t="n">
         <v>1</v>
@@ -10367,7 +10367,7 @@
         <v>1.0435</v>
       </c>
       <c r="D180" s="0" t="n">
-        <v>29.21713147410359</v>
+        <v>90.124674</v>
       </c>
       <c r="E180" s="0" t="inlineStr">
         <is>
@@ -10389,7 +10389,7 @@
         <v>0</v>
       </c>
       <c r="J180" s="0" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="K180" s="0" t="n">
         <v>1</v>
@@ -10418,7 +10418,7 @@
         <v>1.14785</v>
       </c>
       <c r="D181" s="0" t="n">
-        <v>64.92695883134131</v>
+        <v>150.20779</v>
       </c>
       <c r="E181" s="0" t="inlineStr">
         <is>
@@ -10440,7 +10440,7 @@
         <v>0</v>
       </c>
       <c r="J181" s="0" t="n">
-        <v>2</v>
+        <v>4</v>
       </c>
       <c r="K181" s="0" t="n">
         <v>1</v>
@@ -10469,7 +10469,7 @@
         <v>1.14785</v>
       </c>
       <c r="D182" s="0" t="n">
-        <v>64.92695883134131</v>
+        <v>150.20779</v>
       </c>
       <c r="E182" s="0" t="inlineStr">
         <is>
@@ -10491,7 +10491,7 @@
         <v>0</v>
       </c>
       <c r="J182" s="0" t="n">
-        <v>2</v>
+        <v>4</v>
       </c>
       <c r="K182" s="0" t="n">
         <v>1</v>
@@ -10520,7 +10520,7 @@
         <v>1.6696</v>
       </c>
       <c r="D183" s="0" t="n">
-        <v>55.1879150066401</v>
+        <v>127.676621</v>
       </c>
       <c r="E183" s="0" t="inlineStr">
         <is>
@@ -10542,7 +10542,7 @@
         <v>0</v>
       </c>
       <c r="J183" s="0" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="K183" s="0" t="n">
         <v>1</v>
@@ -10571,7 +10571,7 @@
         <v>1.6696</v>
       </c>
       <c r="D184" s="0" t="n">
-        <v>55.1879150066401</v>
+        <v>127.676621</v>
       </c>
       <c r="E184" s="0" t="inlineStr">
         <is>
@@ -10593,7 +10593,7 @@
         <v>0</v>
       </c>
       <c r="J184" s="0" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="K184" s="0" t="n">
         <v>1</v>
@@ -10622,7 +10622,7 @@
         <v>1.6696</v>
       </c>
       <c r="D185" s="0" t="n">
-        <v>55.1879150066401</v>
+        <v>127.676621</v>
       </c>
       <c r="E185" s="0" t="inlineStr">
         <is>
@@ -10644,7 +10644,7 @@
         <v>0</v>
       </c>
       <c r="J185" s="0" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="K185" s="0" t="n">
         <v>1</v>
@@ -10673,7 +10673,7 @@
         <v>0.8348000000000001</v>
       </c>
       <c r="D186" s="0" t="n">
-        <v>121.4134130146083</v>
+        <v>280.888567</v>
       </c>
       <c r="E186" s="0" t="inlineStr">
         <is>
@@ -10695,7 +10695,7 @@
         <v>0.15</v>
       </c>
       <c r="J186" s="0" t="n">
-        <v>3</v>
+        <v>6</v>
       </c>
       <c r="K186" s="0" t="n">
         <v>2</v>
@@ -10724,7 +10724,7 @@
         <v>0.8348000000000001</v>
       </c>
       <c r="D187" s="0" t="n">
-        <v>121.4134130146083</v>
+        <v>280.888567</v>
       </c>
       <c r="E187" s="0" t="inlineStr">
         <is>
@@ -10746,7 +10746,7 @@
         <v>0.15</v>
       </c>
       <c r="J187" s="0" t="n">
-        <v>3</v>
+        <v>6</v>
       </c>
       <c r="K187" s="0" t="n">
         <v>2</v>
@@ -10775,7 +10775,7 @@
         <v>1.0435</v>
       </c>
       <c r="D188" s="0" t="n">
-        <v>101.5457636122178</v>
+        <v>234.924983</v>
       </c>
       <c r="E188" s="0" t="inlineStr">
         <is>
@@ -10797,7 +10797,7 @@
         <v>0.08</v>
       </c>
       <c r="J188" s="0" t="n">
-        <v>2</v>
+        <v>4</v>
       </c>
       <c r="K188" s="0" t="n">
         <v>1</v>
@@ -10826,7 +10826,7 @@
         <v>1.095675</v>
       </c>
       <c r="D189" s="0" t="n">
-        <v>42.20252324037185</v>
+        <v>97.635063</v>
       </c>
       <c r="E189" s="0" t="inlineStr">
         <is>
@@ -10848,7 +10848,7 @@
         <v>0</v>
       </c>
       <c r="J189" s="0" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="K189" s="0" t="n">
         <v>1</v>
@@ -10877,7 +10877,7 @@
         <v>0.8348000000000001</v>
       </c>
       <c r="D190" s="0" t="n">
-        <v>121.4134130146083</v>
+        <v>280.888567</v>
       </c>
       <c r="E190" s="0" t="inlineStr">
         <is>
@@ -10899,7 +10899,7 @@
         <v>0.15</v>
       </c>
       <c r="J190" s="0" t="n">
-        <v>3</v>
+        <v>6</v>
       </c>
       <c r="K190" s="0" t="n">
         <v>2</v>
@@ -10928,7 +10928,7 @@
         <v>1.6696</v>
       </c>
       <c r="D191" s="0" t="n">
-        <v>55.1879150066401</v>
+        <v>127.676621</v>
       </c>
       <c r="E191" s="0" t="inlineStr">
         <is>
@@ -10950,7 +10950,7 @@
         <v>0</v>
       </c>
       <c r="J191" s="0" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="K191" s="0" t="n">
         <v>1</v>
@@ -10979,7 +10979,7 @@
         <v>1.0435</v>
       </c>
       <c r="D192" s="0" t="n">
-        <v>101.5457636122178</v>
+        <v>234.924983</v>
       </c>
       <c r="E192" s="0" t="inlineStr">
         <is>
@@ -11001,7 +11001,7 @@
         <v>0.08</v>
       </c>
       <c r="J192" s="0" t="n">
-        <v>2</v>
+        <v>4</v>
       </c>
       <c r="K192" s="0" t="n">
         <v>1</v>
@@ -11030,7 +11030,7 @@
         <v>1.0435</v>
       </c>
       <c r="D193" s="0" t="n">
-        <v>101.5457636122178</v>
+        <v>234.924983</v>
       </c>
       <c r="E193" s="0" t="inlineStr">
         <is>
@@ -11052,7 +11052,7 @@
         <v>0.08</v>
       </c>
       <c r="J193" s="0" t="n">
-        <v>2</v>
+        <v>4</v>
       </c>
       <c r="K193" s="0" t="n">
         <v>1</v>
@@ -11081,7 +11081,7 @@
         <v>1.045</v>
       </c>
       <c r="D194" s="0" t="n">
-        <v>32.43952896244431</v>
+        <v>100.064648</v>
       </c>
       <c r="E194" s="0" t="inlineStr">
         <is>
@@ -11103,7 +11103,7 @@
         <v>0</v>
       </c>
       <c r="J194" s="0" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="K194" s="0" t="n">
         <v>1</v>
@@ -11132,7 +11132,7 @@
         <v>1.045</v>
       </c>
       <c r="D195" s="0" t="n">
-        <v>32.43952896244431</v>
+        <v>100.064648</v>
       </c>
       <c r="E195" s="0" t="inlineStr">
         <is>
@@ -11154,7 +11154,7 @@
         <v>0</v>
       </c>
       <c r="J195" s="0" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="K195" s="0" t="n">
         <v>1</v>
@@ -11183,7 +11183,7 @@
         <v>1.045</v>
       </c>
       <c r="D196" s="0" t="n">
-        <v>32.43952896244431</v>
+        <v>100.064648</v>
       </c>
       <c r="E196" s="0" t="inlineStr">
         <is>
@@ -11205,7 +11205,7 @@
         <v>0</v>
       </c>
       <c r="J196" s="0" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="K196" s="0" t="n">
         <v>1</v>
@@ -11234,7 +11234,7 @@
         <v>1.1495</v>
       </c>
       <c r="D197" s="0" t="n">
-        <v>72.08784213876513</v>
+        <v>166.774413</v>
       </c>
       <c r="E197" s="0" t="inlineStr">
         <is>
@@ -11256,7 +11256,7 @@
         <v>0</v>
       </c>
       <c r="J197" s="0" t="n">
-        <v>2</v>
+        <v>4</v>
       </c>
       <c r="K197" s="0" t="n">
         <v>1</v>
@@ -11285,7 +11285,7 @@
         <v>1.1495</v>
       </c>
       <c r="D198" s="0" t="n">
-        <v>72.08784213876513</v>
+        <v>166.774413</v>
       </c>
       <c r="E198" s="0" t="inlineStr">
         <is>
@@ -11307,7 +11307,7 @@
         <v>0</v>
       </c>
       <c r="J198" s="0" t="n">
-        <v>2</v>
+        <v>4</v>
       </c>
       <c r="K198" s="0" t="n">
         <v>1</v>
@@ -11336,7 +11336,7 @@
         <v>1.672</v>
       </c>
       <c r="D199" s="0" t="n">
-        <v>61.27466581795035</v>
+        <v>141.758251</v>
       </c>
       <c r="E199" s="0" t="inlineStr">
         <is>
@@ -11358,7 +11358,7 @@
         <v>0</v>
       </c>
       <c r="J199" s="0" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="K199" s="0" t="n">
         <v>1</v>
@@ -11387,7 +11387,7 @@
         <v>1.672</v>
       </c>
       <c r="D200" s="0" t="n">
-        <v>61.27466581795035</v>
+        <v>141.758251</v>
       </c>
       <c r="E200" s="0" t="inlineStr">
         <is>
@@ -11409,7 +11409,7 @@
         <v>0</v>
       </c>
       <c r="J200" s="0" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="K200" s="0" t="n">
         <v>1</v>
@@ -11438,7 +11438,7 @@
         <v>1.672</v>
       </c>
       <c r="D201" s="0" t="n">
-        <v>61.27466581795035</v>
+        <v>141.758251</v>
       </c>
       <c r="E201" s="0" t="inlineStr">
         <is>
@@ -11460,7 +11460,7 @@
         <v>0</v>
       </c>
       <c r="J201" s="0" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="K201" s="0" t="n">
         <v>1</v>
@@ -11489,7 +11489,7 @@
         <v>0.836</v>
       </c>
       <c r="D202" s="0" t="n">
-        <v>134.8042647994908</v>
+        <v>311.868152</v>
       </c>
       <c r="E202" s="0" t="inlineStr">
         <is>
@@ -11511,7 +11511,7 @@
         <v>0.15</v>
       </c>
       <c r="J202" s="0" t="n">
-        <v>3</v>
+        <v>6</v>
       </c>
       <c r="K202" s="0" t="n">
         <v>2</v>
@@ -11540,7 +11540,7 @@
         <v>1.045</v>
       </c>
       <c r="D203" s="0" t="n">
-        <v>112.7453851050286</v>
+        <v>260.835182</v>
       </c>
       <c r="E203" s="0" t="inlineStr">
         <is>
@@ -11562,7 +11562,7 @@
         <v>0.08</v>
       </c>
       <c r="J203" s="0" t="n">
-        <v>2</v>
+        <v>4</v>
       </c>
       <c r="K203" s="0" t="n">
         <v>1</v>
@@ -11591,7 +11591,7 @@
         <v>1.09725</v>
       </c>
       <c r="D204" s="0" t="n">
-        <v>46.85709739019733</v>
+        <v>108.403368</v>
       </c>
       <c r="E204" s="0" t="inlineStr">
         <is>
@@ -11613,7 +11613,7 @@
         <v>0</v>
       </c>
       <c r="J204" s="0" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="K204" s="0" t="n">
         <v>1</v>
@@ -11642,7 +11642,7 @@
         <v>0.836</v>
       </c>
       <c r="D205" s="0" t="n">
-        <v>134.8042647994908</v>
+        <v>311.868152</v>
       </c>
       <c r="E205" s="0" t="inlineStr">
         <is>
@@ -11664,7 +11664,7 @@
         <v>0.15</v>
       </c>
       <c r="J205" s="0" t="n">
-        <v>3</v>
+        <v>6</v>
       </c>
       <c r="K205" s="0" t="n">
         <v>2</v>
@@ -11693,7 +11693,7 @@
         <v>0.836</v>
       </c>
       <c r="D206" s="0" t="n">
-        <v>134.8042647994908</v>
+        <v>311.868152</v>
       </c>
       <c r="E206" s="0" t="inlineStr">
         <is>
@@ -11715,7 +11715,7 @@
         <v>0.15</v>
       </c>
       <c r="J206" s="0" t="n">
-        <v>3</v>
+        <v>6</v>
       </c>
       <c r="K206" s="0" t="n">
         <v>2</v>
@@ -11744,7 +11744,7 @@
         <v>1.672</v>
       </c>
       <c r="D207" s="0" t="n">
-        <v>61.27466581795035</v>
+        <v>141.758251</v>
       </c>
       <c r="E207" s="0" t="inlineStr">
         <is>
@@ -11766,7 +11766,7 @@
         <v>0</v>
       </c>
       <c r="J207" s="0" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="K207" s="0" t="n">
         <v>1</v>
@@ -11795,7 +11795,7 @@
         <v>1.045</v>
       </c>
       <c r="D208" s="0" t="n">
-        <v>112.7453851050286</v>
+        <v>260.835182</v>
       </c>
       <c r="E208" s="0" t="inlineStr">
         <is>
@@ -11817,7 +11817,7 @@
         <v>0.08</v>
       </c>
       <c r="J208" s="0" t="n">
-        <v>2</v>
+        <v>4</v>
       </c>
       <c r="K208" s="0" t="n">
         <v>1</v>
@@ -11846,7 +11846,7 @@
         <v>1.045</v>
       </c>
       <c r="D209" s="0" t="n">
-        <v>112.7453851050286</v>
+        <v>260.835182</v>
       </c>
       <c r="E209" s="0" t="inlineStr">
         <is>
@@ -11868,7 +11868,7 @@
         <v>0.08</v>
       </c>
       <c r="J209" s="0" t="n">
-        <v>2</v>
+        <v>4</v>
       </c>
       <c r="K209" s="0" t="n">
         <v>1</v>
@@ -11897,7 +11897,7 @@
         <v>1.0465</v>
       </c>
       <c r="D210" s="0" t="n">
-        <v>51.33293341331734</v>
+        <v>158.344219</v>
       </c>
       <c r="E210" s="0" t="inlineStr">
         <is>
@@ -11919,7 +11919,7 @@
         <v>0</v>
       </c>
       <c r="J210" s="0" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="K210" s="0" t="n">
         <v>1</v>
@@ -11948,7 +11948,7 @@
         <v>1.0465</v>
       </c>
       <c r="D211" s="0" t="n">
-        <v>51.33293341331734</v>
+        <v>158.344219</v>
       </c>
       <c r="E211" s="0" t="inlineStr">
         <is>
@@ -11970,7 +11970,7 @@
         <v>0</v>
       </c>
       <c r="J211" s="0" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="K211" s="0" t="n">
         <v>1</v>
@@ -11999,7 +11999,7 @@
         <v>1.0465</v>
       </c>
       <c r="D212" s="0" t="n">
-        <v>51.33293341331734</v>
+        <v>158.344219</v>
       </c>
       <c r="E212" s="0" t="inlineStr">
         <is>
@@ -12021,7 +12021,7 @@
         <v>0</v>
       </c>
       <c r="J212" s="0" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="K212" s="0" t="n">
         <v>1</v>
@@ -12050,7 +12050,7 @@
         <v>1.15115</v>
       </c>
       <c r="D213" s="0" t="n">
-        <v>114.0731853629274</v>
+        <v>263.907032</v>
       </c>
       <c r="E213" s="0" t="inlineStr">
         <is>
@@ -12072,7 +12072,7 @@
         <v>0</v>
       </c>
       <c r="J213" s="0" t="n">
-        <v>2</v>
+        <v>4</v>
       </c>
       <c r="K213" s="0" t="n">
         <v>1</v>
@@ -12101,7 +12101,7 @@
         <v>1.15115</v>
       </c>
       <c r="D214" s="0" t="n">
-        <v>114.0731853629274</v>
+        <v>263.907032</v>
       </c>
       <c r="E214" s="0" t="inlineStr">
         <is>
@@ -12123,7 +12123,7 @@
         <v>0</v>
       </c>
       <c r="J214" s="0" t="n">
-        <v>2</v>
+        <v>4</v>
       </c>
       <c r="K214" s="0" t="n">
         <v>1</v>
@@ -12152,7 +12152,7 @@
         <v>1.6744</v>
       </c>
       <c r="D215" s="0" t="n">
-        <v>96.96220755848832</v>
+        <v>224.320978</v>
       </c>
       <c r="E215" s="0" t="inlineStr">
         <is>
@@ -12174,7 +12174,7 @@
         <v>0</v>
       </c>
       <c r="J215" s="0" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="K215" s="0" t="n">
         <v>1</v>
@@ -12203,7 +12203,7 @@
         <v>0.8372000000000001</v>
       </c>
       <c r="D216" s="0" t="n">
-        <v>213.3168566286743</v>
+        <v>493.506151</v>
       </c>
       <c r="E216" s="0" t="inlineStr">
         <is>
@@ -12225,7 +12225,7 @@
         <v>0.15</v>
       </c>
       <c r="J216" s="0" t="n">
-        <v>3</v>
+        <v>6</v>
       </c>
       <c r="K216" s="0" t="n">
         <v>2</v>
@@ -12254,7 +12254,7 @@
         <v>1.6744</v>
       </c>
       <c r="D217" s="0" t="n">
-        <v>96.96220755848832</v>
+        <v>224.320978</v>
       </c>
       <c r="E217" s="0" t="inlineStr">
         <is>
@@ -12276,7 +12276,7 @@
         <v>0</v>
       </c>
       <c r="J217" s="0" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="K217" s="0" t="n">
         <v>1</v>
@@ -12305,7 +12305,7 @@
         <v>1.6744</v>
       </c>
       <c r="D218" s="0" t="n">
-        <v>96.96220755848832</v>
+        <v>224.320978</v>
       </c>
       <c r="E218" s="0" t="inlineStr">
         <is>
@@ -12327,7 +12327,7 @@
         <v>0</v>
       </c>
       <c r="J218" s="0" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="K218" s="0" t="n">
         <v>1</v>
@@ -12356,7 +12356,7 @@
         <v>0.8372000000000001</v>
       </c>
       <c r="D219" s="0" t="n">
-        <v>213.3168566286743</v>
+        <v>493.506151</v>
       </c>
       <c r="E219" s="0" t="inlineStr">
         <is>
@@ -12378,7 +12378,7 @@
         <v>0.15</v>
       </c>
       <c r="J219" s="0" t="n">
-        <v>3</v>
+        <v>6</v>
       </c>
       <c r="K219" s="0" t="n">
         <v>2</v>
@@ -12407,7 +12407,7 @@
         <v>1.0465</v>
       </c>
       <c r="D220" s="0" t="n">
-        <v>178.4104619076185</v>
+        <v>412.750599</v>
       </c>
       <c r="E220" s="0" t="inlineStr">
         <is>
@@ -12429,7 +12429,7 @@
         <v>0.08</v>
       </c>
       <c r="J220" s="0" t="n">
-        <v>2</v>
+        <v>4</v>
       </c>
       <c r="K220" s="0" t="n">
         <v>1</v>
@@ -12458,7 +12458,7 @@
         <v>1.098825</v>
       </c>
       <c r="D221" s="0" t="n">
-        <v>74.14757048590282</v>
+        <v>171.539571</v>
       </c>
       <c r="E221" s="0" t="inlineStr">
         <is>
@@ -12480,7 +12480,7 @@
         <v>0</v>
       </c>
       <c r="J221" s="0" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="K221" s="0" t="n">
         <v>1</v>
@@ -12509,7 +12509,7 @@
         <v>0.8372000000000001</v>
       </c>
       <c r="D222" s="0" t="n">
-        <v>213.3168566286743</v>
+        <v>493.506151</v>
       </c>
       <c r="E222" s="0" t="inlineStr">
         <is>
@@ -12531,7 +12531,7 @@
         <v>0.15</v>
       </c>
       <c r="J222" s="0" t="n">
-        <v>3</v>
+        <v>6</v>
       </c>
       <c r="K222" s="0" t="n">
         <v>2</v>
@@ -12560,7 +12560,7 @@
         <v>1.6744</v>
       </c>
       <c r="D223" s="0" t="n">
-        <v>96.96220755848832</v>
+        <v>224.320978</v>
       </c>
       <c r="E223" s="0" t="inlineStr">
         <is>
@@ -12582,7 +12582,7 @@
         <v>0</v>
       </c>
       <c r="J223" s="0" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="K223" s="0" t="n">
         <v>1</v>
@@ -12611,7 +12611,7 @@
         <v>1.0465</v>
       </c>
       <c r="D224" s="0" t="n">
-        <v>178.4104619076185</v>
+        <v>412.750599</v>
       </c>
       <c r="E224" s="0" t="inlineStr">
         <is>
@@ -12633,7 +12633,7 @@
         <v>0.08</v>
       </c>
       <c r="J224" s="0" t="n">
-        <v>2</v>
+        <v>4</v>
       </c>
       <c r="K224" s="0" t="n">
         <v>1</v>
@@ -12662,7 +12662,7 @@
         <v>1.0465</v>
       </c>
       <c r="D225" s="0" t="n">
-        <v>178.4104619076185</v>
+        <v>412.750599</v>
       </c>
       <c r="E225" s="0" t="inlineStr">
         <is>
@@ -12684,7 +12684,7 @@
         <v>0.08</v>
       </c>
       <c r="J225" s="0" t="n">
-        <v>2</v>
+        <v>4</v>
       </c>
       <c r="K225" s="0" t="n">
         <v>1</v>
@@ -12713,7 +12713,7 @@
         <v>1.0255</v>
       </c>
       <c r="D226" s="0" t="n">
-        <v>6.374719521316381</v>
+        <v>19.663789</v>
       </c>
       <c r="E226" s="0" t="inlineStr">
         <is>
@@ -12735,7 +12735,7 @@
         <v>0</v>
       </c>
       <c r="J226" s="0" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="K226" s="0" t="n">
         <v>1</v>
@@ -12764,7 +12764,7 @@
         <v>1.6408</v>
       </c>
       <c r="D227" s="0" t="n">
-        <v>12.04113687359761</v>
+        <v>27.857035</v>
       </c>
       <c r="E227" s="0" t="inlineStr">
         <is>
@@ -12786,7 +12786,7 @@
         <v>0</v>
       </c>
       <c r="J227" s="0" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="K227" s="0" t="n">
         <v>1</v>
@@ -12815,7 +12815,7 @@
         <v>1.027</v>
       </c>
       <c r="D228" s="0" t="n">
-        <v>6.623108665749656</v>
+        <v>20.429983</v>
       </c>
       <c r="E228" s="0" t="inlineStr">
         <is>
@@ -12837,7 +12837,7 @@
         <v>0</v>
       </c>
       <c r="J228" s="0" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="K228" s="0" t="n">
         <v>1</v>
@@ -12866,7 +12866,7 @@
         <v>1.6432</v>
       </c>
       <c r="D229" s="0" t="n">
-        <v>12.51031636863824</v>
+        <v>28.942476</v>
       </c>
       <c r="E229" s="0" t="inlineStr">
         <is>
@@ -12888,7 +12888,7 @@
         <v>0</v>
       </c>
       <c r="J229" s="0" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="K229" s="0" t="n">
         <v>1</v>
@@ -12917,7 +12917,7 @@
         <v>1.0285</v>
       </c>
       <c r="D230" s="0" t="n">
-        <v>7.902999361837908</v>
+        <v>24.378</v>
       </c>
       <c r="E230" s="0" t="inlineStr">
         <is>
@@ -12939,7 +12939,7 @@
         <v>0</v>
       </c>
       <c r="J230" s="0" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="K230" s="0" t="n">
         <v>1</v>
@@ -12968,7 +12968,7 @@
         <v>1.6456</v>
       </c>
       <c r="D231" s="0" t="n">
-        <v>14.9278876834716</v>
+        <v>34.5355</v>
       </c>
       <c r="E231" s="0" t="inlineStr">
         <is>
@@ -12990,7 +12990,7 @@
         <v>0</v>
       </c>
       <c r="J231" s="0" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="K231" s="0" t="n">
         <v>1</v>
@@ -13019,7 +13019,7 @@
         <v>1.03</v>
       </c>
       <c r="D232" s="0" t="n">
-        <v>9.434964200477326</v>
+        <v>29.103578</v>
       </c>
       <c r="E232" s="0" t="inlineStr">
         <is>
@@ -13041,7 +13041,7 @@
         <v>0</v>
       </c>
       <c r="J232" s="0" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="K232" s="0" t="n">
         <v>1</v>
@@ -13070,7 +13070,7 @@
         <v>1.648</v>
       </c>
       <c r="D233" s="0" t="n">
-        <v>17.82159904534606</v>
+        <v>41.230069</v>
       </c>
       <c r="E233" s="0" t="inlineStr">
         <is>
@@ -13092,7 +13092,7 @@
         <v>0</v>
       </c>
       <c r="J233" s="0" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="K233" s="0" t="n">
         <v>1</v>
@@ -13121,7 +13121,7 @@
         <v>1.0315</v>
       </c>
       <c r="D234" s="0" t="n">
-        <v>16.37373737373738</v>
+        <v>50.507277</v>
       </c>
       <c r="E234" s="0" t="inlineStr">
         <is>
@@ -13143,7 +13143,7 @@
         <v>0</v>
       </c>
       <c r="J234" s="0" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="K234" s="0" t="n">
         <v>1</v>
@@ -13172,7 +13172,7 @@
         <v>1.6504</v>
       </c>
       <c r="D235" s="0" t="n">
-        <v>30.92817059483726</v>
+        <v>71.551975</v>
       </c>
       <c r="E235" s="0" t="inlineStr">
         <is>
@@ -13194,7 +13194,7 @@
         <v>0</v>
       </c>
       <c r="J235" s="0" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="K235" s="0" t="n">
         <v>1</v>
@@ -13223,7 +13223,7 @@
         <v>0.8264</v>
       </c>
       <c r="D236" s="0" t="n">
-        <v>57.6336439888164</v>
+        <v>133.334788</v>
       </c>
       <c r="E236" s="0" t="inlineStr">
         <is>
@@ -13245,7 +13245,7 @@
         <v>0.15</v>
       </c>
       <c r="J236" s="0" t="n">
-        <v>3</v>
+        <v>6</v>
       </c>
       <c r="K236" s="0" t="n">
         <v>2</v>
@@ -13274,7 +13274,7 @@
         <v>0.8264</v>
       </c>
       <c r="D237" s="0" t="n">
-        <v>57.6336439888164</v>
+        <v>133.334788</v>
       </c>
       <c r="E237" s="0" t="inlineStr">
         <is>
@@ -13296,7 +13296,7 @@
         <v>0.15</v>
       </c>
       <c r="J237" s="0" t="n">
-        <v>3</v>
+        <v>6</v>
       </c>
       <c r="K237" s="0" t="n">
         <v>2</v>
@@ -13325,7 +13325,7 @@
         <v>1.6528</v>
       </c>
       <c r="D238" s="0" t="n">
-        <v>26.19711090400746</v>
+        <v>60.606722</v>
       </c>
       <c r="E238" s="0" t="inlineStr">
         <is>
@@ -13347,7 +13347,7 @@
         <v>0</v>
       </c>
       <c r="J238" s="0" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="K238" s="0" t="n">
         <v>1</v>
@@ -13376,7 +13376,7 @@
         <v>1.6552</v>
       </c>
       <c r="D239" s="0" t="n">
-        <v>25.83969804618117</v>
+        <v>59.779851</v>
       </c>
       <c r="E239" s="0" t="inlineStr">
         <is>
@@ -13398,7 +13398,7 @@
         <v>0</v>
       </c>
       <c r="J239" s="0" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="K239" s="0" t="n">
         <v>1</v>
@@ -13427,7 +13427,7 @@
         <v>0.8276</v>
       </c>
       <c r="D240" s="0" t="n">
-        <v>56.84733570159858</v>
+        <v>131.515672</v>
       </c>
       <c r="E240" s="0" t="inlineStr">
         <is>
@@ -13449,7 +13449,7 @@
         <v>0.15</v>
       </c>
       <c r="J240" s="0" t="n">
-        <v>3</v>
+        <v>6</v>
       </c>
       <c r="K240" s="0" t="n">
         <v>2</v>
@@ -13478,7 +13478,7 @@
         <v>0.8276</v>
       </c>
       <c r="D241" s="0" t="n">
-        <v>56.84733570159858</v>
+        <v>131.515672</v>
       </c>
       <c r="E241" s="0" t="inlineStr">
         <is>
@@ -13500,7 +13500,7 @@
         <v>0.15</v>
       </c>
       <c r="J241" s="0" t="n">
-        <v>3</v>
+        <v>6</v>
       </c>
       <c r="K241" s="0" t="n">
         <v>2</v>
@@ -13529,7 +13529,7 @@
         <v>0.8288000000000001</v>
       </c>
       <c r="D242" s="0" t="n">
-        <v>65.48528301886793</v>
+        <v>151.499466</v>
       </c>
       <c r="E242" s="0" t="inlineStr">
         <is>
@@ -13551,7 +13551,7 @@
         <v>0.15</v>
       </c>
       <c r="J242" s="0" t="n">
-        <v>3</v>
+        <v>6</v>
       </c>
       <c r="K242" s="0" t="n">
         <v>2</v>
@@ -13580,7 +13580,7 @@
         <v>1.6576</v>
       </c>
       <c r="D243" s="0" t="n">
-        <v>29.76603773584906</v>
+        <v>68.863394</v>
       </c>
       <c r="E243" s="0" t="inlineStr">
         <is>
@@ -13602,7 +13602,7 @@
         <v>0</v>
       </c>
       <c r="J243" s="0" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="K243" s="0" t="n">
         <v>1</v>
@@ -13631,7 +13631,7 @@
         <v>0.8288000000000001</v>
       </c>
       <c r="D244" s="0" t="n">
-        <v>65.48528301886793</v>
+        <v>151.499466</v>
       </c>
       <c r="E244" s="0" t="inlineStr">
         <is>
@@ -13653,7 +13653,7 @@
         <v>0.15</v>
       </c>
       <c r="J244" s="0" t="n">
-        <v>3</v>
+        <v>6</v>
       </c>
       <c r="K244" s="0" t="n">
         <v>2</v>
@@ -13682,7 +13682,7 @@
         <v>1.66</v>
       </c>
       <c r="D245" s="0" t="n">
-        <v>33.96629659000793</v>
+        <v>78.580645</v>
       </c>
       <c r="E245" s="0" t="inlineStr">
         <is>
@@ -13704,7 +13704,7 @@
         <v>0</v>
       </c>
       <c r="J245" s="0" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="K245" s="0" t="n">
         <v>1</v>
@@ -13733,7 +13733,7 @@
         <v>0.8300000000000001</v>
       </c>
       <c r="D246" s="0" t="n">
-        <v>74.72585249801745</v>
+        <v>172.87742</v>
       </c>
       <c r="E246" s="0" t="inlineStr">
         <is>
@@ -13755,7 +13755,7 @@
         <v>0.15</v>
       </c>
       <c r="J246" s="0" t="n">
-        <v>3</v>
+        <v>6</v>
       </c>
       <c r="K246" s="0" t="n">
         <v>2</v>
@@ -13784,7 +13784,7 @@
         <v>0.8300000000000001</v>
       </c>
       <c r="D247" s="0" t="n">
-        <v>74.72585249801745</v>
+        <v>172.87742</v>
       </c>
       <c r="E247" s="0" t="inlineStr">
         <is>
@@ -13806,7 +13806,7 @@
         <v>0.15</v>
       </c>
       <c r="J247" s="0" t="n">
-        <v>3</v>
+        <v>6</v>
       </c>
       <c r="K247" s="0" t="n">
         <v>2</v>
@@ -13835,7 +13835,7 @@
         <v>0.8311999999999999</v>
       </c>
       <c r="D248" s="0" t="n">
-        <v>121.1539594843462</v>
+        <v>280.288324</v>
       </c>
       <c r="E248" s="0" t="inlineStr">
         <is>
@@ -13857,7 +13857,7 @@
         <v>0.15</v>
       </c>
       <c r="J248" s="0" t="n">
-        <v>3</v>
+        <v>6</v>
       </c>
       <c r="K248" s="0" t="n">
         <v>2</v>
@@ -13886,7 +13886,7 @@
         <v>0.8311999999999999</v>
       </c>
       <c r="D249" s="0" t="n">
-        <v>121.1539594843462</v>
+        <v>280.288324</v>
       </c>
       <c r="E249" s="0" t="inlineStr">
         <is>
@@ -13908,7 +13908,7 @@
         <v>0.15</v>
       </c>
       <c r="J249" s="0" t="n">
-        <v>3</v>
+        <v>6</v>
       </c>
       <c r="K249" s="0" t="n">
         <v>2</v>
@@ -13937,7 +13937,7 @@
         <v>0.8324</v>
       </c>
       <c r="D250" s="0" t="n">
-        <v>121.65170413343</v>
+        <v>281.43985</v>
       </c>
       <c r="E250" s="0" t="inlineStr">
         <is>
@@ -13959,7 +13959,7 @@
         <v>0.15</v>
       </c>
       <c r="J250" s="0" t="n">
-        <v>3</v>
+        <v>6</v>
       </c>
       <c r="K250" s="0" t="n">
         <v>2</v>
@@ -13988,7 +13988,7 @@
         <v>0.8324</v>
       </c>
       <c r="D251" s="0" t="n">
-        <v>121.65170413343</v>
+        <v>281.43985</v>
       </c>
       <c r="E251" s="0" t="inlineStr">
         <is>
@@ -14010,7 +14010,7 @@
         <v>0.15</v>
       </c>
       <c r="J251" s="0" t="n">
-        <v>3</v>
+        <v>6</v>
       </c>
       <c r="K251" s="0" t="n">
         <v>2</v>
@@ -14039,7 +14039,7 @@
         <v>0.8324</v>
       </c>
       <c r="D252" s="0" t="n">
-        <v>121.65170413343</v>
+        <v>281.43985</v>
       </c>
       <c r="E252" s="0" t="inlineStr">
         <is>
@@ -14061,7 +14061,7 @@
         <v>0.15</v>
       </c>
       <c r="J252" s="0" t="n">
-        <v>3</v>
+        <v>6</v>
       </c>
       <c r="K252" s="0" t="n">
         <v>2</v>
@@ -14090,7 +14090,7 @@
         <v>0.8336000000000001</v>
       </c>
       <c r="D253" s="0" t="n">
-        <v>119.2084291187739</v>
+        <v>275.787361</v>
       </c>
       <c r="E253" s="0" t="inlineStr">
         <is>
@@ -14112,7 +14112,7 @@
         <v>0.15</v>
       </c>
       <c r="J253" s="0" t="n">
-        <v>3</v>
+        <v>6</v>
       </c>
       <c r="K253" s="0" t="n">
         <v>2</v>
@@ -14141,7 +14141,7 @@
         <v>0.8336000000000001</v>
       </c>
       <c r="D254" s="0" t="n">
-        <v>119.2084291187739</v>
+        <v>275.787361</v>
       </c>
       <c r="E254" s="0" t="inlineStr">
         <is>
@@ -14163,7 +14163,7 @@
         <v>0.15</v>
       </c>
       <c r="J254" s="0" t="n">
-        <v>3</v>
+        <v>6</v>
       </c>
       <c r="K254" s="0" t="n">
         <v>2</v>
@@ -14192,7 +14192,7 @@
         <v>0.8336000000000001</v>
       </c>
       <c r="D255" s="0" t="n">
-        <v>119.2084291187739</v>
+        <v>275.787361</v>
       </c>
       <c r="E255" s="0" t="inlineStr">
         <is>
@@ -14214,7 +14214,7 @@
         <v>0.15</v>
       </c>
       <c r="J255" s="0" t="n">
-        <v>3</v>
+        <v>6</v>
       </c>
       <c r="K255" s="0" t="n">
         <v>2</v>
@@ -14243,7 +14243,7 @@
         <v>0.8348000000000001</v>
       </c>
       <c r="D256" s="0" t="n">
-        <v>121.4134130146083</v>
+        <v>280.888567</v>
       </c>
       <c r="E256" s="0" t="inlineStr">
         <is>
@@ -14265,7 +14265,7 @@
         <v>0.15</v>
       </c>
       <c r="J256" s="0" t="n">
-        <v>3</v>
+        <v>6</v>
       </c>
       <c r="K256" s="0" t="n">
         <v>2</v>
@@ -14294,7 +14294,7 @@
         <v>0.8348000000000001</v>
       </c>
       <c r="D257" s="0" t="n">
-        <v>121.4134130146083</v>
+        <v>280.888567</v>
       </c>
       <c r="E257" s="0" t="inlineStr">
         <is>
@@ -14316,7 +14316,7 @@
         <v>0.15</v>
       </c>
       <c r="J257" s="0" t="n">
-        <v>3</v>
+        <v>6</v>
       </c>
       <c r="K257" s="0" t="n">
         <v>2</v>
@@ -14345,7 +14345,7 @@
         <v>0.8348000000000001</v>
       </c>
       <c r="D258" s="0" t="n">
-        <v>121.4134130146083</v>
+        <v>280.888567</v>
       </c>
       <c r="E258" s="0" t="inlineStr">
         <is>
@@ -14367,7 +14367,7 @@
         <v>0.15</v>
       </c>
       <c r="J258" s="0" t="n">
-        <v>3</v>
+        <v>6</v>
       </c>
       <c r="K258" s="0" t="n">
         <v>2</v>
@@ -14396,7 +14396,7 @@
         <v>0.836</v>
       </c>
       <c r="D259" s="0" t="n">
-        <v>134.8042647994908</v>
+        <v>311.868152</v>
       </c>
       <c r="E259" s="0" t="inlineStr">
         <is>
@@ -14418,7 +14418,7 @@
         <v>0.15</v>
       </c>
       <c r="J259" s="0" t="n">
-        <v>3</v>
+        <v>6</v>
       </c>
       <c r="K259" s="0" t="n">
         <v>2</v>
@@ -14447,7 +14447,7 @@
         <v>0.836</v>
       </c>
       <c r="D260" s="0" t="n">
-        <v>134.8042647994908</v>
+        <v>311.868152</v>
       </c>
       <c r="E260" s="0" t="inlineStr">
         <is>
@@ -14469,7 +14469,7 @@
         <v>0.15</v>
       </c>
       <c r="J260" s="0" t="n">
-        <v>3</v>
+        <v>6</v>
       </c>
       <c r="K260" s="0" t="n">
         <v>2</v>
@@ -14498,7 +14498,7 @@
         <v>0.836</v>
       </c>
       <c r="D261" s="0" t="n">
-        <v>134.8042647994908</v>
+        <v>311.868152</v>
       </c>
       <c r="E261" s="0" t="inlineStr">
         <is>
@@ -14520,7 +14520,7 @@
         <v>0.15</v>
       </c>
       <c r="J261" s="0" t="n">
-        <v>3</v>
+        <v>6</v>
       </c>
       <c r="K261" s="0" t="n">
         <v>2</v>
@@ -14549,7 +14549,7 @@
         <v>0.8372000000000001</v>
       </c>
       <c r="D262" s="0" t="n">
-        <v>213.3168566286743</v>
+        <v>493.506151</v>
       </c>
       <c r="E262" s="0" t="inlineStr">
         <is>
@@ -14571,7 +14571,7 @@
         <v>0.15</v>
       </c>
       <c r="J262" s="0" t="n">
-        <v>3</v>
+        <v>6</v>
       </c>
       <c r="K262" s="0" t="n">
         <v>2</v>
@@ -14600,7 +14600,7 @@
         <v>0.784875</v>
       </c>
       <c r="D263" s="0" t="n">
-        <v>427.0900059988003</v>
+        <v>988.06793</v>
       </c>
       <c r="E263" s="0" t="inlineStr">
         <is>
@@ -14622,7 +14622,7 @@
         <v>0.22</v>
       </c>
       <c r="J263" s="0" t="n">
-        <v>5</v>
+        <v>9</v>
       </c>
       <c r="K263" s="0" t="n">
         <v>2</v>
@@ -14651,7 +14651,7 @@
         <v>0.8372000000000001</v>
       </c>
       <c r="D264" s="0" t="n">
-        <v>213.3168566286743</v>
+        <v>493.506151</v>
       </c>
       <c r="E264" s="0" t="inlineStr">
         <is>
@@ -14673,7 +14673,7 @@
         <v>0.15</v>
       </c>
       <c r="J264" s="0" t="n">
-        <v>3</v>
+        <v>6</v>
       </c>
       <c r="K264" s="0" t="n">
         <v>2</v>
@@ -14702,7 +14702,7 @@
         <v>0.8372000000000001</v>
       </c>
       <c r="D265" s="0" t="n">
-        <v>213.3168566286743</v>
+        <v>493.506151</v>
       </c>
       <c r="E265" s="0" t="inlineStr">
         <is>
@@ -14724,7 +14724,7 @@
         <v>0.15</v>
       </c>
       <c r="J265" s="0" t="n">
-        <v>3</v>
+        <v>6</v>
       </c>
       <c r="K265" s="0" t="n">
         <v>2</v>
@@ -14753,7 +14753,7 @@
         <v>1.048</v>
       </c>
       <c r="D266" s="0" t="n">
-        <v>51.52685950413223</v>
+        <v>158.942414</v>
       </c>
       <c r="E266" s="0" t="inlineStr">
         <is>
@@ -14775,7 +14775,7 @@
         <v>0</v>
       </c>
       <c r="J266" s="0" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="K266" s="0" t="n">
         <v>1</v>
@@ -14804,7 +14804,7 @@
         <v>1.048</v>
       </c>
       <c r="D267" s="0" t="n">
-        <v>51.52685950413223</v>
+        <v>158.942414</v>
       </c>
       <c r="E267" s="0" t="inlineStr">
         <is>
@@ -14826,7 +14826,7 @@
         <v>0</v>
       </c>
       <c r="J267" s="0" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="K267" s="0" t="n">
         <v>1</v>
@@ -14855,7 +14855,7 @@
         <v>1.048</v>
       </c>
       <c r="D268" s="0" t="n">
-        <v>51.52685950413223</v>
+        <v>158.942414</v>
       </c>
       <c r="E268" s="0" t="inlineStr">
         <is>
@@ -14877,7 +14877,7 @@
         <v>0</v>
       </c>
       <c r="J268" s="0" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="K268" s="0" t="n">
         <v>1</v>
@@ -14906,7 +14906,7 @@
         <v>1.1528</v>
       </c>
       <c r="D269" s="0" t="n">
-        <v>114.504132231405</v>
+        <v>264.904023</v>
       </c>
       <c r="E269" s="0" t="inlineStr">
         <is>
@@ -14928,7 +14928,7 @@
         <v>0</v>
       </c>
       <c r="J269" s="0" t="n">
-        <v>2</v>
+        <v>4</v>
       </c>
       <c r="K269" s="0" t="n">
         <v>1</v>
@@ -14957,7 +14957,7 @@
         <v>1.1528</v>
       </c>
       <c r="D270" s="0" t="n">
-        <v>114.504132231405</v>
+        <v>264.904023</v>
       </c>
       <c r="E270" s="0" t="inlineStr">
         <is>
@@ -14979,7 +14979,7 @@
         <v>0</v>
       </c>
       <c r="J270" s="0" t="n">
-        <v>2</v>
+        <v>4</v>
       </c>
       <c r="K270" s="0" t="n">
         <v>1</v>
@@ -15008,7 +15008,7 @@
         <v>1.6768</v>
       </c>
       <c r="D271" s="0" t="n">
-        <v>97.32851239669422</v>
+        <v>225.16842</v>
       </c>
       <c r="E271" s="0" t="inlineStr">
         <is>
@@ -15030,7 +15030,7 @@
         <v>0</v>
       </c>
       <c r="J271" s="0" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="K271" s="0" t="n">
         <v>1</v>
@@ -15059,7 +15059,7 @@
         <v>0.8384</v>
       </c>
       <c r="D272" s="0" t="n">
-        <v>214.1227272727273</v>
+        <v>495.370523</v>
       </c>
       <c r="E272" s="0" t="inlineStr">
         <is>
@@ -15081,7 +15081,7 @@
         <v>0.15</v>
       </c>
       <c r="J272" s="0" t="n">
-        <v>3</v>
+        <v>6</v>
       </c>
       <c r="K272" s="0" t="n">
         <v>2</v>
@@ -15110,7 +15110,7 @@
         <v>0.8384</v>
       </c>
       <c r="D273" s="0" t="n">
-        <v>214.1227272727273</v>
+        <v>495.370523</v>
       </c>
       <c r="E273" s="0" t="inlineStr">
         <is>
@@ -15132,7 +15132,7 @@
         <v>0.15</v>
       </c>
       <c r="J273" s="0" t="n">
-        <v>3</v>
+        <v>6</v>
       </c>
       <c r="K273" s="0" t="n">
         <v>2</v>
@@ -15161,7 +15161,7 @@
         <v>1.6768</v>
       </c>
       <c r="D274" s="0" t="n">
-        <v>97.32851239669422</v>
+        <v>225.16842</v>
       </c>
       <c r="E274" s="0" t="inlineStr">
         <is>
@@ -15183,7 +15183,7 @@
         <v>0</v>
       </c>
       <c r="J274" s="0" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="K274" s="0" t="n">
         <v>1</v>
@@ -15212,7 +15212,7 @@
         <v>1.6768</v>
       </c>
       <c r="D275" s="0" t="n">
-        <v>97.32851239669422</v>
+        <v>225.16842</v>
       </c>
       <c r="E275" s="0" t="inlineStr">
         <is>
@@ -15234,7 +15234,7 @@
         <v>0</v>
       </c>
       <c r="J275" s="0" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="K275" s="0" t="n">
         <v>1</v>
@@ -15263,7 +15263,7 @@
         <v>0.8384</v>
       </c>
       <c r="D276" s="0" t="n">
-        <v>214.1227272727273</v>
+        <v>495.370523</v>
       </c>
       <c r="E276" s="0" t="inlineStr">
         <is>
@@ -15285,7 +15285,7 @@
         <v>0.15</v>
       </c>
       <c r="J276" s="0" t="n">
-        <v>3</v>
+        <v>6</v>
       </c>
       <c r="K276" s="0" t="n">
         <v>2</v>
@@ -15314,7 +15314,7 @@
         <v>0.8384</v>
       </c>
       <c r="D277" s="0" t="n">
-        <v>214.1227272727273</v>
+        <v>495.370523</v>
       </c>
       <c r="E277" s="0" t="inlineStr">
         <is>
@@ -15336,7 +15336,7 @@
         <v>0.15</v>
       </c>
       <c r="J277" s="0" t="n">
-        <v>3</v>
+        <v>6</v>
       </c>
       <c r="K277" s="0" t="n">
         <v>2</v>
@@ -15365,7 +15365,7 @@
         <v>1.048</v>
       </c>
       <c r="D278" s="0" t="n">
-        <v>179.0844628099174</v>
+        <v>414.309892</v>
       </c>
       <c r="E278" s="0" t="inlineStr">
         <is>
@@ -15387,7 +15387,7 @@
         <v>0.08</v>
       </c>
       <c r="J278" s="0" t="n">
-        <v>2</v>
+        <v>4</v>
       </c>
       <c r="K278" s="0" t="n">
         <v>1</v>
@@ -15416,7 +15416,7 @@
         <v>1.1004</v>
       </c>
       <c r="D279" s="0" t="n">
-        <v>74.42768595041322</v>
+        <v>172.187615</v>
       </c>
       <c r="E279" s="0" t="inlineStr">
         <is>
@@ -15438,7 +15438,7 @@
         <v>0</v>
       </c>
       <c r="J279" s="0" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="K279" s="0" t="n">
         <v>1</v>
@@ -15467,7 +15467,7 @@
         <v>0.8384</v>
       </c>
       <c r="D280" s="0" t="n">
-        <v>214.1227272727273</v>
+        <v>495.370523</v>
       </c>
       <c r="E280" s="0" t="inlineStr">
         <is>
@@ -15489,7 +15489,7 @@
         <v>0.15</v>
       </c>
       <c r="J280" s="0" t="n">
-        <v>3</v>
+        <v>6</v>
       </c>
       <c r="K280" s="0" t="n">
         <v>2</v>
@@ -15518,7 +15518,7 @@
         <v>0.8384</v>
       </c>
       <c r="D281" s="0" t="n">
-        <v>214.1227272727273</v>
+        <v>495.370523</v>
       </c>
       <c r="E281" s="0" t="inlineStr">
         <is>
@@ -15540,7 +15540,7 @@
         <v>0.15</v>
       </c>
       <c r="J281" s="0" t="n">
-        <v>3</v>
+        <v>6</v>
       </c>
       <c r="K281" s="0" t="n">
         <v>2</v>
@@ -15569,7 +15569,7 @@
         <v>1.6768</v>
       </c>
       <c r="D282" s="0" t="n">
-        <v>97.32851239669422</v>
+        <v>225.16842</v>
       </c>
       <c r="E282" s="0" t="inlineStr">
         <is>
@@ -15591,7 +15591,7 @@
         <v>0</v>
       </c>
       <c r="J282" s="0" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="K282" s="0" t="n">
         <v>1</v>
@@ -15620,7 +15620,7 @@
         <v>1.048</v>
       </c>
       <c r="D283" s="0" t="n">
-        <v>179.0844628099174</v>
+        <v>414.309892</v>
       </c>
       <c r="E283" s="0" t="inlineStr">
         <is>
@@ -15642,7 +15642,7 @@
         <v>0.08</v>
       </c>
       <c r="J283" s="0" t="n">
-        <v>2</v>
+        <v>4</v>
       </c>
       <c r="K283" s="0" t="n">
         <v>1</v>
@@ -15671,7 +15671,7 @@
         <v>1.048</v>
       </c>
       <c r="D284" s="0" t="n">
-        <v>179.0844628099174</v>
+        <v>414.309892</v>
       </c>
       <c r="E284" s="0" t="inlineStr">
         <is>
@@ -15693,7 +15693,7 @@
         <v>0.08</v>
       </c>
       <c r="J284" s="0" t="n">
-        <v>2</v>
+        <v>4</v>
       </c>
       <c r="K284" s="0" t="n">
         <v>1</v>
@@ -15722,7 +15722,7 @@
         <v>0.8384</v>
       </c>
       <c r="D285" s="0" t="n">
-        <v>214.1227272727273</v>
+        <v>495.370523</v>
       </c>
       <c r="E285" s="0" t="inlineStr">
         <is>
@@ -15744,7 +15744,7 @@
         <v>0.15</v>
       </c>
       <c r="J285" s="0" t="n">
-        <v>3</v>
+        <v>6</v>
       </c>
       <c r="K285" s="0" t="n">
         <v>2</v>
@@ -15773,7 +15773,7 @@
         <v>1.0495</v>
       </c>
       <c r="D286" s="0" t="n">
-        <v>50.80313837375179</v>
+        <v>156.709986</v>
       </c>
       <c r="E286" s="0" t="inlineStr">
         <is>
@@ -15795,7 +15795,7 @@
         <v>0</v>
       </c>
       <c r="J286" s="0" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="K286" s="0" t="n">
         <v>1</v>
@@ -15824,7 +15824,7 @@
         <v>1.0495</v>
       </c>
       <c r="D287" s="0" t="n">
-        <v>50.80313837375179</v>
+        <v>156.709986</v>
       </c>
       <c r="E287" s="0" t="inlineStr">
         <is>
@@ -15846,7 +15846,7 @@
         <v>0</v>
       </c>
       <c r="J287" s="0" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="K287" s="0" t="n">
         <v>1</v>
@@ -15875,7 +15875,7 @@
         <v>1.0495</v>
       </c>
       <c r="D288" s="0" t="n">
-        <v>50.80313837375179</v>
+        <v>156.709986</v>
       </c>
       <c r="E288" s="0" t="inlineStr">
         <is>
@@ -15897,7 +15897,7 @@
         <v>0</v>
       </c>
       <c r="J288" s="0" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="K288" s="0" t="n">
         <v>1</v>
@@ -15926,7 +15926,7 @@
         <v>1.15445</v>
       </c>
       <c r="D289" s="0" t="n">
-        <v>112.8958630527817</v>
+        <v>261.183311</v>
       </c>
       <c r="E289" s="0" t="inlineStr">
         <is>
@@ -15948,7 +15948,7 @@
         <v>0</v>
       </c>
       <c r="J289" s="0" t="n">
-        <v>2</v>
+        <v>4</v>
       </c>
       <c r="K289" s="0" t="n">
         <v>1</v>
@@ -15977,7 +15977,7 @@
         <v>1.15445</v>
       </c>
       <c r="D290" s="0" t="n">
-        <v>112.8958630527817</v>
+        <v>261.183311</v>
       </c>
       <c r="E290" s="0" t="inlineStr">
         <is>
@@ -15999,7 +15999,7 @@
         <v>0</v>
       </c>
       <c r="J290" s="0" t="n">
-        <v>2</v>
+        <v>4</v>
       </c>
       <c r="K290" s="0" t="n">
         <v>1</v>
@@ -16028,7 +16028,7 @@
         <v>1.6792</v>
       </c>
       <c r="D291" s="0" t="n">
-        <v>95.96148359486448</v>
+        <v>222.005814</v>
       </c>
       <c r="E291" s="0" t="inlineStr">
         <is>
@@ -16050,7 +16050,7 @@
         <v>0</v>
       </c>
       <c r="J291" s="0" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="K291" s="0" t="n">
         <v>1</v>
@@ -16079,7 +16079,7 @@
         <v>0.8396000000000001</v>
       </c>
       <c r="D292" s="0" t="n">
-        <v>211.1152639087018</v>
+        <v>488.412791</v>
       </c>
       <c r="E292" s="0" t="inlineStr">
         <is>
@@ -16101,7 +16101,7 @@
         <v>0.15</v>
       </c>
       <c r="J292" s="0" t="n">
-        <v>3</v>
+        <v>6</v>
       </c>
       <c r="K292" s="0" t="n">
         <v>2</v>
@@ -16130,7 +16130,7 @@
         <v>0.8396000000000001</v>
       </c>
       <c r="D293" s="0" t="n">
-        <v>211.1152639087018</v>
+        <v>488.412791</v>
       </c>
       <c r="E293" s="0" t="inlineStr">
         <is>
@@ -16152,7 +16152,7 @@
         <v>0.15</v>
       </c>
       <c r="J293" s="0" t="n">
-        <v>3</v>
+        <v>6</v>
       </c>
       <c r="K293" s="0" t="n">
         <v>2</v>
@@ -16181,7 +16181,7 @@
         <v>1.6792</v>
       </c>
       <c r="D294" s="0" t="n">
-        <v>95.96148359486448</v>
+        <v>222.005814</v>
       </c>
       <c r="E294" s="0" t="inlineStr">
         <is>
@@ -16203,7 +16203,7 @@
         <v>0</v>
       </c>
       <c r="J294" s="0" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="K294" s="0" t="n">
         <v>1</v>
@@ -16232,7 +16232,7 @@
         <v>1.6792</v>
       </c>
       <c r="D295" s="0" t="n">
-        <v>95.96148359486448</v>
+        <v>222.005814</v>
       </c>
       <c r="E295" s="0" t="inlineStr">
         <is>
@@ -16254,7 +16254,7 @@
         <v>0</v>
       </c>
       <c r="J295" s="0" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="K295" s="0" t="n">
         <v>1</v>
@@ -16283,7 +16283,7 @@
         <v>0.8396000000000001</v>
       </c>
       <c r="D296" s="0" t="n">
-        <v>211.1152639087018</v>
+        <v>488.412791</v>
       </c>
       <c r="E296" s="0" t="inlineStr">
         <is>
@@ -16305,7 +16305,7 @@
         <v>0.15</v>
       </c>
       <c r="J296" s="0" t="n">
-        <v>3</v>
+        <v>6</v>
       </c>
       <c r="K296" s="0" t="n">
         <v>2</v>
@@ -16334,7 +16334,7 @@
         <v>0.8396000000000001</v>
       </c>
       <c r="D297" s="0" t="n">
-        <v>211.1152639087018</v>
+        <v>488.412791</v>
       </c>
       <c r="E297" s="0" t="inlineStr">
         <is>
@@ -16356,7 +16356,7 @@
         <v>0.15</v>
       </c>
       <c r="J297" s="0" t="n">
-        <v>3</v>
+        <v>6</v>
       </c>
       <c r="K297" s="0" t="n">
         <v>2</v>
@@ -16385,7 +16385,7 @@
         <v>0.8396000000000001</v>
       </c>
       <c r="D298" s="0" t="n">
-        <v>211.1152639087018</v>
+        <v>488.412791</v>
       </c>
       <c r="E298" s="0" t="inlineStr">
         <is>
@@ -16407,7 +16407,7 @@
         <v>0.15</v>
       </c>
       <c r="J298" s="0" t="n">
-        <v>3</v>
+        <v>6</v>
       </c>
       <c r="K298" s="0" t="n">
         <v>2</v>
@@ -16436,7 +16436,7 @@
         <v>1.0495</v>
       </c>
       <c r="D299" s="0" t="n">
-        <v>176.5691298145506</v>
+        <v>408.490698</v>
       </c>
       <c r="E299" s="0" t="inlineStr">
         <is>
@@ -16458,7 +16458,7 @@
         <v>0.08</v>
       </c>
       <c r="J299" s="0" t="n">
-        <v>2</v>
+        <v>4</v>
       </c>
       <c r="K299" s="0" t="n">
         <v>1</v>
@@ -16487,7 +16487,7 @@
         <v>1.101975</v>
       </c>
       <c r="D300" s="0" t="n">
-        <v>73.38231098430813</v>
+        <v>169.769152</v>
       </c>
       <c r="E300" s="0" t="inlineStr">
         <is>
@@ -16509,7 +16509,7 @@
         <v>0</v>
       </c>
       <c r="J300" s="0" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="K300" s="0" t="n">
         <v>1</v>
@@ -16538,7 +16538,7 @@
         <v>0.8396000000000001</v>
       </c>
       <c r="D301" s="0" t="n">
-        <v>211.1152639087018</v>
+        <v>488.412791</v>
       </c>
       <c r="E301" s="0" t="inlineStr">
         <is>
@@ -16560,7 +16560,7 @@
         <v>0.15</v>
       </c>
       <c r="J301" s="0" t="n">
-        <v>3</v>
+        <v>6</v>
       </c>
       <c r="K301" s="0" t="n">
         <v>2</v>
@@ -16589,7 +16589,7 @@
         <v>1.6792</v>
       </c>
       <c r="D302" s="0" t="n">
-        <v>95.96148359486448</v>
+        <v>222.005814</v>
       </c>
       <c r="E302" s="0" t="inlineStr">
         <is>
@@ -16611,7 +16611,7 @@
         <v>0</v>
       </c>
       <c r="J302" s="0" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="K302" s="0" t="n">
         <v>1</v>
@@ -16640,7 +16640,7 @@
         <v>1.0495</v>
       </c>
       <c r="D303" s="0" t="n">
-        <v>176.5691298145506</v>
+        <v>408.490698</v>
       </c>
       <c r="E303" s="0" t="inlineStr">
         <is>
@@ -16662,7 +16662,7 @@
         <v>0.08</v>
       </c>
       <c r="J303" s="0" t="n">
-        <v>2</v>
+        <v>4</v>
       </c>
       <c r="K303" s="0" t="n">
         <v>1</v>
@@ -16691,7 +16691,7 @@
         <v>1.0495</v>
       </c>
       <c r="D304" s="0" t="n">
-        <v>176.5691298145506</v>
+        <v>408.490698</v>
       </c>
       <c r="E304" s="0" t="inlineStr">
         <is>
@@ -16713,7 +16713,7 @@
         <v>0.08</v>
       </c>
       <c r="J304" s="0" t="n">
-        <v>2</v>
+        <v>4</v>
       </c>
       <c r="K304" s="0" t="n">
         <v>1</v>
@@ -16742,7 +16742,7 @@
         <v>0.8396000000000001</v>
       </c>
       <c r="D305" s="0" t="n">
-        <v>211.1152639087018</v>
+        <v>488.412791</v>
       </c>
       <c r="E305" s="0" t="inlineStr">
         <is>
@@ -16764,7 +16764,7 @@
         <v>0.15</v>
       </c>
       <c r="J305" s="0" t="n">
-        <v>3</v>
+        <v>6</v>
       </c>
       <c r="K305" s="0" t="n">
         <v>2</v>
@@ -16793,7 +16793,7 @@
         <v>1.051</v>
       </c>
       <c r="D306" s="0" t="n">
-        <v>49.96671251719395</v>
+        <v>154.129904</v>
       </c>
       <c r="E306" s="0" t="inlineStr">
         <is>
@@ -16815,7 +16815,7 @@
         <v>0</v>
       </c>
       <c r="J306" s="0" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="K306" s="0" t="n">
         <v>1</v>
@@ -16844,7 +16844,7 @@
         <v>1.051</v>
       </c>
       <c r="D307" s="0" t="n">
-        <v>49.96671251719395</v>
+        <v>154.129904</v>
       </c>
       <c r="E307" s="0" t="inlineStr">
         <is>
@@ -16866,7 +16866,7 @@
         <v>0</v>
       </c>
       <c r="J307" s="0" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="K307" s="0" t="n">
         <v>1</v>
@@ -16895,7 +16895,7 @@
         <v>1.051</v>
       </c>
       <c r="D308" s="0" t="n">
-        <v>49.96671251719395</v>
+        <v>154.129904</v>
       </c>
       <c r="E308" s="0" t="inlineStr">
         <is>
@@ -16917,7 +16917,7 @@
         <v>0</v>
       </c>
       <c r="J308" s="0" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="K308" s="0" t="n">
         <v>1</v>
@@ -16946,7 +16946,7 @@
         <v>1.1561</v>
       </c>
       <c r="D309" s="0" t="n">
-        <v>111.0371389270977</v>
+        <v>256.883173</v>
       </c>
       <c r="E309" s="0" t="inlineStr">
         <is>
@@ -16968,7 +16968,7 @@
         <v>0</v>
       </c>
       <c r="J309" s="0" t="n">
-        <v>2</v>
+        <v>4</v>
       </c>
       <c r="K309" s="0" t="n">
         <v>1</v>
@@ -16997,7 +16997,7 @@
         <v>1.1561</v>
       </c>
       <c r="D310" s="0" t="n">
-        <v>111.0371389270977</v>
+        <v>256.883173</v>
       </c>
       <c r="E310" s="0" t="inlineStr">
         <is>
@@ -17019,7 +17019,7 @@
         <v>0</v>
       </c>
       <c r="J310" s="0" t="n">
-        <v>2</v>
+        <v>4</v>
       </c>
       <c r="K310" s="0" t="n">
         <v>1</v>
@@ -17048,7 +17048,7 @@
         <v>1.6816</v>
       </c>
       <c r="D311" s="0" t="n">
-        <v>94.38156808803301</v>
+        <v>218.350697</v>
       </c>
       <c r="E311" s="0" t="inlineStr">
         <is>
@@ -17070,7 +17070,7 @@
         <v>0</v>
       </c>
       <c r="J311" s="0" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="K311" s="0" t="n">
         <v>1</v>
@@ -17099,7 +17099,7 @@
         <v>0.8408</v>
       </c>
       <c r="D312" s="0" t="n">
-        <v>207.6394497936726</v>
+        <v>480.371534</v>
       </c>
       <c r="E312" s="0" t="inlineStr">
         <is>
@@ -17121,7 +17121,7 @@
         <v>0.15</v>
       </c>
       <c r="J312" s="0" t="n">
-        <v>3</v>
+        <v>6</v>
       </c>
       <c r="K312" s="0" t="n">
         <v>2</v>
@@ -17150,7 +17150,7 @@
         <v>1.6816</v>
       </c>
       <c r="D313" s="0" t="n">
-        <v>94.38156808803301</v>
+        <v>218.350697</v>
       </c>
       <c r="E313" s="0" t="inlineStr">
         <is>
@@ -17172,7 +17172,7 @@
         <v>0</v>
       </c>
       <c r="J313" s="0" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="K313" s="0" t="n">
         <v>1</v>
@@ -17201,7 +17201,7 @@
         <v>1.6816</v>
       </c>
       <c r="D314" s="0" t="n">
-        <v>94.38156808803301</v>
+        <v>218.350697</v>
       </c>
       <c r="E314" s="0" t="inlineStr">
         <is>
@@ -17223,7 +17223,7 @@
         <v>0</v>
       </c>
       <c r="J314" s="0" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="K314" s="0" t="n">
         <v>1</v>
@@ -17252,7 +17252,7 @@
         <v>0.8408</v>
       </c>
       <c r="D315" s="0" t="n">
-        <v>207.6394497936726</v>
+        <v>480.371534</v>
       </c>
       <c r="E315" s="0" t="inlineStr">
         <is>
@@ -17274,7 +17274,7 @@
         <v>0.15</v>
       </c>
       <c r="J315" s="0" t="n">
-        <v>3</v>
+        <v>6</v>
       </c>
       <c r="K315" s="0" t="n">
         <v>2</v>
@@ -17303,7 +17303,7 @@
         <v>0.8408</v>
       </c>
       <c r="D316" s="0" t="n">
-        <v>207.6394497936726</v>
+        <v>480.371534</v>
       </c>
       <c r="E316" s="0" t="inlineStr">
         <is>
@@ -17325,7 +17325,7 @@
         <v>0.15</v>
       </c>
       <c r="J316" s="0" t="n">
-        <v>3</v>
+        <v>6</v>
       </c>
       <c r="K316" s="0" t="n">
         <v>2</v>
@@ -17354,7 +17354,7 @@
         <v>0.8408</v>
       </c>
       <c r="D317" s="0" t="n">
-        <v>207.6394497936726</v>
+        <v>480.371534</v>
       </c>
       <c r="E317" s="0" t="inlineStr">
         <is>
@@ -17376,7 +17376,7 @@
         <v>0.15</v>
       </c>
       <c r="J317" s="0" t="n">
-        <v>3</v>
+        <v>6</v>
       </c>
       <c r="K317" s="0" t="n">
         <v>2</v>
@@ -17405,7 +17405,7 @@
         <v>1.051</v>
       </c>
       <c r="D318" s="0" t="n">
-        <v>173.6620852819808</v>
+        <v>401.765283</v>
       </c>
       <c r="E318" s="0" t="inlineStr">
         <is>
@@ -17427,7 +17427,7 @@
         <v>0.08</v>
       </c>
       <c r="J318" s="0" t="n">
-        <v>2</v>
+        <v>4</v>
       </c>
       <c r="K318" s="0" t="n">
         <v>1</v>
@@ -17456,7 +17456,7 @@
         <v>1.10355</v>
       </c>
       <c r="D319" s="0" t="n">
-        <v>72.17414030261348</v>
+        <v>166.974063</v>
       </c>
       <c r="E319" s="0" t="inlineStr">
         <is>
@@ -17478,7 +17478,7 @@
         <v>0</v>
       </c>
       <c r="J319" s="0" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="K319" s="0" t="n">
         <v>1</v>
@@ -17507,7 +17507,7 @@
         <v>0.8408</v>
       </c>
       <c r="D320" s="0" t="n">
-        <v>207.6394497936726</v>
+        <v>480.371534</v>
       </c>
       <c r="E320" s="0" t="inlineStr">
         <is>
@@ -17529,7 +17529,7 @@
         <v>0.15</v>
       </c>
       <c r="J320" s="0" t="n">
-        <v>3</v>
+        <v>6</v>
       </c>
       <c r="K320" s="0" t="n">
         <v>2</v>
@@ -17558,7 +17558,7 @@
         <v>0.8408</v>
       </c>
       <c r="D321" s="0" t="n">
-        <v>207.6394497936726</v>
+        <v>480.371534</v>
       </c>
       <c r="E321" s="0" t="inlineStr">
         <is>
@@ -17580,7 +17580,7 @@
         <v>0.15</v>
       </c>
       <c r="J321" s="0" t="n">
-        <v>3</v>
+        <v>6</v>
       </c>
       <c r="K321" s="0" t="n">
         <v>2</v>
@@ -17609,7 +17609,7 @@
         <v>1.6816</v>
       </c>
       <c r="D322" s="0" t="n">
-        <v>94.38156808803301</v>
+        <v>218.350697</v>
       </c>
       <c r="E322" s="0" t="inlineStr">
         <is>
@@ -17631,7 +17631,7 @@
         <v>0</v>
       </c>
       <c r="J322" s="0" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="K322" s="0" t="n">
         <v>1</v>
@@ -17660,7 +17660,7 @@
         <v>1.051</v>
       </c>
       <c r="D323" s="0" t="n">
-        <v>173.6620852819808</v>
+        <v>401.765283</v>
       </c>
       <c r="E323" s="0" t="inlineStr">
         <is>
@@ -17682,7 +17682,7 @@
         <v>0.08</v>
       </c>
       <c r="J323" s="0" t="n">
-        <v>2</v>
+        <v>4</v>
       </c>
       <c r="K323" s="0" t="n">
         <v>1</v>
@@ -17711,7 +17711,7 @@
         <v>1.051</v>
       </c>
       <c r="D324" s="0" t="n">
-        <v>173.6620852819808</v>
+        <v>401.765283</v>
       </c>
       <c r="E324" s="0" t="inlineStr">
         <is>
@@ -17733,7 +17733,7 @@
         <v>0.08</v>
       </c>
       <c r="J324" s="0" t="n">
-        <v>2</v>
+        <v>4</v>
       </c>
       <c r="K324" s="0" t="n">
         <v>1</v>
@@ -17762,7 +17762,7 @@
         <v>0.8408</v>
       </c>
       <c r="D325" s="0" t="n">
-        <v>207.6394497936726</v>
+        <v>480.371534</v>
       </c>
       <c r="E325" s="0" t="inlineStr">
         <is>
@@ -17784,7 +17784,7 @@
         <v>0.15</v>
       </c>
       <c r="J325" s="0" t="n">
-        <v>3</v>
+        <v>6</v>
       </c>
       <c r="K325" s="0" t="n">
         <v>2</v>
@@ -17813,7 +17813,7 @@
         <v>1.0525</v>
       </c>
       <c r="D326" s="0" t="n">
-        <v>51.5205298013245</v>
+        <v>158.922889</v>
       </c>
       <c r="E326" s="0" t="inlineStr">
         <is>
@@ -17835,7 +17835,7 @@
         <v>0</v>
       </c>
       <c r="J326" s="0" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="K326" s="0" t="n">
         <v>1</v>
@@ -17864,7 +17864,7 @@
         <v>1.0525</v>
       </c>
       <c r="D327" s="0" t="n">
-        <v>51.5205298013245</v>
+        <v>158.922889</v>
       </c>
       <c r="E327" s="0" t="inlineStr">
         <is>
@@ -17886,7 +17886,7 @@
         <v>0</v>
       </c>
       <c r="J327" s="0" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="K327" s="0" t="n">
         <v>1</v>
@@ -17915,7 +17915,7 @@
         <v>1.0525</v>
       </c>
       <c r="D328" s="0" t="n">
-        <v>51.5205298013245</v>
+        <v>158.922889</v>
       </c>
       <c r="E328" s="0" t="inlineStr">
         <is>
@@ -17937,7 +17937,7 @@
         <v>0</v>
       </c>
       <c r="J328" s="0" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="K328" s="0" t="n">
         <v>1</v>
@@ -17966,7 +17966,7 @@
         <v>1.15775</v>
       </c>
       <c r="D329" s="0" t="n">
-        <v>114.4900662251656</v>
+        <v>264.871482</v>
       </c>
       <c r="E329" s="0" t="inlineStr">
         <is>
@@ -17988,7 +17988,7 @@
         <v>0</v>
       </c>
       <c r="J329" s="0" t="n">
-        <v>2</v>
+        <v>4</v>
       </c>
       <c r="K329" s="0" t="n">
         <v>1</v>
@@ -18017,7 +18017,7 @@
         <v>1.15775</v>
       </c>
       <c r="D330" s="0" t="n">
-        <v>114.4900662251656</v>
+        <v>264.871482</v>
       </c>
       <c r="E330" s="0" t="inlineStr">
         <is>
@@ -18039,7 +18039,7 @@
         <v>0</v>
       </c>
       <c r="J330" s="0" t="n">
-        <v>2</v>
+        <v>4</v>
       </c>
       <c r="K330" s="0" t="n">
         <v>1</v>
@@ -18068,7 +18068,7 @@
         <v>1.684</v>
       </c>
       <c r="D331" s="0" t="n">
-        <v>97.31655629139073</v>
+        <v>225.140759</v>
       </c>
       <c r="E331" s="0" t="inlineStr">
         <is>
@@ -18090,7 +18090,7 @@
         <v>0</v>
       </c>
       <c r="J331" s="0" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="K331" s="0" t="n">
         <v>1</v>
@@ -18119,7 +18119,7 @@
         <v>0.8420000000000001</v>
       </c>
       <c r="D332" s="0" t="n">
-        <v>214.0964238410596</v>
+        <v>495.309671</v>
       </c>
       <c r="E332" s="0" t="inlineStr">
         <is>
@@ -18141,7 +18141,7 @@
         <v>0.15</v>
       </c>
       <c r="J332" s="0" t="n">
-        <v>3</v>
+        <v>6</v>
       </c>
       <c r="K332" s="0" t="n">
         <v>2</v>
@@ -18170,7 +18170,7 @@
         <v>1.684</v>
       </c>
       <c r="D333" s="0" t="n">
-        <v>97.31655629139073</v>
+        <v>225.140759</v>
       </c>
       <c r="E333" s="0" t="inlineStr">
         <is>
@@ -18192,7 +18192,7 @@
         <v>0</v>
       </c>
       <c r="J333" s="0" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="K333" s="0" t="n">
         <v>1</v>
@@ -18221,7 +18221,7 @@
         <v>1.684</v>
       </c>
       <c r="D334" s="0" t="n">
-        <v>97.31655629139073</v>
+        <v>225.140759</v>
       </c>
       <c r="E334" s="0" t="inlineStr">
         <is>
@@ -18243,7 +18243,7 @@
         <v>0</v>
       </c>
       <c r="J334" s="0" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="K334" s="0" t="n">
         <v>1</v>
@@ -18272,7 +18272,7 @@
         <v>0.8420000000000001</v>
       </c>
       <c r="D335" s="0" t="n">
-        <v>214.0964238410596</v>
+        <v>495.309671</v>
       </c>
       <c r="E335" s="0" t="inlineStr">
         <is>
@@ -18294,7 +18294,7 @@
         <v>0.15</v>
       </c>
       <c r="J335" s="0" t="n">
-        <v>3</v>
+        <v>6</v>
       </c>
       <c r="K335" s="0" t="n">
         <v>2</v>
@@ -18323,7 +18323,7 @@
         <v>0.8420000000000001</v>
       </c>
       <c r="D336" s="0" t="n">
-        <v>214.0964238410596</v>
+        <v>495.309671</v>
       </c>
       <c r="E336" s="0" t="inlineStr">
         <is>
@@ -18345,7 +18345,7 @@
         <v>0.15</v>
       </c>
       <c r="J336" s="0" t="n">
-        <v>3</v>
+        <v>6</v>
       </c>
       <c r="K336" s="0" t="n">
         <v>2</v>
@@ -18374,7 +18374,7 @@
         <v>0.8420000000000001</v>
       </c>
       <c r="D337" s="0" t="n">
-        <v>214.0964238410596</v>
+        <v>495.309671</v>
       </c>
       <c r="E337" s="0" t="inlineStr">
         <is>
@@ -18396,7 +18396,7 @@
         <v>0.15</v>
       </c>
       <c r="J337" s="0" t="n">
-        <v>3</v>
+        <v>6</v>
       </c>
       <c r="K337" s="0" t="n">
         <v>2</v>
@@ -18425,7 +18425,7 @@
         <v>1.0525</v>
       </c>
       <c r="D338" s="0" t="n">
-        <v>179.0624635761589</v>
+        <v>414.258997</v>
       </c>
       <c r="E338" s="0" t="inlineStr">
         <is>
@@ -18447,7 +18447,7 @@
         <v>0.08</v>
       </c>
       <c r="J338" s="0" t="n">
-        <v>2</v>
+        <v>4</v>
       </c>
       <c r="K338" s="0" t="n">
         <v>1</v>
@@ -18476,7 +18476,7 @@
         <v>1.105125</v>
       </c>
       <c r="D339" s="0" t="n">
-        <v>74.41854304635761</v>
+        <v>172.166463</v>
       </c>
       <c r="E339" s="0" t="inlineStr">
         <is>
@@ -18498,7 +18498,7 @@
         <v>0</v>
       </c>
       <c r="J339" s="0" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="K339" s="0" t="n">
         <v>1</v>
@@ -18527,7 +18527,7 @@
         <v>0.8420000000000001</v>
       </c>
       <c r="D340" s="0" t="n">
-        <v>214.0964238410596</v>
+        <v>495.309671</v>
       </c>
       <c r="E340" s="0" t="inlineStr">
         <is>
@@ -18549,7 +18549,7 @@
         <v>0.15</v>
       </c>
       <c r="J340" s="0" t="n">
-        <v>3</v>
+        <v>6</v>
       </c>
       <c r="K340" s="0" t="n">
         <v>2</v>
@@ -18578,7 +18578,7 @@
         <v>0.8420000000000001</v>
       </c>
       <c r="D341" s="0" t="n">
-        <v>214.0964238410596</v>
+        <v>495.309671</v>
       </c>
       <c r="E341" s="0" t="inlineStr">
         <is>
@@ -18600,7 +18600,7 @@
         <v>0.15</v>
       </c>
       <c r="J341" s="0" t="n">
-        <v>3</v>
+        <v>6</v>
       </c>
       <c r="K341" s="0" t="n">
         <v>2</v>
@@ -18629,7 +18629,7 @@
         <v>1.684</v>
       </c>
       <c r="D342" s="0" t="n">
-        <v>97.31655629139073</v>
+        <v>225.140759</v>
       </c>
       <c r="E342" s="0" t="inlineStr">
         <is>
@@ -18651,7 +18651,7 @@
         <v>0</v>
       </c>
       <c r="J342" s="0" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="K342" s="0" t="n">
         <v>1</v>
@@ -18680,7 +18680,7 @@
         <v>1.0525</v>
       </c>
       <c r="D343" s="0" t="n">
-        <v>179.0624635761589</v>
+        <v>414.258997</v>
       </c>
       <c r="E343" s="0" t="inlineStr">
         <is>
@@ -18702,7 +18702,7 @@
         <v>0.08</v>
       </c>
       <c r="J343" s="0" t="n">
-        <v>2</v>
+        <v>4</v>
       </c>
       <c r="K343" s="0" t="n">
         <v>1</v>
@@ -18731,7 +18731,7 @@
         <v>1.0525</v>
       </c>
       <c r="D344" s="0" t="n">
-        <v>179.0624635761589</v>
+        <v>414.258997</v>
       </c>
       <c r="E344" s="0" t="inlineStr">
         <is>
@@ -18753,7 +18753,7 @@
         <v>0.08</v>
       </c>
       <c r="J344" s="0" t="n">
-        <v>2</v>
+        <v>4</v>
       </c>
       <c r="K344" s="0" t="n">
         <v>1</v>
@@ -18782,7 +18782,7 @@
         <v>0.8420000000000001</v>
       </c>
       <c r="D345" s="0" t="n">
-        <v>214.0964238410596</v>
+        <v>495.309671</v>
       </c>
       <c r="E345" s="0" t="inlineStr">
         <is>
@@ -18804,7 +18804,7 @@
         <v>0.15</v>
       </c>
       <c r="J345" s="0" t="n">
-        <v>3</v>
+        <v>6</v>
       </c>
       <c r="K345" s="0" t="n">
         <v>2</v>
@@ -18833,7 +18833,7 @@
         <v>1.054</v>
       </c>
       <c r="D346" s="0" t="n">
-        <v>97.73564954682779</v>
+        <v>301.480436</v>
       </c>
       <c r="E346" s="0" t="inlineStr">
         <is>
@@ -18855,7 +18855,7 @@
         <v>0</v>
       </c>
       <c r="J346" s="0" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="K346" s="0" t="n">
         <v>1</v>
@@ -18884,7 +18884,7 @@
         <v>1.054</v>
       </c>
       <c r="D347" s="0" t="n">
-        <v>97.73564954682779</v>
+        <v>301.480436</v>
       </c>
       <c r="E347" s="0" t="inlineStr">
         <is>
@@ -18906,7 +18906,7 @@
         <v>0</v>
       </c>
       <c r="J347" s="0" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="K347" s="0" t="n">
         <v>1</v>
@@ -18935,7 +18935,7 @@
         <v>1.054</v>
       </c>
       <c r="D348" s="0" t="n">
-        <v>97.73564954682779</v>
+        <v>301.480436</v>
       </c>
       <c r="E348" s="0" t="inlineStr">
         <is>
@@ -18957,7 +18957,7 @@
         <v>0</v>
       </c>
       <c r="J348" s="0" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="K348" s="0" t="n">
         <v>1</v>
@@ -18986,7 +18986,7 @@
         <v>1.1594</v>
       </c>
       <c r="D349" s="0" t="n">
-        <v>217.190332326284</v>
+        <v>502.467393</v>
       </c>
       <c r="E349" s="0" t="inlineStr">
         <is>
@@ -19008,7 +19008,7 @@
         <v>0</v>
       </c>
       <c r="J349" s="0" t="n">
-        <v>2</v>
+        <v>4</v>
       </c>
       <c r="K349" s="0" t="n">
         <v>1</v>
@@ -19037,7 +19037,7 @@
         <v>1.1594</v>
       </c>
       <c r="D350" s="0" t="n">
-        <v>217.190332326284</v>
+        <v>502.467393</v>
       </c>
       <c r="E350" s="0" t="inlineStr">
         <is>
@@ -19059,7 +19059,7 @@
         <v>0</v>
       </c>
       <c r="J350" s="0" t="n">
-        <v>2</v>
+        <v>4</v>
       </c>
       <c r="K350" s="0" t="n">
         <v>1</v>
@@ -19088,7 +19088,7 @@
         <v>1.6864</v>
       </c>
       <c r="D351" s="0" t="n">
-        <v>184.6117824773414</v>
+        <v>427.097284</v>
       </c>
       <c r="E351" s="0" t="inlineStr">
         <is>
@@ -19110,7 +19110,7 @@
         <v>0</v>
       </c>
       <c r="J351" s="0" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="K351" s="0" t="n">
         <v>1</v>
@@ -19139,7 +19139,7 @@
         <v>0.8432000000000001</v>
       </c>
       <c r="D352" s="0" t="n">
-        <v>406.1459214501511</v>
+        <v>939.614025</v>
       </c>
       <c r="E352" s="0" t="inlineStr">
         <is>
@@ -19161,7 +19161,7 @@
         <v>0.15</v>
       </c>
       <c r="J352" s="0" t="n">
-        <v>3</v>
+        <v>6</v>
       </c>
       <c r="K352" s="0" t="n">
         <v>2</v>
@@ -19190,7 +19190,7 @@
         <v>0.8432000000000001</v>
       </c>
       <c r="D353" s="0" t="n">
-        <v>406.1459214501511</v>
+        <v>939.614025</v>
       </c>
       <c r="E353" s="0" t="inlineStr">
         <is>
@@ -19212,7 +19212,7 @@
         <v>0.15</v>
       </c>
       <c r="J353" s="0" t="n">
-        <v>3</v>
+        <v>6</v>
       </c>
       <c r="K353" s="0" t="n">
         <v>2</v>
@@ -19241,7 +19241,7 @@
         <v>1.6864</v>
       </c>
       <c r="D354" s="0" t="n">
-        <v>184.6117824773414</v>
+        <v>427.097284</v>
       </c>
       <c r="E354" s="0" t="inlineStr">
         <is>
@@ -19263,7 +19263,7 @@
         <v>0</v>
       </c>
       <c r="J354" s="0" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="K354" s="0" t="n">
         <v>1</v>
@@ -19292,7 +19292,7 @@
         <v>1.6864</v>
       </c>
       <c r="D355" s="0" t="n">
-        <v>184.6117824773414</v>
+        <v>427.097284</v>
       </c>
       <c r="E355" s="0" t="inlineStr">
         <is>
@@ -19314,7 +19314,7 @@
         <v>0</v>
       </c>
       <c r="J355" s="0" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="K355" s="0" t="n">
         <v>1</v>
@@ -19343,7 +19343,7 @@
         <v>0.8432000000000001</v>
       </c>
       <c r="D356" s="0" t="n">
-        <v>406.1459214501511</v>
+        <v>939.614025</v>
       </c>
       <c r="E356" s="0" t="inlineStr">
         <is>
@@ -19365,7 +19365,7 @@
         <v>0.15</v>
       </c>
       <c r="J356" s="0" t="n">
-        <v>3</v>
+        <v>6</v>
       </c>
       <c r="K356" s="0" t="n">
         <v>2</v>
@@ -19394,7 +19394,7 @@
         <v>0.8432000000000001</v>
       </c>
       <c r="D357" s="0" t="n">
-        <v>406.1459214501511</v>
+        <v>939.614025</v>
       </c>
       <c r="E357" s="0" t="inlineStr">
         <is>
@@ -19416,7 +19416,7 @@
         <v>0.15</v>
       </c>
       <c r="J357" s="0" t="n">
-        <v>3</v>
+        <v>6</v>
       </c>
       <c r="K357" s="0" t="n">
         <v>2</v>
@@ -19445,7 +19445,7 @@
         <v>0.8432000000000001</v>
       </c>
       <c r="D358" s="0" t="n">
-        <v>406.1459214501511</v>
+        <v>939.614025</v>
       </c>
       <c r="E358" s="0" t="inlineStr">
         <is>
@@ -19467,7 +19467,7 @@
         <v>0.15</v>
       </c>
       <c r="J358" s="0" t="n">
-        <v>3</v>
+        <v>6</v>
       </c>
       <c r="K358" s="0" t="n">
         <v>2</v>
@@ -19496,7 +19496,7 @@
         <v>1.054</v>
       </c>
       <c r="D359" s="0" t="n">
-        <v>339.6856797583082</v>
+        <v>785.859003</v>
       </c>
       <c r="E359" s="0" t="inlineStr">
         <is>
@@ -19518,7 +19518,7 @@
         <v>0.08</v>
       </c>
       <c r="J359" s="0" t="n">
-        <v>2</v>
+        <v>4</v>
       </c>
       <c r="K359" s="0" t="n">
         <v>1</v>
@@ -19547,7 +19547,7 @@
         <v>1.1067</v>
       </c>
       <c r="D360" s="0" t="n">
-        <v>141.1737160120846</v>
+        <v>326.603806</v>
       </c>
       <c r="E360" s="0" t="inlineStr">
         <is>
@@ -19569,7 +19569,7 @@
         <v>0</v>
       </c>
       <c r="J360" s="0" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="K360" s="0" t="n">
         <v>1</v>
@@ -19598,7 +19598,7 @@
         <v>0.8432000000000001</v>
       </c>
       <c r="D361" s="0" t="n">
-        <v>406.1459214501511</v>
+        <v>939.614025</v>
       </c>
       <c r="E361" s="0" t="inlineStr">
         <is>
@@ -19620,7 +19620,7 @@
         <v>0.15</v>
       </c>
       <c r="J361" s="0" t="n">
-        <v>3</v>
+        <v>6</v>
       </c>
       <c r="K361" s="0" t="n">
         <v>2</v>
@@ -19649,7 +19649,7 @@
         <v>0.8432000000000001</v>
       </c>
       <c r="D362" s="0" t="n">
-        <v>406.1459214501511</v>
+        <v>939.614025</v>
       </c>
       <c r="E362" s="0" t="inlineStr">
         <is>
@@ -19671,7 +19671,7 @@
         <v>0.15</v>
       </c>
       <c r="J362" s="0" t="n">
-        <v>3</v>
+        <v>6</v>
       </c>
       <c r="K362" s="0" t="n">
         <v>2</v>
@@ -19700,7 +19700,7 @@
         <v>1.6864</v>
       </c>
       <c r="D363" s="0" t="n">
-        <v>184.6117824773414</v>
+        <v>427.097284</v>
       </c>
       <c r="E363" s="0" t="inlineStr">
         <is>
@@ -19722,7 +19722,7 @@
         <v>0</v>
       </c>
       <c r="J363" s="0" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="K363" s="0" t="n">
         <v>1</v>
@@ -19751,7 +19751,7 @@
         <v>1.054</v>
       </c>
       <c r="D364" s="0" t="n">
-        <v>339.6856797583082</v>
+        <v>785.859003</v>
       </c>
       <c r="E364" s="0" t="inlineStr">
         <is>
@@ -19773,7 +19773,7 @@
         <v>0.08</v>
       </c>
       <c r="J364" s="0" t="n">
-        <v>2</v>
+        <v>4</v>
       </c>
       <c r="K364" s="0" t="n">
         <v>1</v>
@@ -19802,7 +19802,7 @@
         <v>1.054</v>
       </c>
       <c r="D365" s="0" t="n">
-        <v>339.6856797583082</v>
+        <v>785.859003</v>
       </c>
       <c r="E365" s="0" t="inlineStr">
         <is>
@@ -19824,7 +19824,7 @@
         <v>0.08</v>
       </c>
       <c r="J365" s="0" t="n">
-        <v>2</v>
+        <v>4</v>
       </c>
       <c r="K365" s="0" t="n">
         <v>1</v>
@@ -19853,7 +19853,7 @@
         <v>0.6851</v>
       </c>
       <c r="D366" s="0" t="n">
-        <v>814.463746223565</v>
+        <v>1884.252725</v>
       </c>
       <c r="E366" s="0" t="inlineStr">
         <is>
@@ -19875,7 +19875,7 @@
         <v>0.25</v>
       </c>
       <c r="J366" s="0" t="n">
-        <v>14</v>
+        <v>26</v>
       </c>
       <c r="K366" s="0" t="n">
         <v>4</v>
@@ -19904,7 +19904,7 @@
         <v>0.8264</v>
       </c>
       <c r="D367" s="0" t="n">
-        <v>57.6336439888164</v>
+        <v>133.334788</v>
       </c>
       <c r="E367" s="0" t="inlineStr">
         <is>
@@ -19926,7 +19926,7 @@
         <v>0.15</v>
       </c>
       <c r="J367" s="0" t="n">
-        <v>3</v>
+        <v>6</v>
       </c>
       <c r="K367" s="0" t="n">
         <v>2</v>
@@ -19955,7 +19955,7 @@
         <v>0.8276</v>
       </c>
       <c r="D368" s="0" t="n">
-        <v>56.84733570159858</v>
+        <v>131.515672</v>
       </c>
       <c r="E368" s="0" t="inlineStr">
         <is>
@@ -19977,7 +19977,7 @@
         <v>0.15</v>
       </c>
       <c r="J368" s="0" t="n">
-        <v>3</v>
+        <v>6</v>
       </c>
       <c r="K368" s="0" t="n">
         <v>2</v>
@@ -20006,7 +20006,7 @@
         <v>0.8288000000000001</v>
       </c>
       <c r="D369" s="0" t="n">
-        <v>65.48528301886793</v>
+        <v>151.499466</v>
       </c>
       <c r="E369" s="0" t="inlineStr">
         <is>
@@ -20028,7 +20028,7 @@
         <v>0.15</v>
       </c>
       <c r="J369" s="0" t="n">
-        <v>3</v>
+        <v>6</v>
       </c>
       <c r="K369" s="0" t="n">
         <v>2</v>
@@ -20057,7 +20057,7 @@
         <v>0.8288000000000001</v>
       </c>
       <c r="D370" s="0" t="n">
-        <v>65.48528301886793</v>
+        <v>151.499466</v>
       </c>
       <c r="E370" s="0" t="inlineStr">
         <is>
@@ -20079,7 +20079,7 @@
         <v>0.15</v>
       </c>
       <c r="J370" s="0" t="n">
-        <v>3</v>
+        <v>6</v>
       </c>
       <c r="K370" s="0" t="n">
         <v>2</v>
@@ -20108,7 +20108,7 @@
         <v>0.8300000000000001</v>
       </c>
       <c r="D371" s="0" t="n">
-        <v>74.72585249801745</v>
+        <v>172.87742</v>
       </c>
       <c r="E371" s="0" t="inlineStr">
         <is>
@@ -20130,7 +20130,7 @@
         <v>0.15</v>
       </c>
       <c r="J371" s="0" t="n">
-        <v>3</v>
+        <v>6</v>
       </c>
       <c r="K371" s="0" t="n">
         <v>2</v>
@@ -20159,7 +20159,7 @@
         <v>0.8300000000000001</v>
       </c>
       <c r="D372" s="0" t="n">
-        <v>74.72585249801745</v>
+        <v>172.87742</v>
       </c>
       <c r="E372" s="0" t="inlineStr">
         <is>
@@ -20181,7 +20181,7 @@
         <v>0.15</v>
       </c>
       <c r="J372" s="0" t="n">
-        <v>3</v>
+        <v>6</v>
       </c>
       <c r="K372" s="0" t="n">
         <v>2</v>
@@ -20210,7 +20210,7 @@
         <v>0.8311999999999999</v>
       </c>
       <c r="D373" s="0" t="n">
-        <v>121.1539594843462</v>
+        <v>280.288324</v>
       </c>
       <c r="E373" s="0" t="inlineStr">
         <is>
@@ -20232,7 +20232,7 @@
         <v>0.15</v>
       </c>
       <c r="J373" s="0" t="n">
-        <v>3</v>
+        <v>6</v>
       </c>
       <c r="K373" s="0" t="n">
         <v>2</v>
@@ -20261,7 +20261,7 @@
         <v>0.8311999999999999</v>
       </c>
       <c r="D374" s="0" t="n">
-        <v>121.1539594843462</v>
+        <v>280.288324</v>
       </c>
       <c r="E374" s="0" t="inlineStr">
         <is>
@@ -20283,7 +20283,7 @@
         <v>0.15</v>
       </c>
       <c r="J374" s="0" t="n">
-        <v>3</v>
+        <v>6</v>
       </c>
       <c r="K374" s="0" t="n">
         <v>2</v>
@@ -20312,7 +20312,7 @@
         <v>0.8324</v>
       </c>
       <c r="D375" s="0" t="n">
-        <v>121.65170413343</v>
+        <v>281.43985</v>
       </c>
       <c r="E375" s="0" t="inlineStr">
         <is>
@@ -20334,7 +20334,7 @@
         <v>0.15</v>
       </c>
       <c r="J375" s="0" t="n">
-        <v>3</v>
+        <v>6</v>
       </c>
       <c r="K375" s="0" t="n">
         <v>2</v>
@@ -20363,7 +20363,7 @@
         <v>0.8324</v>
       </c>
       <c r="D376" s="0" t="n">
-        <v>121.65170413343</v>
+        <v>281.43985</v>
       </c>
       <c r="E376" s="0" t="inlineStr">
         <is>
@@ -20385,7 +20385,7 @@
         <v>0.15</v>
       </c>
       <c r="J376" s="0" t="n">
-        <v>3</v>
+        <v>6</v>
       </c>
       <c r="K376" s="0" t="n">
         <v>2</v>
@@ -20414,7 +20414,7 @@
         <v>0.8336000000000001</v>
       </c>
       <c r="D377" s="0" t="n">
-        <v>119.2084291187739</v>
+        <v>275.787361</v>
       </c>
       <c r="E377" s="0" t="inlineStr">
         <is>
@@ -20436,7 +20436,7 @@
         <v>0.15</v>
       </c>
       <c r="J377" s="0" t="n">
-        <v>3</v>
+        <v>6</v>
       </c>
       <c r="K377" s="0" t="n">
         <v>2</v>
@@ -20465,7 +20465,7 @@
         <v>0.8336000000000001</v>
       </c>
       <c r="D378" s="0" t="n">
-        <v>119.2084291187739</v>
+        <v>275.787361</v>
       </c>
       <c r="E378" s="0" t="inlineStr">
         <is>
@@ -20487,7 +20487,7 @@
         <v>0.15</v>
       </c>
       <c r="J378" s="0" t="n">
-        <v>3</v>
+        <v>6</v>
       </c>
       <c r="K378" s="0" t="n">
         <v>2</v>
@@ -20516,7 +20516,7 @@
         <v>0.8348000000000001</v>
       </c>
       <c r="D379" s="0" t="n">
-        <v>121.4134130146083</v>
+        <v>280.888567</v>
       </c>
       <c r="E379" s="0" t="inlineStr">
         <is>
@@ -20538,7 +20538,7 @@
         <v>0.15</v>
       </c>
       <c r="J379" s="0" t="n">
-        <v>3</v>
+        <v>6</v>
       </c>
       <c r="K379" s="0" t="n">
         <v>2</v>
@@ -20567,7 +20567,7 @@
         <v>0.8348000000000001</v>
       </c>
       <c r="D380" s="0" t="n">
-        <v>121.4134130146083</v>
+        <v>280.888567</v>
       </c>
       <c r="E380" s="0" t="inlineStr">
         <is>
@@ -20589,7 +20589,7 @@
         <v>0.15</v>
       </c>
       <c r="J380" s="0" t="n">
-        <v>3</v>
+        <v>6</v>
       </c>
       <c r="K380" s="0" t="n">
         <v>2</v>
@@ -20618,7 +20618,7 @@
         <v>0.836</v>
       </c>
       <c r="D381" s="0" t="n">
-        <v>134.8042647994908</v>
+        <v>311.868152</v>
       </c>
       <c r="E381" s="0" t="inlineStr">
         <is>
@@ -20640,7 +20640,7 @@
         <v>0.15</v>
       </c>
       <c r="J381" s="0" t="n">
-        <v>3</v>
+        <v>6</v>
       </c>
       <c r="K381" s="0" t="n">
         <v>2</v>
@@ -20669,7 +20669,7 @@
         <v>0.836</v>
       </c>
       <c r="D382" s="0" t="n">
-        <v>134.8042647994908</v>
+        <v>311.868152</v>
       </c>
       <c r="E382" s="0" t="inlineStr">
         <is>
@@ -20691,7 +20691,7 @@
         <v>0.15</v>
       </c>
       <c r="J382" s="0" t="n">
-        <v>3</v>
+        <v>6</v>
       </c>
       <c r="K382" s="0" t="n">
         <v>2</v>
@@ -20720,7 +20720,7 @@
         <v>0.8372000000000001</v>
       </c>
       <c r="D383" s="0" t="n">
-        <v>213.3168566286743</v>
+        <v>493.506151</v>
       </c>
       <c r="E383" s="0" t="inlineStr">
         <is>
@@ -20742,7 +20742,7 @@
         <v>0.15</v>
       </c>
       <c r="J383" s="0" t="n">
-        <v>3</v>
+        <v>6</v>
       </c>
       <c r="K383" s="0" t="n">
         <v>2</v>
@@ -20771,7 +20771,7 @@
         <v>0.8372000000000001</v>
       </c>
       <c r="D384" s="0" t="n">
-        <v>213.3168566286743</v>
+        <v>493.506151</v>
       </c>
       <c r="E384" s="0" t="inlineStr">
         <is>
@@ -20793,7 +20793,7 @@
         <v>0.15</v>
       </c>
       <c r="J384" s="0" t="n">
-        <v>3</v>
+        <v>6</v>
       </c>
       <c r="K384" s="0" t="n">
         <v>2</v>
@@ -20822,7 +20822,7 @@
         <v>0.8384</v>
       </c>
       <c r="D385" s="0" t="n">
-        <v>214.1227272727273</v>
+        <v>495.370523</v>
       </c>
       <c r="E385" s="0" t="inlineStr">
         <is>
@@ -20844,7 +20844,7 @@
         <v>0.15</v>
       </c>
       <c r="J385" s="0" t="n">
-        <v>3</v>
+        <v>6</v>
       </c>
       <c r="K385" s="0" t="n">
         <v>2</v>
@@ -20873,7 +20873,7 @@
         <v>0.8396000000000001</v>
       </c>
       <c r="D386" s="0" t="n">
-        <v>211.1152639087018</v>
+        <v>488.412791</v>
       </c>
       <c r="E386" s="0" t="inlineStr">
         <is>
@@ -20895,7 +20895,7 @@
         <v>0.15</v>
       </c>
       <c r="J386" s="0" t="n">
-        <v>3</v>
+        <v>6</v>
       </c>
       <c r="K386" s="0" t="n">
         <v>2</v>
@@ -20924,7 +20924,7 @@
         <v>0.8408</v>
       </c>
       <c r="D387" s="0" t="n">
-        <v>207.6394497936726</v>
+        <v>480.371534</v>
       </c>
       <c r="E387" s="0" t="inlineStr">
         <is>
@@ -20946,7 +20946,7 @@
         <v>0.15</v>
       </c>
       <c r="J387" s="0" t="n">
-        <v>3</v>
+        <v>6</v>
       </c>
       <c r="K387" s="0" t="n">
         <v>2</v>
@@ -20975,7 +20975,7 @@
         <v>0.8420000000000001</v>
       </c>
       <c r="D388" s="0" t="n">
-        <v>214.0964238410596</v>
+        <v>495.309671</v>
       </c>
       <c r="E388" s="0" t="inlineStr">
         <is>
@@ -20997,7 +20997,7 @@
         <v>0.15</v>
       </c>
       <c r="J388" s="0" t="n">
-        <v>3</v>
+        <v>6</v>
       </c>
       <c r="K388" s="0" t="n">
         <v>2</v>
@@ -21026,7 +21026,7 @@
         <v>0.8432000000000001</v>
       </c>
       <c r="D389" s="0" t="n">
-        <v>406.1459214501511</v>
+        <v>939.614025</v>
       </c>
       <c r="E389" s="0" t="inlineStr">
         <is>
@@ -21048,7 +21048,7 @@
         <v>0.15</v>
       </c>
       <c r="J389" s="0" t="n">
-        <v>3</v>
+        <v>6</v>
       </c>
       <c r="K389" s="0" t="n">
         <v>2</v>
@@ -21077,7 +21077,7 @@
         <v>0.8264</v>
       </c>
       <c r="D390" s="0" t="n">
-        <v>57.6336439888164</v>
+        <v>133.334788</v>
       </c>
       <c r="E390" s="0" t="inlineStr">
         <is>
@@ -21099,7 +21099,7 @@
         <v>0.15</v>
       </c>
       <c r="J390" s="0" t="n">
-        <v>3</v>
+        <v>6</v>
       </c>
       <c r="K390" s="0" t="n">
         <v>2</v>
@@ -21128,7 +21128,7 @@
         <v>0.8264</v>
       </c>
       <c r="D391" s="0" t="n">
-        <v>57.6336439888164</v>
+        <v>133.334788</v>
       </c>
       <c r="E391" s="0" t="inlineStr">
         <is>
@@ -21150,7 +21150,7 @@
         <v>0.15</v>
       </c>
       <c r="J391" s="0" t="n">
-        <v>3</v>
+        <v>6</v>
       </c>
       <c r="K391" s="0" t="n">
         <v>2</v>
@@ -21179,7 +21179,7 @@
         <v>0.8276</v>
       </c>
       <c r="D392" s="0" t="n">
-        <v>56.84733570159858</v>
+        <v>131.515672</v>
       </c>
       <c r="E392" s="0" t="inlineStr">
         <is>
@@ -21201,7 +21201,7 @@
         <v>0.15</v>
       </c>
       <c r="J392" s="0" t="n">
-        <v>3</v>
+        <v>6</v>
       </c>
       <c r="K392" s="0" t="n">
         <v>2</v>
@@ -21230,7 +21230,7 @@
         <v>0.8276</v>
       </c>
       <c r="D393" s="0" t="n">
-        <v>56.84733570159858</v>
+        <v>131.515672</v>
       </c>
       <c r="E393" s="0" t="inlineStr">
         <is>
@@ -21252,7 +21252,7 @@
         <v>0.15</v>
       </c>
       <c r="J393" s="0" t="n">
-        <v>3</v>
+        <v>6</v>
       </c>
       <c r="K393" s="0" t="n">
         <v>2</v>
@@ -21281,7 +21281,7 @@
         <v>0.8288000000000001</v>
       </c>
       <c r="D394" s="0" t="n">
-        <v>65.48528301886793</v>
+        <v>151.499466</v>
       </c>
       <c r="E394" s="0" t="inlineStr">
         <is>
@@ -21303,7 +21303,7 @@
         <v>0.15</v>
       </c>
       <c r="J394" s="0" t="n">
-        <v>3</v>
+        <v>6</v>
       </c>
       <c r="K394" s="0" t="n">
         <v>2</v>
@@ -21332,7 +21332,7 @@
         <v>0.8300000000000001</v>
       </c>
       <c r="D395" s="0" t="n">
-        <v>74.72585249801745</v>
+        <v>172.87742</v>
       </c>
       <c r="E395" s="0" t="inlineStr">
         <is>
@@ -21354,7 +21354,7 @@
         <v>0.15</v>
       </c>
       <c r="J395" s="0" t="n">
-        <v>3</v>
+        <v>6</v>
       </c>
       <c r="K395" s="0" t="n">
         <v>2</v>
@@ -21383,7 +21383,7 @@
         <v>0.8311999999999999</v>
       </c>
       <c r="D396" s="0" t="n">
-        <v>121.1539594843462</v>
+        <v>280.288324</v>
       </c>
       <c r="E396" s="0" t="inlineStr">
         <is>
@@ -21405,7 +21405,7 @@
         <v>0.15</v>
       </c>
       <c r="J396" s="0" t="n">
-        <v>3</v>
+        <v>6</v>
       </c>
       <c r="K396" s="0" t="n">
         <v>2</v>
@@ -21434,7 +21434,7 @@
         <v>1.021</v>
       </c>
       <c r="D397" s="0" t="n">
-        <v>3.765254274509803</v>
+        <v>11.614498</v>
       </c>
       <c r="E397" s="0" t="inlineStr">
         <is>
@@ -21456,7 +21456,7 @@
         <v>0</v>
       </c>
       <c r="J397" s="0" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="K397" s="0" t="n">
         <v>1</v>
@@ -21485,7 +21485,7 @@
         <v>1.021</v>
       </c>
       <c r="D398" s="0" t="n">
-        <v>3.765254274509803</v>
+        <v>11.614498</v>
       </c>
       <c r="E398" s="0" t="inlineStr">
         <is>
@@ -21507,7 +21507,7 @@
         <v>0</v>
       </c>
       <c r="J398" s="0" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="K398" s="0" t="n">
         <v>1</v>
@@ -21536,7 +21536,7 @@
         <v>1.021</v>
       </c>
       <c r="D399" s="0" t="n">
-        <v>3.765254274509803</v>
+        <v>11.614498</v>
       </c>
       <c r="E399" s="0" t="inlineStr">
         <is>
@@ -21558,7 +21558,7 @@
         <v>0</v>
       </c>
       <c r="J399" s="0" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="K399" s="0" t="n">
         <v>1</v>
@@ -21587,7 +21587,7 @@
         <v>1.021</v>
       </c>
       <c r="D400" s="0" t="n">
-        <v>3.765254274509803</v>
+        <v>11.614498</v>
       </c>
       <c r="E400" s="0" t="inlineStr">
         <is>
@@ -21609,7 +21609,7 @@
         <v>0</v>
       </c>
       <c r="J400" s="0" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="K400" s="0" t="n">
         <v>1</v>
@@ -21638,7 +21638,7 @@
         <v>1.021</v>
       </c>
       <c r="D401" s="0" t="n">
-        <v>3.765254274509803</v>
+        <v>11.614498</v>
       </c>
       <c r="E401" s="0" t="inlineStr">
         <is>
@@ -21660,7 +21660,7 @@
         <v>0</v>
       </c>
       <c r="J401" s="0" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="K401" s="0" t="n">
         <v>1</v>
@@ -21689,7 +21689,7 @@
         <v>1.0225</v>
       </c>
       <c r="D402" s="0" t="n">
-        <v>4.310909483203125</v>
+        <v>13.297654</v>
       </c>
       <c r="E402" s="0" t="inlineStr">
         <is>
@@ -21711,7 +21711,7 @@
         <v>0</v>
       </c>
       <c r="J402" s="0" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="K402" s="0" t="n">
         <v>1</v>
@@ -21740,7 +21740,7 @@
         <v>1.0225</v>
       </c>
       <c r="D403" s="0" t="n">
-        <v>4.310909483203125</v>
+        <v>13.297654</v>
       </c>
       <c r="E403" s="0" t="inlineStr">
         <is>
@@ -21762,7 +21762,7 @@
         <v>0</v>
       </c>
       <c r="J403" s="0" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="K403" s="0" t="n">
         <v>1</v>
@@ -21791,7 +21791,7 @@
         <v>1.0225</v>
       </c>
       <c r="D404" s="0" t="n">
-        <v>4.310909483203125</v>
+        <v>13.297654</v>
       </c>
       <c r="E404" s="0" t="inlineStr">
         <is>
@@ -21813,7 +21813,7 @@
         <v>0</v>
       </c>
       <c r="J404" s="0" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="K404" s="0" t="n">
         <v>1</v>
@@ -21842,7 +21842,7 @@
         <v>1.0225</v>
       </c>
       <c r="D405" s="0" t="n">
-        <v>4.310909483203125</v>
+        <v>13.297654</v>
       </c>
       <c r="E405" s="0" t="inlineStr">
         <is>
@@ -21864,7 +21864,7 @@
         <v>0</v>
       </c>
       <c r="J405" s="0" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="K405" s="0" t="n">
         <v>1</v>
@@ -21893,7 +21893,7 @@
         <v>1.0225</v>
       </c>
       <c r="D406" s="0" t="n">
-        <v>4.310909483203125</v>
+        <v>13.297654</v>
       </c>
       <c r="E406" s="0" t="inlineStr">
         <is>
@@ -21915,7 +21915,7 @@
         <v>0</v>
       </c>
       <c r="J406" s="0" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="K406" s="0" t="n">
         <v>1</v>
@@ -21944,7 +21944,7 @@
         <v>1.024</v>
       </c>
       <c r="D407" s="0" t="n">
-        <v>6.596355493763032</v>
+        <v>20.347459</v>
       </c>
       <c r="E407" s="0" t="inlineStr">
         <is>
@@ -21966,7 +21966,7 @@
         <v>0</v>
       </c>
       <c r="J407" s="0" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="K407" s="0" t="n">
         <v>1</v>
@@ -21995,7 +21995,7 @@
         <v>1.024</v>
       </c>
       <c r="D408" s="0" t="n">
-        <v>6.596355493763032</v>
+        <v>20.347459</v>
       </c>
       <c r="E408" s="0" t="inlineStr">
         <is>
@@ -22017,7 +22017,7 @@
         <v>0</v>
       </c>
       <c r="J408" s="0" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="K408" s="0" t="n">
         <v>1</v>
@@ -22046,7 +22046,7 @@
         <v>1.024</v>
       </c>
       <c r="D409" s="0" t="n">
-        <v>6.596355493763032</v>
+        <v>20.347459</v>
       </c>
       <c r="E409" s="0" t="inlineStr">
         <is>
@@ -22068,7 +22068,7 @@
         <v>0</v>
       </c>
       <c r="J409" s="0" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="K409" s="0" t="n">
         <v>1</v>
@@ -22097,7 +22097,7 @@
         <v>1.024</v>
       </c>
       <c r="D410" s="0" t="n">
-        <v>6.596355493763032</v>
+        <v>20.347459</v>
       </c>
       <c r="E410" s="0" t="inlineStr">
         <is>
@@ -22119,7 +22119,7 @@
         <v>0</v>
       </c>
       <c r="J410" s="0" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="K410" s="0" t="n">
         <v>1</v>
@@ -22148,7 +22148,7 @@
         <v>1.024</v>
       </c>
       <c r="D411" s="0" t="n">
-        <v>6.596355493763032</v>
+        <v>20.347459</v>
       </c>
       <c r="E411" s="0" t="inlineStr">
         <is>
@@ -22170,7 +22170,7 @@
         <v>0</v>
       </c>
       <c r="J411" s="0" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="K411" s="0" t="n">
         <v>1</v>
@@ -22199,7 +22199,7 @@
         <v>1.0255</v>
       </c>
       <c r="D412" s="0" t="n">
-        <v>6.374719521316381</v>
+        <v>19.663789</v>
       </c>
       <c r="E412" s="0" t="inlineStr">
         <is>
@@ -22221,7 +22221,7 @@
         <v>0</v>
       </c>
       <c r="J412" s="0" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="K412" s="0" t="n">
         <v>1</v>
@@ -22250,7 +22250,7 @@
         <v>1.0255</v>
       </c>
       <c r="D413" s="0" t="n">
-        <v>6.374719521316381</v>
+        <v>19.663789</v>
       </c>
       <c r="E413" s="0" t="inlineStr">
         <is>
@@ -22272,7 +22272,7 @@
         <v>0</v>
       </c>
       <c r="J413" s="0" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="K413" s="0" t="n">
         <v>1</v>
@@ -22301,7 +22301,7 @@
         <v>1.027</v>
       </c>
       <c r="D414" s="0" t="n">
-        <v>6.623108665749656</v>
+        <v>20.429983</v>
       </c>
       <c r="E414" s="0" t="inlineStr">
         <is>
@@ -22323,7 +22323,7 @@
         <v>0</v>
       </c>
       <c r="J414" s="0" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="K414" s="0" t="n">
         <v>1</v>
@@ -22352,7 +22352,7 @@
         <v>1.027</v>
       </c>
       <c r="D415" s="0" t="n">
-        <v>6.623108665749656</v>
+        <v>20.429983</v>
       </c>
       <c r="E415" s="0" t="inlineStr">
         <is>
@@ -22374,7 +22374,7 @@
         <v>0</v>
       </c>
       <c r="J415" s="0" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="K415" s="0" t="n">
         <v>1</v>
@@ -22403,7 +22403,7 @@
         <v>1.0285</v>
       </c>
       <c r="D416" s="0" t="n">
-        <v>7.902999361837908</v>
+        <v>24.378</v>
       </c>
       <c r="E416" s="0" t="inlineStr">
         <is>
@@ -22425,7 +22425,7 @@
         <v>0</v>
       </c>
       <c r="J416" s="0" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="K416" s="0" t="n">
         <v>1</v>
@@ -22454,7 +22454,7 @@
         <v>1.0285</v>
       </c>
       <c r="D417" s="0" t="n">
-        <v>7.902999361837908</v>
+        <v>24.378</v>
       </c>
       <c r="E417" s="0" t="inlineStr">
         <is>
@@ -22476,7 +22476,7 @@
         <v>0</v>
       </c>
       <c r="J417" s="0" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="K417" s="0" t="n">
         <v>1</v>
@@ -22505,7 +22505,7 @@
         <v>1.03</v>
       </c>
       <c r="D418" s="0" t="n">
-        <v>9.434964200477326</v>
+        <v>29.103578</v>
       </c>
       <c r="E418" s="0" t="inlineStr">
         <is>
@@ -22527,7 +22527,7 @@
         <v>0</v>
       </c>
       <c r="J418" s="0" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="K418" s="0" t="n">
         <v>1</v>
@@ -22556,7 +22556,7 @@
         <v>1.03</v>
       </c>
       <c r="D419" s="0" t="n">
-        <v>9.434964200477326</v>
+        <v>29.103578</v>
       </c>
       <c r="E419" s="0" t="inlineStr">
         <is>
@@ -22578,7 +22578,7 @@
         <v>0</v>
       </c>
       <c r="J419" s="0" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="K419" s="0" t="n">
         <v>1</v>
@@ -22607,7 +22607,7 @@
         <v>1.0315</v>
       </c>
       <c r="D420" s="0" t="n">
-        <v>16.37373737373738</v>
+        <v>50.507277</v>
       </c>
       <c r="E420" s="0" t="inlineStr">
         <is>
@@ -22629,7 +22629,7 @@
         <v>0</v>
       </c>
       <c r="J420" s="0" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="K420" s="0" t="n">
         <v>1</v>
@@ -22658,7 +22658,7 @@
         <v>1.0315</v>
       </c>
       <c r="D421" s="0" t="n">
-        <v>16.37373737373738</v>
+        <v>50.507277</v>
       </c>
       <c r="E421" s="0" t="inlineStr">
         <is>
@@ -22680,7 +22680,7 @@
         <v>0</v>
       </c>
       <c r="J421" s="0" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="K421" s="0" t="n">
         <v>1</v>
@@ -22709,7 +22709,7 @@
         <v>1.033</v>
       </c>
       <c r="D422" s="0" t="n">
-        <v>13.8690587138863</v>
+        <v>42.781215</v>
       </c>
       <c r="E422" s="0" t="inlineStr">
         <is>
@@ -22731,7 +22731,7 @@
         <v>0</v>
       </c>
       <c r="J422" s="0" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="K422" s="0" t="n">
         <v>1</v>
@@ -22760,7 +22760,7 @@
         <v>1.033</v>
       </c>
       <c r="D423" s="0" t="n">
-        <v>13.8690587138863</v>
+        <v>42.781215</v>
       </c>
       <c r="E423" s="0" t="inlineStr">
         <is>
@@ -22782,7 +22782,7 @@
         <v>0</v>
       </c>
       <c r="J423" s="0" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="K423" s="0" t="n">
         <v>1</v>
@@ -22811,7 +22811,7 @@
         <v>1.033</v>
       </c>
       <c r="D424" s="0" t="n">
-        <v>13.8690587138863</v>
+        <v>42.781215</v>
       </c>
       <c r="E424" s="0" t="inlineStr">
         <is>
@@ -22833,7 +22833,7 @@
         <v>0</v>
       </c>
       <c r="J424" s="0" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="K424" s="0" t="n">
         <v>1</v>
@@ -22862,7 +22862,7 @@
         <v>1.033</v>
       </c>
       <c r="D425" s="0" t="n">
-        <v>13.8690587138863</v>
+        <v>42.781215</v>
       </c>
       <c r="E425" s="0" t="inlineStr">
         <is>
@@ -22884,7 +22884,7 @@
         <v>0</v>
       </c>
       <c r="J425" s="0" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="K425" s="0" t="n">
         <v>1</v>
@@ -22913,7 +22913,7 @@
         <v>1.033</v>
       </c>
       <c r="D426" s="0" t="n">
-        <v>13.8690587138863</v>
+        <v>42.781215</v>
       </c>
       <c r="E426" s="0" t="inlineStr">
         <is>
@@ -22935,7 +22935,7 @@
         <v>0</v>
       </c>
       <c r="J426" s="0" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="K426" s="0" t="n">
         <v>1</v>
@@ -22964,7 +22964,7 @@
         <v>1.0345</v>
       </c>
       <c r="D427" s="0" t="n">
-        <v>13.67984014209591</v>
+        <v>42.197542</v>
       </c>
       <c r="E427" s="0" t="inlineStr">
         <is>
@@ -22986,7 +22986,7 @@
         <v>0</v>
       </c>
       <c r="J427" s="0" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="K427" s="0" t="n">
         <v>1</v>
@@ -23015,7 +23015,7 @@
         <v>1.0345</v>
       </c>
       <c r="D428" s="0" t="n">
-        <v>13.67984014209591</v>
+        <v>42.197542</v>
       </c>
       <c r="E428" s="0" t="inlineStr">
         <is>
@@ -23037,7 +23037,7 @@
         <v>0</v>
       </c>
       <c r="J428" s="0" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="K428" s="0" t="n">
         <v>1</v>
@@ -23066,7 +23066,7 @@
         <v>1.036</v>
       </c>
       <c r="D429" s="0" t="n">
-        <v>15.75849056603774</v>
+        <v>48.609454</v>
       </c>
       <c r="E429" s="0" t="inlineStr">
         <is>
@@ -23088,7 +23088,7 @@
         <v>0</v>
       </c>
       <c r="J429" s="0" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="K429" s="0" t="n">
         <v>1</v>
@@ -23117,7 +23117,7 @@
         <v>1.036</v>
       </c>
       <c r="D430" s="0" t="n">
-        <v>15.75849056603774</v>
+        <v>48.609454</v>
       </c>
       <c r="E430" s="0" t="inlineStr">
         <is>
@@ -23139,7 +23139,7 @@
         <v>0</v>
       </c>
       <c r="J430" s="0" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="K430" s="0" t="n">
         <v>1</v>
@@ -23168,7 +23168,7 @@
         <v>1.0375</v>
       </c>
       <c r="D431" s="0" t="n">
-        <v>17.98215701823949</v>
+        <v>55.468691</v>
       </c>
       <c r="E431" s="0" t="inlineStr">
         <is>
@@ -23190,7 +23190,7 @@
         <v>0</v>
       </c>
       <c r="J431" s="0" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="K431" s="0" t="n">
         <v>1</v>
@@ -23219,7 +23219,7 @@
         <v>1.0375</v>
       </c>
       <c r="D432" s="0" t="n">
-        <v>17.98215701823949</v>
+        <v>55.468691</v>
       </c>
       <c r="E432" s="0" t="inlineStr">
         <is>
@@ -23241,7 +23241,7 @@
         <v>0</v>
       </c>
       <c r="J432" s="0" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="K432" s="0" t="n">
         <v>1</v>
@@ -23270,7 +23270,7 @@
         <v>1.039</v>
       </c>
       <c r="D433" s="0" t="n">
-        <v>29.15469613259668</v>
+        <v>89.93208300000001</v>
       </c>
       <c r="E433" s="0" t="inlineStr">
         <is>
@@ -23292,7 +23292,7 @@
         <v>0</v>
       </c>
       <c r="J433" s="0" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="K433" s="0" t="n">
         <v>1</v>
@@ -23321,7 +23321,7 @@
         <v>1.039</v>
       </c>
       <c r="D434" s="0" t="n">
-        <v>29.15469613259668</v>
+        <v>89.93208300000001</v>
       </c>
       <c r="E434" s="0" t="inlineStr">
         <is>
@@ -23343,7 +23343,7 @@
         <v>0</v>
       </c>
       <c r="J434" s="0" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="K434" s="0" t="n">
         <v>1</v>
@@ -23372,7 +23372,7 @@
         <v>1.0405</v>
       </c>
       <c r="D435" s="0" t="n">
-        <v>29.27447425670776</v>
+        <v>90.30155600000001</v>
       </c>
       <c r="E435" s="0" t="inlineStr">
         <is>
@@ -23394,7 +23394,7 @@
         <v>0</v>
       </c>
       <c r="J435" s="0" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="K435" s="0" t="n">
         <v>1</v>
@@ -23423,7 +23423,7 @@
         <v>1.0405</v>
       </c>
       <c r="D436" s="0" t="n">
-        <v>29.27447425670776</v>
+        <v>90.30155600000001</v>
       </c>
       <c r="E436" s="0" t="inlineStr">
         <is>
@@ -23445,7 +23445,7 @@
         <v>0</v>
       </c>
       <c r="J436" s="0" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="K436" s="0" t="n">
         <v>1</v>
@@ -23474,7 +23474,7 @@
         <v>1.0405</v>
       </c>
       <c r="D437" s="0" t="n">
-        <v>29.27447425670776</v>
+        <v>90.30155600000001</v>
       </c>
       <c r="E437" s="0" t="inlineStr">
         <is>
@@ -23496,7 +23496,7 @@
         <v>0</v>
       </c>
       <c r="J437" s="0" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="K437" s="0" t="n">
         <v>1</v>
@@ -23525,7 +23525,7 @@
         <v>1.0405</v>
       </c>
       <c r="D438" s="0" t="n">
-        <v>29.27447425670776</v>
+        <v>90.30155600000001</v>
       </c>
       <c r="E438" s="0" t="inlineStr">
         <is>
@@ -23547,7 +23547,7 @@
         <v>0</v>
       </c>
       <c r="J438" s="0" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="K438" s="0" t="n">
         <v>1</v>
@@ -23576,7 +23576,7 @@
         <v>1.0405</v>
       </c>
       <c r="D439" s="0" t="n">
-        <v>29.27447425670776</v>
+        <v>90.30155600000001</v>
       </c>
       <c r="E439" s="0" t="inlineStr">
         <is>
@@ -23598,7 +23598,7 @@
         <v>0</v>
       </c>
       <c r="J439" s="0" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="K439" s="0" t="n">
         <v>1</v>
@@ -23627,7 +23627,7 @@
         <v>1.042</v>
       </c>
       <c r="D440" s="0" t="n">
-        <v>28.68652037617554</v>
+        <v>88.48792299999999</v>
       </c>
       <c r="E440" s="0" t="inlineStr">
         <is>
@@ -23649,7 +23649,7 @@
         <v>0</v>
       </c>
       <c r="J440" s="0" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="K440" s="0" t="n">
         <v>1</v>
@@ -23678,7 +23678,7 @@
         <v>1.042</v>
       </c>
       <c r="D441" s="0" t="n">
-        <v>28.68652037617554</v>
+        <v>88.48792299999999</v>
       </c>
       <c r="E441" s="0" t="inlineStr">
         <is>
@@ -23700,7 +23700,7 @@
         <v>0</v>
       </c>
       <c r="J441" s="0" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="K441" s="0" t="n">
         <v>1</v>
@@ -23729,7 +23729,7 @@
         <v>1.0435</v>
       </c>
       <c r="D442" s="0" t="n">
-        <v>29.21713147410359</v>
+        <v>90.124674</v>
       </c>
       <c r="E442" s="0" t="inlineStr">
         <is>
@@ -23751,7 +23751,7 @@
         <v>0</v>
       </c>
       <c r="J442" s="0" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="K442" s="0" t="n">
         <v>1</v>
@@ -23780,7 +23780,7 @@
         <v>1.0435</v>
       </c>
       <c r="D443" s="0" t="n">
-        <v>29.21713147410359</v>
+        <v>90.124674</v>
       </c>
       <c r="E443" s="0" t="inlineStr">
         <is>
@@ -23802,7 +23802,7 @@
         <v>0</v>
       </c>
       <c r="J443" s="0" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="K443" s="0" t="n">
         <v>1</v>
@@ -23831,7 +23831,7 @@
         <v>1.045</v>
       </c>
       <c r="D444" s="0" t="n">
-        <v>32.43952896244431</v>
+        <v>100.064648</v>
       </c>
       <c r="E444" s="0" t="inlineStr">
         <is>
@@ -23853,7 +23853,7 @@
         <v>0</v>
       </c>
       <c r="J444" s="0" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="K444" s="0" t="n">
         <v>1</v>
@@ -23882,7 +23882,7 @@
         <v>1.045</v>
       </c>
       <c r="D445" s="0" t="n">
-        <v>32.43952896244431</v>
+        <v>100.064648</v>
       </c>
       <c r="E445" s="0" t="inlineStr">
         <is>
@@ -23904,7 +23904,7 @@
         <v>0</v>
       </c>
       <c r="J445" s="0" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="K445" s="0" t="n">
         <v>1</v>
@@ -23933,7 +23933,7 @@
         <v>1.0465</v>
       </c>
       <c r="D446" s="0" t="n">
-        <v>51.33293341331734</v>
+        <v>158.344219</v>
       </c>
       <c r="E446" s="0" t="inlineStr">
         <is>
@@ -23955,7 +23955,7 @@
         <v>0</v>
       </c>
       <c r="J446" s="0" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="K446" s="0" t="n">
         <v>1</v>
@@ -23984,7 +23984,7 @@
         <v>1.0465</v>
       </c>
       <c r="D447" s="0" t="n">
-        <v>51.33293341331734</v>
+        <v>158.344219</v>
       </c>
       <c r="E447" s="0" t="inlineStr">
         <is>
@@ -24006,7 +24006,7 @@
         <v>0</v>
       </c>
       <c r="J447" s="0" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="K447" s="0" t="n">
         <v>1</v>
@@ -24035,7 +24035,7 @@
         <v>1.048</v>
       </c>
       <c r="D448" s="0" t="n">
-        <v>51.52685950413223</v>
+        <v>158.942414</v>
       </c>
       <c r="E448" s="0" t="inlineStr">
         <is>
@@ -24057,7 +24057,7 @@
         <v>0</v>
       </c>
       <c r="J448" s="0" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="K448" s="0" t="n">
         <v>1</v>
@@ -24086,7 +24086,7 @@
         <v>1.048</v>
       </c>
       <c r="D449" s="0" t="n">
-        <v>51.52685950413223</v>
+        <v>158.942414</v>
       </c>
       <c r="E449" s="0" t="inlineStr">
         <is>
@@ -24108,7 +24108,7 @@
         <v>0</v>
       </c>
       <c r="J449" s="0" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="K449" s="0" t="n">
         <v>1</v>
@@ -24137,7 +24137,7 @@
         <v>1.0495</v>
       </c>
       <c r="D450" s="0" t="n">
-        <v>50.80313837375179</v>
+        <v>156.709986</v>
       </c>
       <c r="E450" s="0" t="inlineStr">
         <is>
@@ -24159,7 +24159,7 @@
         <v>0</v>
       </c>
       <c r="J450" s="0" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="K450" s="0" t="n">
         <v>1</v>
@@ -24188,7 +24188,7 @@
         <v>1.0495</v>
       </c>
       <c r="D451" s="0" t="n">
-        <v>50.80313837375179</v>
+        <v>156.709986</v>
       </c>
       <c r="E451" s="0" t="inlineStr">
         <is>
@@ -24210,7 +24210,7 @@
         <v>0</v>
       </c>
       <c r="J451" s="0" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="K451" s="0" t="n">
         <v>1</v>
@@ -24239,7 +24239,7 @@
         <v>1.051</v>
       </c>
       <c r="D452" s="0" t="n">
-        <v>49.96671251719395</v>
+        <v>154.129904</v>
       </c>
       <c r="E452" s="0" t="inlineStr">
         <is>
@@ -24261,7 +24261,7 @@
         <v>0</v>
       </c>
       <c r="J452" s="0" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="K452" s="0" t="n">
         <v>1</v>
@@ -24290,7 +24290,7 @@
         <v>1.051</v>
       </c>
       <c r="D453" s="0" t="n">
-        <v>49.96671251719395</v>
+        <v>154.129904</v>
       </c>
       <c r="E453" s="0" t="inlineStr">
         <is>
@@ -24312,7 +24312,7 @@
         <v>0</v>
       </c>
       <c r="J453" s="0" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="K453" s="0" t="n">
         <v>1</v>
@@ -24341,7 +24341,7 @@
         <v>1.0525</v>
       </c>
       <c r="D454" s="0" t="n">
-        <v>51.5205298013245</v>
+        <v>158.922889</v>
       </c>
       <c r="E454" s="0" t="inlineStr">
         <is>
@@ -24363,7 +24363,7 @@
         <v>0</v>
       </c>
       <c r="J454" s="0" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="K454" s="0" t="n">
         <v>1</v>
@@ -24392,7 +24392,7 @@
         <v>1.0525</v>
       </c>
       <c r="D455" s="0" t="n">
-        <v>51.5205298013245</v>
+        <v>158.922889</v>
       </c>
       <c r="E455" s="0" t="inlineStr">
         <is>
@@ -24414,7 +24414,7 @@
         <v>0</v>
       </c>
       <c r="J455" s="0" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="K455" s="0" t="n">
         <v>1</v>
@@ -24443,7 +24443,7 @@
         <v>1.054</v>
       </c>
       <c r="D456" s="0" t="n">
-        <v>97.73564954682779</v>
+        <v>301.480436</v>
       </c>
       <c r="E456" s="0" t="inlineStr">
         <is>
@@ -24465,7 +24465,7 @@
         <v>0</v>
       </c>
       <c r="J456" s="0" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="K456" s="0" t="n">
         <v>1</v>
@@ -24494,7 +24494,7 @@
         <v>1.054</v>
       </c>
       <c r="D457" s="0" t="n">
-        <v>97.73564954682779</v>
+        <v>301.480436</v>
       </c>
       <c r="E457" s="0" t="inlineStr">
         <is>
@@ -24516,7 +24516,7 @@
         <v>0</v>
       </c>
       <c r="J457" s="0" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="K457" s="0" t="n">
         <v>1</v>

--- a/Luban/Config/Datas/Levels/L13/EnemyData.xlsx
+++ b/Luban/Config/Datas/Levels/L13/EnemyData.xlsx
@@ -1,14 +1,14 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
-<workbook xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
+<workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <workbookPr/>
   <bookViews>
     <workbookView visibility="visible" minimized="0" showHorizontalScroll="1" showVerticalScroll="1" showSheetTabs="1" windowWidth="25920" windowHeight="12900" tabRatio="600" firstSheet="0" activeTab="0" autoFilterDateGrouping="1"/>
   </bookViews>
   <sheets>
-    <sheet name="Sheet1" sheetId="1" state="visible" r:id="rId1"/>
-    <sheet name="Sheet2" sheetId="2" state="visible" r:id="rId2"/>
-    <sheet name="Sheet3" sheetId="3" state="visible" r:id="rId3"/>
+    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Sheet1" sheetId="1" state="visible" r:id="rId1"/>
+    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Sheet2" sheetId="2" state="visible" r:id="rId2"/>
+    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Sheet3" sheetId="3" state="visible" r:id="rId3"/>
   </sheets>
   <definedNames/>
   <calcPr calcId="191029" fullCalcOnLoad="1"/>
@@ -1388,10 +1388,10 @@
         <v>3580136</v>
       </c>
       <c r="C4" s="0" t="n">
-        <v>1.1198</v>
+        <v>1.1</v>
       </c>
       <c r="D4" s="0" t="n">
-        <v>13.94571</v>
+        <v>9</v>
       </c>
       <c r="E4" s="0" t="inlineStr">
         <is>
@@ -1413,7 +1413,7 @@
         <v>0</v>
       </c>
       <c r="J4" s="0" t="n">
-        <v>4</v>
+        <v>2</v>
       </c>
       <c r="K4" s="0" t="n">
         <v>1</v>
@@ -1439,10 +1439,10 @@
         <v>3580144</v>
       </c>
       <c r="C5" s="0" t="n">
-        <v>1.1198</v>
+        <v>1.1</v>
       </c>
       <c r="D5" s="0" t="n">
-        <v>13.94571</v>
+        <v>9</v>
       </c>
       <c r="E5" s="0" t="inlineStr">
         <is>
@@ -1464,7 +1464,7 @@
         <v>0</v>
       </c>
       <c r="J5" s="0" t="n">
-        <v>4</v>
+        <v>2</v>
       </c>
       <c r="K5" s="0" t="n">
         <v>1</v>
@@ -1490,10 +1490,10 @@
         <v>3582136</v>
       </c>
       <c r="C6" s="0" t="n">
-        <v>1.12145</v>
+        <v>1.1</v>
       </c>
       <c r="D6" s="0" t="n">
-        <v>14.602553</v>
+        <v>11</v>
       </c>
       <c r="E6" s="0" t="inlineStr">
         <is>
@@ -1515,7 +1515,7 @@
         <v>0</v>
       </c>
       <c r="J6" s="0" t="n">
-        <v>4</v>
+        <v>2</v>
       </c>
       <c r="K6" s="0" t="n">
         <v>1</v>
@@ -1541,10 +1541,10 @@
         <v>3582144</v>
       </c>
       <c r="C7" s="0" t="n">
-        <v>1.12145</v>
+        <v>1.1</v>
       </c>
       <c r="D7" s="0" t="n">
-        <v>14.602553</v>
+        <v>11</v>
       </c>
       <c r="E7" s="0" t="inlineStr">
         <is>
@@ -1566,7 +1566,7 @@
         <v>0</v>
       </c>
       <c r="J7" s="0" t="n">
-        <v>4</v>
+        <v>2</v>
       </c>
       <c r="K7" s="0" t="n">
         <v>1</v>
@@ -1592,10 +1592,10 @@
         <v>3584136</v>
       </c>
       <c r="C8" s="0" t="n">
-        <v>1.1231</v>
+        <v>1.1</v>
       </c>
       <c r="D8" s="0" t="n">
-        <v>19.357497</v>
+        <v>14.5</v>
       </c>
       <c r="E8" s="0" t="inlineStr">
         <is>
@@ -1617,7 +1617,7 @@
         <v>0</v>
       </c>
       <c r="J8" s="0" t="n">
-        <v>4</v>
+        <v>2</v>
       </c>
       <c r="K8" s="0" t="n">
         <v>1</v>
@@ -1643,10 +1643,10 @@
         <v>3584144</v>
       </c>
       <c r="C9" s="0" t="n">
-        <v>1.1231</v>
+        <v>1.1</v>
       </c>
       <c r="D9" s="0" t="n">
-        <v>19.357497</v>
+        <v>14.5</v>
       </c>
       <c r="E9" s="0" t="inlineStr">
         <is>
@@ -1668,7 +1668,7 @@
         <v>0</v>
       </c>
       <c r="J9" s="0" t="n">
-        <v>4</v>
+        <v>2</v>
       </c>
       <c r="K9" s="0" t="n">
         <v>1</v>
@@ -1697,7 +1697,7 @@
         <v>1.07205</v>
       </c>
       <c r="D10" s="0" t="n">
-        <v>12.582373</v>
+        <v>8</v>
       </c>
       <c r="E10" s="0" t="inlineStr">
         <is>
@@ -1745,10 +1745,10 @@
         <v>3586136</v>
       </c>
       <c r="C11" s="0" t="n">
-        <v>1.12475</v>
+        <v>1.1</v>
       </c>
       <c r="D11" s="0" t="n">
-        <v>22.162757</v>
+        <v>17</v>
       </c>
       <c r="E11" s="0" t="inlineStr">
         <is>
@@ -1770,7 +1770,7 @@
         <v>0</v>
       </c>
       <c r="J11" s="0" t="n">
-        <v>4</v>
+        <v>2</v>
       </c>
       <c r="K11" s="0" t="n">
         <v>1</v>
@@ -1796,10 +1796,10 @@
         <v>3586144</v>
       </c>
       <c r="C12" s="0" t="n">
-        <v>1.12475</v>
+        <v>1.1</v>
       </c>
       <c r="D12" s="0" t="n">
-        <v>22.162757</v>
+        <v>17</v>
       </c>
       <c r="E12" s="0" t="inlineStr">
         <is>
@@ -1821,7 +1821,7 @@
         <v>0</v>
       </c>
       <c r="J12" s="0" t="n">
-        <v>4</v>
+        <v>2</v>
       </c>
       <c r="K12" s="0" t="n">
         <v>1</v>
@@ -1850,7 +1850,7 @@
         <v>1.073625</v>
       </c>
       <c r="D13" s="0" t="n">
-        <v>14.405792</v>
+        <v>10</v>
       </c>
       <c r="E13" s="0" t="inlineStr">
         <is>
@@ -2204,10 +2204,10 @@
         <v>3590091</v>
       </c>
       <c r="C20" s="0" t="n">
-        <v>1.0255</v>
+        <v>1.08</v>
       </c>
       <c r="D20" s="0" t="n">
-        <v>19.663789</v>
+        <v>21</v>
       </c>
       <c r="E20" s="0" t="inlineStr">
         <is>
@@ -2229,7 +2229,7 @@
         <v>0</v>
       </c>
       <c r="J20" s="0" t="n">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="K20" s="0" t="n">
         <v>1</v>
@@ -2255,10 +2255,10 @@
         <v>3590107</v>
       </c>
       <c r="C21" s="0" t="n">
-        <v>1.0255</v>
+        <v>1.08</v>
       </c>
       <c r="D21" s="0" t="n">
-        <v>19.663789</v>
+        <v>21</v>
       </c>
       <c r="E21" s="0" t="inlineStr">
         <is>
@@ -2280,7 +2280,7 @@
         <v>0</v>
       </c>
       <c r="J21" s="0" t="n">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="K21" s="0" t="n">
         <v>1</v>
@@ -2765,10 +2765,10 @@
         <v>3592091</v>
       </c>
       <c r="C31" s="0" t="n">
-        <v>1.027</v>
+        <v>1.2</v>
       </c>
       <c r="D31" s="0" t="n">
-        <v>20.429983</v>
+        <v>28</v>
       </c>
       <c r="E31" s="0" t="inlineStr">
         <is>
@@ -2790,7 +2790,7 @@
         <v>0</v>
       </c>
       <c r="J31" s="0" t="n">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="K31" s="0" t="n">
         <v>1</v>
@@ -2816,10 +2816,10 @@
         <v>3592115</v>
       </c>
       <c r="C32" s="0" t="n">
-        <v>1.027</v>
+        <v>1.2</v>
       </c>
       <c r="D32" s="0" t="n">
-        <v>20.429983</v>
+        <v>28</v>
       </c>
       <c r="E32" s="0" t="inlineStr">
         <is>
@@ -2841,7 +2841,7 @@
         <v>0</v>
       </c>
       <c r="J32" s="0" t="n">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="K32" s="0" t="n">
         <v>1</v>
@@ -3326,10 +3326,10 @@
         <v>3594107</v>
       </c>
       <c r="C42" s="0" t="n">
-        <v>1.0285</v>
+        <v>1.24</v>
       </c>
       <c r="D42" s="0" t="n">
-        <v>24.378</v>
+        <v>32</v>
       </c>
       <c r="E42" s="0" t="inlineStr">
         <is>
@@ -3351,7 +3351,7 @@
         <v>0</v>
       </c>
       <c r="J42" s="0" t="n">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="K42" s="0" t="n">
         <v>1</v>
@@ -3377,10 +3377,10 @@
         <v>3594115</v>
       </c>
       <c r="C43" s="0" t="n">
-        <v>1.0285</v>
+        <v>1.24</v>
       </c>
       <c r="D43" s="0" t="n">
-        <v>24.378</v>
+        <v>32</v>
       </c>
       <c r="E43" s="0" t="inlineStr">
         <is>
@@ -3402,7 +3402,7 @@
         <v>0</v>
       </c>
       <c r="J43" s="0" t="n">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="K43" s="0" t="n">
         <v>1</v>
@@ -3887,10 +3887,10 @@
         <v>3596091</v>
       </c>
       <c r="C53" s="0" t="n">
-        <v>1.03</v>
+        <v>1.36</v>
       </c>
       <c r="D53" s="0" t="n">
-        <v>29.103578</v>
+        <v>42</v>
       </c>
       <c r="E53" s="0" t="inlineStr">
         <is>
@@ -3912,7 +3912,7 @@
         <v>0</v>
       </c>
       <c r="J53" s="0" t="n">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="K53" s="0" t="n">
         <v>1</v>
@@ -3938,10 +3938,10 @@
         <v>3596107</v>
       </c>
       <c r="C54" s="0" t="n">
-        <v>1.03</v>
+        <v>1.36</v>
       </c>
       <c r="D54" s="0" t="n">
-        <v>29.103578</v>
+        <v>42</v>
       </c>
       <c r="E54" s="0" t="inlineStr">
         <is>
@@ -3963,7 +3963,7 @@
         <v>0</v>
       </c>
       <c r="J54" s="0" t="n">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="K54" s="0" t="n">
         <v>1</v>
@@ -4448,10 +4448,10 @@
         <v>3598091</v>
       </c>
       <c r="C64" s="0" t="n">
-        <v>1.0315</v>
+        <v>1.2</v>
       </c>
       <c r="D64" s="0" t="n">
-        <v>50.507277</v>
+        <v>52</v>
       </c>
       <c r="E64" s="0" t="inlineStr">
         <is>
@@ -4473,7 +4473,7 @@
         <v>0</v>
       </c>
       <c r="J64" s="0" t="n">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="K64" s="0" t="n">
         <v>1</v>
@@ -4499,10 +4499,10 @@
         <v>3598115</v>
       </c>
       <c r="C65" s="0" t="n">
-        <v>1.0315</v>
+        <v>1.2</v>
       </c>
       <c r="D65" s="0" t="n">
-        <v>50.507277</v>
+        <v>52</v>
       </c>
       <c r="E65" s="0" t="inlineStr">
         <is>
@@ -4524,7 +4524,7 @@
         <v>0</v>
       </c>
       <c r="J65" s="0" t="n">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="K65" s="0" t="n">
         <v>1</v>
@@ -5621,10 +5621,10 @@
         <v>3602091</v>
       </c>
       <c r="C87" s="0" t="n">
-        <v>1.0345</v>
+        <v>1.2</v>
       </c>
       <c r="D87" s="0" t="n">
-        <v>42.197542</v>
+        <v>62</v>
       </c>
       <c r="E87" s="0" t="inlineStr">
         <is>
@@ -5646,7 +5646,7 @@
         <v>0</v>
       </c>
       <c r="J87" s="0" t="n">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="K87" s="0" t="n">
         <v>1</v>
@@ -5672,10 +5672,10 @@
         <v>3602107</v>
       </c>
       <c r="C88" s="0" t="n">
-        <v>1.0345</v>
+        <v>1.2</v>
       </c>
       <c r="D88" s="0" t="n">
-        <v>42.197542</v>
+        <v>62</v>
       </c>
       <c r="E88" s="0" t="inlineStr">
         <is>
@@ -5697,7 +5697,7 @@
         <v>0</v>
       </c>
       <c r="J88" s="0" t="n">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="K88" s="0" t="n">
         <v>1</v>
@@ -5723,10 +5723,10 @@
         <v>3602115</v>
       </c>
       <c r="C89" s="0" t="n">
-        <v>1.0345</v>
+        <v>1.2</v>
       </c>
       <c r="D89" s="0" t="n">
-        <v>42.197542</v>
+        <v>62</v>
       </c>
       <c r="E89" s="0" t="inlineStr">
         <is>
@@ -5748,7 +5748,7 @@
         <v>0</v>
       </c>
       <c r="J89" s="0" t="n">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="K89" s="0" t="n">
         <v>1</v>
@@ -6386,10 +6386,10 @@
         <v>3604091</v>
       </c>
       <c r="C102" s="0" t="n">
-        <v>1.036</v>
+        <v>1.1</v>
       </c>
       <c r="D102" s="0" t="n">
-        <v>48.609454</v>
+        <v>55</v>
       </c>
       <c r="E102" s="0" t="inlineStr">
         <is>
@@ -6411,7 +6411,7 @@
         <v>0</v>
       </c>
       <c r="J102" s="0" t="n">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="K102" s="0" t="n">
         <v>1</v>
@@ -6437,10 +6437,10 @@
         <v>3604107</v>
       </c>
       <c r="C103" s="0" t="n">
-        <v>1.036</v>
+        <v>1.1</v>
       </c>
       <c r="D103" s="0" t="n">
-        <v>48.609454</v>
+        <v>55</v>
       </c>
       <c r="E103" s="0" t="inlineStr">
         <is>
@@ -6462,7 +6462,7 @@
         <v>0</v>
       </c>
       <c r="J103" s="0" t="n">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="K103" s="0" t="n">
         <v>1</v>
@@ -6488,10 +6488,10 @@
         <v>3604115</v>
       </c>
       <c r="C104" s="0" t="n">
-        <v>1.036</v>
+        <v>1.1</v>
       </c>
       <c r="D104" s="0" t="n">
-        <v>48.609454</v>
+        <v>55</v>
       </c>
       <c r="E104" s="0" t="inlineStr">
         <is>
@@ -6513,7 +6513,7 @@
         <v>0</v>
       </c>
       <c r="J104" s="0" t="n">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="K104" s="0" t="n">
         <v>1</v>
@@ -7151,10 +7151,10 @@
         <v>3606091</v>
       </c>
       <c r="C117" s="0" t="n">
-        <v>1.0375</v>
+        <v>1.24</v>
       </c>
       <c r="D117" s="0" t="n">
-        <v>55.468691</v>
+        <v>68</v>
       </c>
       <c r="E117" s="0" t="inlineStr">
         <is>
@@ -7176,7 +7176,7 @@
         <v>0</v>
       </c>
       <c r="J117" s="0" t="n">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="K117" s="0" t="n">
         <v>1</v>
@@ -7202,10 +7202,10 @@
         <v>3606107</v>
       </c>
       <c r="C118" s="0" t="n">
-        <v>1.0375</v>
+        <v>1.24</v>
       </c>
       <c r="D118" s="0" t="n">
-        <v>55.468691</v>
+        <v>68</v>
       </c>
       <c r="E118" s="0" t="inlineStr">
         <is>
@@ -7227,7 +7227,7 @@
         <v>0</v>
       </c>
       <c r="J118" s="0" t="n">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="K118" s="0" t="n">
         <v>1</v>
@@ -7253,10 +7253,10 @@
         <v>3606115</v>
       </c>
       <c r="C119" s="0" t="n">
-        <v>1.0375</v>
+        <v>1.24</v>
       </c>
       <c r="D119" s="0" t="n">
-        <v>55.468691</v>
+        <v>68</v>
       </c>
       <c r="E119" s="0" t="inlineStr">
         <is>
@@ -7278,7 +7278,7 @@
         <v>0</v>
       </c>
       <c r="J119" s="0" t="n">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="K119" s="0" t="n">
         <v>1</v>
@@ -7916,10 +7916,10 @@
         <v>3608091</v>
       </c>
       <c r="C132" s="0" t="n">
-        <v>1.039</v>
+        <v>1.28</v>
       </c>
       <c r="D132" s="0" t="n">
-        <v>89.93208300000001</v>
+        <v>104</v>
       </c>
       <c r="E132" s="0" t="inlineStr">
         <is>
@@ -7941,7 +7941,7 @@
         <v>0</v>
       </c>
       <c r="J132" s="0" t="n">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="K132" s="0" t="n">
         <v>1</v>
@@ -7967,10 +7967,10 @@
         <v>3608107</v>
       </c>
       <c r="C133" s="0" t="n">
-        <v>1.039</v>
+        <v>1.28</v>
       </c>
       <c r="D133" s="0" t="n">
-        <v>89.93208300000001</v>
+        <v>104</v>
       </c>
       <c r="E133" s="0" t="inlineStr">
         <is>
@@ -7992,7 +7992,7 @@
         <v>0</v>
       </c>
       <c r="J133" s="0" t="n">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="K133" s="0" t="n">
         <v>1</v>
@@ -8018,10 +8018,10 @@
         <v>3608115</v>
       </c>
       <c r="C134" s="0" t="n">
-        <v>1.039</v>
+        <v>1.28</v>
       </c>
       <c r="D134" s="0" t="n">
-        <v>89.93208300000001</v>
+        <v>104</v>
       </c>
       <c r="E134" s="0" t="inlineStr">
         <is>
@@ -8043,7 +8043,7 @@
         <v>0</v>
       </c>
       <c r="J134" s="0" t="n">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="K134" s="0" t="n">
         <v>1</v>
@@ -9446,10 +9446,10 @@
         <v>3612091</v>
       </c>
       <c r="C162" s="0" t="n">
-        <v>1.042</v>
+        <v>1.2</v>
       </c>
       <c r="D162" s="0" t="n">
-        <v>88.48792299999999</v>
+        <v>102</v>
       </c>
       <c r="E162" s="0" t="inlineStr">
         <is>
@@ -9471,7 +9471,7 @@
         <v>0</v>
       </c>
       <c r="J162" s="0" t="n">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="K162" s="0" t="n">
         <v>1</v>
@@ -9497,10 +9497,10 @@
         <v>3612107</v>
       </c>
       <c r="C163" s="0" t="n">
-        <v>1.042</v>
+        <v>1.2</v>
       </c>
       <c r="D163" s="0" t="n">
-        <v>88.48792299999999</v>
+        <v>102</v>
       </c>
       <c r="E163" s="0" t="inlineStr">
         <is>
@@ -9522,7 +9522,7 @@
         <v>0</v>
       </c>
       <c r="J163" s="0" t="n">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="K163" s="0" t="n">
         <v>1</v>
@@ -9548,10 +9548,10 @@
         <v>3612115</v>
       </c>
       <c r="C164" s="0" t="n">
-        <v>1.042</v>
+        <v>1.2</v>
       </c>
       <c r="D164" s="0" t="n">
-        <v>88.48792299999999</v>
+        <v>102</v>
       </c>
       <c r="E164" s="0" t="inlineStr">
         <is>
@@ -9573,7 +9573,7 @@
         <v>0</v>
       </c>
       <c r="J164" s="0" t="n">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="K164" s="0" t="n">
         <v>1</v>
@@ -10262,10 +10262,10 @@
         <v>3614091</v>
       </c>
       <c r="C178" s="0" t="n">
-        <v>1.0435</v>
+        <v>1.28</v>
       </c>
       <c r="D178" s="0" t="n">
-        <v>90.124674</v>
+        <v>112</v>
       </c>
       <c r="E178" s="0" t="inlineStr">
         <is>
@@ -10287,7 +10287,7 @@
         <v>0</v>
       </c>
       <c r="J178" s="0" t="n">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="K178" s="0" t="n">
         <v>1</v>
@@ -10313,10 +10313,10 @@
         <v>3614107</v>
       </c>
       <c r="C179" s="0" t="n">
-        <v>1.0435</v>
+        <v>1.28</v>
       </c>
       <c r="D179" s="0" t="n">
-        <v>90.124674</v>
+        <v>112</v>
       </c>
       <c r="E179" s="0" t="inlineStr">
         <is>
@@ -10338,7 +10338,7 @@
         <v>0</v>
       </c>
       <c r="J179" s="0" t="n">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="K179" s="0" t="n">
         <v>1</v>
@@ -10364,10 +10364,10 @@
         <v>3614115</v>
       </c>
       <c r="C180" s="0" t="n">
-        <v>1.0435</v>
+        <v>1.28</v>
       </c>
       <c r="D180" s="0" t="n">
-        <v>90.124674</v>
+        <v>112</v>
       </c>
       <c r="E180" s="0" t="inlineStr">
         <is>
@@ -10389,7 +10389,7 @@
         <v>0</v>
       </c>
       <c r="J180" s="0" t="n">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="K180" s="0" t="n">
         <v>1</v>
@@ -11078,10 +11078,10 @@
         <v>3616091</v>
       </c>
       <c r="C194" s="0" t="n">
-        <v>1.045</v>
+        <v>1.22</v>
       </c>
       <c r="D194" s="0" t="n">
-        <v>100.064648</v>
+        <v>116</v>
       </c>
       <c r="E194" s="0" t="inlineStr">
         <is>
@@ -11103,7 +11103,7 @@
         <v>0</v>
       </c>
       <c r="J194" s="0" t="n">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="K194" s="0" t="n">
         <v>1</v>
@@ -11129,10 +11129,10 @@
         <v>3616107</v>
       </c>
       <c r="C195" s="0" t="n">
-        <v>1.045</v>
+        <v>1.22</v>
       </c>
       <c r="D195" s="0" t="n">
-        <v>100.064648</v>
+        <v>116</v>
       </c>
       <c r="E195" s="0" t="inlineStr">
         <is>
@@ -11154,7 +11154,7 @@
         <v>0</v>
       </c>
       <c r="J195" s="0" t="n">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="K195" s="0" t="n">
         <v>1</v>
@@ -11180,10 +11180,10 @@
         <v>3616115</v>
       </c>
       <c r="C196" s="0" t="n">
-        <v>1.045</v>
+        <v>1.22</v>
       </c>
       <c r="D196" s="0" t="n">
-        <v>100.064648</v>
+        <v>116</v>
       </c>
       <c r="E196" s="0" t="inlineStr">
         <is>
@@ -11205,7 +11205,7 @@
         <v>0</v>
       </c>
       <c r="J196" s="0" t="n">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="K196" s="0" t="n">
         <v>1</v>
@@ -11894,10 +11894,10 @@
         <v>3618091</v>
       </c>
       <c r="C210" s="0" t="n">
-        <v>1.0465</v>
+        <v>1.12</v>
       </c>
       <c r="D210" s="0" t="n">
-        <v>158.344219</v>
+        <v>148</v>
       </c>
       <c r="E210" s="0" t="inlineStr">
         <is>
@@ -11919,7 +11919,7 @@
         <v>0</v>
       </c>
       <c r="J210" s="0" t="n">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="K210" s="0" t="n">
         <v>1</v>
@@ -11945,10 +11945,10 @@
         <v>3618107</v>
       </c>
       <c r="C211" s="0" t="n">
-        <v>1.0465</v>
+        <v>1.12</v>
       </c>
       <c r="D211" s="0" t="n">
-        <v>158.344219</v>
+        <v>148</v>
       </c>
       <c r="E211" s="0" t="inlineStr">
         <is>
@@ -11970,7 +11970,7 @@
         <v>0</v>
       </c>
       <c r="J211" s="0" t="n">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="K211" s="0" t="n">
         <v>1</v>
@@ -11996,10 +11996,10 @@
         <v>3618115</v>
       </c>
       <c r="C212" s="0" t="n">
-        <v>1.0465</v>
+        <v>1.12</v>
       </c>
       <c r="D212" s="0" t="n">
-        <v>158.344219</v>
+        <v>148</v>
       </c>
       <c r="E212" s="0" t="inlineStr">
         <is>
@@ -12021,7 +12021,7 @@
         <v>0</v>
       </c>
       <c r="J212" s="0" t="n">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="K212" s="0" t="n">
         <v>1</v>
@@ -12710,10 +12710,10 @@
         <v>3590115</v>
       </c>
       <c r="C226" s="0" t="n">
-        <v>1.0255</v>
+        <v>1.08</v>
       </c>
       <c r="D226" s="0" t="n">
-        <v>19.663789</v>
+        <v>21</v>
       </c>
       <c r="E226" s="0" t="inlineStr">
         <is>
@@ -12735,7 +12735,7 @@
         <v>0</v>
       </c>
       <c r="J226" s="0" t="n">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="K226" s="0" t="n">
         <v>1</v>
@@ -12812,10 +12812,10 @@
         <v>3592107</v>
       </c>
       <c r="C228" s="0" t="n">
-        <v>1.027</v>
+        <v>1.2</v>
       </c>
       <c r="D228" s="0" t="n">
-        <v>20.429983</v>
+        <v>28</v>
       </c>
       <c r="E228" s="0" t="inlineStr">
         <is>
@@ -12837,7 +12837,7 @@
         <v>0</v>
       </c>
       <c r="J228" s="0" t="n">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="K228" s="0" t="n">
         <v>1</v>
@@ -12914,10 +12914,10 @@
         <v>3594091</v>
       </c>
       <c r="C230" s="0" t="n">
-        <v>1.0285</v>
+        <v>1.24</v>
       </c>
       <c r="D230" s="0" t="n">
-        <v>24.378</v>
+        <v>32</v>
       </c>
       <c r="E230" s="0" t="inlineStr">
         <is>
@@ -12939,7 +12939,7 @@
         <v>0</v>
       </c>
       <c r="J230" s="0" t="n">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="K230" s="0" t="n">
         <v>1</v>
@@ -13016,10 +13016,10 @@
         <v>3596115</v>
       </c>
       <c r="C232" s="0" t="n">
-        <v>1.03</v>
+        <v>1.36</v>
       </c>
       <c r="D232" s="0" t="n">
-        <v>29.103578</v>
+        <v>42</v>
       </c>
       <c r="E232" s="0" t="inlineStr">
         <is>
@@ -13041,7 +13041,7 @@
         <v>0</v>
       </c>
       <c r="J232" s="0" t="n">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="K232" s="0" t="n">
         <v>1</v>
@@ -13118,10 +13118,10 @@
         <v>3598107</v>
       </c>
       <c r="C234" s="0" t="n">
-        <v>1.0315</v>
+        <v>1.2</v>
       </c>
       <c r="D234" s="0" t="n">
-        <v>50.507277</v>
+        <v>52</v>
       </c>
       <c r="E234" s="0" t="inlineStr">
         <is>
@@ -13143,7 +13143,7 @@
         <v>0</v>
       </c>
       <c r="J234" s="0" t="n">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="K234" s="0" t="n">
         <v>1</v>
@@ -14750,10 +14750,10 @@
         <v>10017702</v>
       </c>
       <c r="C266" s="0" t="n">
-        <v>1.048</v>
+        <v>1.24</v>
       </c>
       <c r="D266" s="0" t="n">
-        <v>158.942414</v>
+        <v>160</v>
       </c>
       <c r="E266" s="0" t="inlineStr">
         <is>
@@ -14775,7 +14775,7 @@
         <v>0</v>
       </c>
       <c r="J266" s="0" t="n">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="K266" s="0" t="n">
         <v>1</v>
@@ -14801,10 +14801,10 @@
         <v>10017703</v>
       </c>
       <c r="C267" s="0" t="n">
-        <v>1.048</v>
+        <v>1.24</v>
       </c>
       <c r="D267" s="0" t="n">
-        <v>158.942414</v>
+        <v>160</v>
       </c>
       <c r="E267" s="0" t="inlineStr">
         <is>
@@ -14826,7 +14826,7 @@
         <v>0</v>
       </c>
       <c r="J267" s="0" t="n">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="K267" s="0" t="n">
         <v>1</v>
@@ -14852,10 +14852,10 @@
         <v>10017704</v>
       </c>
       <c r="C268" s="0" t="n">
-        <v>1.048</v>
+        <v>1.24</v>
       </c>
       <c r="D268" s="0" t="n">
-        <v>158.942414</v>
+        <v>160</v>
       </c>
       <c r="E268" s="0" t="inlineStr">
         <is>
@@ -14877,7 +14877,7 @@
         <v>0</v>
       </c>
       <c r="J268" s="0" t="n">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="K268" s="0" t="n">
         <v>1</v>
@@ -15770,10 +15770,10 @@
         <v>10017722</v>
       </c>
       <c r="C286" s="0" t="n">
-        <v>1.0495</v>
+        <v>1.3</v>
       </c>
       <c r="D286" s="0" t="n">
-        <v>156.709986</v>
+        <v>172</v>
       </c>
       <c r="E286" s="0" t="inlineStr">
         <is>
@@ -15795,7 +15795,7 @@
         <v>0</v>
       </c>
       <c r="J286" s="0" t="n">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="K286" s="0" t="n">
         <v>1</v>
@@ -15821,10 +15821,10 @@
         <v>10017723</v>
       </c>
       <c r="C287" s="0" t="n">
-        <v>1.0495</v>
+        <v>1.3</v>
       </c>
       <c r="D287" s="0" t="n">
-        <v>156.709986</v>
+        <v>172</v>
       </c>
       <c r="E287" s="0" t="inlineStr">
         <is>
@@ -15846,7 +15846,7 @@
         <v>0</v>
       </c>
       <c r="J287" s="0" t="n">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="K287" s="0" t="n">
         <v>1</v>
@@ -15872,10 +15872,10 @@
         <v>10017724</v>
       </c>
       <c r="C288" s="0" t="n">
-        <v>1.0495</v>
+        <v>1.3</v>
       </c>
       <c r="D288" s="0" t="n">
-        <v>156.709986</v>
+        <v>172</v>
       </c>
       <c r="E288" s="0" t="inlineStr">
         <is>
@@ -15897,7 +15897,7 @@
         <v>0</v>
       </c>
       <c r="J288" s="0" t="n">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="K288" s="0" t="n">
         <v>1</v>
@@ -16790,10 +16790,10 @@
         <v>10017742</v>
       </c>
       <c r="C306" s="0" t="n">
-        <v>1.051</v>
+        <v>1.42</v>
       </c>
       <c r="D306" s="0" t="n">
-        <v>154.129904</v>
+        <v>196</v>
       </c>
       <c r="E306" s="0" t="inlineStr">
         <is>
@@ -16815,7 +16815,7 @@
         <v>0</v>
       </c>
       <c r="J306" s="0" t="n">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="K306" s="0" t="n">
         <v>1</v>
@@ -16841,10 +16841,10 @@
         <v>10017743</v>
       </c>
       <c r="C307" s="0" t="n">
-        <v>1.051</v>
+        <v>1.42</v>
       </c>
       <c r="D307" s="0" t="n">
-        <v>154.129904</v>
+        <v>196</v>
       </c>
       <c r="E307" s="0" t="inlineStr">
         <is>
@@ -16866,7 +16866,7 @@
         <v>0</v>
       </c>
       <c r="J307" s="0" t="n">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="K307" s="0" t="n">
         <v>1</v>
@@ -16892,10 +16892,10 @@
         <v>10017744</v>
       </c>
       <c r="C308" s="0" t="n">
-        <v>1.051</v>
+        <v>1.42</v>
       </c>
       <c r="D308" s="0" t="n">
-        <v>154.129904</v>
+        <v>196</v>
       </c>
       <c r="E308" s="0" t="inlineStr">
         <is>
@@ -16917,7 +16917,7 @@
         <v>0</v>
       </c>
       <c r="J308" s="0" t="n">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="K308" s="0" t="n">
         <v>1</v>
@@ -17810,10 +17810,10 @@
         <v>10017762</v>
       </c>
       <c r="C326" s="0" t="n">
-        <v>1.0525</v>
+        <v>1.2</v>
       </c>
       <c r="D326" s="0" t="n">
-        <v>158.922889</v>
+        <v>180</v>
       </c>
       <c r="E326" s="0" t="inlineStr">
         <is>
@@ -17835,7 +17835,7 @@
         <v>0</v>
       </c>
       <c r="J326" s="0" t="n">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="K326" s="0" t="n">
         <v>1</v>
@@ -17861,10 +17861,10 @@
         <v>10017763</v>
       </c>
       <c r="C327" s="0" t="n">
-        <v>1.0525</v>
+        <v>1.2</v>
       </c>
       <c r="D327" s="0" t="n">
-        <v>158.922889</v>
+        <v>180</v>
       </c>
       <c r="E327" s="0" t="inlineStr">
         <is>
@@ -17886,7 +17886,7 @@
         <v>0</v>
       </c>
       <c r="J327" s="0" t="n">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="K327" s="0" t="n">
         <v>1</v>
@@ -17912,10 +17912,10 @@
         <v>10017764</v>
       </c>
       <c r="C328" s="0" t="n">
-        <v>1.0525</v>
+        <v>1.2</v>
       </c>
       <c r="D328" s="0" t="n">
-        <v>158.922889</v>
+        <v>180</v>
       </c>
       <c r="E328" s="0" t="inlineStr">
         <is>
@@ -17937,7 +17937,7 @@
         <v>0</v>
       </c>
       <c r="J328" s="0" t="n">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="K328" s="0" t="n">
         <v>1</v>
@@ -18830,10 +18830,10 @@
         <v>10017782</v>
       </c>
       <c r="C346" s="0" t="n">
-        <v>1.054</v>
+        <v>1.34</v>
       </c>
       <c r="D346" s="0" t="n">
-        <v>301.480436</v>
+        <v>286</v>
       </c>
       <c r="E346" s="0" t="inlineStr">
         <is>
@@ -18855,7 +18855,7 @@
         <v>0</v>
       </c>
       <c r="J346" s="0" t="n">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="K346" s="0" t="n">
         <v>1</v>
@@ -18881,10 +18881,10 @@
         <v>10017783</v>
       </c>
       <c r="C347" s="0" t="n">
-        <v>1.054</v>
+        <v>1.34</v>
       </c>
       <c r="D347" s="0" t="n">
-        <v>301.480436</v>
+        <v>286</v>
       </c>
       <c r="E347" s="0" t="inlineStr">
         <is>
@@ -18906,7 +18906,7 @@
         <v>0</v>
       </c>
       <c r="J347" s="0" t="n">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="K347" s="0" t="n">
         <v>1</v>
@@ -18932,10 +18932,10 @@
         <v>10017784</v>
       </c>
       <c r="C348" s="0" t="n">
-        <v>1.054</v>
+        <v>1.34</v>
       </c>
       <c r="D348" s="0" t="n">
-        <v>301.480436</v>
+        <v>286</v>
       </c>
       <c r="E348" s="0" t="inlineStr">
         <is>
@@ -18957,7 +18957,7 @@
         <v>0</v>
       </c>
       <c r="J348" s="0" t="n">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="K348" s="0" t="n">
         <v>1</v>
@@ -21941,10 +21941,10 @@
         <v>3588019</v>
       </c>
       <c r="C407" s="0" t="n">
-        <v>1.024</v>
+        <v>1.16</v>
       </c>
       <c r="D407" s="0" t="n">
-        <v>20.347459</v>
+        <v>24</v>
       </c>
       <c r="E407" s="0" t="inlineStr">
         <is>
@@ -21966,7 +21966,7 @@
         <v>0</v>
       </c>
       <c r="J407" s="0" t="n">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="K407" s="0" t="n">
         <v>1</v>
@@ -21992,10 +21992,10 @@
         <v>3588091</v>
       </c>
       <c r="C408" s="0" t="n">
-        <v>1.024</v>
+        <v>1.16</v>
       </c>
       <c r="D408" s="0" t="n">
-        <v>20.347459</v>
+        <v>24</v>
       </c>
       <c r="E408" s="0" t="inlineStr">
         <is>
@@ -22017,7 +22017,7 @@
         <v>0</v>
       </c>
       <c r="J408" s="0" t="n">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="K408" s="0" t="n">
         <v>1</v>
@@ -22043,10 +22043,10 @@
         <v>3588099</v>
       </c>
       <c r="C409" s="0" t="n">
-        <v>1.024</v>
+        <v>1.16</v>
       </c>
       <c r="D409" s="0" t="n">
-        <v>20.347459</v>
+        <v>24</v>
       </c>
       <c r="E409" s="0" t="inlineStr">
         <is>
@@ -22068,7 +22068,7 @@
         <v>0</v>
       </c>
       <c r="J409" s="0" t="n">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="K409" s="0" t="n">
         <v>1</v>
@@ -22094,10 +22094,10 @@
         <v>3588107</v>
       </c>
       <c r="C410" s="0" t="n">
-        <v>1.024</v>
+        <v>1.16</v>
       </c>
       <c r="D410" s="0" t="n">
-        <v>20.347459</v>
+        <v>24</v>
       </c>
       <c r="E410" s="0" t="inlineStr">
         <is>
@@ -22119,7 +22119,7 @@
         <v>0</v>
       </c>
       <c r="J410" s="0" t="n">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="K410" s="0" t="n">
         <v>1</v>
@@ -22145,10 +22145,10 @@
         <v>3588115</v>
       </c>
       <c r="C411" s="0" t="n">
-        <v>1.024</v>
+        <v>1.16</v>
       </c>
       <c r="D411" s="0" t="n">
-        <v>20.347459</v>
+        <v>24</v>
       </c>
       <c r="E411" s="0" t="inlineStr">
         <is>
@@ -22170,7 +22170,7 @@
         <v>0</v>
       </c>
       <c r="J411" s="0" t="n">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="K411" s="0" t="n">
         <v>1</v>
@@ -22196,10 +22196,10 @@
         <v>3590019</v>
       </c>
       <c r="C412" s="0" t="n">
-        <v>1.0255</v>
+        <v>1.08</v>
       </c>
       <c r="D412" s="0" t="n">
-        <v>19.663789</v>
+        <v>21</v>
       </c>
       <c r="E412" s="0" t="inlineStr">
         <is>
@@ -22221,7 +22221,7 @@
         <v>0</v>
       </c>
       <c r="J412" s="0" t="n">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="K412" s="0" t="n">
         <v>1</v>
@@ -22247,10 +22247,10 @@
         <v>3590099</v>
       </c>
       <c r="C413" s="0" t="n">
-        <v>1.0255</v>
+        <v>1.08</v>
       </c>
       <c r="D413" s="0" t="n">
-        <v>19.663789</v>
+        <v>21</v>
       </c>
       <c r="E413" s="0" t="inlineStr">
         <is>
@@ -22272,7 +22272,7 @@
         <v>0</v>
       </c>
       <c r="J413" s="0" t="n">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="K413" s="0" t="n">
         <v>1</v>
@@ -22298,10 +22298,10 @@
         <v>3592019</v>
       </c>
       <c r="C414" s="0" t="n">
-        <v>1.027</v>
+        <v>1.2</v>
       </c>
       <c r="D414" s="0" t="n">
-        <v>20.429983</v>
+        <v>28</v>
       </c>
       <c r="E414" s="0" t="inlineStr">
         <is>
@@ -22323,7 +22323,7 @@
         <v>0</v>
       </c>
       <c r="J414" s="0" t="n">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="K414" s="0" t="n">
         <v>1</v>
@@ -22349,10 +22349,10 @@
         <v>3592099</v>
       </c>
       <c r="C415" s="0" t="n">
-        <v>1.027</v>
+        <v>1.2</v>
       </c>
       <c r="D415" s="0" t="n">
-        <v>20.429983</v>
+        <v>28</v>
       </c>
       <c r="E415" s="0" t="inlineStr">
         <is>
@@ -22374,7 +22374,7 @@
         <v>0</v>
       </c>
       <c r="J415" s="0" t="n">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="K415" s="0" t="n">
         <v>1</v>
@@ -22400,10 +22400,10 @@
         <v>3594019</v>
       </c>
       <c r="C416" s="0" t="n">
-        <v>1.0285</v>
+        <v>1.24</v>
       </c>
       <c r="D416" s="0" t="n">
-        <v>24.378</v>
+        <v>32</v>
       </c>
       <c r="E416" s="0" t="inlineStr">
         <is>
@@ -22425,7 +22425,7 @@
         <v>0</v>
       </c>
       <c r="J416" s="0" t="n">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="K416" s="0" t="n">
         <v>1</v>
@@ -22451,10 +22451,10 @@
         <v>3594099</v>
       </c>
       <c r="C417" s="0" t="n">
-        <v>1.0285</v>
+        <v>1.24</v>
       </c>
       <c r="D417" s="0" t="n">
-        <v>24.378</v>
+        <v>32</v>
       </c>
       <c r="E417" s="0" t="inlineStr">
         <is>
@@ -22476,7 +22476,7 @@
         <v>0</v>
       </c>
       <c r="J417" s="0" t="n">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="K417" s="0" t="n">
         <v>1</v>
@@ -22502,10 +22502,10 @@
         <v>3596019</v>
       </c>
       <c r="C418" s="0" t="n">
-        <v>1.03</v>
+        <v>1.36</v>
       </c>
       <c r="D418" s="0" t="n">
-        <v>29.103578</v>
+        <v>42</v>
       </c>
       <c r="E418" s="0" t="inlineStr">
         <is>
@@ -22527,7 +22527,7 @@
         <v>0</v>
       </c>
       <c r="J418" s="0" t="n">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="K418" s="0" t="n">
         <v>1</v>
@@ -22553,10 +22553,10 @@
         <v>3596099</v>
       </c>
       <c r="C419" s="0" t="n">
-        <v>1.03</v>
+        <v>1.36</v>
       </c>
       <c r="D419" s="0" t="n">
-        <v>29.103578</v>
+        <v>42</v>
       </c>
       <c r="E419" s="0" t="inlineStr">
         <is>
@@ -22578,7 +22578,7 @@
         <v>0</v>
       </c>
       <c r="J419" s="0" t="n">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="K419" s="0" t="n">
         <v>1</v>
@@ -22604,10 +22604,10 @@
         <v>3598019</v>
       </c>
       <c r="C420" s="0" t="n">
-        <v>1.0315</v>
+        <v>1.2</v>
       </c>
       <c r="D420" s="0" t="n">
-        <v>50.507277</v>
+        <v>52</v>
       </c>
       <c r="E420" s="0" t="inlineStr">
         <is>
@@ -22629,7 +22629,7 @@
         <v>0</v>
       </c>
       <c r="J420" s="0" t="n">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="K420" s="0" t="n">
         <v>1</v>
@@ -22655,10 +22655,10 @@
         <v>3598099</v>
       </c>
       <c r="C421" s="0" t="n">
-        <v>1.0315</v>
+        <v>1.2</v>
       </c>
       <c r="D421" s="0" t="n">
-        <v>50.507277</v>
+        <v>52</v>
       </c>
       <c r="E421" s="0" t="inlineStr">
         <is>
@@ -22680,7 +22680,7 @@
         <v>0</v>
       </c>
       <c r="J421" s="0" t="n">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="K421" s="0" t="n">
         <v>1</v>
@@ -22706,10 +22706,10 @@
         <v>3600019</v>
       </c>
       <c r="C422" s="0" t="n">
-        <v>1.033</v>
+        <v>1.26</v>
       </c>
       <c r="D422" s="0" t="n">
-        <v>42.781215</v>
+        <v>58</v>
       </c>
       <c r="E422" s="0" t="inlineStr">
         <is>
@@ -22731,7 +22731,7 @@
         <v>0</v>
       </c>
       <c r="J422" s="0" t="n">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="K422" s="0" t="n">
         <v>1</v>
@@ -22757,10 +22757,10 @@
         <v>3600091</v>
       </c>
       <c r="C423" s="0" t="n">
-        <v>1.033</v>
+        <v>1.26</v>
       </c>
       <c r="D423" s="0" t="n">
-        <v>42.781215</v>
+        <v>58</v>
       </c>
       <c r="E423" s="0" t="inlineStr">
         <is>
@@ -22782,7 +22782,7 @@
         <v>0</v>
       </c>
       <c r="J423" s="0" t="n">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="K423" s="0" t="n">
         <v>1</v>
@@ -22808,10 +22808,10 @@
         <v>3600099</v>
       </c>
       <c r="C424" s="0" t="n">
-        <v>1.033</v>
+        <v>1.26</v>
       </c>
       <c r="D424" s="0" t="n">
-        <v>42.781215</v>
+        <v>58</v>
       </c>
       <c r="E424" s="0" t="inlineStr">
         <is>
@@ -22833,7 +22833,7 @@
         <v>0</v>
       </c>
       <c r="J424" s="0" t="n">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="K424" s="0" t="n">
         <v>1</v>
@@ -22859,10 +22859,10 @@
         <v>3600107</v>
       </c>
       <c r="C425" s="0" t="n">
-        <v>1.033</v>
+        <v>1.26</v>
       </c>
       <c r="D425" s="0" t="n">
-        <v>42.781215</v>
+        <v>58</v>
       </c>
       <c r="E425" s="0" t="inlineStr">
         <is>
@@ -22884,7 +22884,7 @@
         <v>0</v>
       </c>
       <c r="J425" s="0" t="n">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="K425" s="0" t="n">
         <v>1</v>
@@ -22910,10 +22910,10 @@
         <v>3600115</v>
       </c>
       <c r="C426" s="0" t="n">
-        <v>1.033</v>
+        <v>1.26</v>
       </c>
       <c r="D426" s="0" t="n">
-        <v>42.781215</v>
+        <v>58</v>
       </c>
       <c r="E426" s="0" t="inlineStr">
         <is>
@@ -22935,7 +22935,7 @@
         <v>0</v>
       </c>
       <c r="J426" s="0" t="n">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="K426" s="0" t="n">
         <v>1</v>
@@ -22961,10 +22961,10 @@
         <v>3602019</v>
       </c>
       <c r="C427" s="0" t="n">
-        <v>1.0345</v>
+        <v>1.2</v>
       </c>
       <c r="D427" s="0" t="n">
-        <v>42.197542</v>
+        <v>62</v>
       </c>
       <c r="E427" s="0" t="inlineStr">
         <is>
@@ -22986,7 +22986,7 @@
         <v>0</v>
       </c>
       <c r="J427" s="0" t="n">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="K427" s="0" t="n">
         <v>1</v>
@@ -23012,10 +23012,10 @@
         <v>3602099</v>
       </c>
       <c r="C428" s="0" t="n">
-        <v>1.0345</v>
+        <v>1.2</v>
       </c>
       <c r="D428" s="0" t="n">
-        <v>42.197542</v>
+        <v>62</v>
       </c>
       <c r="E428" s="0" t="inlineStr">
         <is>
@@ -23037,7 +23037,7 @@
         <v>0</v>
       </c>
       <c r="J428" s="0" t="n">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="K428" s="0" t="n">
         <v>1</v>
@@ -23063,10 +23063,10 @@
         <v>3604019</v>
       </c>
       <c r="C429" s="0" t="n">
-        <v>1.036</v>
+        <v>1.1</v>
       </c>
       <c r="D429" s="0" t="n">
-        <v>48.609454</v>
+        <v>55</v>
       </c>
       <c r="E429" s="0" t="inlineStr">
         <is>
@@ -23088,7 +23088,7 @@
         <v>0</v>
       </c>
       <c r="J429" s="0" t="n">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="K429" s="0" t="n">
         <v>1</v>
@@ -23114,10 +23114,10 @@
         <v>3604099</v>
       </c>
       <c r="C430" s="0" t="n">
-        <v>1.036</v>
+        <v>1.1</v>
       </c>
       <c r="D430" s="0" t="n">
-        <v>48.609454</v>
+        <v>55</v>
       </c>
       <c r="E430" s="0" t="inlineStr">
         <is>
@@ -23139,7 +23139,7 @@
         <v>0</v>
       </c>
       <c r="J430" s="0" t="n">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="K430" s="0" t="n">
         <v>1</v>
@@ -23165,10 +23165,10 @@
         <v>3606019</v>
       </c>
       <c r="C431" s="0" t="n">
-        <v>1.0375</v>
+        <v>1.24</v>
       </c>
       <c r="D431" s="0" t="n">
-        <v>55.468691</v>
+        <v>68</v>
       </c>
       <c r="E431" s="0" t="inlineStr">
         <is>
@@ -23190,7 +23190,7 @@
         <v>0</v>
       </c>
       <c r="J431" s="0" t="n">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="K431" s="0" t="n">
         <v>1</v>
@@ -23216,10 +23216,10 @@
         <v>3606099</v>
       </c>
       <c r="C432" s="0" t="n">
-        <v>1.0375</v>
+        <v>1.24</v>
       </c>
       <c r="D432" s="0" t="n">
-        <v>55.468691</v>
+        <v>68</v>
       </c>
       <c r="E432" s="0" t="inlineStr">
         <is>
@@ -23241,7 +23241,7 @@
         <v>0</v>
       </c>
       <c r="J432" s="0" t="n">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="K432" s="0" t="n">
         <v>1</v>
@@ -23267,10 +23267,10 @@
         <v>3608019</v>
       </c>
       <c r="C433" s="0" t="n">
-        <v>1.039</v>
+        <v>1.28</v>
       </c>
       <c r="D433" s="0" t="n">
-        <v>89.93208300000001</v>
+        <v>104</v>
       </c>
       <c r="E433" s="0" t="inlineStr">
         <is>
@@ -23292,7 +23292,7 @@
         <v>0</v>
       </c>
       <c r="J433" s="0" t="n">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="K433" s="0" t="n">
         <v>1</v>
@@ -23318,10 +23318,10 @@
         <v>3608099</v>
       </c>
       <c r="C434" s="0" t="n">
-        <v>1.039</v>
+        <v>1.28</v>
       </c>
       <c r="D434" s="0" t="n">
-        <v>89.93208300000001</v>
+        <v>104</v>
       </c>
       <c r="E434" s="0" t="inlineStr">
         <is>
@@ -23343,7 +23343,7 @@
         <v>0</v>
       </c>
       <c r="J434" s="0" t="n">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="K434" s="0" t="n">
         <v>1</v>
@@ -23369,10 +23369,10 @@
         <v>3610019</v>
       </c>
       <c r="C435" s="0" t="n">
-        <v>1.0405</v>
+        <v>1.4</v>
       </c>
       <c r="D435" s="0" t="n">
-        <v>90.30155600000001</v>
+        <v>116</v>
       </c>
       <c r="E435" s="0" t="inlineStr">
         <is>
@@ -23394,7 +23394,7 @@
         <v>0</v>
       </c>
       <c r="J435" s="0" t="n">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="K435" s="0" t="n">
         <v>1</v>
@@ -23420,10 +23420,10 @@
         <v>3610091</v>
       </c>
       <c r="C436" s="0" t="n">
-        <v>1.0405</v>
+        <v>1.4</v>
       </c>
       <c r="D436" s="0" t="n">
-        <v>90.30155600000001</v>
+        <v>116</v>
       </c>
       <c r="E436" s="0" t="inlineStr">
         <is>
@@ -23445,7 +23445,7 @@
         <v>0</v>
       </c>
       <c r="J436" s="0" t="n">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="K436" s="0" t="n">
         <v>1</v>
@@ -23471,10 +23471,10 @@
         <v>3610099</v>
       </c>
       <c r="C437" s="0" t="n">
-        <v>1.0405</v>
+        <v>1.4</v>
       </c>
       <c r="D437" s="0" t="n">
-        <v>90.30155600000001</v>
+        <v>116</v>
       </c>
       <c r="E437" s="0" t="inlineStr">
         <is>
@@ -23496,7 +23496,7 @@
         <v>0</v>
       </c>
       <c r="J437" s="0" t="n">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="K437" s="0" t="n">
         <v>1</v>
@@ -23522,10 +23522,10 @@
         <v>3610107</v>
       </c>
       <c r="C438" s="0" t="n">
-        <v>1.0405</v>
+        <v>1.4</v>
       </c>
       <c r="D438" s="0" t="n">
-        <v>90.30155600000001</v>
+        <v>116</v>
       </c>
       <c r="E438" s="0" t="inlineStr">
         <is>
@@ -23547,7 +23547,7 @@
         <v>0</v>
       </c>
       <c r="J438" s="0" t="n">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="K438" s="0" t="n">
         <v>1</v>
@@ -23573,10 +23573,10 @@
         <v>3610115</v>
       </c>
       <c r="C439" s="0" t="n">
-        <v>1.0405</v>
+        <v>1.4</v>
       </c>
       <c r="D439" s="0" t="n">
-        <v>90.30155600000001</v>
+        <v>116</v>
       </c>
       <c r="E439" s="0" t="inlineStr">
         <is>
@@ -23598,7 +23598,7 @@
         <v>0</v>
       </c>
       <c r="J439" s="0" t="n">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="K439" s="0" t="n">
         <v>1</v>
@@ -23624,10 +23624,10 @@
         <v>3612019</v>
       </c>
       <c r="C440" s="0" t="n">
-        <v>1.042</v>
+        <v>1.2</v>
       </c>
       <c r="D440" s="0" t="n">
-        <v>88.48792299999999</v>
+        <v>102</v>
       </c>
       <c r="E440" s="0" t="inlineStr">
         <is>
@@ -23649,7 +23649,7 @@
         <v>0</v>
       </c>
       <c r="J440" s="0" t="n">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="K440" s="0" t="n">
         <v>1</v>
@@ -23675,10 +23675,10 @@
         <v>3612099</v>
       </c>
       <c r="C441" s="0" t="n">
-        <v>1.042</v>
+        <v>1.2</v>
       </c>
       <c r="D441" s="0" t="n">
-        <v>88.48792299999999</v>
+        <v>102</v>
       </c>
       <c r="E441" s="0" t="inlineStr">
         <is>
@@ -23700,7 +23700,7 @@
         <v>0</v>
       </c>
       <c r="J441" s="0" t="n">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="K441" s="0" t="n">
         <v>1</v>
@@ -23726,10 +23726,10 @@
         <v>3614019</v>
       </c>
       <c r="C442" s="0" t="n">
-        <v>1.0435</v>
+        <v>1.28</v>
       </c>
       <c r="D442" s="0" t="n">
-        <v>90.124674</v>
+        <v>112</v>
       </c>
       <c r="E442" s="0" t="inlineStr">
         <is>
@@ -23751,7 +23751,7 @@
         <v>0</v>
       </c>
       <c r="J442" s="0" t="n">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="K442" s="0" t="n">
         <v>1</v>
@@ -23777,10 +23777,10 @@
         <v>3614099</v>
       </c>
       <c r="C443" s="0" t="n">
-        <v>1.0435</v>
+        <v>1.28</v>
       </c>
       <c r="D443" s="0" t="n">
-        <v>90.124674</v>
+        <v>112</v>
       </c>
       <c r="E443" s="0" t="inlineStr">
         <is>
@@ -23802,7 +23802,7 @@
         <v>0</v>
       </c>
       <c r="J443" s="0" t="n">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="K443" s="0" t="n">
         <v>1</v>
@@ -23828,10 +23828,10 @@
         <v>3616019</v>
       </c>
       <c r="C444" s="0" t="n">
-        <v>1.045</v>
+        <v>1.22</v>
       </c>
       <c r="D444" s="0" t="n">
-        <v>100.064648</v>
+        <v>116</v>
       </c>
       <c r="E444" s="0" t="inlineStr">
         <is>
@@ -23853,7 +23853,7 @@
         <v>0</v>
       </c>
       <c r="J444" s="0" t="n">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="K444" s="0" t="n">
         <v>1</v>
@@ -23879,10 +23879,10 @@
         <v>3616099</v>
       </c>
       <c r="C445" s="0" t="n">
-        <v>1.045</v>
+        <v>1.22</v>
       </c>
       <c r="D445" s="0" t="n">
-        <v>100.064648</v>
+        <v>116</v>
       </c>
       <c r="E445" s="0" t="inlineStr">
         <is>
@@ -23904,7 +23904,7 @@
         <v>0</v>
       </c>
       <c r="J445" s="0" t="n">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="K445" s="0" t="n">
         <v>1</v>
@@ -23930,10 +23930,10 @@
         <v>3618019</v>
       </c>
       <c r="C446" s="0" t="n">
-        <v>1.0465</v>
+        <v>1.12</v>
       </c>
       <c r="D446" s="0" t="n">
-        <v>158.344219</v>
+        <v>148</v>
       </c>
       <c r="E446" s="0" t="inlineStr">
         <is>
@@ -23955,7 +23955,7 @@
         <v>0</v>
       </c>
       <c r="J446" s="0" t="n">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="K446" s="0" t="n">
         <v>1</v>
@@ -23981,10 +23981,10 @@
         <v>3618099</v>
       </c>
       <c r="C447" s="0" t="n">
-        <v>1.0465</v>
+        <v>1.12</v>
       </c>
       <c r="D447" s="0" t="n">
-        <v>158.344219</v>
+        <v>148</v>
       </c>
       <c r="E447" s="0" t="inlineStr">
         <is>
@@ -24006,7 +24006,7 @@
         <v>0</v>
       </c>
       <c r="J447" s="0" t="n">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="K447" s="0" t="n">
         <v>1</v>
@@ -24032,10 +24032,10 @@
         <v>10048590</v>
       </c>
       <c r="C448" s="0" t="n">
-        <v>1.048</v>
+        <v>1.24</v>
       </c>
       <c r="D448" s="0" t="n">
-        <v>158.942414</v>
+        <v>160</v>
       </c>
       <c r="E448" s="0" t="inlineStr">
         <is>
@@ -24057,7 +24057,7 @@
         <v>0</v>
       </c>
       <c r="J448" s="0" t="n">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="K448" s="0" t="n">
         <v>1</v>
@@ -24083,10 +24083,10 @@
         <v>10048591</v>
       </c>
       <c r="C449" s="0" t="n">
-        <v>1.048</v>
+        <v>1.24</v>
       </c>
       <c r="D449" s="0" t="n">
-        <v>158.942414</v>
+        <v>160</v>
       </c>
       <c r="E449" s="0" t="inlineStr">
         <is>
@@ -24108,7 +24108,7 @@
         <v>0</v>
       </c>
       <c r="J449" s="0" t="n">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="K449" s="0" t="n">
         <v>1</v>
@@ -24134,10 +24134,10 @@
         <v>10048592</v>
       </c>
       <c r="C450" s="0" t="n">
-        <v>1.0495</v>
+        <v>1.3</v>
       </c>
       <c r="D450" s="0" t="n">
-        <v>156.709986</v>
+        <v>172</v>
       </c>
       <c r="E450" s="0" t="inlineStr">
         <is>
@@ -24159,7 +24159,7 @@
         <v>0</v>
       </c>
       <c r="J450" s="0" t="n">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="K450" s="0" t="n">
         <v>1</v>
@@ -24185,10 +24185,10 @@
         <v>10048593</v>
       </c>
       <c r="C451" s="0" t="n">
-        <v>1.0495</v>
+        <v>1.3</v>
       </c>
       <c r="D451" s="0" t="n">
-        <v>156.709986</v>
+        <v>172</v>
       </c>
       <c r="E451" s="0" t="inlineStr">
         <is>
@@ -24210,7 +24210,7 @@
         <v>0</v>
       </c>
       <c r="J451" s="0" t="n">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="K451" s="0" t="n">
         <v>1</v>
@@ -24236,10 +24236,10 @@
         <v>10048594</v>
       </c>
       <c r="C452" s="0" t="n">
-        <v>1.051</v>
+        <v>1.42</v>
       </c>
       <c r="D452" s="0" t="n">
-        <v>154.129904</v>
+        <v>196</v>
       </c>
       <c r="E452" s="0" t="inlineStr">
         <is>
@@ -24261,7 +24261,7 @@
         <v>0</v>
       </c>
       <c r="J452" s="0" t="n">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="K452" s="0" t="n">
         <v>1</v>
@@ -24287,10 +24287,10 @@
         <v>10048595</v>
       </c>
       <c r="C453" s="0" t="n">
-        <v>1.051</v>
+        <v>1.42</v>
       </c>
       <c r="D453" s="0" t="n">
-        <v>154.129904</v>
+        <v>196</v>
       </c>
       <c r="E453" s="0" t="inlineStr">
         <is>
@@ -24312,7 +24312,7 @@
         <v>0</v>
       </c>
       <c r="J453" s="0" t="n">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="K453" s="0" t="n">
         <v>1</v>
@@ -24338,10 +24338,10 @@
         <v>10048596</v>
       </c>
       <c r="C454" s="0" t="n">
-        <v>1.0525</v>
+        <v>1.2</v>
       </c>
       <c r="D454" s="0" t="n">
-        <v>158.922889</v>
+        <v>180</v>
       </c>
       <c r="E454" s="0" t="inlineStr">
         <is>
@@ -24363,7 +24363,7 @@
         <v>0</v>
       </c>
       <c r="J454" s="0" t="n">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="K454" s="0" t="n">
         <v>1</v>
@@ -24389,10 +24389,10 @@
         <v>10048597</v>
       </c>
       <c r="C455" s="0" t="n">
-        <v>1.0525</v>
+        <v>1.2</v>
       </c>
       <c r="D455" s="0" t="n">
-        <v>158.922889</v>
+        <v>180</v>
       </c>
       <c r="E455" s="0" t="inlineStr">
         <is>
@@ -24414,7 +24414,7 @@
         <v>0</v>
       </c>
       <c r="J455" s="0" t="n">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="K455" s="0" t="n">
         <v>1</v>
@@ -24440,10 +24440,10 @@
         <v>10048598</v>
       </c>
       <c r="C456" s="0" t="n">
-        <v>1.054</v>
+        <v>1.34</v>
       </c>
       <c r="D456" s="0" t="n">
-        <v>301.480436</v>
+        <v>286</v>
       </c>
       <c r="E456" s="0" t="inlineStr">
         <is>
@@ -24465,7 +24465,7 @@
         <v>0</v>
       </c>
       <c r="J456" s="0" t="n">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="K456" s="0" t="n">
         <v>1</v>
@@ -24491,10 +24491,10 @@
         <v>10048599</v>
       </c>
       <c r="C457" s="0" t="n">
-        <v>1.054</v>
+        <v>1.34</v>
       </c>
       <c r="D457" s="0" t="n">
-        <v>301.480436</v>
+        <v>286</v>
       </c>
       <c r="E457" s="0" t="inlineStr">
         <is>
@@ -24516,7 +24516,7 @@
         <v>0</v>
       </c>
       <c r="J457" s="0" t="n">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="K457" s="0" t="n">
         <v>1</v>

--- a/Luban/Config/Datas/Levels/L13/EnemyData.xlsx
+++ b/Luban/Config/Datas/Levels/L13/EnemyData.xlsx
@@ -1,14 +1,14 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
-<workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
+<workbook xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <workbookPr/>
   <bookViews>
     <workbookView visibility="visible" minimized="0" showHorizontalScroll="1" showVerticalScroll="1" showSheetTabs="1" windowWidth="25920" windowHeight="12900" tabRatio="600" firstSheet="0" activeTab="0" autoFilterDateGrouping="1"/>
   </bookViews>
   <sheets>
-    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Sheet1" sheetId="1" state="visible" r:id="rId1"/>
-    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Sheet2" sheetId="2" state="visible" r:id="rId2"/>
-    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Sheet3" sheetId="3" state="visible" r:id="rId3"/>
+    <sheet name="Sheet1" sheetId="1" state="visible" r:id="rId1"/>
+    <sheet name="Sheet2" sheetId="2" state="visible" r:id="rId2"/>
+    <sheet name="Sheet3" sheetId="3" state="visible" r:id="rId3"/>
   </sheets>
   <definedNames/>
   <calcPr calcId="191029" fullCalcOnLoad="1"/>
@@ -1122,7 +1122,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:P457"/>
+  <dimension ref="A1:Q457"/>
   <sheetFormatPr baseColWidth="8" defaultColWidth="9" defaultRowHeight="14.4"/>
   <cols>
     <col width="9" customWidth="1" style="2" min="1" max="1"/>
@@ -1140,6 +1140,7 @@
     <col width="9" customWidth="1" style="2" min="13" max="14"/>
     <col width="17.3333333333333" customWidth="1" style="2" min="15" max="15"/>
     <col width="9" customWidth="1" style="2" min="16" max="16384"/>
+    <col width="10" customWidth="1" style="2" min="17" max="17"/>
   </cols>
   <sheetData>
     <row r="1">
@@ -1223,6 +1224,11 @@
           <t>desc</t>
         </is>
       </c>
+      <c r="Q1" s="0" t="inlineStr">
+        <is>
+          <t>levelId</t>
+        </is>
+      </c>
     </row>
     <row r="2">
       <c r="A2" s="0" t="inlineStr">
@@ -1272,37 +1278,42 @@
       </c>
       <c r="J2" s="0" t="inlineStr">
         <is>
+          <t>float</t>
+        </is>
+      </c>
+      <c r="K2" s="0" t="inlineStr">
+        <is>
           <t>int</t>
         </is>
       </c>
-      <c r="K2" s="0" t="inlineStr">
+      <c r="L2" s="0" t="inlineStr">
+        <is>
+          <t>float</t>
+        </is>
+      </c>
+      <c r="M2" s="0" t="inlineStr">
+        <is>
+          <t>float</t>
+        </is>
+      </c>
+      <c r="N2" s="0" t="inlineStr">
         <is>
           <t>int</t>
         </is>
       </c>
-      <c r="L2" s="0" t="inlineStr">
-        <is>
-          <t>float</t>
-        </is>
-      </c>
-      <c r="M2" s="0" t="inlineStr">
-        <is>
-          <t>float</t>
-        </is>
-      </c>
-      <c r="N2" s="0" t="inlineStr">
+      <c r="O2" s="0" t="inlineStr">
+        <is>
+          <t>string</t>
+        </is>
+      </c>
+      <c r="P2" s="0" t="inlineStr">
+        <is>
+          <t>string</t>
+        </is>
+      </c>
+      <c r="Q2" s="0" t="inlineStr">
         <is>
           <t>int</t>
-        </is>
-      </c>
-      <c r="O2" s="0" t="inlineStr">
-        <is>
-          <t>string</t>
-        </is>
-      </c>
-      <c r="P2" s="0" t="inlineStr">
-        <is>
-          <t>string</t>
         </is>
       </c>
     </row>
@@ -1380,6 +1391,11 @@
       <c r="P3" s="0" t="inlineStr">
         <is>
           <t>备注</t>
+        </is>
+      </c>
+      <c r="Q3" s="0" t="inlineStr">
+        <is>
+          <t>所属关卡 id（本表每关独立一份，2026-10-30 拆分）</t>
         </is>
       </c>
     </row>
@@ -1433,6 +1449,9 @@
           <t>Balance variant; canonical=17; role=normal; profile=D04; level=13; wave=1</t>
         </is>
       </c>
+      <c r="Q4" s="0" t="n">
+        <v>13</v>
+      </c>
     </row>
     <row r="5">
       <c r="B5" s="0" t="n">
@@ -1484,6 +1503,9 @@
           <t>Balance variant; canonical=18; role=normal; profile=D04; level=13; wave=1</t>
         </is>
       </c>
+      <c r="Q5" s="0" t="n">
+        <v>13</v>
+      </c>
     </row>
     <row r="6">
       <c r="B6" s="0" t="n">
@@ -1535,6 +1557,9 @@
           <t>Balance variant; canonical=17; role=normal; profile=D04; level=13; wave=2</t>
         </is>
       </c>
+      <c r="Q6" s="0" t="n">
+        <v>13</v>
+      </c>
     </row>
     <row r="7" customFormat="1" s="1">
       <c r="B7" s="0" t="n">
@@ -1586,6 +1611,9 @@
           <t>Balance variant; canonical=18; role=normal; profile=D04; level=13; wave=2</t>
         </is>
       </c>
+      <c r="Q7" s="0" t="n">
+        <v>13</v>
+      </c>
     </row>
     <row r="8" customFormat="1" s="1">
       <c r="B8" s="0" t="n">
@@ -1637,6 +1665,9 @@
           <t>Balance variant; canonical=17; role=normal; profile=D04; level=13; wave=3</t>
         </is>
       </c>
+      <c r="Q8" s="0" t="n">
+        <v>13</v>
+      </c>
     </row>
     <row r="9" customFormat="1" s="1">
       <c r="B9" s="0" t="n">
@@ -1688,6 +1719,9 @@
           <t>Balance variant; canonical=18; role=normal; profile=D04; level=13; wave=3</t>
         </is>
       </c>
+      <c r="Q9" s="0" t="n">
+        <v>13</v>
+      </c>
     </row>
     <row r="10" customFormat="1" s="1">
       <c r="B10" s="0" t="n">
@@ -1739,6 +1773,9 @@
           <t>Balance variant; canonical=84; role=swarm; profile=D04; level=13; wave=3</t>
         </is>
       </c>
+      <c r="Q10" s="0" t="n">
+        <v>13</v>
+      </c>
     </row>
     <row r="11" customFormat="1" s="1">
       <c r="B11" s="0" t="n">
@@ -1790,6 +1827,9 @@
           <t>Balance variant; canonical=17; role=normal; profile=D04; level=13; wave=4</t>
         </is>
       </c>
+      <c r="Q11" s="0" t="n">
+        <v>13</v>
+      </c>
     </row>
     <row r="12">
       <c r="B12" s="0" t="n">
@@ -1841,6 +1881,9 @@
           <t>Balance variant; canonical=18; role=normal; profile=D04; level=13; wave=4</t>
         </is>
       </c>
+      <c r="Q12" s="0" t="n">
+        <v>13</v>
+      </c>
     </row>
     <row r="13">
       <c r="B13" s="0" t="n">
@@ -1892,6 +1935,9 @@
           <t>Balance variant; canonical=84; role=swarm; profile=D04; level=13; wave=4</t>
         </is>
       </c>
+      <c r="Q13" s="0" t="n">
+        <v>13</v>
+      </c>
     </row>
     <row r="14">
       <c r="B14" s="0" t="n">
@@ -1943,6 +1989,9 @@
           <t>Balance variant; canonical=17; role=normal; profile=D04; level=13; wave=5</t>
         </is>
       </c>
+      <c r="Q14" s="0" t="n">
+        <v>13</v>
+      </c>
     </row>
     <row r="15">
       <c r="B15" s="0" t="n">
@@ -1994,6 +2043,9 @@
           <t>Balance variant; canonical=18; role=normal; profile=D04; level=13; wave=5</t>
         </is>
       </c>
+      <c r="Q15" s="0" t="n">
+        <v>13</v>
+      </c>
     </row>
     <row r="16">
       <c r="B16" s="0" t="n">
@@ -2045,6 +2097,9 @@
           <t>Balance variant; canonical=83; role=medium; profile=D04; level=13; wave=5</t>
         </is>
       </c>
+      <c r="Q16" s="0" t="n">
+        <v>13</v>
+      </c>
     </row>
     <row r="17">
       <c r="B17" s="0" t="n">
@@ -2096,6 +2151,9 @@
           <t>Balance variant; canonical=84; role=swarm; profile=D04; level=13; wave=5</t>
         </is>
       </c>
+      <c r="Q17" s="0" t="n">
+        <v>13</v>
+      </c>
     </row>
     <row r="18">
       <c r="B18" s="0" t="n">
@@ -2147,6 +2205,9 @@
           <t>Balance variant; canonical=108; role=medium; profile=D04; level=13; wave=5</t>
         </is>
       </c>
+      <c r="Q18" s="0" t="n">
+        <v>13</v>
+      </c>
     </row>
     <row r="19">
       <c r="B19" s="0" t="n">
@@ -2198,6 +2259,9 @@
           <t>Balance variant; canonical=123; role=medium; profile=D04; level=13; wave=5</t>
         </is>
       </c>
+      <c r="Q19" s="0" t="n">
+        <v>13</v>
+      </c>
     </row>
     <row r="20">
       <c r="B20" s="0" t="n">
@@ -2249,6 +2313,9 @@
           <t>Balance variant; canonical=11; role=air; profile=D04; level=13; wave=6</t>
         </is>
       </c>
+      <c r="Q20" s="0" t="n">
+        <v>13</v>
+      </c>
     </row>
     <row r="21">
       <c r="B21" s="0" t="n">
@@ -2300,6 +2367,9 @@
           <t>Balance variant; canonical=13; role=air; profile=D04; level=13; wave=6</t>
         </is>
       </c>
+      <c r="Q21" s="0" t="n">
+        <v>13</v>
+      </c>
     </row>
     <row r="22">
       <c r="B22" s="0" t="n">
@@ -2351,6 +2421,9 @@
           <t>Balance variant; canonical=17; role=normal; profile=D04; level=13; wave=6</t>
         </is>
       </c>
+      <c r="Q22" s="0" t="n">
+        <v>13</v>
+      </c>
     </row>
     <row r="23">
       <c r="B23" s="0" t="n">
@@ -2402,6 +2475,9 @@
           <t>Balance variant; canonical=18; role=normal; profile=D04; level=13; wave=6</t>
         </is>
       </c>
+      <c r="Q23" s="0" t="n">
+        <v>13</v>
+      </c>
     </row>
     <row r="24">
       <c r="B24" s="0" t="n">
@@ -2453,6 +2529,9 @@
           <t>Balance variant; canonical=30; role=fast; profile=D04; level=13; wave=6</t>
         </is>
       </c>
+      <c r="Q24" s="0" t="n">
+        <v>13</v>
+      </c>
     </row>
     <row r="25">
       <c r="B25" s="0" t="n">
@@ -2504,6 +2583,9 @@
           <t>Balance variant; canonical=64; role=fast; profile=D04; level=13; wave=6</t>
         </is>
       </c>
+      <c r="Q25" s="0" t="n">
+        <v>13</v>
+      </c>
     </row>
     <row r="26">
       <c r="B26" s="0" t="n">
@@ -2555,6 +2637,9 @@
           <t>Balance variant; canonical=83; role=medium; profile=D04; level=13; wave=6</t>
         </is>
       </c>
+      <c r="Q26" s="0" t="n">
+        <v>13</v>
+      </c>
     </row>
     <row r="27">
       <c r="B27" s="0" t="n">
@@ -2606,6 +2691,9 @@
           <t>Balance variant; canonical=84; role=swarm; profile=D04; level=13; wave=6</t>
         </is>
       </c>
+      <c r="Q27" s="0" t="n">
+        <v>13</v>
+      </c>
     </row>
     <row r="28">
       <c r="B28" s="0" t="n">
@@ -2657,6 +2745,9 @@
           <t>Balance variant; canonical=98; role=fast; profile=D04; level=13; wave=6</t>
         </is>
       </c>
+      <c r="Q28" s="0" t="n">
+        <v>13</v>
+      </c>
     </row>
     <row r="29">
       <c r="B29" s="0" t="n">
@@ -2708,6 +2799,9 @@
           <t>Balance variant; canonical=108; role=medium; profile=D04; level=13; wave=6</t>
         </is>
       </c>
+      <c r="Q29" s="0" t="n">
+        <v>13</v>
+      </c>
     </row>
     <row r="30">
       <c r="B30" s="0" t="n">
@@ -2759,6 +2853,9 @@
           <t>Balance variant; canonical=123; role=medium; profile=D04; level=13; wave=6</t>
         </is>
       </c>
+      <c r="Q30" s="0" t="n">
+        <v>13</v>
+      </c>
     </row>
     <row r="31">
       <c r="B31" s="0" t="n">
@@ -2810,6 +2907,9 @@
           <t>Balance variant; canonical=11; role=air; profile=D04; level=13; wave=7</t>
         </is>
       </c>
+      <c r="Q31" s="0" t="n">
+        <v>13</v>
+      </c>
     </row>
     <row r="32">
       <c r="B32" s="0" t="n">
@@ -2861,6 +2961,9 @@
           <t>Balance variant; canonical=14; role=air; profile=D04; level=13; wave=7</t>
         </is>
       </c>
+      <c r="Q32" s="0" t="n">
+        <v>13</v>
+      </c>
     </row>
     <row r="33">
       <c r="B33" s="0" t="n">
@@ -2912,6 +3015,9 @@
           <t>Balance variant; canonical=17; role=normal; profile=D04; level=13; wave=7</t>
         </is>
       </c>
+      <c r="Q33" s="0" t="n">
+        <v>13</v>
+      </c>
     </row>
     <row r="34">
       <c r="B34" s="0" t="n">
@@ -2963,6 +3069,9 @@
           <t>Balance variant; canonical=18; role=normal; profile=D04; level=13; wave=7</t>
         </is>
       </c>
+      <c r="Q34" s="0" t="n">
+        <v>13</v>
+      </c>
     </row>
     <row r="35">
       <c r="B35" s="0" t="n">
@@ -3014,6 +3123,9 @@
           <t>Balance variant; canonical=30; role=fast; profile=D04; level=13; wave=7</t>
         </is>
       </c>
+      <c r="Q35" s="0" t="n">
+        <v>13</v>
+      </c>
     </row>
     <row r="36">
       <c r="B36" s="0" t="n">
@@ -3065,6 +3177,9 @@
           <t>Balance variant; canonical=58; role=fast; profile=D04; level=13; wave=7</t>
         </is>
       </c>
+      <c r="Q36" s="0" t="n">
+        <v>13</v>
+      </c>
     </row>
     <row r="37">
       <c r="B37" s="0" t="n">
@@ -3116,6 +3231,9 @@
           <t>Balance variant; canonical=83; role=medium; profile=D04; level=13; wave=7</t>
         </is>
       </c>
+      <c r="Q37" s="0" t="n">
+        <v>13</v>
+      </c>
     </row>
     <row r="38">
       <c r="B38" s="0" t="n">
@@ -3167,6 +3285,9 @@
           <t>Balance variant; canonical=84; role=swarm; profile=D04; level=13; wave=7</t>
         </is>
       </c>
+      <c r="Q38" s="0" t="n">
+        <v>13</v>
+      </c>
     </row>
     <row r="39">
       <c r="B39" s="0" t="n">
@@ -3218,6 +3339,9 @@
           <t>Balance variant; canonical=98; role=fast; profile=D04; level=13; wave=7</t>
         </is>
       </c>
+      <c r="Q39" s="0" t="n">
+        <v>13</v>
+      </c>
     </row>
     <row r="40">
       <c r="B40" s="0" t="n">
@@ -3269,6 +3393,9 @@
           <t>Balance variant; canonical=108; role=medium; profile=D04; level=13; wave=7</t>
         </is>
       </c>
+      <c r="Q40" s="0" t="n">
+        <v>13</v>
+      </c>
     </row>
     <row r="41">
       <c r="B41" s="0" t="n">
@@ -3320,6 +3447,9 @@
           <t>Balance variant; canonical=123; role=medium; profile=D04; level=13; wave=7</t>
         </is>
       </c>
+      <c r="Q41" s="0" t="n">
+        <v>13</v>
+      </c>
     </row>
     <row r="42">
       <c r="B42" s="0" t="n">
@@ -3371,6 +3501,9 @@
           <t>Balance variant; canonical=13; role=air; profile=D04; level=13; wave=8</t>
         </is>
       </c>
+      <c r="Q42" s="0" t="n">
+        <v>13</v>
+      </c>
     </row>
     <row r="43">
       <c r="B43" s="0" t="n">
@@ -3422,6 +3555,9 @@
           <t>Balance variant; canonical=14; role=air; profile=D04; level=13; wave=8</t>
         </is>
       </c>
+      <c r="Q43" s="0" t="n">
+        <v>13</v>
+      </c>
     </row>
     <row r="44">
       <c r="B44" s="0" t="n">
@@ -3473,6 +3609,9 @@
           <t>Balance variant; canonical=17; role=normal; profile=D04; level=13; wave=8</t>
         </is>
       </c>
+      <c r="Q44" s="0" t="n">
+        <v>13</v>
+      </c>
     </row>
     <row r="45">
       <c r="B45" s="0" t="n">
@@ -3524,6 +3663,9 @@
           <t>Balance variant; canonical=18; role=normal; profile=D04; level=13; wave=8</t>
         </is>
       </c>
+      <c r="Q45" s="0" t="n">
+        <v>13</v>
+      </c>
     </row>
     <row r="46">
       <c r="B46" s="0" t="n">
@@ -3575,6 +3717,9 @@
           <t>Balance variant; canonical=58; role=fast; profile=D04; level=13; wave=8</t>
         </is>
       </c>
+      <c r="Q46" s="0" t="n">
+        <v>13</v>
+      </c>
     </row>
     <row r="47">
       <c r="B47" s="0" t="n">
@@ -3626,6 +3771,9 @@
           <t>Balance variant; canonical=64; role=fast; profile=D04; level=13; wave=8</t>
         </is>
       </c>
+      <c r="Q47" s="0" t="n">
+        <v>13</v>
+      </c>
     </row>
     <row r="48">
       <c r="B48" s="0" t="n">
@@ -3677,6 +3825,9 @@
           <t>Balance variant; canonical=83; role=medium; profile=D04; level=13; wave=8</t>
         </is>
       </c>
+      <c r="Q48" s="0" t="n">
+        <v>13</v>
+      </c>
     </row>
     <row r="49">
       <c r="B49" s="0" t="n">
@@ -3728,6 +3879,9 @@
           <t>Balance variant; canonical=84; role=swarm; profile=D04; level=13; wave=8</t>
         </is>
       </c>
+      <c r="Q49" s="0" t="n">
+        <v>13</v>
+      </c>
     </row>
     <row r="50">
       <c r="B50" s="0" t="n">
@@ -3779,6 +3933,9 @@
           <t>Balance variant; canonical=98; role=fast; profile=D04; level=13; wave=8</t>
         </is>
       </c>
+      <c r="Q50" s="0" t="n">
+        <v>13</v>
+      </c>
     </row>
     <row r="51">
       <c r="B51" s="0" t="n">
@@ -3830,6 +3987,9 @@
           <t>Balance variant; canonical=108; role=medium; profile=D04; level=13; wave=8</t>
         </is>
       </c>
+      <c r="Q51" s="0" t="n">
+        <v>13</v>
+      </c>
     </row>
     <row r="52">
       <c r="B52" s="0" t="n">
@@ -3881,6 +4041,9 @@
           <t>Balance variant; canonical=123; role=medium; profile=D04; level=13; wave=8</t>
         </is>
       </c>
+      <c r="Q52" s="0" t="n">
+        <v>13</v>
+      </c>
     </row>
     <row r="53">
       <c r="B53" s="0" t="n">
@@ -3932,6 +4095,9 @@
           <t>Balance variant; canonical=11; role=air; profile=D04; level=13; wave=9</t>
         </is>
       </c>
+      <c r="Q53" s="0" t="n">
+        <v>13</v>
+      </c>
     </row>
     <row r="54">
       <c r="B54" s="0" t="n">
@@ -3983,6 +4149,9 @@
           <t>Balance variant; canonical=13; role=air; profile=D04; level=13; wave=9</t>
         </is>
       </c>
+      <c r="Q54" s="0" t="n">
+        <v>13</v>
+      </c>
     </row>
     <row r="55">
       <c r="B55" s="0" t="n">
@@ -4034,6 +4203,9 @@
           <t>Balance variant; canonical=17; role=normal; profile=D04; level=13; wave=9</t>
         </is>
       </c>
+      <c r="Q55" s="0" t="n">
+        <v>13</v>
+      </c>
     </row>
     <row r="56">
       <c r="B56" s="0" t="n">
@@ -4085,6 +4257,9 @@
           <t>Balance variant; canonical=18; role=normal; profile=D04; level=13; wave=9</t>
         </is>
       </c>
+      <c r="Q56" s="0" t="n">
+        <v>13</v>
+      </c>
     </row>
     <row r="57">
       <c r="B57" s="0" t="n">
@@ -4136,6 +4311,9 @@
           <t>Balance variant; canonical=30; role=fast; profile=D04; level=13; wave=9</t>
         </is>
       </c>
+      <c r="Q57" s="0" t="n">
+        <v>13</v>
+      </c>
     </row>
     <row r="58">
       <c r="B58" s="0" t="n">
@@ -4187,6 +4365,9 @@
           <t>Balance variant; canonical=58; role=fast; profile=D04; level=13; wave=9</t>
         </is>
       </c>
+      <c r="Q58" s="0" t="n">
+        <v>13</v>
+      </c>
     </row>
     <row r="59">
       <c r="B59" s="0" t="n">
@@ -4238,6 +4419,9 @@
           <t>Balance variant; canonical=64; role=fast; profile=D04; level=13; wave=9</t>
         </is>
       </c>
+      <c r="Q59" s="0" t="n">
+        <v>13</v>
+      </c>
     </row>
     <row r="60">
       <c r="B60" s="0" t="n">
@@ -4289,6 +4473,9 @@
           <t>Balance variant; canonical=83; role=medium; profile=D04; level=13; wave=9</t>
         </is>
       </c>
+      <c r="Q60" s="0" t="n">
+        <v>13</v>
+      </c>
     </row>
     <row r="61">
       <c r="B61" s="0" t="n">
@@ -4340,6 +4527,9 @@
           <t>Balance variant; canonical=84; role=swarm; profile=D04; level=13; wave=9</t>
         </is>
       </c>
+      <c r="Q61" s="0" t="n">
+        <v>13</v>
+      </c>
     </row>
     <row r="62">
       <c r="B62" s="0" t="n">
@@ -4391,6 +4581,9 @@
           <t>Balance variant; canonical=108; role=medium; profile=D04; level=13; wave=9</t>
         </is>
       </c>
+      <c r="Q62" s="0" t="n">
+        <v>13</v>
+      </c>
     </row>
     <row r="63">
       <c r="B63" s="0" t="n">
@@ -4442,6 +4635,9 @@
           <t>Balance variant; canonical=123; role=medium; profile=D04; level=13; wave=9</t>
         </is>
       </c>
+      <c r="Q63" s="0" t="n">
+        <v>13</v>
+      </c>
     </row>
     <row r="64">
       <c r="B64" s="0" t="n">
@@ -4493,6 +4689,9 @@
           <t>Balance variant; canonical=11; role=air; profile=D04; level=13; wave=10</t>
         </is>
       </c>
+      <c r="Q64" s="0" t="n">
+        <v>13</v>
+      </c>
     </row>
     <row r="65">
       <c r="B65" s="0" t="n">
@@ -4544,6 +4743,9 @@
           <t>Balance variant; canonical=14; role=air; profile=D04; level=13; wave=10</t>
         </is>
       </c>
+      <c r="Q65" s="0" t="n">
+        <v>13</v>
+      </c>
     </row>
     <row r="66">
       <c r="B66" s="0" t="n">
@@ -4595,6 +4797,9 @@
           <t>Balance variant; canonical=17; role=normal; profile=D04; level=13; wave=10</t>
         </is>
       </c>
+      <c r="Q66" s="0" t="n">
+        <v>13</v>
+      </c>
     </row>
     <row r="67">
       <c r="B67" s="0" t="n">
@@ -4646,6 +4851,9 @@
           <t>Balance variant; canonical=18; role=normal; profile=D04; level=13; wave=10</t>
         </is>
       </c>
+      <c r="Q67" s="0" t="n">
+        <v>13</v>
+      </c>
     </row>
     <row r="68">
       <c r="B68" s="0" t="n">
@@ -4697,6 +4905,9 @@
           <t>Balance variant; canonical=30; role=fast; profile=D04; level=13; wave=10</t>
         </is>
       </c>
+      <c r="Q68" s="0" t="n">
+        <v>13</v>
+      </c>
     </row>
     <row r="69">
       <c r="B69" s="0" t="n">
@@ -4748,6 +4959,9 @@
           <t>Balance variant; canonical=64; role=fast; profile=D04; level=13; wave=10</t>
         </is>
       </c>
+      <c r="Q69" s="0" t="n">
+        <v>13</v>
+      </c>
     </row>
     <row r="70">
       <c r="B70" s="0" t="n">
@@ -4799,6 +5013,9 @@
           <t>Balance variant; canonical=83; role=medium; profile=D04; level=13; wave=10</t>
         </is>
       </c>
+      <c r="Q70" s="0" t="n">
+        <v>13</v>
+      </c>
     </row>
     <row r="71">
       <c r="B71" s="0" t="n">
@@ -4850,6 +5067,9 @@
           <t>Balance variant; canonical=84; role=swarm; profile=D04; level=13; wave=10</t>
         </is>
       </c>
+      <c r="Q71" s="0" t="n">
+        <v>13</v>
+      </c>
     </row>
     <row r="72">
       <c r="B72" s="0" t="n">
@@ -4901,6 +5121,9 @@
           <t>Balance variant; canonical=98; role=fast; profile=D04; level=13; wave=10</t>
         </is>
       </c>
+      <c r="Q72" s="0" t="n">
+        <v>13</v>
+      </c>
     </row>
     <row r="73">
       <c r="B73" s="0" t="n">
@@ -4952,6 +5175,9 @@
           <t>Balance variant; canonical=108; role=medium; profile=D04; level=13; wave=10</t>
         </is>
       </c>
+      <c r="Q73" s="0" t="n">
+        <v>13</v>
+      </c>
     </row>
     <row r="74">
       <c r="B74" s="0" t="n">
@@ -5003,6 +5229,9 @@
           <t>Balance variant; canonical=123; role=medium; profile=D04; level=13; wave=10</t>
         </is>
       </c>
+      <c r="Q74" s="0" t="n">
+        <v>13</v>
+      </c>
     </row>
     <row r="75">
       <c r="B75" s="0" t="n">
@@ -5054,6 +5283,9 @@
           <t>Balance variant; canonical=17; role=normal; profile=D04; level=13; wave=11</t>
         </is>
       </c>
+      <c r="Q75" s="0" t="n">
+        <v>13</v>
+      </c>
     </row>
     <row r="76">
       <c r="B76" s="0" t="n">
@@ -5105,6 +5337,9 @@
           <t>Balance variant; canonical=18; role=normal; profile=D04; level=13; wave=11</t>
         </is>
       </c>
+      <c r="Q76" s="0" t="n">
+        <v>13</v>
+      </c>
     </row>
     <row r="77">
       <c r="B77" s="0" t="n">
@@ -5156,6 +5391,9 @@
           <t>Balance variant; canonical=30; role=fast; profile=D04; level=13; wave=11</t>
         </is>
       </c>
+      <c r="Q77" s="0" t="n">
+        <v>13</v>
+      </c>
     </row>
     <row r="78">
       <c r="B78" s="0" t="n">
@@ -5207,6 +5445,9 @@
           <t>Balance variant; canonical=58; role=fast; profile=D04; level=13; wave=11</t>
         </is>
       </c>
+      <c r="Q78" s="0" t="n">
+        <v>13</v>
+      </c>
     </row>
     <row r="79">
       <c r="B79" s="0" t="n">
@@ -5258,6 +5499,9 @@
           <t>Balance variant; canonical=80; role=heavy; profile=D04; level=13; wave=11</t>
         </is>
       </c>
+      <c r="Q79" s="0" t="n">
+        <v>13</v>
+      </c>
     </row>
     <row r="80">
       <c r="B80" s="0" t="n">
@@ -5309,6 +5553,9 @@
           <t>Balance variant; canonical=83; role=medium; profile=D04; level=13; wave=11</t>
         </is>
       </c>
+      <c r="Q80" s="0" t="n">
+        <v>13</v>
+      </c>
     </row>
     <row r="81">
       <c r="B81" s="0" t="n">
@@ -5360,6 +5607,9 @@
           <t>Balance variant; canonical=84; role=swarm; profile=D04; level=13; wave=11</t>
         </is>
       </c>
+      <c r="Q81" s="0" t="n">
+        <v>13</v>
+      </c>
     </row>
     <row r="82">
       <c r="B82" s="0" t="n">
@@ -5411,6 +5661,9 @@
           <t>Balance variant; canonical=86; role=heavy; profile=D04; level=13; wave=11</t>
         </is>
       </c>
+      <c r="Q82" s="0" t="n">
+        <v>13</v>
+      </c>
     </row>
     <row r="83">
       <c r="B83" s="0" t="n">
@@ -5462,6 +5715,9 @@
           <t>Balance variant; canonical=88; role=heavy; profile=D04; level=13; wave=11</t>
         </is>
       </c>
+      <c r="Q83" s="0" t="n">
+        <v>13</v>
+      </c>
     </row>
     <row r="84">
       <c r="B84" s="0" t="n">
@@ -5513,6 +5769,9 @@
           <t>Balance variant; canonical=98; role=fast; profile=D04; level=13; wave=11</t>
         </is>
       </c>
+      <c r="Q84" s="0" t="n">
+        <v>13</v>
+      </c>
     </row>
     <row r="85">
       <c r="B85" s="0" t="n">
@@ -5564,6 +5823,9 @@
           <t>Balance variant; canonical=108; role=medium; profile=D04; level=13; wave=11</t>
         </is>
       </c>
+      <c r="Q85" s="0" t="n">
+        <v>13</v>
+      </c>
     </row>
     <row r="86">
       <c r="B86" s="0" t="n">
@@ -5615,6 +5877,9 @@
           <t>Balance variant; canonical=123; role=medium; profile=D04; level=13; wave=11</t>
         </is>
       </c>
+      <c r="Q86" s="0" t="n">
+        <v>13</v>
+      </c>
     </row>
     <row r="87">
       <c r="B87" s="0" t="n">
@@ -5666,6 +5931,9 @@
           <t>Balance variant; canonical=11; role=air; profile=D04; level=13; wave=12</t>
         </is>
       </c>
+      <c r="Q87" s="0" t="n">
+        <v>13</v>
+      </c>
     </row>
     <row r="88">
       <c r="B88" s="0" t="n">
@@ -5717,6 +5985,9 @@
           <t>Balance variant; canonical=13; role=air; profile=D04; level=13; wave=12</t>
         </is>
       </c>
+      <c r="Q88" s="0" t="n">
+        <v>13</v>
+      </c>
     </row>
     <row r="89">
       <c r="B89" s="0" t="n">
@@ -5768,6 +6039,9 @@
           <t>Balance variant; canonical=14; role=air; profile=D04; level=13; wave=12</t>
         </is>
       </c>
+      <c r="Q89" s="0" t="n">
+        <v>13</v>
+      </c>
     </row>
     <row r="90">
       <c r="B90" s="0" t="n">
@@ -5819,6 +6093,9 @@
           <t>Balance variant; canonical=17; role=normal; profile=D04; level=13; wave=12</t>
         </is>
       </c>
+      <c r="Q90" s="0" t="n">
+        <v>13</v>
+      </c>
     </row>
     <row r="91">
       <c r="B91" s="0" t="n">
@@ -5870,6 +6147,9 @@
           <t>Balance variant; canonical=18; role=normal; profile=D04; level=13; wave=12</t>
         </is>
       </c>
+      <c r="Q91" s="0" t="n">
+        <v>13</v>
+      </c>
     </row>
     <row r="92">
       <c r="B92" s="0" t="n">
@@ -5921,6 +6201,9 @@
           <t>Balance variant; canonical=31; role=heavy; profile=D04; level=13; wave=12</t>
         </is>
       </c>
+      <c r="Q92" s="0" t="n">
+        <v>13</v>
+      </c>
     </row>
     <row r="93">
       <c r="B93" s="0" t="n">
@@ -5972,6 +6255,9 @@
           <t>Balance variant; canonical=58; role=fast; profile=D04; level=13; wave=12</t>
         </is>
       </c>
+      <c r="Q93" s="0" t="n">
+        <v>13</v>
+      </c>
     </row>
     <row r="94">
       <c r="B94" s="0" t="n">
@@ -6023,6 +6309,9 @@
           <t>Balance variant; canonical=64; role=fast; profile=D04; level=13; wave=12</t>
         </is>
       </c>
+      <c r="Q94" s="0" t="n">
+        <v>13</v>
+      </c>
     </row>
     <row r="95">
       <c r="B95" s="0" t="n">
@@ -6074,6 +6363,9 @@
           <t>Balance variant; canonical=80; role=heavy; profile=D04; level=13; wave=12</t>
         </is>
       </c>
+      <c r="Q95" s="0" t="n">
+        <v>13</v>
+      </c>
     </row>
     <row r="96">
       <c r="B96" s="0" t="n">
@@ -6125,6 +6417,9 @@
           <t>Balance variant; canonical=83; role=medium; profile=D04; level=13; wave=12</t>
         </is>
       </c>
+      <c r="Q96" s="0" t="n">
+        <v>13</v>
+      </c>
     </row>
     <row r="97">
       <c r="B97" s="0" t="n">
@@ -6176,6 +6471,9 @@
           <t>Balance variant; canonical=84; role=swarm; profile=D04; level=13; wave=12</t>
         </is>
       </c>
+      <c r="Q97" s="0" t="n">
+        <v>13</v>
+      </c>
     </row>
     <row r="98">
       <c r="B98" s="0" t="n">
@@ -6227,6 +6525,9 @@
           <t>Balance variant; canonical=86; role=heavy; profile=D04; level=13; wave=12</t>
         </is>
       </c>
+      <c r="Q98" s="0" t="n">
+        <v>13</v>
+      </c>
     </row>
     <row r="99">
       <c r="B99" s="0" t="n">
@@ -6278,6 +6579,9 @@
           <t>Balance variant; canonical=98; role=fast; profile=D04; level=13; wave=12</t>
         </is>
       </c>
+      <c r="Q99" s="0" t="n">
+        <v>13</v>
+      </c>
     </row>
     <row r="100">
       <c r="B100" s="0" t="n">
@@ -6329,6 +6633,9 @@
           <t>Balance variant; canonical=108; role=medium; profile=D04; level=13; wave=12</t>
         </is>
       </c>
+      <c r="Q100" s="0" t="n">
+        <v>13</v>
+      </c>
     </row>
     <row r="101">
       <c r="B101" s="0" t="n">
@@ -6380,6 +6687,9 @@
           <t>Balance variant; canonical=123; role=medium; profile=D04; level=13; wave=12</t>
         </is>
       </c>
+      <c r="Q101" s="0" t="n">
+        <v>13</v>
+      </c>
     </row>
     <row r="102">
       <c r="B102" s="0" t="n">
@@ -6431,6 +6741,9 @@
           <t>Balance variant; canonical=11; role=air; profile=D04; level=13; wave=13</t>
         </is>
       </c>
+      <c r="Q102" s="0" t="n">
+        <v>13</v>
+      </c>
     </row>
     <row r="103">
       <c r="B103" s="0" t="n">
@@ -6482,6 +6795,9 @@
           <t>Balance variant; canonical=13; role=air; profile=D04; level=13; wave=13</t>
         </is>
       </c>
+      <c r="Q103" s="0" t="n">
+        <v>13</v>
+      </c>
     </row>
     <row r="104">
       <c r="B104" s="0" t="n">
@@ -6533,6 +6849,9 @@
           <t>Balance variant; canonical=14; role=air; profile=D04; level=13; wave=13</t>
         </is>
       </c>
+      <c r="Q104" s="0" t="n">
+        <v>13</v>
+      </c>
     </row>
     <row r="105">
       <c r="B105" s="0" t="n">
@@ -6584,6 +6903,9 @@
           <t>Balance variant; canonical=17; role=normal; profile=D04; level=13; wave=13</t>
         </is>
       </c>
+      <c r="Q105" s="0" t="n">
+        <v>13</v>
+      </c>
     </row>
     <row r="106">
       <c r="B106" s="0" t="n">
@@ -6635,6 +6957,9 @@
           <t>Balance variant; canonical=18; role=normal; profile=D04; level=13; wave=13</t>
         </is>
       </c>
+      <c r="Q106" s="0" t="n">
+        <v>13</v>
+      </c>
     </row>
     <row r="107">
       <c r="B107" s="0" t="n">
@@ -6686,6 +7011,9 @@
           <t>Balance variant; canonical=30; role=fast; profile=D04; level=13; wave=13</t>
         </is>
       </c>
+      <c r="Q107" s="0" t="n">
+        <v>13</v>
+      </c>
     </row>
     <row r="108">
       <c r="B108" s="0" t="n">
@@ -6737,6 +7065,9 @@
           <t>Balance variant; canonical=31; role=heavy; profile=D04; level=13; wave=13</t>
         </is>
       </c>
+      <c r="Q108" s="0" t="n">
+        <v>13</v>
+      </c>
     </row>
     <row r="109">
       <c r="B109" s="0" t="n">
@@ -6788,6 +7119,9 @@
           <t>Balance variant; canonical=40; role=heavy; profile=D04; level=13; wave=13</t>
         </is>
       </c>
+      <c r="Q109" s="0" t="n">
+        <v>13</v>
+      </c>
     </row>
     <row r="110">
       <c r="B110" s="0" t="n">
@@ -6839,6 +7173,9 @@
           <t>Balance variant; canonical=58; role=fast; profile=D04; level=13; wave=13</t>
         </is>
       </c>
+      <c r="Q110" s="0" t="n">
+        <v>13</v>
+      </c>
     </row>
     <row r="111">
       <c r="B111" s="0" t="n">
@@ -6890,6 +7227,9 @@
           <t>Balance variant; canonical=64; role=fast; profile=D04; level=13; wave=13</t>
         </is>
       </c>
+      <c r="Q111" s="0" t="n">
+        <v>13</v>
+      </c>
     </row>
     <row r="112">
       <c r="B112" s="0" t="n">
@@ -6941,6 +7281,9 @@
           <t>Balance variant; canonical=83; role=medium; profile=D04; level=13; wave=13</t>
         </is>
       </c>
+      <c r="Q112" s="0" t="n">
+        <v>13</v>
+      </c>
     </row>
     <row r="113">
       <c r="B113" s="0" t="n">
@@ -6992,6 +7335,9 @@
           <t>Balance variant; canonical=84; role=swarm; profile=D04; level=13; wave=13</t>
         </is>
       </c>
+      <c r="Q113" s="0" t="n">
+        <v>13</v>
+      </c>
     </row>
     <row r="114">
       <c r="B114" s="0" t="n">
@@ -7043,6 +7389,9 @@
           <t>Balance variant; canonical=86; role=heavy; profile=D04; level=13; wave=13</t>
         </is>
       </c>
+      <c r="Q114" s="0" t="n">
+        <v>13</v>
+      </c>
     </row>
     <row r="115">
       <c r="B115" s="0" t="n">
@@ -7094,6 +7443,9 @@
           <t>Balance variant; canonical=108; role=medium; profile=D04; level=13; wave=13</t>
         </is>
       </c>
+      <c r="Q115" s="0" t="n">
+        <v>13</v>
+      </c>
     </row>
     <row r="116">
       <c r="B116" s="0" t="n">
@@ -7145,6 +7497,9 @@
           <t>Balance variant; canonical=123; role=medium; profile=D04; level=13; wave=13</t>
         </is>
       </c>
+      <c r="Q116" s="0" t="n">
+        <v>13</v>
+      </c>
     </row>
     <row r="117">
       <c r="B117" s="0" t="n">
@@ -7196,6 +7551,9 @@
           <t>Balance variant; canonical=11; role=air; profile=D04; level=13; wave=14</t>
         </is>
       </c>
+      <c r="Q117" s="0" t="n">
+        <v>13</v>
+      </c>
     </row>
     <row r="118">
       <c r="B118" s="0" t="n">
@@ -7247,6 +7605,9 @@
           <t>Balance variant; canonical=13; role=air; profile=D04; level=13; wave=14</t>
         </is>
       </c>
+      <c r="Q118" s="0" t="n">
+        <v>13</v>
+      </c>
     </row>
     <row r="119">
       <c r="B119" s="0" t="n">
@@ -7298,6 +7659,9 @@
           <t>Balance variant; canonical=14; role=air; profile=D04; level=13; wave=14</t>
         </is>
       </c>
+      <c r="Q119" s="0" t="n">
+        <v>13</v>
+      </c>
     </row>
     <row r="120">
       <c r="B120" s="0" t="n">
@@ -7349,6 +7713,9 @@
           <t>Balance variant; canonical=17; role=normal; profile=D04; level=13; wave=14</t>
         </is>
       </c>
+      <c r="Q120" s="0" t="n">
+        <v>13</v>
+      </c>
     </row>
     <row r="121">
       <c r="B121" s="0" t="n">
@@ -7400,6 +7767,9 @@
           <t>Balance variant; canonical=18; role=normal; profile=D04; level=13; wave=14</t>
         </is>
       </c>
+      <c r="Q121" s="0" t="n">
+        <v>13</v>
+      </c>
     </row>
     <row r="122">
       <c r="B122" s="0" t="n">
@@ -7451,6 +7821,9 @@
           <t>Balance variant; canonical=30; role=fast; profile=D04; level=13; wave=14</t>
         </is>
       </c>
+      <c r="Q122" s="0" t="n">
+        <v>13</v>
+      </c>
     </row>
     <row r="123">
       <c r="B123" s="0" t="n">
@@ -7502,6 +7875,9 @@
           <t>Balance variant; canonical=31; role=heavy; profile=D04; level=13; wave=14</t>
         </is>
       </c>
+      <c r="Q123" s="0" t="n">
+        <v>13</v>
+      </c>
     </row>
     <row r="124">
       <c r="B124" s="0" t="n">
@@ -7553,6 +7929,9 @@
           <t>Balance variant; canonical=40; role=heavy; profile=D04; level=13; wave=14</t>
         </is>
       </c>
+      <c r="Q124" s="0" t="n">
+        <v>13</v>
+      </c>
     </row>
     <row r="125">
       <c r="B125" s="0" t="n">
@@ -7604,6 +7983,9 @@
           <t>Balance variant; canonical=64; role=fast; profile=D04; level=13; wave=14</t>
         </is>
       </c>
+      <c r="Q125" s="0" t="n">
+        <v>13</v>
+      </c>
     </row>
     <row r="126">
       <c r="B126" s="0" t="n">
@@ -7655,6 +8037,9 @@
           <t>Balance variant; canonical=83; role=medium; profile=D04; level=13; wave=14</t>
         </is>
       </c>
+      <c r="Q126" s="0" t="n">
+        <v>13</v>
+      </c>
     </row>
     <row r="127">
       <c r="B127" s="0" t="n">
@@ -7706,6 +8091,9 @@
           <t>Balance variant; canonical=84; role=swarm; profile=D04; level=13; wave=14</t>
         </is>
       </c>
+      <c r="Q127" s="0" t="n">
+        <v>13</v>
+      </c>
     </row>
     <row r="128">
       <c r="B128" s="0" t="n">
@@ -7757,6 +8145,9 @@
           <t>Balance variant; canonical=98; role=fast; profile=D04; level=13; wave=14</t>
         </is>
       </c>
+      <c r="Q128" s="0" t="n">
+        <v>13</v>
+      </c>
     </row>
     <row r="129">
       <c r="B129" s="0" t="n">
@@ -7808,6 +8199,9 @@
           <t>Balance variant; canonical=108; role=medium; profile=D04; level=13; wave=14</t>
         </is>
       </c>
+      <c r="Q129" s="0" t="n">
+        <v>13</v>
+      </c>
     </row>
     <row r="130">
       <c r="B130" s="0" t="n">
@@ -7859,6 +8253,9 @@
           <t>Balance variant; canonical=123; role=medium; profile=D04; level=13; wave=14</t>
         </is>
       </c>
+      <c r="Q130" s="0" t="n">
+        <v>13</v>
+      </c>
     </row>
     <row r="131">
       <c r="B131" s="0" t="n">
@@ -7910,6 +8307,9 @@
           <t>Balance variant; canonical=127; role=heavy; profile=D04; level=13; wave=14</t>
         </is>
       </c>
+      <c r="Q131" s="0" t="n">
+        <v>13</v>
+      </c>
     </row>
     <row r="132">
       <c r="B132" s="0" t="n">
@@ -7961,6 +8361,9 @@
           <t>Balance variant; canonical=11; role=air; profile=D04; level=13; wave=15</t>
         </is>
       </c>
+      <c r="Q132" s="0" t="n">
+        <v>13</v>
+      </c>
     </row>
     <row r="133">
       <c r="B133" s="0" t="n">
@@ -8012,6 +8415,9 @@
           <t>Balance variant; canonical=13; role=air; profile=D04; level=13; wave=15</t>
         </is>
       </c>
+      <c r="Q133" s="0" t="n">
+        <v>13</v>
+      </c>
     </row>
     <row r="134">
       <c r="B134" s="0" t="n">
@@ -8063,6 +8469,9 @@
           <t>Balance variant; canonical=14; role=air; profile=D04; level=13; wave=15</t>
         </is>
       </c>
+      <c r="Q134" s="0" t="n">
+        <v>13</v>
+      </c>
     </row>
     <row r="135">
       <c r="B135" s="0" t="n">
@@ -8114,6 +8523,9 @@
           <t>Balance variant; canonical=17; role=normal; profile=D04; level=13; wave=15</t>
         </is>
       </c>
+      <c r="Q135" s="0" t="n">
+        <v>13</v>
+      </c>
     </row>
     <row r="136">
       <c r="B136" s="0" t="n">
@@ -8165,6 +8577,9 @@
           <t>Balance variant; canonical=18; role=normal; profile=D04; level=13; wave=15</t>
         </is>
       </c>
+      <c r="Q136" s="0" t="n">
+        <v>13</v>
+      </c>
     </row>
     <row r="137">
       <c r="B137" s="0" t="n">
@@ -8216,6 +8631,9 @@
           <t>Balance variant; canonical=30; role=fast; profile=D04; level=13; wave=15</t>
         </is>
       </c>
+      <c r="Q137" s="0" t="n">
+        <v>13</v>
+      </c>
     </row>
     <row r="138">
       <c r="B138" s="0" t="n">
@@ -8267,6 +8685,9 @@
           <t>Balance variant; canonical=40; role=heavy; profile=D04; level=13; wave=15</t>
         </is>
       </c>
+      <c r="Q138" s="0" t="n">
+        <v>13</v>
+      </c>
     </row>
     <row r="139">
       <c r="B139" s="0" t="n">
@@ -8318,6 +8739,9 @@
           <t>Balance variant; canonical=58; role=fast; profile=D04; level=13; wave=15</t>
         </is>
       </c>
+      <c r="Q139" s="0" t="n">
+        <v>13</v>
+      </c>
     </row>
     <row r="140">
       <c r="B140" s="0" t="n">
@@ -8369,6 +8793,9 @@
           <t>Balance variant; canonical=64; role=fast; profile=D04; level=13; wave=15</t>
         </is>
       </c>
+      <c r="Q140" s="0" t="n">
+        <v>13</v>
+      </c>
     </row>
     <row r="141">
       <c r="B141" s="0" t="n">
@@ -8420,6 +8847,9 @@
           <t>Balance variant; canonical=67; role=elite; profile=D04; level=13; wave=15</t>
         </is>
       </c>
+      <c r="Q141" s="0" t="n">
+        <v>13</v>
+      </c>
     </row>
     <row r="142">
       <c r="B142" s="0" t="n">
@@ -8471,6 +8901,9 @@
           <t>Balance variant; canonical=70; role=heavy; profile=D04; level=13; wave=15</t>
         </is>
       </c>
+      <c r="Q142" s="0" t="n">
+        <v>13</v>
+      </c>
     </row>
     <row r="143">
       <c r="B143" s="0" t="n">
@@ -8522,6 +8955,9 @@
           <t>Balance variant; canonical=83; role=medium; profile=D04; level=13; wave=15</t>
         </is>
       </c>
+      <c r="Q143" s="0" t="n">
+        <v>13</v>
+      </c>
     </row>
     <row r="144">
       <c r="B144" s="0" t="n">
@@ -8573,6 +9009,9 @@
           <t>Balance variant; canonical=84; role=swarm; profile=D04; level=13; wave=15</t>
         </is>
       </c>
+      <c r="Q144" s="0" t="n">
+        <v>13</v>
+      </c>
     </row>
     <row r="145">
       <c r="B145" s="0" t="n">
@@ -8624,6 +9063,9 @@
           <t>Balance variant; canonical=98; role=fast; profile=D04; level=13; wave=15</t>
         </is>
       </c>
+      <c r="Q145" s="0" t="n">
+        <v>13</v>
+      </c>
     </row>
     <row r="146">
       <c r="B146" s="0" t="n">
@@ -8675,6 +9117,9 @@
           <t>Balance variant; canonical=108; role=medium; profile=D04; level=13; wave=15</t>
         </is>
       </c>
+      <c r="Q146" s="0" t="n">
+        <v>13</v>
+      </c>
     </row>
     <row r="147">
       <c r="B147" s="0" t="n">
@@ -8726,6 +9171,9 @@
           <t>Balance variant; canonical=123; role=medium; profile=D04; level=13; wave=15</t>
         </is>
       </c>
+      <c r="Q147" s="0" t="n">
+        <v>13</v>
+      </c>
     </row>
     <row r="148">
       <c r="B148" s="0" t="n">
@@ -8777,6 +9225,9 @@
           <t>Balance variant; canonical=127; role=heavy; profile=D04; level=13; wave=15</t>
         </is>
       </c>
+      <c r="Q148" s="0" t="n">
+        <v>13</v>
+      </c>
     </row>
     <row r="149">
       <c r="B149" s="0" t="n">
@@ -8828,6 +9279,9 @@
           <t>Balance variant; canonical=17; role=normal; profile=D04; level=13; wave=16</t>
         </is>
       </c>
+      <c r="Q149" s="0" t="n">
+        <v>13</v>
+      </c>
     </row>
     <row r="150">
       <c r="B150" s="0" t="n">
@@ -8879,6 +9333,9 @@
           <t>Balance variant; canonical=18; role=normal; profile=D04; level=13; wave=16</t>
         </is>
       </c>
+      <c r="Q150" s="0" t="n">
+        <v>13</v>
+      </c>
     </row>
     <row r="151">
       <c r="B151" s="0" t="n">
@@ -8930,6 +9387,9 @@
           <t>Balance variant; canonical=30; role=fast; profile=D04; level=13; wave=16</t>
         </is>
       </c>
+      <c r="Q151" s="0" t="n">
+        <v>13</v>
+      </c>
     </row>
     <row r="152">
       <c r="B152" s="0" t="n">
@@ -8981,6 +9441,9 @@
           <t>Balance variant; canonical=58; role=fast; profile=D04; level=13; wave=16</t>
         </is>
       </c>
+      <c r="Q152" s="0" t="n">
+        <v>13</v>
+      </c>
     </row>
     <row r="153">
       <c r="B153" s="0" t="n">
@@ -9032,6 +9495,9 @@
           <t>Balance variant; canonical=64; role=fast; profile=D04; level=13; wave=16</t>
         </is>
       </c>
+      <c r="Q153" s="0" t="n">
+        <v>13</v>
+      </c>
     </row>
     <row r="154">
       <c r="B154" s="0" t="n">
@@ -9083,6 +9549,9 @@
           <t>Balance variant; canonical=67; role=heavy; profile=D04; level=13; wave=16</t>
         </is>
       </c>
+      <c r="Q154" s="0" t="n">
+        <v>13</v>
+      </c>
     </row>
     <row r="155">
       <c r="B155" s="0" t="n">
@@ -9134,6 +9603,9 @@
           <t>Balance variant; canonical=70; role=heavy; profile=D04; level=13; wave=16</t>
         </is>
       </c>
+      <c r="Q155" s="0" t="n">
+        <v>13</v>
+      </c>
     </row>
     <row r="156">
       <c r="B156" s="0" t="n">
@@ -9185,6 +9657,9 @@
           <t>Balance variant; canonical=83; role=medium; profile=D04; level=13; wave=16</t>
         </is>
       </c>
+      <c r="Q156" s="0" t="n">
+        <v>13</v>
+      </c>
     </row>
     <row r="157">
       <c r="B157" s="0" t="n">
@@ -9236,6 +9711,9 @@
           <t>Balance variant; canonical=84; role=swarm; profile=D04; level=13; wave=16</t>
         </is>
       </c>
+      <c r="Q157" s="0" t="n">
+        <v>13</v>
+      </c>
     </row>
     <row r="158">
       <c r="B158" s="0" t="n">
@@ -9287,6 +9765,9 @@
           <t>Balance variant; canonical=98; role=fast; profile=D04; level=13; wave=16</t>
         </is>
       </c>
+      <c r="Q158" s="0" t="n">
+        <v>13</v>
+      </c>
     </row>
     <row r="159">
       <c r="B159" s="0" t="n">
@@ -9338,6 +9819,9 @@
           <t>Balance variant; canonical=108; role=medium; profile=D04; level=13; wave=16</t>
         </is>
       </c>
+      <c r="Q159" s="0" t="n">
+        <v>13</v>
+      </c>
     </row>
     <row r="160">
       <c r="B160" s="0" t="n">
@@ -9389,6 +9873,9 @@
           <t>Balance variant; canonical=123; role=medium; profile=D04; level=13; wave=16</t>
         </is>
       </c>
+      <c r="Q160" s="0" t="n">
+        <v>13</v>
+      </c>
     </row>
     <row r="161">
       <c r="B161" s="0" t="n">
@@ -9440,6 +9927,9 @@
           <t>Balance variant; canonical=127; role=heavy; profile=D04; level=13; wave=16</t>
         </is>
       </c>
+      <c r="Q161" s="0" t="n">
+        <v>13</v>
+      </c>
     </row>
     <row r="162">
       <c r="B162" s="0" t="n">
@@ -9491,6 +9981,9 @@
           <t>Balance variant; canonical=11; role=air; profile=D04; level=13; wave=17</t>
         </is>
       </c>
+      <c r="Q162" s="0" t="n">
+        <v>13</v>
+      </c>
     </row>
     <row r="163">
       <c r="B163" s="0" t="n">
@@ -9542,6 +10035,9 @@
           <t>Balance variant; canonical=13; role=air; profile=D04; level=13; wave=17</t>
         </is>
       </c>
+      <c r="Q163" s="0" t="n">
+        <v>13</v>
+      </c>
     </row>
     <row r="164">
       <c r="B164" s="0" t="n">
@@ -9593,6 +10089,9 @@
           <t>Balance variant; canonical=14; role=air; profile=D04; level=13; wave=17</t>
         </is>
       </c>
+      <c r="Q164" s="0" t="n">
+        <v>13</v>
+      </c>
     </row>
     <row r="165">
       <c r="B165" s="0" t="n">
@@ -9644,6 +10143,9 @@
           <t>Balance variant; canonical=17; role=normal; profile=D04; level=13; wave=17</t>
         </is>
       </c>
+      <c r="Q165" s="0" t="n">
+        <v>13</v>
+      </c>
     </row>
     <row r="166">
       <c r="B166" s="0" t="n">
@@ -9695,6 +10197,9 @@
           <t>Balance variant; canonical=18; role=normal; profile=D04; level=13; wave=17</t>
         </is>
       </c>
+      <c r="Q166" s="0" t="n">
+        <v>13</v>
+      </c>
     </row>
     <row r="167">
       <c r="B167" s="0" t="n">
@@ -9746,6 +10251,9 @@
           <t>Balance variant; canonical=30; role=fast; profile=D04; level=13; wave=17</t>
         </is>
       </c>
+      <c r="Q167" s="0" t="n">
+        <v>13</v>
+      </c>
     </row>
     <row r="168">
       <c r="B168" s="0" t="n">
@@ -9797,6 +10305,9 @@
           <t>Balance variant; canonical=58; role=fast; profile=D04; level=13; wave=17</t>
         </is>
       </c>
+      <c r="Q168" s="0" t="n">
+        <v>13</v>
+      </c>
     </row>
     <row r="169">
       <c r="B169" s="0" t="n">
@@ -9848,6 +10359,9 @@
           <t>Balance variant; canonical=64; role=fast; profile=D04; level=13; wave=17</t>
         </is>
       </c>
+      <c r="Q169" s="0" t="n">
+        <v>13</v>
+      </c>
     </row>
     <row r="170">
       <c r="B170" s="0" t="n">
@@ -9899,6 +10413,9 @@
           <t>Balance variant; canonical=67; role=heavy; profile=D04; level=13; wave=17</t>
         </is>
       </c>
+      <c r="Q170" s="0" t="n">
+        <v>13</v>
+      </c>
     </row>
     <row r="171">
       <c r="B171" s="0" t="n">
@@ -9950,6 +10467,9 @@
           <t>Balance variant; canonical=70; role=heavy; profile=D04; level=13; wave=17</t>
         </is>
       </c>
+      <c r="Q171" s="0" t="n">
+        <v>13</v>
+      </c>
     </row>
     <row r="172">
       <c r="B172" s="0" t="n">
@@ -10001,6 +10521,9 @@
           <t>Balance variant; canonical=83; role=medium; profile=D04; level=13; wave=17</t>
         </is>
       </c>
+      <c r="Q172" s="0" t="n">
+        <v>13</v>
+      </c>
     </row>
     <row r="173">
       <c r="B173" s="0" t="n">
@@ -10052,6 +10575,9 @@
           <t>Balance variant; canonical=84; role=swarm; profile=D04; level=13; wave=17</t>
         </is>
       </c>
+      <c r="Q173" s="0" t="n">
+        <v>13</v>
+      </c>
     </row>
     <row r="174">
       <c r="B174" s="0" t="n">
@@ -10103,6 +10629,9 @@
           <t>Balance variant; canonical=88; role=heavy; profile=D04; level=13; wave=17</t>
         </is>
       </c>
+      <c r="Q174" s="0" t="n">
+        <v>13</v>
+      </c>
     </row>
     <row r="175">
       <c r="B175" s="0" t="n">
@@ -10154,6 +10683,9 @@
           <t>Balance variant; canonical=98; role=fast; profile=D04; level=13; wave=17</t>
         </is>
       </c>
+      <c r="Q175" s="0" t="n">
+        <v>13</v>
+      </c>
     </row>
     <row r="176">
       <c r="B176" s="0" t="n">
@@ -10205,6 +10737,9 @@
           <t>Balance variant; canonical=108; role=medium; profile=D04; level=13; wave=17</t>
         </is>
       </c>
+      <c r="Q176" s="0" t="n">
+        <v>13</v>
+      </c>
     </row>
     <row r="177">
       <c r="B177" s="0" t="n">
@@ -10256,6 +10791,9 @@
           <t>Balance variant; canonical=123; role=medium; profile=D04; level=13; wave=17</t>
         </is>
       </c>
+      <c r="Q177" s="0" t="n">
+        <v>13</v>
+      </c>
     </row>
     <row r="178">
       <c r="B178" s="0" t="n">
@@ -10307,6 +10845,9 @@
           <t>Balance variant; canonical=11; role=air; profile=D04; level=13; wave=18</t>
         </is>
       </c>
+      <c r="Q178" s="0" t="n">
+        <v>13</v>
+      </c>
     </row>
     <row r="179">
       <c r="B179" s="0" t="n">
@@ -10358,6 +10899,9 @@
           <t>Balance variant; canonical=13; role=air; profile=D04; level=13; wave=18</t>
         </is>
       </c>
+      <c r="Q179" s="0" t="n">
+        <v>13</v>
+      </c>
     </row>
     <row r="180">
       <c r="B180" s="0" t="n">
@@ -10409,6 +10953,9 @@
           <t>Balance variant; canonical=14; role=air; profile=D04; level=13; wave=18</t>
         </is>
       </c>
+      <c r="Q180" s="0" t="n">
+        <v>13</v>
+      </c>
     </row>
     <row r="181">
       <c r="B181" s="0" t="n">
@@ -10460,6 +11007,9 @@
           <t>Balance variant; canonical=17; role=normal; profile=D04; level=13; wave=18</t>
         </is>
       </c>
+      <c r="Q181" s="0" t="n">
+        <v>13</v>
+      </c>
     </row>
     <row r="182">
       <c r="B182" s="0" t="n">
@@ -10511,6 +11061,9 @@
           <t>Balance variant; canonical=18; role=normal; profile=D04; level=13; wave=18</t>
         </is>
       </c>
+      <c r="Q182" s="0" t="n">
+        <v>13</v>
+      </c>
     </row>
     <row r="183">
       <c r="B183" s="0" t="n">
@@ -10562,6 +11115,9 @@
           <t>Balance variant; canonical=30; role=fast; profile=D04; level=13; wave=18</t>
         </is>
       </c>
+      <c r="Q183" s="0" t="n">
+        <v>13</v>
+      </c>
     </row>
     <row r="184">
       <c r="B184" s="0" t="n">
@@ -10613,6 +11169,9 @@
           <t>Balance variant; canonical=58; role=fast; profile=D04; level=13; wave=18</t>
         </is>
       </c>
+      <c r="Q184" s="0" t="n">
+        <v>13</v>
+      </c>
     </row>
     <row r="185">
       <c r="B185" s="0" t="n">
@@ -10664,6 +11223,9 @@
           <t>Balance variant; canonical=64; role=fast; profile=D04; level=13; wave=18</t>
         </is>
       </c>
+      <c r="Q185" s="0" t="n">
+        <v>13</v>
+      </c>
     </row>
     <row r="186">
       <c r="B186" s="0" t="n">
@@ -10715,6 +11277,9 @@
           <t>Balance variant; canonical=67; role=heavy; profile=D04; level=13; wave=18</t>
         </is>
       </c>
+      <c r="Q186" s="0" t="n">
+        <v>13</v>
+      </c>
     </row>
     <row r="187">
       <c r="B187" s="0" t="n">
@@ -10766,6 +11331,9 @@
           <t>Balance variant; canonical=80; role=heavy; profile=D04; level=13; wave=18</t>
         </is>
       </c>
+      <c r="Q187" s="0" t="n">
+        <v>13</v>
+      </c>
     </row>
     <row r="188">
       <c r="B188" s="0" t="n">
@@ -10817,6 +11385,9 @@
           <t>Balance variant; canonical=83; role=medium; profile=D04; level=13; wave=18</t>
         </is>
       </c>
+      <c r="Q188" s="0" t="n">
+        <v>13</v>
+      </c>
     </row>
     <row r="189">
       <c r="B189" s="0" t="n">
@@ -10868,6 +11439,9 @@
           <t>Balance variant; canonical=84; role=swarm; profile=D04; level=13; wave=18</t>
         </is>
       </c>
+      <c r="Q189" s="0" t="n">
+        <v>13</v>
+      </c>
     </row>
     <row r="190">
       <c r="B190" s="0" t="n">
@@ -10919,6 +11493,9 @@
           <t>Balance variant; canonical=88; role=heavy; profile=D04; level=13; wave=18</t>
         </is>
       </c>
+      <c r="Q190" s="0" t="n">
+        <v>13</v>
+      </c>
     </row>
     <row r="191">
       <c r="B191" s="0" t="n">
@@ -10970,6 +11547,9 @@
           <t>Balance variant; canonical=98; role=fast; profile=D04; level=13; wave=18</t>
         </is>
       </c>
+      <c r="Q191" s="0" t="n">
+        <v>13</v>
+      </c>
     </row>
     <row r="192">
       <c r="B192" s="0" t="n">
@@ -11021,6 +11601,9 @@
           <t>Balance variant; canonical=108; role=medium; profile=D04; level=13; wave=18</t>
         </is>
       </c>
+      <c r="Q192" s="0" t="n">
+        <v>13</v>
+      </c>
     </row>
     <row r="193">
       <c r="B193" s="0" t="n">
@@ -11072,6 +11655,9 @@
           <t>Balance variant; canonical=123; role=medium; profile=D04; level=13; wave=18</t>
         </is>
       </c>
+      <c r="Q193" s="0" t="n">
+        <v>13</v>
+      </c>
     </row>
     <row r="194">
       <c r="B194" s="0" t="n">
@@ -11123,6 +11709,9 @@
           <t>Balance variant; canonical=11; role=air; profile=D04; level=13; wave=19</t>
         </is>
       </c>
+      <c r="Q194" s="0" t="n">
+        <v>13</v>
+      </c>
     </row>
     <row r="195">
       <c r="B195" s="0" t="n">
@@ -11174,6 +11763,9 @@
           <t>Balance variant; canonical=13; role=air; profile=D04; level=13; wave=19</t>
         </is>
       </c>
+      <c r="Q195" s="0" t="n">
+        <v>13</v>
+      </c>
     </row>
     <row r="196">
       <c r="B196" s="0" t="n">
@@ -11225,6 +11817,9 @@
           <t>Balance variant; canonical=14; role=air; profile=D04; level=13; wave=19</t>
         </is>
       </c>
+      <c r="Q196" s="0" t="n">
+        <v>13</v>
+      </c>
     </row>
     <row r="197">
       <c r="B197" s="0" t="n">
@@ -11276,6 +11871,9 @@
           <t>Balance variant; canonical=17; role=normal; profile=D04; level=13; wave=19</t>
         </is>
       </c>
+      <c r="Q197" s="0" t="n">
+        <v>13</v>
+      </c>
     </row>
     <row r="198">
       <c r="B198" s="0" t="n">
@@ -11327,6 +11925,9 @@
           <t>Balance variant; canonical=18; role=normal; profile=D04; level=13; wave=19</t>
         </is>
       </c>
+      <c r="Q198" s="0" t="n">
+        <v>13</v>
+      </c>
     </row>
     <row r="199">
       <c r="B199" s="0" t="n">
@@ -11378,6 +11979,9 @@
           <t>Balance variant; canonical=30; role=fast; profile=D04; level=13; wave=19</t>
         </is>
       </c>
+      <c r="Q199" s="0" t="n">
+        <v>13</v>
+      </c>
     </row>
     <row r="200">
       <c r="B200" s="0" t="n">
@@ -11429,6 +12033,9 @@
           <t>Balance variant; canonical=58; role=fast; profile=D04; level=13; wave=19</t>
         </is>
       </c>
+      <c r="Q200" s="0" t="n">
+        <v>13</v>
+      </c>
     </row>
     <row r="201">
       <c r="B201" s="0" t="n">
@@ -11480,6 +12087,9 @@
           <t>Balance variant; canonical=64; role=fast; profile=D04; level=13; wave=19</t>
         </is>
       </c>
+      <c r="Q201" s="0" t="n">
+        <v>13</v>
+      </c>
     </row>
     <row r="202">
       <c r="B202" s="0" t="n">
@@ -11531,6 +12141,9 @@
           <t>Balance variant; canonical=80; role=heavy; profile=D04; level=13; wave=19</t>
         </is>
       </c>
+      <c r="Q202" s="0" t="n">
+        <v>13</v>
+      </c>
     </row>
     <row r="203">
       <c r="B203" s="0" t="n">
@@ -11582,6 +12195,9 @@
           <t>Balance variant; canonical=83; role=medium; profile=D04; level=13; wave=19</t>
         </is>
       </c>
+      <c r="Q203" s="0" t="n">
+        <v>13</v>
+      </c>
     </row>
     <row r="204">
       <c r="B204" s="0" t="n">
@@ -11633,6 +12249,9 @@
           <t>Balance variant; canonical=84; role=swarm; profile=D04; level=13; wave=19</t>
         </is>
       </c>
+      <c r="Q204" s="0" t="n">
+        <v>13</v>
+      </c>
     </row>
     <row r="205">
       <c r="B205" s="0" t="n">
@@ -11684,6 +12303,9 @@
           <t>Balance variant; canonical=86; role=heavy; profile=D04; level=13; wave=19</t>
         </is>
       </c>
+      <c r="Q205" s="0" t="n">
+        <v>13</v>
+      </c>
     </row>
     <row r="206">
       <c r="B206" s="0" t="n">
@@ -11735,6 +12357,9 @@
           <t>Balance variant; canonical=88; role=heavy; profile=D04; level=13; wave=19</t>
         </is>
       </c>
+      <c r="Q206" s="0" t="n">
+        <v>13</v>
+      </c>
     </row>
     <row r="207">
       <c r="B207" s="0" t="n">
@@ -11786,6 +12411,9 @@
           <t>Balance variant; canonical=98; role=fast; profile=D04; level=13; wave=19</t>
         </is>
       </c>
+      <c r="Q207" s="0" t="n">
+        <v>13</v>
+      </c>
     </row>
     <row r="208">
       <c r="B208" s="0" t="n">
@@ -11837,6 +12465,9 @@
           <t>Balance variant; canonical=108; role=medium; profile=D04; level=13; wave=19</t>
         </is>
       </c>
+      <c r="Q208" s="0" t="n">
+        <v>13</v>
+      </c>
     </row>
     <row r="209">
       <c r="B209" s="0" t="n">
@@ -11888,6 +12519,9 @@
           <t>Balance variant; canonical=123; role=medium; profile=D04; level=13; wave=19</t>
         </is>
       </c>
+      <c r="Q209" s="0" t="n">
+        <v>13</v>
+      </c>
     </row>
     <row r="210">
       <c r="B210" s="0" t="n">
@@ -11939,6 +12573,9 @@
           <t>Balance variant; canonical=11; role=air; profile=D04; level=13; wave=20</t>
         </is>
       </c>
+      <c r="Q210" s="0" t="n">
+        <v>13</v>
+      </c>
     </row>
     <row r="211">
       <c r="B211" s="0" t="n">
@@ -11990,6 +12627,9 @@
           <t>Balance variant; canonical=13; role=air; profile=D04; level=13; wave=20</t>
         </is>
       </c>
+      <c r="Q211" s="0" t="n">
+        <v>13</v>
+      </c>
     </row>
     <row r="212">
       <c r="B212" s="0" t="n">
@@ -12041,6 +12681,9 @@
           <t>Balance variant; canonical=14; role=air; profile=D04; level=13; wave=20</t>
         </is>
       </c>
+      <c r="Q212" s="0" t="n">
+        <v>13</v>
+      </c>
     </row>
     <row r="213">
       <c r="B213" s="0" t="n">
@@ -12092,6 +12735,9 @@
           <t>Balance variant; canonical=17; role=normal; profile=D04; level=13; wave=20</t>
         </is>
       </c>
+      <c r="Q213" s="0" t="n">
+        <v>13</v>
+      </c>
     </row>
     <row r="214">
       <c r="B214" s="0" t="n">
@@ -12143,6 +12789,9 @@
           <t>Balance variant; canonical=18; role=normal; profile=D04; level=13; wave=20</t>
         </is>
       </c>
+      <c r="Q214" s="0" t="n">
+        <v>13</v>
+      </c>
     </row>
     <row r="215">
       <c r="B215" s="0" t="n">
@@ -12194,6 +12843,9 @@
           <t>Balance variant; canonical=30; role=fast; profile=D04; level=13; wave=20</t>
         </is>
       </c>
+      <c r="Q215" s="0" t="n">
+        <v>13</v>
+      </c>
     </row>
     <row r="216">
       <c r="B216" s="0" t="n">
@@ -12245,6 +12897,9 @@
           <t>Balance variant; canonical=31; role=heavy; profile=D04; level=13; wave=20</t>
         </is>
       </c>
+      <c r="Q216" s="0" t="n">
+        <v>13</v>
+      </c>
     </row>
     <row r="217">
       <c r="B217" s="0" t="n">
@@ -12296,6 +12951,9 @@
           <t>Balance variant; canonical=58; role=fast; profile=D04; level=13; wave=20</t>
         </is>
       </c>
+      <c r="Q217" s="0" t="n">
+        <v>13</v>
+      </c>
     </row>
     <row r="218">
       <c r="B218" s="0" t="n">
@@ -12347,6 +13005,9 @@
           <t>Balance variant; canonical=64; role=fast; profile=D04; level=13; wave=20</t>
         </is>
       </c>
+      <c r="Q218" s="0" t="n">
+        <v>13</v>
+      </c>
     </row>
     <row r="219">
       <c r="B219" s="0" t="n">
@@ -12398,6 +13059,9 @@
           <t>Balance variant; canonical=80; role=heavy; profile=D04; level=13; wave=20</t>
         </is>
       </c>
+      <c r="Q219" s="0" t="n">
+        <v>13</v>
+      </c>
     </row>
     <row r="220">
       <c r="B220" s="0" t="n">
@@ -12449,6 +13113,9 @@
           <t>Balance variant; canonical=83; role=medium; profile=D04; level=13; wave=20</t>
         </is>
       </c>
+      <c r="Q220" s="0" t="n">
+        <v>13</v>
+      </c>
     </row>
     <row r="221">
       <c r="B221" s="0" t="n">
@@ -12500,6 +13167,9 @@
           <t>Balance variant; canonical=84; role=swarm; profile=D04; level=13; wave=20</t>
         </is>
       </c>
+      <c r="Q221" s="0" t="n">
+        <v>13</v>
+      </c>
     </row>
     <row r="222">
       <c r="B222" s="0" t="n">
@@ -12551,6 +13221,9 @@
           <t>Balance variant; canonical=86; role=heavy; profile=D04; level=13; wave=20</t>
         </is>
       </c>
+      <c r="Q222" s="0" t="n">
+        <v>13</v>
+      </c>
     </row>
     <row r="223">
       <c r="B223" s="0" t="n">
@@ -12602,6 +13275,9 @@
           <t>Balance variant; canonical=98; role=fast; profile=D04; level=13; wave=20</t>
         </is>
       </c>
+      <c r="Q223" s="0" t="n">
+        <v>13</v>
+      </c>
     </row>
     <row r="224">
       <c r="B224" s="0" t="n">
@@ -12653,6 +13329,9 @@
           <t>Balance variant; canonical=108; role=medium; profile=D04; level=13; wave=20</t>
         </is>
       </c>
+      <c r="Q224" s="0" t="n">
+        <v>13</v>
+      </c>
     </row>
     <row r="225">
       <c r="B225" s="0" t="n">
@@ -12704,6 +13383,9 @@
           <t>Balance variant; canonical=123; role=medium; profile=D04; level=13; wave=20</t>
         </is>
       </c>
+      <c r="Q225" s="0" t="n">
+        <v>13</v>
+      </c>
     </row>
     <row r="226">
       <c r="B226" s="0" t="n">
@@ -12755,6 +13437,9 @@
           <t>Balance variant; canonical=14; role=air; profile=D04; level=13; wave=6</t>
         </is>
       </c>
+      <c r="Q226" s="0" t="n">
+        <v>13</v>
+      </c>
     </row>
     <row r="227">
       <c r="B227" s="0" t="n">
@@ -12806,6 +13491,9 @@
           <t>Balance variant; canonical=58; role=fast; profile=D04; level=13; wave=6</t>
         </is>
       </c>
+      <c r="Q227" s="0" t="n">
+        <v>13</v>
+      </c>
     </row>
     <row r="228">
       <c r="B228" s="0" t="n">
@@ -12857,6 +13545,9 @@
           <t>Balance variant; canonical=13; role=air; profile=D04; level=13; wave=7</t>
         </is>
       </c>
+      <c r="Q228" s="0" t="n">
+        <v>13</v>
+      </c>
     </row>
     <row r="229">
       <c r="B229" s="0" t="n">
@@ -12908,6 +13599,9 @@
           <t>Balance variant; canonical=64; role=fast; profile=D04; level=13; wave=7</t>
         </is>
       </c>
+      <c r="Q229" s="0" t="n">
+        <v>13</v>
+      </c>
     </row>
     <row r="230">
       <c r="B230" s="0" t="n">
@@ -12959,6 +13653,9 @@
           <t>Balance variant; canonical=11; role=air; profile=D04; level=13; wave=8</t>
         </is>
       </c>
+      <c r="Q230" s="0" t="n">
+        <v>13</v>
+      </c>
     </row>
     <row r="231">
       <c r="B231" s="0" t="n">
@@ -13010,6 +13707,9 @@
           <t>Balance variant; canonical=30; role=fast; profile=D04; level=13; wave=8</t>
         </is>
       </c>
+      <c r="Q231" s="0" t="n">
+        <v>13</v>
+      </c>
     </row>
     <row r="232">
       <c r="B232" s="0" t="n">
@@ -13061,6 +13761,9 @@
           <t>Balance variant; canonical=14; role=air; profile=D04; level=13; wave=9</t>
         </is>
       </c>
+      <c r="Q232" s="0" t="n">
+        <v>13</v>
+      </c>
     </row>
     <row r="233">
       <c r="B233" s="0" t="n">
@@ -13112,6 +13815,9 @@
           <t>Balance variant; canonical=98; role=fast; profile=D04; level=13; wave=9</t>
         </is>
       </c>
+      <c r="Q233" s="0" t="n">
+        <v>13</v>
+      </c>
     </row>
     <row r="234">
       <c r="B234" s="0" t="n">
@@ -13163,6 +13869,9 @@
           <t>Balance variant; canonical=13; role=air; profile=D04; level=13; wave=10</t>
         </is>
       </c>
+      <c r="Q234" s="0" t="n">
+        <v>13</v>
+      </c>
     </row>
     <row r="235">
       <c r="B235" s="0" t="n">
@@ -13214,6 +13923,9 @@
           <t>Balance variant; canonical=58; role=fast; profile=D04; level=13; wave=10</t>
         </is>
       </c>
+      <c r="Q235" s="0" t="n">
+        <v>13</v>
+      </c>
     </row>
     <row r="236">
       <c r="B236" s="0" t="n">
@@ -13265,6 +13977,9 @@
           <t>Balance variant; canonical=31; role=heavy; profile=D04; level=13; wave=11</t>
         </is>
       </c>
+      <c r="Q236" s="0" t="n">
+        <v>13</v>
+      </c>
     </row>
     <row r="237">
       <c r="B237" s="0" t="n">
@@ -13316,6 +14031,9 @@
           <t>Balance variant; canonical=40; role=heavy; profile=D04; level=13; wave=11</t>
         </is>
       </c>
+      <c r="Q237" s="0" t="n">
+        <v>13</v>
+      </c>
     </row>
     <row r="238">
       <c r="B238" s="0" t="n">
@@ -13367,6 +14085,9 @@
           <t>Balance variant; canonical=64; role=fast; profile=D04; level=13; wave=11</t>
         </is>
       </c>
+      <c r="Q238" s="0" t="n">
+        <v>13</v>
+      </c>
     </row>
     <row r="239">
       <c r="B239" s="0" t="n">
@@ -13418,6 +14139,9 @@
           <t>Balance variant; canonical=30; role=fast; profile=D04; level=13; wave=12</t>
         </is>
       </c>
+      <c r="Q239" s="0" t="n">
+        <v>13</v>
+      </c>
     </row>
     <row r="240">
       <c r="B240" s="0" t="n">
@@ -13469,6 +14193,9 @@
           <t>Balance variant; canonical=40; role=heavy; profile=D04; level=13; wave=12</t>
         </is>
       </c>
+      <c r="Q240" s="0" t="n">
+        <v>13</v>
+      </c>
     </row>
     <row r="241">
       <c r="B241" s="0" t="n">
@@ -13520,6 +14247,9 @@
           <t>Balance variant; canonical=127; role=heavy; profile=D04; level=13; wave=12</t>
         </is>
       </c>
+      <c r="Q241" s="0" t="n">
+        <v>13</v>
+      </c>
     </row>
     <row r="242">
       <c r="B242" s="0" t="n">
@@ -13571,6 +14301,9 @@
           <t>Balance variant; canonical=70; role=heavy; profile=D04; level=13; wave=13</t>
         </is>
       </c>
+      <c r="Q242" s="0" t="n">
+        <v>13</v>
+      </c>
     </row>
     <row r="243">
       <c r="B243" s="0" t="n">
@@ -13622,6 +14355,9 @@
           <t>Balance variant; canonical=98; role=fast; profile=D04; level=13; wave=13</t>
         </is>
       </c>
+      <c r="Q243" s="0" t="n">
+        <v>13</v>
+      </c>
     </row>
     <row r="244">
       <c r="B244" s="0" t="n">
@@ -13673,6 +14409,9 @@
           <t>Balance variant; canonical=127; role=heavy; profile=D04; level=13; wave=13</t>
         </is>
       </c>
+      <c r="Q244" s="0" t="n">
+        <v>13</v>
+      </c>
     </row>
     <row r="245">
       <c r="B245" s="0" t="n">
@@ -13724,6 +14463,9 @@
           <t>Balance variant; canonical=58; role=fast; profile=D04; level=13; wave=14</t>
         </is>
       </c>
+      <c r="Q245" s="0" t="n">
+        <v>13</v>
+      </c>
     </row>
     <row r="246">
       <c r="B246" s="0" t="n">
@@ -13775,6 +14517,9 @@
           <t>Balance variant; canonical=67; role=heavy; profile=D04; level=13; wave=14</t>
         </is>
       </c>
+      <c r="Q246" s="0" t="n">
+        <v>13</v>
+      </c>
     </row>
     <row r="247">
       <c r="B247" s="0" t="n">
@@ -13826,6 +14571,9 @@
           <t>Balance variant; canonical=70; role=heavy; profile=D04; level=13; wave=14</t>
         </is>
       </c>
+      <c r="Q247" s="0" t="n">
+        <v>13</v>
+      </c>
     </row>
     <row r="248">
       <c r="B248" s="0" t="n">
@@ -13877,6 +14625,9 @@
           <t>Balance variant; canonical=67; role=heavy; profile=D04; level=13; wave=15</t>
         </is>
       </c>
+      <c r="Q248" s="0" t="n">
+        <v>13</v>
+      </c>
     </row>
     <row r="249">
       <c r="B249" s="0" t="n">
@@ -13928,6 +14679,9 @@
           <t>Balance variant; canonical=88; role=heavy; profile=D04; level=13; wave=15</t>
         </is>
       </c>
+      <c r="Q249" s="0" t="n">
+        <v>13</v>
+      </c>
     </row>
     <row r="250">
       <c r="B250" s="0" t="n">
@@ -13979,6 +14733,9 @@
           <t>Balance variant; canonical=80; role=heavy; profile=D04; level=13; wave=16</t>
         </is>
       </c>
+      <c r="Q250" s="0" t="n">
+        <v>13</v>
+      </c>
     </row>
     <row r="251">
       <c r="B251" s="0" t="n">
@@ -14030,6 +14787,9 @@
           <t>Balance variant; canonical=86; role=heavy; profile=D04; level=13; wave=16</t>
         </is>
       </c>
+      <c r="Q251" s="0" t="n">
+        <v>13</v>
+      </c>
     </row>
     <row r="252">
       <c r="B252" s="0" t="n">
@@ -14081,6 +14841,9 @@
           <t>Balance variant; canonical=88; role=heavy; profile=D04; level=13; wave=16</t>
         </is>
       </c>
+      <c r="Q252" s="0" t="n">
+        <v>13</v>
+      </c>
     </row>
     <row r="253">
       <c r="B253" s="0" t="n">
@@ -14132,6 +14895,9 @@
           <t>Balance variant; canonical=31; role=heavy; profile=D04; level=13; wave=17</t>
         </is>
       </c>
+      <c r="Q253" s="0" t="n">
+        <v>13</v>
+      </c>
     </row>
     <row r="254">
       <c r="B254" s="0" t="n">
@@ -14183,6 +14949,9 @@
           <t>Balance variant; canonical=80; role=heavy; profile=D04; level=13; wave=17</t>
         </is>
       </c>
+      <c r="Q254" s="0" t="n">
+        <v>13</v>
+      </c>
     </row>
     <row r="255">
       <c r="B255" s="0" t="n">
@@ -14234,6 +15003,9 @@
           <t>Balance variant; canonical=86; role=heavy; profile=D04; level=13; wave=17</t>
         </is>
       </c>
+      <c r="Q255" s="0" t="n">
+        <v>13</v>
+      </c>
     </row>
     <row r="256">
       <c r="B256" s="0" t="n">
@@ -14285,6 +15057,9 @@
           <t>Balance variant; canonical=31; role=heavy; profile=D04; level=13; wave=18</t>
         </is>
       </c>
+      <c r="Q256" s="0" t="n">
+        <v>13</v>
+      </c>
     </row>
     <row r="257">
       <c r="B257" s="0" t="n">
@@ -14336,6 +15111,9 @@
           <t>Balance variant; canonical=40; role=heavy; profile=D04; level=13; wave=18</t>
         </is>
       </c>
+      <c r="Q257" s="0" t="n">
+        <v>13</v>
+      </c>
     </row>
     <row r="258">
       <c r="B258" s="0" t="n">
@@ -14387,6 +15165,9 @@
           <t>Balance variant; canonical=86; role=heavy; profile=D04; level=13; wave=18</t>
         </is>
       </c>
+      <c r="Q258" s="0" t="n">
+        <v>13</v>
+      </c>
     </row>
     <row r="259">
       <c r="B259" s="0" t="n">
@@ -14438,6 +15219,9 @@
           <t>Balance variant; canonical=31; role=heavy; profile=D04; level=13; wave=19</t>
         </is>
       </c>
+      <c r="Q259" s="0" t="n">
+        <v>13</v>
+      </c>
     </row>
     <row r="260">
       <c r="B260" s="0" t="n">
@@ -14489,6 +15273,9 @@
           <t>Balance variant; canonical=40; role=heavy; profile=D04; level=13; wave=19</t>
         </is>
       </c>
+      <c r="Q260" s="0" t="n">
+        <v>13</v>
+      </c>
     </row>
     <row r="261">
       <c r="B261" s="0" t="n">
@@ -14540,6 +15327,9 @@
           <t>Balance variant; canonical=127; role=heavy; profile=D04; level=13; wave=19</t>
         </is>
       </c>
+      <c r="Q261" s="0" t="n">
+        <v>13</v>
+      </c>
     </row>
     <row r="262">
       <c r="B262" s="0" t="n">
@@ -14591,6 +15381,9 @@
           <t>Balance variant; canonical=40; role=heavy; profile=D04; level=13; wave=20</t>
         </is>
       </c>
+      <c r="Q262" s="0" t="n">
+        <v>13</v>
+      </c>
     </row>
     <row r="263">
       <c r="B263" s="0" t="n">
@@ -14642,6 +15435,9 @@
           <t>Balance variant; canonical=67; role=elite; profile=D04; level=13; wave=20</t>
         </is>
       </c>
+      <c r="Q263" s="0" t="n">
+        <v>13</v>
+      </c>
     </row>
     <row r="264">
       <c r="B264" s="0" t="n">
@@ -14693,6 +15489,9 @@
           <t>Balance variant; canonical=70; role=heavy; profile=D04; level=13; wave=20</t>
         </is>
       </c>
+      <c r="Q264" s="0" t="n">
+        <v>13</v>
+      </c>
     </row>
     <row r="265">
       <c r="B265" s="0" t="n">
@@ -14744,6 +15543,9 @@
           <t>Balance variant; canonical=127; role=heavy; profile=D04; level=13; wave=20</t>
         </is>
       </c>
+      <c r="Q265" s="0" t="n">
+        <v>13</v>
+      </c>
     </row>
     <row r="266">
       <c r="B266" s="0" t="n">
@@ -14795,6 +15597,9 @@
           <t>Balance variant; canonical=11; role=air; profile=D04; level=13; wave=21</t>
         </is>
       </c>
+      <c r="Q266" s="0" t="n">
+        <v>13</v>
+      </c>
     </row>
     <row r="267">
       <c r="B267" s="0" t="n">
@@ -14846,6 +15651,9 @@
           <t>Balance variant; canonical=13; role=air; profile=D04; level=13; wave=21</t>
         </is>
       </c>
+      <c r="Q267" s="0" t="n">
+        <v>13</v>
+      </c>
     </row>
     <row r="268">
       <c r="B268" s="0" t="n">
@@ -14897,6 +15705,9 @@
           <t>Balance variant; canonical=14; role=air; profile=D04; level=13; wave=21</t>
         </is>
       </c>
+      <c r="Q268" s="0" t="n">
+        <v>13</v>
+      </c>
     </row>
     <row r="269">
       <c r="B269" s="0" t="n">
@@ -14948,6 +15759,9 @@
           <t>Balance variant; canonical=17; role=normal; profile=D04; level=13; wave=21</t>
         </is>
       </c>
+      <c r="Q269" s="0" t="n">
+        <v>13</v>
+      </c>
     </row>
     <row r="270">
       <c r="B270" s="0" t="n">
@@ -14999,6 +15813,9 @@
           <t>Balance variant; canonical=18; role=normal; profile=D04; level=13; wave=21</t>
         </is>
       </c>
+      <c r="Q270" s="0" t="n">
+        <v>13</v>
+      </c>
     </row>
     <row r="271">
       <c r="B271" s="0" t="n">
@@ -15050,6 +15867,9 @@
           <t>Balance variant; canonical=30; role=fast; profile=D04; level=13; wave=21</t>
         </is>
       </c>
+      <c r="Q271" s="0" t="n">
+        <v>13</v>
+      </c>
     </row>
     <row r="272">
       <c r="B272" s="0" t="n">
@@ -15101,6 +15921,9 @@
           <t>Balance variant; canonical=31; role=heavy; profile=D04; level=13; wave=21</t>
         </is>
       </c>
+      <c r="Q272" s="0" t="n">
+        <v>13</v>
+      </c>
     </row>
     <row r="273">
       <c r="B273" s="0" t="n">
@@ -15152,6 +15975,9 @@
           <t>Balance variant; canonical=40; role=heavy; profile=D04; level=13; wave=21</t>
         </is>
       </c>
+      <c r="Q273" s="0" t="n">
+        <v>13</v>
+      </c>
     </row>
     <row r="274">
       <c r="B274" s="0" t="n">
@@ -15203,6 +16029,9 @@
           <t>Balance variant; canonical=58; role=fast; profile=D04; level=13; wave=21</t>
         </is>
       </c>
+      <c r="Q274" s="0" t="n">
+        <v>13</v>
+      </c>
     </row>
     <row r="275">
       <c r="B275" s="0" t="n">
@@ -15254,6 +16083,9 @@
           <t>Balance variant; canonical=64; role=fast; profile=D04; level=13; wave=21</t>
         </is>
       </c>
+      <c r="Q275" s="0" t="n">
+        <v>13</v>
+      </c>
     </row>
     <row r="276">
       <c r="B276" s="0" t="n">
@@ -15305,6 +16137,9 @@
           <t>Balance variant; canonical=67; role=heavy; profile=D04; level=13; wave=21</t>
         </is>
       </c>
+      <c r="Q276" s="0" t="n">
+        <v>13</v>
+      </c>
     </row>
     <row r="277">
       <c r="B277" s="0" t="n">
@@ -15356,6 +16191,9 @@
           <t>Balance variant; canonical=70; role=heavy; profile=D04; level=13; wave=21</t>
         </is>
       </c>
+      <c r="Q277" s="0" t="n">
+        <v>13</v>
+      </c>
     </row>
     <row r="278">
       <c r="B278" s="0" t="n">
@@ -15407,6 +16245,9 @@
           <t>Balance variant; canonical=83; role=medium; profile=D04; level=13; wave=21</t>
         </is>
       </c>
+      <c r="Q278" s="0" t="n">
+        <v>13</v>
+      </c>
     </row>
     <row r="279">
       <c r="B279" s="0" t="n">
@@ -15458,6 +16299,9 @@
           <t>Balance variant; canonical=84; role=swarm; profile=D04; level=13; wave=21</t>
         </is>
       </c>
+      <c r="Q279" s="0" t="n">
+        <v>13</v>
+      </c>
     </row>
     <row r="280">
       <c r="B280" s="0" t="n">
@@ -15509,6 +16353,9 @@
           <t>Balance variant; canonical=86; role=heavy; profile=D04; level=13; wave=21</t>
         </is>
       </c>
+      <c r="Q280" s="0" t="n">
+        <v>13</v>
+      </c>
     </row>
     <row r="281">
       <c r="B281" s="0" t="n">
@@ -15560,6 +16407,9 @@
           <t>Balance variant; canonical=88; role=heavy; profile=D04; level=13; wave=21</t>
         </is>
       </c>
+      <c r="Q281" s="0" t="n">
+        <v>13</v>
+      </c>
     </row>
     <row r="282">
       <c r="B282" s="0" t="n">
@@ -15611,6 +16461,9 @@
           <t>Balance variant; canonical=98; role=fast; profile=D04; level=13; wave=21</t>
         </is>
       </c>
+      <c r="Q282" s="0" t="n">
+        <v>13</v>
+      </c>
     </row>
     <row r="283">
       <c r="B283" s="0" t="n">
@@ -15662,6 +16515,9 @@
           <t>Balance variant; canonical=108; role=medium; profile=D04; level=13; wave=21</t>
         </is>
       </c>
+      <c r="Q283" s="0" t="n">
+        <v>13</v>
+      </c>
     </row>
     <row r="284">
       <c r="B284" s="0" t="n">
@@ -15713,6 +16569,9 @@
           <t>Balance variant; canonical=123; role=medium; profile=D04; level=13; wave=21</t>
         </is>
       </c>
+      <c r="Q284" s="0" t="n">
+        <v>13</v>
+      </c>
     </row>
     <row r="285">
       <c r="B285" s="0" t="n">
@@ -15764,6 +16623,9 @@
           <t>Balance variant; canonical=127; role=heavy; profile=D04; level=13; wave=21</t>
         </is>
       </c>
+      <c r="Q285" s="0" t="n">
+        <v>13</v>
+      </c>
     </row>
     <row r="286">
       <c r="B286" s="0" t="n">
@@ -15815,6 +16677,9 @@
           <t>Balance variant; canonical=11; role=air; profile=D04; level=13; wave=22</t>
         </is>
       </c>
+      <c r="Q286" s="0" t="n">
+        <v>13</v>
+      </c>
     </row>
     <row r="287">
       <c r="B287" s="0" t="n">
@@ -15866,6 +16731,9 @@
           <t>Balance variant; canonical=13; role=air; profile=D04; level=13; wave=22</t>
         </is>
       </c>
+      <c r="Q287" s="0" t="n">
+        <v>13</v>
+      </c>
     </row>
     <row r="288">
       <c r="B288" s="0" t="n">
@@ -15917,6 +16785,9 @@
           <t>Balance variant; canonical=14; role=air; profile=D04; level=13; wave=22</t>
         </is>
       </c>
+      <c r="Q288" s="0" t="n">
+        <v>13</v>
+      </c>
     </row>
     <row r="289">
       <c r="B289" s="0" t="n">
@@ -15968,6 +16839,9 @@
           <t>Balance variant; canonical=17; role=normal; profile=D04; level=13; wave=22</t>
         </is>
       </c>
+      <c r="Q289" s="0" t="n">
+        <v>13</v>
+      </c>
     </row>
     <row r="290">
       <c r="B290" s="0" t="n">
@@ -16019,6 +16893,9 @@
           <t>Balance variant; canonical=18; role=normal; profile=D04; level=13; wave=22</t>
         </is>
       </c>
+      <c r="Q290" s="0" t="n">
+        <v>13</v>
+      </c>
     </row>
     <row r="291">
       <c r="B291" s="0" t="n">
@@ -16070,6 +16947,9 @@
           <t>Balance variant; canonical=30; role=fast; profile=D04; level=13; wave=22</t>
         </is>
       </c>
+      <c r="Q291" s="0" t="n">
+        <v>13</v>
+      </c>
     </row>
     <row r="292">
       <c r="B292" s="0" t="n">
@@ -16121,6 +17001,9 @@
           <t>Balance variant; canonical=31; role=heavy; profile=D04; level=13; wave=22</t>
         </is>
       </c>
+      <c r="Q292" s="0" t="n">
+        <v>13</v>
+      </c>
     </row>
     <row r="293">
       <c r="B293" s="0" t="n">
@@ -16172,6 +17055,9 @@
           <t>Balance variant; canonical=40; role=heavy; profile=D04; level=13; wave=22</t>
         </is>
       </c>
+      <c r="Q293" s="0" t="n">
+        <v>13</v>
+      </c>
     </row>
     <row r="294">
       <c r="B294" s="0" t="n">
@@ -16223,6 +17109,9 @@
           <t>Balance variant; canonical=58; role=fast; profile=D04; level=13; wave=22</t>
         </is>
       </c>
+      <c r="Q294" s="0" t="n">
+        <v>13</v>
+      </c>
     </row>
     <row r="295">
       <c r="B295" s="0" t="n">
@@ -16274,6 +17163,9 @@
           <t>Balance variant; canonical=64; role=fast; profile=D04; level=13; wave=22</t>
         </is>
       </c>
+      <c r="Q295" s="0" t="n">
+        <v>13</v>
+      </c>
     </row>
     <row r="296">
       <c r="B296" s="0" t="n">
@@ -16325,6 +17217,9 @@
           <t>Balance variant; canonical=67; role=heavy; profile=D04; level=13; wave=22</t>
         </is>
       </c>
+      <c r="Q296" s="0" t="n">
+        <v>13</v>
+      </c>
     </row>
     <row r="297">
       <c r="B297" s="0" t="n">
@@ -16376,6 +17271,9 @@
           <t>Balance variant; canonical=70; role=heavy; profile=D04; level=13; wave=22</t>
         </is>
       </c>
+      <c r="Q297" s="0" t="n">
+        <v>13</v>
+      </c>
     </row>
     <row r="298">
       <c r="B298" s="0" t="n">
@@ -16427,6 +17325,9 @@
           <t>Balance variant; canonical=80; role=heavy; profile=D04; level=13; wave=22</t>
         </is>
       </c>
+      <c r="Q298" s="0" t="n">
+        <v>13</v>
+      </c>
     </row>
     <row r="299">
       <c r="B299" s="0" t="n">
@@ -16478,6 +17379,9 @@
           <t>Balance variant; canonical=83; role=medium; profile=D04; level=13; wave=22</t>
         </is>
       </c>
+      <c r="Q299" s="0" t="n">
+        <v>13</v>
+      </c>
     </row>
     <row r="300">
       <c r="B300" s="0" t="n">
@@ -16529,6 +17433,9 @@
           <t>Balance variant; canonical=84; role=swarm; profile=D04; level=13; wave=22</t>
         </is>
       </c>
+      <c r="Q300" s="0" t="n">
+        <v>13</v>
+      </c>
     </row>
     <row r="301">
       <c r="B301" s="0" t="n">
@@ -16580,6 +17487,9 @@
           <t>Balance variant; canonical=88; role=heavy; profile=D04; level=13; wave=22</t>
         </is>
       </c>
+      <c r="Q301" s="0" t="n">
+        <v>13</v>
+      </c>
     </row>
     <row r="302">
       <c r="B302" s="0" t="n">
@@ -16631,6 +17541,9 @@
           <t>Balance variant; canonical=98; role=fast; profile=D04; level=13; wave=22</t>
         </is>
       </c>
+      <c r="Q302" s="0" t="n">
+        <v>13</v>
+      </c>
     </row>
     <row r="303">
       <c r="B303" s="0" t="n">
@@ -16682,6 +17595,9 @@
           <t>Balance variant; canonical=108; role=medium; profile=D04; level=13; wave=22</t>
         </is>
       </c>
+      <c r="Q303" s="0" t="n">
+        <v>13</v>
+      </c>
     </row>
     <row r="304">
       <c r="B304" s="0" t="n">
@@ -16733,6 +17649,9 @@
           <t>Balance variant; canonical=123; role=medium; profile=D04; level=13; wave=22</t>
         </is>
       </c>
+      <c r="Q304" s="0" t="n">
+        <v>13</v>
+      </c>
     </row>
     <row r="305">
       <c r="B305" s="0" t="n">
@@ -16784,6 +17703,9 @@
           <t>Balance variant; canonical=127; role=heavy; profile=D04; level=13; wave=22</t>
         </is>
       </c>
+      <c r="Q305" s="0" t="n">
+        <v>13</v>
+      </c>
     </row>
     <row r="306">
       <c r="B306" s="0" t="n">
@@ -16835,6 +17757,9 @@
           <t>Balance variant; canonical=11; role=air; profile=D04; level=13; wave=23</t>
         </is>
       </c>
+      <c r="Q306" s="0" t="n">
+        <v>13</v>
+      </c>
     </row>
     <row r="307">
       <c r="B307" s="0" t="n">
@@ -16886,6 +17811,9 @@
           <t>Balance variant; canonical=13; role=air; profile=D04; level=13; wave=23</t>
         </is>
       </c>
+      <c r="Q307" s="0" t="n">
+        <v>13</v>
+      </c>
     </row>
     <row r="308">
       <c r="B308" s="0" t="n">
@@ -16937,6 +17865,9 @@
           <t>Balance variant; canonical=14; role=air; profile=D04; level=13; wave=23</t>
         </is>
       </c>
+      <c r="Q308" s="0" t="n">
+        <v>13</v>
+      </c>
     </row>
     <row r="309">
       <c r="B309" s="0" t="n">
@@ -16988,6 +17919,9 @@
           <t>Balance variant; canonical=17; role=normal; profile=D04; level=13; wave=23</t>
         </is>
       </c>
+      <c r="Q309" s="0" t="n">
+        <v>13</v>
+      </c>
     </row>
     <row r="310">
       <c r="B310" s="0" t="n">
@@ -17039,6 +17973,9 @@
           <t>Balance variant; canonical=18; role=normal; profile=D04; level=13; wave=23</t>
         </is>
       </c>
+      <c r="Q310" s="0" t="n">
+        <v>13</v>
+      </c>
     </row>
     <row r="311">
       <c r="B311" s="0" t="n">
@@ -17090,6 +18027,9 @@
           <t>Balance variant; canonical=30; role=fast; profile=D04; level=13; wave=23</t>
         </is>
       </c>
+      <c r="Q311" s="0" t="n">
+        <v>13</v>
+      </c>
     </row>
     <row r="312">
       <c r="B312" s="0" t="n">
@@ -17141,6 +18081,9 @@
           <t>Balance variant; canonical=40; role=heavy; profile=D04; level=13; wave=23</t>
         </is>
       </c>
+      <c r="Q312" s="0" t="n">
+        <v>13</v>
+      </c>
     </row>
     <row r="313">
       <c r="B313" s="0" t="n">
@@ -17192,6 +18135,9 @@
           <t>Balance variant; canonical=58; role=fast; profile=D04; level=13; wave=23</t>
         </is>
       </c>
+      <c r="Q313" s="0" t="n">
+        <v>13</v>
+      </c>
     </row>
     <row r="314">
       <c r="B314" s="0" t="n">
@@ -17243,6 +18189,9 @@
           <t>Balance variant; canonical=64; role=fast; profile=D04; level=13; wave=23</t>
         </is>
       </c>
+      <c r="Q314" s="0" t="n">
+        <v>13</v>
+      </c>
     </row>
     <row r="315">
       <c r="B315" s="0" t="n">
@@ -17294,6 +18243,9 @@
           <t>Balance variant; canonical=67; role=heavy; profile=D04; level=13; wave=23</t>
         </is>
       </c>
+      <c r="Q315" s="0" t="n">
+        <v>13</v>
+      </c>
     </row>
     <row r="316">
       <c r="B316" s="0" t="n">
@@ -17345,6 +18297,9 @@
           <t>Balance variant; canonical=70; role=heavy; profile=D04; level=13; wave=23</t>
         </is>
       </c>
+      <c r="Q316" s="0" t="n">
+        <v>13</v>
+      </c>
     </row>
     <row r="317">
       <c r="B317" s="0" t="n">
@@ -17396,6 +18351,9 @@
           <t>Balance variant; canonical=80; role=heavy; profile=D04; level=13; wave=23</t>
         </is>
       </c>
+      <c r="Q317" s="0" t="n">
+        <v>13</v>
+      </c>
     </row>
     <row r="318">
       <c r="B318" s="0" t="n">
@@ -17447,6 +18405,9 @@
           <t>Balance variant; canonical=83; role=medium; profile=D04; level=13; wave=23</t>
         </is>
       </c>
+      <c r="Q318" s="0" t="n">
+        <v>13</v>
+      </c>
     </row>
     <row r="319">
       <c r="B319" s="0" t="n">
@@ -17498,6 +18459,9 @@
           <t>Balance variant; canonical=84; role=swarm; profile=D04; level=13; wave=23</t>
         </is>
       </c>
+      <c r="Q319" s="0" t="n">
+        <v>13</v>
+      </c>
     </row>
     <row r="320">
       <c r="B320" s="0" t="n">
@@ -17549,6 +18513,9 @@
           <t>Balance variant; canonical=86; role=heavy; profile=D04; level=13; wave=23</t>
         </is>
       </c>
+      <c r="Q320" s="0" t="n">
+        <v>13</v>
+      </c>
     </row>
     <row r="321">
       <c r="B321" s="0" t="n">
@@ -17600,6 +18567,9 @@
           <t>Balance variant; canonical=88; role=heavy; profile=D04; level=13; wave=23</t>
         </is>
       </c>
+      <c r="Q321" s="0" t="n">
+        <v>13</v>
+      </c>
     </row>
     <row r="322">
       <c r="B322" s="0" t="n">
@@ -17651,6 +18621,9 @@
           <t>Balance variant; canonical=98; role=fast; profile=D04; level=13; wave=23</t>
         </is>
       </c>
+      <c r="Q322" s="0" t="n">
+        <v>13</v>
+      </c>
     </row>
     <row r="323">
       <c r="B323" s="0" t="n">
@@ -17702,6 +18675,9 @@
           <t>Balance variant; canonical=108; role=medium; profile=D04; level=13; wave=23</t>
         </is>
       </c>
+      <c r="Q323" s="0" t="n">
+        <v>13</v>
+      </c>
     </row>
     <row r="324">
       <c r="B324" s="0" t="n">
@@ -17753,6 +18729,9 @@
           <t>Balance variant; canonical=123; role=medium; profile=D04; level=13; wave=23</t>
         </is>
       </c>
+      <c r="Q324" s="0" t="n">
+        <v>13</v>
+      </c>
     </row>
     <row r="325">
       <c r="B325" s="0" t="n">
@@ -17804,6 +18783,9 @@
           <t>Balance variant; canonical=127; role=heavy; profile=D04; level=13; wave=23</t>
         </is>
       </c>
+      <c r="Q325" s="0" t="n">
+        <v>13</v>
+      </c>
     </row>
     <row r="326">
       <c r="B326" s="0" t="n">
@@ -17855,6 +18837,9 @@
           <t>Balance variant; canonical=11; role=air; profile=D04; level=13; wave=24</t>
         </is>
       </c>
+      <c r="Q326" s="0" t="n">
+        <v>13</v>
+      </c>
     </row>
     <row r="327">
       <c r="B327" s="0" t="n">
@@ -17906,6 +18891,9 @@
           <t>Balance variant; canonical=13; role=air; profile=D04; level=13; wave=24</t>
         </is>
       </c>
+      <c r="Q327" s="0" t="n">
+        <v>13</v>
+      </c>
     </row>
     <row r="328">
       <c r="B328" s="0" t="n">
@@ -17957,6 +18945,9 @@
           <t>Balance variant; canonical=14; role=air; profile=D04; level=13; wave=24</t>
         </is>
       </c>
+      <c r="Q328" s="0" t="n">
+        <v>13</v>
+      </c>
     </row>
     <row r="329">
       <c r="B329" s="0" t="n">
@@ -18008,6 +18999,9 @@
           <t>Balance variant; canonical=17; role=normal; profile=D04; level=13; wave=24</t>
         </is>
       </c>
+      <c r="Q329" s="0" t="n">
+        <v>13</v>
+      </c>
     </row>
     <row r="330">
       <c r="B330" s="0" t="n">
@@ -18059,6 +19053,9 @@
           <t>Balance variant; canonical=18; role=normal; profile=D04; level=13; wave=24</t>
         </is>
       </c>
+      <c r="Q330" s="0" t="n">
+        <v>13</v>
+      </c>
     </row>
     <row r="331">
       <c r="B331" s="0" t="n">
@@ -18110,6 +19107,9 @@
           <t>Balance variant; canonical=30; role=fast; profile=D04; level=13; wave=24</t>
         </is>
       </c>
+      <c r="Q331" s="0" t="n">
+        <v>13</v>
+      </c>
     </row>
     <row r="332">
       <c r="B332" s="0" t="n">
@@ -18161,6 +19161,9 @@
           <t>Balance variant; canonical=31; role=heavy; profile=D04; level=13; wave=24</t>
         </is>
       </c>
+      <c r="Q332" s="0" t="n">
+        <v>13</v>
+      </c>
     </row>
     <row r="333">
       <c r="B333" s="0" t="n">
@@ -18212,6 +19215,9 @@
           <t>Balance variant; canonical=58; role=fast; profile=D04; level=13; wave=24</t>
         </is>
       </c>
+      <c r="Q333" s="0" t="n">
+        <v>13</v>
+      </c>
     </row>
     <row r="334">
       <c r="B334" s="0" t="n">
@@ -18263,6 +19269,9 @@
           <t>Balance variant; canonical=64; role=fast; profile=D04; level=13; wave=24</t>
         </is>
       </c>
+      <c r="Q334" s="0" t="n">
+        <v>13</v>
+      </c>
     </row>
     <row r="335">
       <c r="B335" s="0" t="n">
@@ -18314,6 +19323,9 @@
           <t>Balance variant; canonical=67; role=heavy; profile=D04; level=13; wave=24</t>
         </is>
       </c>
+      <c r="Q335" s="0" t="n">
+        <v>13</v>
+      </c>
     </row>
     <row r="336">
       <c r="B336" s="0" t="n">
@@ -18365,6 +19377,9 @@
           <t>Balance variant; canonical=70; role=heavy; profile=D04; level=13; wave=24</t>
         </is>
       </c>
+      <c r="Q336" s="0" t="n">
+        <v>13</v>
+      </c>
     </row>
     <row r="337">
       <c r="B337" s="0" t="n">
@@ -18416,6 +19431,9 @@
           <t>Balance variant; canonical=80; role=heavy; profile=D04; level=13; wave=24</t>
         </is>
       </c>
+      <c r="Q337" s="0" t="n">
+        <v>13</v>
+      </c>
     </row>
     <row r="338">
       <c r="B338" s="0" t="n">
@@ -18467,6 +19485,9 @@
           <t>Balance variant; canonical=83; role=medium; profile=D04; level=13; wave=24</t>
         </is>
       </c>
+      <c r="Q338" s="0" t="n">
+        <v>13</v>
+      </c>
     </row>
     <row r="339">
       <c r="B339" s="0" t="n">
@@ -18518,6 +19539,9 @@
           <t>Balance variant; canonical=84; role=swarm; profile=D04; level=13; wave=24</t>
         </is>
       </c>
+      <c r="Q339" s="0" t="n">
+        <v>13</v>
+      </c>
     </row>
     <row r="340">
       <c r="B340" s="0" t="n">
@@ -18569,6 +19593,9 @@
           <t>Balance variant; canonical=86; role=heavy; profile=D04; level=13; wave=24</t>
         </is>
       </c>
+      <c r="Q340" s="0" t="n">
+        <v>13</v>
+      </c>
     </row>
     <row r="341">
       <c r="B341" s="0" t="n">
@@ -18620,6 +19647,9 @@
           <t>Balance variant; canonical=88; role=heavy; profile=D04; level=13; wave=24</t>
         </is>
       </c>
+      <c r="Q341" s="0" t="n">
+        <v>13</v>
+      </c>
     </row>
     <row r="342">
       <c r="B342" s="0" t="n">
@@ -18671,6 +19701,9 @@
           <t>Balance variant; canonical=98; role=fast; profile=D04; level=13; wave=24</t>
         </is>
       </c>
+      <c r="Q342" s="0" t="n">
+        <v>13</v>
+      </c>
     </row>
     <row r="343">
       <c r="B343" s="0" t="n">
@@ -18722,6 +19755,9 @@
           <t>Balance variant; canonical=108; role=medium; profile=D04; level=13; wave=24</t>
         </is>
       </c>
+      <c r="Q343" s="0" t="n">
+        <v>13</v>
+      </c>
     </row>
     <row r="344">
       <c r="B344" s="0" t="n">
@@ -18773,6 +19809,9 @@
           <t>Balance variant; canonical=123; role=medium; profile=D04; level=13; wave=24</t>
         </is>
       </c>
+      <c r="Q344" s="0" t="n">
+        <v>13</v>
+      </c>
     </row>
     <row r="345">
       <c r="B345" s="0" t="n">
@@ -18824,6 +19863,9 @@
           <t>Balance variant; canonical=127; role=heavy; profile=D04; level=13; wave=24</t>
         </is>
       </c>
+      <c r="Q345" s="0" t="n">
+        <v>13</v>
+      </c>
     </row>
     <row r="346">
       <c r="B346" s="0" t="n">
@@ -18875,6 +19917,9 @@
           <t>Balance variant; canonical=11; role=air; profile=D04; level=13; wave=25</t>
         </is>
       </c>
+      <c r="Q346" s="0" t="n">
+        <v>13</v>
+      </c>
     </row>
     <row r="347">
       <c r="B347" s="0" t="n">
@@ -18926,6 +19971,9 @@
           <t>Balance variant; canonical=13; role=air; profile=D04; level=13; wave=25</t>
         </is>
       </c>
+      <c r="Q347" s="0" t="n">
+        <v>13</v>
+      </c>
     </row>
     <row r="348">
       <c r="B348" s="0" t="n">
@@ -18977,6 +20025,9 @@
           <t>Balance variant; canonical=14; role=air; profile=D04; level=13; wave=25</t>
         </is>
       </c>
+      <c r="Q348" s="0" t="n">
+        <v>13</v>
+      </c>
     </row>
     <row r="349">
       <c r="B349" s="0" t="n">
@@ -19028,6 +20079,9 @@
           <t>Balance variant; canonical=17; role=normal; profile=D04; level=13; wave=25</t>
         </is>
       </c>
+      <c r="Q349" s="0" t="n">
+        <v>13</v>
+      </c>
     </row>
     <row r="350">
       <c r="B350" s="0" t="n">
@@ -19079,6 +20133,9 @@
           <t>Balance variant; canonical=18; role=normal; profile=D04; level=13; wave=25</t>
         </is>
       </c>
+      <c r="Q350" s="0" t="n">
+        <v>13</v>
+      </c>
     </row>
     <row r="351">
       <c r="B351" s="0" t="n">
@@ -19130,6 +20187,9 @@
           <t>Balance variant; canonical=30; role=fast; profile=D04; level=13; wave=25</t>
         </is>
       </c>
+      <c r="Q351" s="0" t="n">
+        <v>13</v>
+      </c>
     </row>
     <row r="352">
       <c r="B352" s="0" t="n">
@@ -19181,6 +20241,9 @@
           <t>Balance variant; canonical=31; role=heavy; profile=D04; level=13; wave=25</t>
         </is>
       </c>
+      <c r="Q352" s="0" t="n">
+        <v>13</v>
+      </c>
     </row>
     <row r="353">
       <c r="B353" s="0" t="n">
@@ -19232,6 +20295,9 @@
           <t>Balance variant; canonical=40; role=heavy; profile=D04; level=13; wave=25</t>
         </is>
       </c>
+      <c r="Q353" s="0" t="n">
+        <v>13</v>
+      </c>
     </row>
     <row r="354">
       <c r="B354" s="0" t="n">
@@ -19283,6 +20349,9 @@
           <t>Balance variant; canonical=58; role=fast; profile=D04; level=13; wave=25</t>
         </is>
       </c>
+      <c r="Q354" s="0" t="n">
+        <v>13</v>
+      </c>
     </row>
     <row r="355">
       <c r="B355" s="0" t="n">
@@ -19334,6 +20403,9 @@
           <t>Balance variant; canonical=64; role=fast; profile=D04; level=13; wave=25</t>
         </is>
       </c>
+      <c r="Q355" s="0" t="n">
+        <v>13</v>
+      </c>
     </row>
     <row r="356">
       <c r="B356" s="0" t="n">
@@ -19385,6 +20457,9 @@
           <t>Balance variant; canonical=67; role=heavy; profile=D04; level=13; wave=25</t>
         </is>
       </c>
+      <c r="Q356" s="0" t="n">
+        <v>13</v>
+      </c>
     </row>
     <row r="357">
       <c r="B357" s="0" t="n">
@@ -19436,6 +20511,9 @@
           <t>Balance variant; canonical=70; role=heavy; profile=D04; level=13; wave=25</t>
         </is>
       </c>
+      <c r="Q357" s="0" t="n">
+        <v>13</v>
+      </c>
     </row>
     <row r="358">
       <c r="B358" s="0" t="n">
@@ -19487,6 +20565,9 @@
           <t>Balance variant; canonical=80; role=heavy; profile=D04; level=13; wave=25</t>
         </is>
       </c>
+      <c r="Q358" s="0" t="n">
+        <v>13</v>
+      </c>
     </row>
     <row r="359">
       <c r="B359" s="0" t="n">
@@ -19538,6 +20619,9 @@
           <t>Balance variant; canonical=83; role=medium; profile=D04; level=13; wave=25</t>
         </is>
       </c>
+      <c r="Q359" s="0" t="n">
+        <v>13</v>
+      </c>
     </row>
     <row r="360">
       <c r="B360" s="0" t="n">
@@ -19589,6 +20673,9 @@
           <t>Balance variant; canonical=84; role=swarm; profile=D04; level=13; wave=25</t>
         </is>
       </c>
+      <c r="Q360" s="0" t="n">
+        <v>13</v>
+      </c>
     </row>
     <row r="361">
       <c r="B361" s="0" t="n">
@@ -19640,6 +20727,9 @@
           <t>Balance variant; canonical=86; role=heavy; profile=D04; level=13; wave=25</t>
         </is>
       </c>
+      <c r="Q361" s="0" t="n">
+        <v>13</v>
+      </c>
     </row>
     <row r="362">
       <c r="B362" s="0" t="n">
@@ -19691,6 +20781,9 @@
           <t>Balance variant; canonical=88; role=heavy; profile=D04; level=13; wave=25</t>
         </is>
       </c>
+      <c r="Q362" s="0" t="n">
+        <v>13</v>
+      </c>
     </row>
     <row r="363">
       <c r="B363" s="0" t="n">
@@ -19742,6 +20835,9 @@
           <t>Balance variant; canonical=98; role=fast; profile=D04; level=13; wave=25</t>
         </is>
       </c>
+      <c r="Q363" s="0" t="n">
+        <v>13</v>
+      </c>
     </row>
     <row r="364">
       <c r="B364" s="0" t="n">
@@ -19793,6 +20889,9 @@
           <t>Balance variant; canonical=108; role=medium; profile=D04; level=13; wave=25</t>
         </is>
       </c>
+      <c r="Q364" s="0" t="n">
+        <v>13</v>
+      </c>
     </row>
     <row r="365">
       <c r="B365" s="0" t="n">
@@ -19844,6 +20943,9 @@
           <t>Balance variant; canonical=123; role=medium; profile=D04; level=13; wave=25</t>
         </is>
       </c>
+      <c r="Q365" s="0" t="n">
+        <v>13</v>
+      </c>
     </row>
     <row r="366">
       <c r="B366" s="0" t="n">
@@ -19895,6 +20997,9 @@
           <t>Balance variant; canonical=130; role=boss; profile=D04; level=13; wave=25</t>
         </is>
       </c>
+      <c r="Q366" s="0" t="n">
+        <v>13</v>
+      </c>
     </row>
     <row r="367">
       <c r="B367" s="0" t="n">
@@ -19946,6 +21051,9 @@
           <t>Balance variant; canonical=127; role=heavy; profile=D04; level=13; wave=11</t>
         </is>
       </c>
+      <c r="Q367" s="0" t="n">
+        <v>13</v>
+      </c>
     </row>
     <row r="368">
       <c r="B368" s="0" t="n">
@@ -19997,6 +21105,9 @@
           <t>Balance variant; canonical=70; role=heavy; profile=D04; level=13; wave=12</t>
         </is>
       </c>
+      <c r="Q368" s="0" t="n">
+        <v>13</v>
+      </c>
     </row>
     <row r="369">
       <c r="B369" s="0" t="n">
@@ -20048,6 +21159,9 @@
           <t>Balance variant; canonical=67; role=heavy; profile=D04; level=13; wave=13</t>
         </is>
       </c>
+      <c r="Q369" s="0" t="n">
+        <v>13</v>
+      </c>
     </row>
     <row r="370">
       <c r="B370" s="0" t="n">
@@ -20099,6 +21213,9 @@
           <t>Balance variant; canonical=88; role=heavy; profile=D04; level=13; wave=13</t>
         </is>
       </c>
+      <c r="Q370" s="0" t="n">
+        <v>13</v>
+      </c>
     </row>
     <row r="371">
       <c r="B371" s="0" t="n">
@@ -20150,6 +21267,9 @@
           <t>Balance variant; canonical=80; role=heavy; profile=D04; level=13; wave=14</t>
         </is>
       </c>
+      <c r="Q371" s="0" t="n">
+        <v>13</v>
+      </c>
     </row>
     <row r="372">
       <c r="B372" s="0" t="n">
@@ -20201,6 +21321,9 @@
           <t>Balance variant; canonical=88; role=heavy; profile=D04; level=13; wave=14</t>
         </is>
       </c>
+      <c r="Q372" s="0" t="n">
+        <v>13</v>
+      </c>
     </row>
     <row r="373">
       <c r="B373" s="0" t="n">
@@ -20252,6 +21375,9 @@
           <t>Balance variant; canonical=80; role=heavy; profile=D04; level=13; wave=15</t>
         </is>
       </c>
+      <c r="Q373" s="0" t="n">
+        <v>13</v>
+      </c>
     </row>
     <row r="374">
       <c r="B374" s="0" t="n">
@@ -20303,6 +21429,9 @@
           <t>Balance variant; canonical=86; role=heavy; profile=D04; level=13; wave=15</t>
         </is>
       </c>
+      <c r="Q374" s="0" t="n">
+        <v>13</v>
+      </c>
     </row>
     <row r="375">
       <c r="B375" s="0" t="n">
@@ -20354,6 +21483,9 @@
           <t>Balance variant; canonical=31; role=heavy; profile=D04; level=13; wave=16</t>
         </is>
       </c>
+      <c r="Q375" s="0" t="n">
+        <v>13</v>
+      </c>
     </row>
     <row r="376">
       <c r="B376" s="0" t="n">
@@ -20405,6 +21537,9 @@
           <t>Balance variant; canonical=40; role=heavy; profile=D04; level=13; wave=16</t>
         </is>
       </c>
+      <c r="Q376" s="0" t="n">
+        <v>13</v>
+      </c>
     </row>
     <row r="377">
       <c r="B377" s="0" t="n">
@@ -20456,6 +21591,9 @@
           <t>Balance variant; canonical=40; role=heavy; profile=D04; level=13; wave=17</t>
         </is>
       </c>
+      <c r="Q377" s="0" t="n">
+        <v>13</v>
+      </c>
     </row>
     <row r="378">
       <c r="B378" s="0" t="n">
@@ -20507,6 +21645,9 @@
           <t>Balance variant; canonical=127; role=heavy; profile=D04; level=13; wave=17</t>
         </is>
       </c>
+      <c r="Q378" s="0" t="n">
+        <v>13</v>
+      </c>
     </row>
     <row r="379">
       <c r="B379" s="0" t="n">
@@ -20558,6 +21699,9 @@
           <t>Balance variant; canonical=70; role=heavy; profile=D04; level=13; wave=18</t>
         </is>
       </c>
+      <c r="Q379" s="0" t="n">
+        <v>13</v>
+      </c>
     </row>
     <row r="380">
       <c r="B380" s="0" t="n">
@@ -20609,6 +21753,9 @@
           <t>Balance variant; canonical=127; role=heavy; profile=D04; level=13; wave=18</t>
         </is>
       </c>
+      <c r="Q380" s="0" t="n">
+        <v>13</v>
+      </c>
     </row>
     <row r="381">
       <c r="B381" s="0" t="n">
@@ -20660,6 +21807,9 @@
           <t>Balance variant; canonical=67; role=heavy; profile=D04; level=13; wave=19</t>
         </is>
       </c>
+      <c r="Q381" s="0" t="n">
+        <v>13</v>
+      </c>
     </row>
     <row r="382">
       <c r="B382" s="0" t="n">
@@ -20711,6 +21861,9 @@
           <t>Balance variant; canonical=70; role=heavy; profile=D04; level=13; wave=19</t>
         </is>
       </c>
+      <c r="Q382" s="0" t="n">
+        <v>13</v>
+      </c>
     </row>
     <row r="383">
       <c r="B383" s="0" t="n">
@@ -20762,6 +21915,9 @@
           <t>Balance variant; canonical=67; role=heavy; profile=D04; level=13; wave=20</t>
         </is>
       </c>
+      <c r="Q383" s="0" t="n">
+        <v>13</v>
+      </c>
     </row>
     <row r="384">
       <c r="B384" s="0" t="n">
@@ -20813,6 +21969,9 @@
           <t>Balance variant; canonical=88; role=heavy; profile=D04; level=13; wave=20</t>
         </is>
       </c>
+      <c r="Q384" s="0" t="n">
+        <v>13</v>
+      </c>
     </row>
     <row r="385">
       <c r="B385" s="0" t="n">
@@ -20864,6 +22023,9 @@
           <t>Balance variant; canonical=80; role=heavy; profile=D04; level=13; wave=21</t>
         </is>
       </c>
+      <c r="Q385" s="0" t="n">
+        <v>13</v>
+      </c>
     </row>
     <row r="386">
       <c r="B386" s="0" t="n">
@@ -20915,6 +22077,9 @@
           <t>Balance variant; canonical=86; role=heavy; profile=D04; level=13; wave=22</t>
         </is>
       </c>
+      <c r="Q386" s="0" t="n">
+        <v>13</v>
+      </c>
     </row>
     <row r="387">
       <c r="B387" s="0" t="n">
@@ -20966,6 +22131,9 @@
           <t>Balance variant; canonical=31; role=heavy; profile=D04; level=13; wave=23</t>
         </is>
       </c>
+      <c r="Q387" s="0" t="n">
+        <v>13</v>
+      </c>
     </row>
     <row r="388">
       <c r="B388" s="0" t="n">
@@ -21017,6 +22185,9 @@
           <t>Balance variant; canonical=40; role=heavy; profile=D04; level=13; wave=24</t>
         </is>
       </c>
+      <c r="Q388" s="0" t="n">
+        <v>13</v>
+      </c>
     </row>
     <row r="389">
       <c r="B389" s="0" t="n">
@@ -21068,6 +22239,9 @@
           <t>Balance variant; canonical=127; role=heavy; profile=D04; level=13; wave=25</t>
         </is>
       </c>
+      <c r="Q389" s="0" t="n">
+        <v>13</v>
+      </c>
     </row>
     <row r="390">
       <c r="B390" s="0" t="n">
@@ -21119,6 +22293,9 @@
           <t>Balance variant; canonical=67; role=heavy; profile=D04; level=13; wave=11</t>
         </is>
       </c>
+      <c r="Q390" s="0" t="n">
+        <v>13</v>
+      </c>
     </row>
     <row r="391">
       <c r="B391" s="0" t="n">
@@ -21170,6 +22347,9 @@
           <t>Balance variant; canonical=70; role=heavy; profile=D04; level=13; wave=11</t>
         </is>
       </c>
+      <c r="Q391" s="0" t="n">
+        <v>13</v>
+      </c>
     </row>
     <row r="392">
       <c r="B392" s="0" t="n">
@@ -21221,6 +22401,9 @@
           <t>Balance variant; canonical=67; role=heavy; profile=D04; level=13; wave=12</t>
         </is>
       </c>
+      <c r="Q392" s="0" t="n">
+        <v>13</v>
+      </c>
     </row>
     <row r="393">
       <c r="B393" s="0" t="n">
@@ -21272,6 +22455,9 @@
           <t>Balance variant; canonical=88; role=heavy; profile=D04; level=13; wave=12</t>
         </is>
       </c>
+      <c r="Q393" s="0" t="n">
+        <v>13</v>
+      </c>
     </row>
     <row r="394">
       <c r="B394" s="0" t="n">
@@ -21323,6 +22509,9 @@
           <t>Balance variant; canonical=80; role=heavy; profile=D04; level=13; wave=13</t>
         </is>
       </c>
+      <c r="Q394" s="0" t="n">
+        <v>13</v>
+      </c>
     </row>
     <row r="395">
       <c r="B395" s="0" t="n">
@@ -21374,6 +22563,9 @@
           <t>Balance variant; canonical=86; role=heavy; profile=D04; level=13; wave=14</t>
         </is>
       </c>
+      <c r="Q395" s="0" t="n">
+        <v>13</v>
+      </c>
     </row>
     <row r="396">
       <c r="B396" s="0" t="n">
@@ -21425,6 +22617,9 @@
           <t>Balance variant; canonical=31; role=heavy; profile=D04; level=13; wave=15</t>
         </is>
       </c>
+      <c r="Q396" s="0" t="n">
+        <v>13</v>
+      </c>
     </row>
     <row r="397">
       <c r="B397" s="0" t="n">
@@ -21476,6 +22671,9 @@
           <t>Balance variant; canonical=2; role=air; profile=D04; level=13; wave=3</t>
         </is>
       </c>
+      <c r="Q397" s="0" t="n">
+        <v>13</v>
+      </c>
     </row>
     <row r="398">
       <c r="B398" s="0" t="n">
@@ -21527,6 +22725,9 @@
           <t>Balance variant; canonical=11; role=air; profile=D04; level=13; wave=3</t>
         </is>
       </c>
+      <c r="Q398" s="0" t="n">
+        <v>13</v>
+      </c>
     </row>
     <row r="399">
       <c r="B399" s="0" t="n">
@@ -21578,6 +22779,9 @@
           <t>Balance variant; canonical=12; role=air; profile=D04; level=13; wave=3</t>
         </is>
       </c>
+      <c r="Q399" s="0" t="n">
+        <v>13</v>
+      </c>
     </row>
     <row r="400">
       <c r="B400" s="0" t="n">
@@ -21629,6 +22833,9 @@
           <t>Balance variant; canonical=13; role=air; profile=D04; level=13; wave=3</t>
         </is>
       </c>
+      <c r="Q400" s="0" t="n">
+        <v>13</v>
+      </c>
     </row>
     <row r="401">
       <c r="B401" s="0" t="n">
@@ -21680,6 +22887,9 @@
           <t>Balance variant; canonical=14; role=air; profile=D04; level=13; wave=3</t>
         </is>
       </c>
+      <c r="Q401" s="0" t="n">
+        <v>13</v>
+      </c>
     </row>
     <row r="402">
       <c r="B402" s="0" t="n">
@@ -21731,6 +22941,9 @@
           <t>Balance variant; canonical=2; role=air; profile=D04; level=13; wave=4</t>
         </is>
       </c>
+      <c r="Q402" s="0" t="n">
+        <v>13</v>
+      </c>
     </row>
     <row r="403">
       <c r="B403" s="0" t="n">
@@ -21782,6 +22995,9 @@
           <t>Balance variant; canonical=11; role=air; profile=D04; level=13; wave=4</t>
         </is>
       </c>
+      <c r="Q403" s="0" t="n">
+        <v>13</v>
+      </c>
     </row>
     <row r="404">
       <c r="B404" s="0" t="n">
@@ -21833,6 +23049,9 @@
           <t>Balance variant; canonical=12; role=air; profile=D04; level=13; wave=4</t>
         </is>
       </c>
+      <c r="Q404" s="0" t="n">
+        <v>13</v>
+      </c>
     </row>
     <row r="405">
       <c r="B405" s="0" t="n">
@@ -21884,6 +23103,9 @@
           <t>Balance variant; canonical=13; role=air; profile=D04; level=13; wave=4</t>
         </is>
       </c>
+      <c r="Q405" s="0" t="n">
+        <v>13</v>
+      </c>
     </row>
     <row r="406">
       <c r="B406" s="0" t="n">
@@ -21935,6 +23157,9 @@
           <t>Balance variant; canonical=14; role=air; profile=D04; level=13; wave=4</t>
         </is>
       </c>
+      <c r="Q406" s="0" t="n">
+        <v>13</v>
+      </c>
     </row>
     <row r="407">
       <c r="B407" s="0" t="n">
@@ -21986,6 +23211,9 @@
           <t>Balance variant; canonical=2; role=air; profile=D04; level=13; wave=5</t>
         </is>
       </c>
+      <c r="Q407" s="0" t="n">
+        <v>13</v>
+      </c>
     </row>
     <row r="408">
       <c r="B408" s="0" t="n">
@@ -22037,6 +23265,9 @@
           <t>Balance variant; canonical=11; role=air; profile=D04; level=13; wave=5</t>
         </is>
       </c>
+      <c r="Q408" s="0" t="n">
+        <v>13</v>
+      </c>
     </row>
     <row r="409">
       <c r="B409" s="0" t="n">
@@ -22088,6 +23319,9 @@
           <t>Balance variant; canonical=12; role=air; profile=D04; level=13; wave=5</t>
         </is>
       </c>
+      <c r="Q409" s="0" t="n">
+        <v>13</v>
+      </c>
     </row>
     <row r="410">
       <c r="B410" s="0" t="n">
@@ -22139,6 +23373,9 @@
           <t>Balance variant; canonical=13; role=air; profile=D04; level=13; wave=5</t>
         </is>
       </c>
+      <c r="Q410" s="0" t="n">
+        <v>13</v>
+      </c>
     </row>
     <row r="411">
       <c r="B411" s="0" t="n">
@@ -22190,6 +23427,9 @@
           <t>Balance variant; canonical=14; role=air; profile=D04; level=13; wave=5</t>
         </is>
       </c>
+      <c r="Q411" s="0" t="n">
+        <v>13</v>
+      </c>
     </row>
     <row r="412">
       <c r="B412" s="0" t="n">
@@ -22241,6 +23481,9 @@
           <t>Balance variant; canonical=2; role=air; profile=D04; level=13; wave=6</t>
         </is>
       </c>
+      <c r="Q412" s="0" t="n">
+        <v>13</v>
+      </c>
     </row>
     <row r="413">
       <c r="B413" s="0" t="n">
@@ -22292,6 +23535,9 @@
           <t>Balance variant; canonical=12; role=air; profile=D04; level=13; wave=6</t>
         </is>
       </c>
+      <c r="Q413" s="0" t="n">
+        <v>13</v>
+      </c>
     </row>
     <row r="414">
       <c r="B414" s="0" t="n">
@@ -22343,6 +23589,9 @@
           <t>Balance variant; canonical=2; role=air; profile=D04; level=13; wave=7</t>
         </is>
       </c>
+      <c r="Q414" s="0" t="n">
+        <v>13</v>
+      </c>
     </row>
     <row r="415">
       <c r="B415" s="0" t="n">
@@ -22394,6 +23643,9 @@
           <t>Balance variant; canonical=12; role=air; profile=D04; level=13; wave=7</t>
         </is>
       </c>
+      <c r="Q415" s="0" t="n">
+        <v>13</v>
+      </c>
     </row>
     <row r="416">
       <c r="B416" s="0" t="n">
@@ -22445,6 +23697,9 @@
           <t>Balance variant; canonical=2; role=air; profile=D04; level=13; wave=8</t>
         </is>
       </c>
+      <c r="Q416" s="0" t="n">
+        <v>13</v>
+      </c>
     </row>
     <row r="417">
       <c r="B417" s="0" t="n">
@@ -22496,6 +23751,9 @@
           <t>Balance variant; canonical=12; role=air; profile=D04; level=13; wave=8</t>
         </is>
       </c>
+      <c r="Q417" s="0" t="n">
+        <v>13</v>
+      </c>
     </row>
     <row r="418">
       <c r="B418" s="0" t="n">
@@ -22547,6 +23805,9 @@
           <t>Balance variant; canonical=2; role=air; profile=D04; level=13; wave=9</t>
         </is>
       </c>
+      <c r="Q418" s="0" t="n">
+        <v>13</v>
+      </c>
     </row>
     <row r="419">
       <c r="B419" s="0" t="n">
@@ -22598,6 +23859,9 @@
           <t>Balance variant; canonical=12; role=air; profile=D04; level=13; wave=9</t>
         </is>
       </c>
+      <c r="Q419" s="0" t="n">
+        <v>13</v>
+      </c>
     </row>
     <row r="420">
       <c r="B420" s="0" t="n">
@@ -22649,6 +23913,9 @@
           <t>Balance variant; canonical=2; role=air; profile=D04; level=13; wave=10</t>
         </is>
       </c>
+      <c r="Q420" s="0" t="n">
+        <v>13</v>
+      </c>
     </row>
     <row r="421">
       <c r="B421" s="0" t="n">
@@ -22700,6 +23967,9 @@
           <t>Balance variant; canonical=12; role=air; profile=D04; level=13; wave=10</t>
         </is>
       </c>
+      <c r="Q421" s="0" t="n">
+        <v>13</v>
+      </c>
     </row>
     <row r="422">
       <c r="B422" s="0" t="n">
@@ -22751,6 +24021,9 @@
           <t>Balance variant; canonical=2; role=air; profile=D04; level=13; wave=11</t>
         </is>
       </c>
+      <c r="Q422" s="0" t="n">
+        <v>13</v>
+      </c>
     </row>
     <row r="423">
       <c r="B423" s="0" t="n">
@@ -22802,6 +24075,9 @@
           <t>Balance variant; canonical=11; role=air; profile=D04; level=13; wave=11</t>
         </is>
       </c>
+      <c r="Q423" s="0" t="n">
+        <v>13</v>
+      </c>
     </row>
     <row r="424">
       <c r="B424" s="0" t="n">
@@ -22853,6 +24129,9 @@
           <t>Balance variant; canonical=12; role=air; profile=D04; level=13; wave=11</t>
         </is>
       </c>
+      <c r="Q424" s="0" t="n">
+        <v>13</v>
+      </c>
     </row>
     <row r="425">
       <c r="B425" s="0" t="n">
@@ -22904,6 +24183,9 @@
           <t>Balance variant; canonical=13; role=air; profile=D04; level=13; wave=11</t>
         </is>
       </c>
+      <c r="Q425" s="0" t="n">
+        <v>13</v>
+      </c>
     </row>
     <row r="426">
       <c r="B426" s="0" t="n">
@@ -22955,6 +24237,9 @@
           <t>Balance variant; canonical=14; role=air; profile=D04; level=13; wave=11</t>
         </is>
       </c>
+      <c r="Q426" s="0" t="n">
+        <v>13</v>
+      </c>
     </row>
     <row r="427">
       <c r="B427" s="0" t="n">
@@ -23006,6 +24291,9 @@
           <t>Balance variant; canonical=2; role=air; profile=D04; level=13; wave=12</t>
         </is>
       </c>
+      <c r="Q427" s="0" t="n">
+        <v>13</v>
+      </c>
     </row>
     <row r="428">
       <c r="B428" s="0" t="n">
@@ -23057,6 +24345,9 @@
           <t>Balance variant; canonical=12; role=air; profile=D04; level=13; wave=12</t>
         </is>
       </c>
+      <c r="Q428" s="0" t="n">
+        <v>13</v>
+      </c>
     </row>
     <row r="429">
       <c r="B429" s="0" t="n">
@@ -23108,6 +24399,9 @@
           <t>Balance variant; canonical=2; role=air; profile=D04; level=13; wave=13</t>
         </is>
       </c>
+      <c r="Q429" s="0" t="n">
+        <v>13</v>
+      </c>
     </row>
     <row r="430">
       <c r="B430" s="0" t="n">
@@ -23159,6 +24453,9 @@
           <t>Balance variant; canonical=12; role=air; profile=D04; level=13; wave=13</t>
         </is>
       </c>
+      <c r="Q430" s="0" t="n">
+        <v>13</v>
+      </c>
     </row>
     <row r="431">
       <c r="B431" s="0" t="n">
@@ -23210,6 +24507,9 @@
           <t>Balance variant; canonical=2; role=air; profile=D04; level=13; wave=14</t>
         </is>
       </c>
+      <c r="Q431" s="0" t="n">
+        <v>13</v>
+      </c>
     </row>
     <row r="432">
       <c r="B432" s="0" t="n">
@@ -23261,6 +24561,9 @@
           <t>Balance variant; canonical=12; role=air; profile=D04; level=13; wave=14</t>
         </is>
       </c>
+      <c r="Q432" s="0" t="n">
+        <v>13</v>
+      </c>
     </row>
     <row r="433">
       <c r="B433" s="0" t="n">
@@ -23312,6 +24615,9 @@
           <t>Balance variant; canonical=2; role=air; profile=D04; level=13; wave=15</t>
         </is>
       </c>
+      <c r="Q433" s="0" t="n">
+        <v>13</v>
+      </c>
     </row>
     <row r="434">
       <c r="B434" s="0" t="n">
@@ -23363,6 +24669,9 @@
           <t>Balance variant; canonical=12; role=air; profile=D04; level=13; wave=15</t>
         </is>
       </c>
+      <c r="Q434" s="0" t="n">
+        <v>13</v>
+      </c>
     </row>
     <row r="435">
       <c r="B435" s="0" t="n">
@@ -23414,6 +24723,9 @@
           <t>Balance variant; canonical=2; role=air; profile=D04; level=13; wave=16</t>
         </is>
       </c>
+      <c r="Q435" s="0" t="n">
+        <v>13</v>
+      </c>
     </row>
     <row r="436">
       <c r="B436" s="0" t="n">
@@ -23465,6 +24777,9 @@
           <t>Balance variant; canonical=11; role=air; profile=D04; level=13; wave=16</t>
         </is>
       </c>
+      <c r="Q436" s="0" t="n">
+        <v>13</v>
+      </c>
     </row>
     <row r="437">
       <c r="B437" s="0" t="n">
@@ -23516,6 +24831,9 @@
           <t>Balance variant; canonical=12; role=air; profile=D04; level=13; wave=16</t>
         </is>
       </c>
+      <c r="Q437" s="0" t="n">
+        <v>13</v>
+      </c>
     </row>
     <row r="438">
       <c r="B438" s="0" t="n">
@@ -23567,6 +24885,9 @@
           <t>Balance variant; canonical=13; role=air; profile=D04; level=13; wave=16</t>
         </is>
       </c>
+      <c r="Q438" s="0" t="n">
+        <v>13</v>
+      </c>
     </row>
     <row r="439">
       <c r="B439" s="0" t="n">
@@ -23618,6 +24939,9 @@
           <t>Balance variant; canonical=14; role=air; profile=D04; level=13; wave=16</t>
         </is>
       </c>
+      <c r="Q439" s="0" t="n">
+        <v>13</v>
+      </c>
     </row>
     <row r="440">
       <c r="B440" s="0" t="n">
@@ -23669,6 +24993,9 @@
           <t>Balance variant; canonical=2; role=air; profile=D04; level=13; wave=17</t>
         </is>
       </c>
+      <c r="Q440" s="0" t="n">
+        <v>13</v>
+      </c>
     </row>
     <row r="441">
       <c r="B441" s="0" t="n">
@@ -23720,6 +25047,9 @@
           <t>Balance variant; canonical=12; role=air; profile=D04; level=13; wave=17</t>
         </is>
       </c>
+      <c r="Q441" s="0" t="n">
+        <v>13</v>
+      </c>
     </row>
     <row r="442">
       <c r="B442" s="0" t="n">
@@ -23771,6 +25101,9 @@
           <t>Balance variant; canonical=2; role=air; profile=D04; level=13; wave=18</t>
         </is>
       </c>
+      <c r="Q442" s="0" t="n">
+        <v>13</v>
+      </c>
     </row>
     <row r="443">
       <c r="B443" s="0" t="n">
@@ -23822,6 +25155,9 @@
           <t>Balance variant; canonical=12; role=air; profile=D04; level=13; wave=18</t>
         </is>
       </c>
+      <c r="Q443" s="0" t="n">
+        <v>13</v>
+      </c>
     </row>
     <row r="444">
       <c r="B444" s="0" t="n">
@@ -23873,6 +25209,9 @@
           <t>Balance variant; canonical=2; role=air; profile=D04; level=13; wave=19</t>
         </is>
       </c>
+      <c r="Q444" s="0" t="n">
+        <v>13</v>
+      </c>
     </row>
     <row r="445">
       <c r="B445" s="0" t="n">
@@ -23924,6 +25263,9 @@
           <t>Balance variant; canonical=12; role=air; profile=D04; level=13; wave=19</t>
         </is>
       </c>
+      <c r="Q445" s="0" t="n">
+        <v>13</v>
+      </c>
     </row>
     <row r="446">
       <c r="B446" s="0" t="n">
@@ -23975,6 +25317,9 @@
           <t>Balance variant; canonical=2; role=air; profile=D04; level=13; wave=20</t>
         </is>
       </c>
+      <c r="Q446" s="0" t="n">
+        <v>13</v>
+      </c>
     </row>
     <row r="447">
       <c r="B447" s="0" t="n">
@@ -24026,6 +25371,9 @@
           <t>Balance variant; canonical=12; role=air; profile=D04; level=13; wave=20</t>
         </is>
       </c>
+      <c r="Q447" s="0" t="n">
+        <v>13</v>
+      </c>
     </row>
     <row r="448">
       <c r="B448" s="0" t="n">
@@ -24077,6 +25425,9 @@
           <t>Balance variant; canonical=2; role=air; profile=D04; level=13; wave=21</t>
         </is>
       </c>
+      <c r="Q448" s="0" t="n">
+        <v>13</v>
+      </c>
     </row>
     <row r="449">
       <c r="B449" s="0" t="n">
@@ -24128,6 +25479,9 @@
           <t>Balance variant; canonical=12; role=air; profile=D04; level=13; wave=21</t>
         </is>
       </c>
+      <c r="Q449" s="0" t="n">
+        <v>13</v>
+      </c>
     </row>
     <row r="450">
       <c r="B450" s="0" t="n">
@@ -24179,6 +25533,9 @@
           <t>Balance variant; canonical=2; role=air; profile=D04; level=13; wave=22</t>
         </is>
       </c>
+      <c r="Q450" s="0" t="n">
+        <v>13</v>
+      </c>
     </row>
     <row r="451">
       <c r="B451" s="0" t="n">
@@ -24230,6 +25587,9 @@
           <t>Balance variant; canonical=12; role=air; profile=D04; level=13; wave=22</t>
         </is>
       </c>
+      <c r="Q451" s="0" t="n">
+        <v>13</v>
+      </c>
     </row>
     <row r="452">
       <c r="B452" s="0" t="n">
@@ -24281,6 +25641,9 @@
           <t>Balance variant; canonical=2; role=air; profile=D04; level=13; wave=23</t>
         </is>
       </c>
+      <c r="Q452" s="0" t="n">
+        <v>13</v>
+      </c>
     </row>
     <row r="453">
       <c r="B453" s="0" t="n">
@@ -24332,6 +25695,9 @@
           <t>Balance variant; canonical=12; role=air; profile=D04; level=13; wave=23</t>
         </is>
       </c>
+      <c r="Q453" s="0" t="n">
+        <v>13</v>
+      </c>
     </row>
     <row r="454">
       <c r="B454" s="0" t="n">
@@ -24383,6 +25749,9 @@
           <t>Balance variant; canonical=2; role=air; profile=D04; level=13; wave=24</t>
         </is>
       </c>
+      <c r="Q454" s="0" t="n">
+        <v>13</v>
+      </c>
     </row>
     <row r="455">
       <c r="B455" s="0" t="n">
@@ -24434,6 +25803,9 @@
           <t>Balance variant; canonical=12; role=air; profile=D04; level=13; wave=24</t>
         </is>
       </c>
+      <c r="Q455" s="0" t="n">
+        <v>13</v>
+      </c>
     </row>
     <row r="456">
       <c r="B456" s="0" t="n">
@@ -24485,6 +25857,9 @@
           <t>Balance variant; canonical=2; role=air; profile=D04; level=13; wave=25</t>
         </is>
       </c>
+      <c r="Q456" s="0" t="n">
+        <v>13</v>
+      </c>
     </row>
     <row r="457">
       <c r="B457" s="0" t="n">
@@ -24535,6 +25910,9 @@
         <is>
           <t>Balance variant; canonical=12; role=air; profile=D04; level=13; wave=25</t>
         </is>
+      </c>
+      <c r="Q457" s="0" t="n">
+        <v>13</v>
       </c>
     </row>
   </sheetData>
